--- a/project_clinic_order_management_db_definition.xlsx
+++ b/project_clinic_order_management_db_definition.xlsx
@@ -242,19 +242,19 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.1 Draft</t>
+          <t xml:space="preserve">0.2 Draft</t>
         </is>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">作成日</t>
+          <t xml:space="preserve">更新日</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-21</t>
+          <t xml:space="preserve">2026-07-22</t>
         </is>
       </c>
     </row>
@@ -290,7 +290,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supabaseのpatient_orders / patient_order_items</t>
+          <t xml:space="preserve">Supabaseのpatient_orders / patient_order_items / order_shipping_addresses / patient_order_events</t>
         </is>
       </c>
     </row>
@@ -333,24 +333,24 @@
     <row r="13" ht="34" customHeight="1">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">重要課題2</t>
+          <t xml:space="preserve">実装済み2</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">配送先を保持せずdeliveryを選択できるため、配送設計確定まで自宅配送を無効化する。</t>
+          <t xml:space="preserve">自宅配送時はorder_shipping_addressesへ注文時点の配送先を保存し、住所なし配送を拒否する。</t>
         </is>
       </c>
     </row>
     <row r="14" ht="34" customHeight="1">
       <c r="A14" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">重要課題3</t>
+          <t xml:space="preserve">重要課題2</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">状態変更履歴・変更者・理由が未保存。patient_order_eventsをPhase 1で追加する。</t>
+          <t xml:space="preserve">patient_order_eventsは実装済み。変更理由の保存は今後追加する。</t>
         </is>
       </c>
     </row>
@@ -476,7 +476,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -696,27 +696,27 @@
     <row r="10" ht="34" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Phase 1</t>
+          <t xml:space="preserve">現行</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文操作履歴</t>
+          <t xml:space="preserve">注文配送先</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_order_events</t>
+          <t xml:space="preserve">order_shipping_addresses</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">将来案</t>
+          <t xml:space="preserve">実装済み</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">状態変更、操作者、理由を追跡する監査イベント。</t>
+          <t xml:space="preserve">自宅配送注文に対して、注文時点の配送先を1対1で保存する履歴スナップショット。</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -728,27 +728,27 @@
     <row r="11" ht="34" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shopify接続</t>
+          <t xml:space="preserve">現行</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部コマース接続</t>
+          <t xml:space="preserve">注文操作履歴</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_accounts</t>
+          <t xml:space="preserve">patient_order_events</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">将来案</t>
+          <t xml:space="preserve">実装済み</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shopifyストア等の外部接続先。医院との対応方式は接続構成確定後に決定する。</t>
+          <t xml:space="preserve">注文登録と状態変更について、操作者と変更前後の状態を保存する監査イベント。</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -765,22 +765,22 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文拡張</t>
+          <t xml:space="preserve">外部コマース接続</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders</t>
+          <t xml:space="preserve">commerce_accounts</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">既存テーブル拡張案</t>
+          <t xml:space="preserve">将来案</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">既存IDを維持し、外部・金額・排他制御の列を追加する。</t>
+          <t xml:space="preserve">Shopifyストア等の外部接続先。医院との対応方式は接続構成確定後に決定する。</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -797,12 +797,12 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文明細拡張</t>
+          <t xml:space="preserve">患者注文拡張</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_order_items</t>
+          <t xml:space="preserve">patient_orders</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -812,7 +812,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部明細と通貨を明確化し、既存スナップショットを維持する。</t>
+          <t xml:space="preserve">既存IDを維持し、外部・金額・排他制御の列を追加する。</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -824,27 +824,27 @@
     <row r="14" ht="34" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">決済接続</t>
+          <t xml:space="preserve">Shopify接続</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">決済返金投影</t>
+          <t xml:space="preserve">患者注文明細拡張</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">order_transaction_projections</t>
+          <t xml:space="preserve">patient_order_items</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">将来案</t>
+          <t xml:space="preserve">既存テーブル拡張案</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shopify上の決済・返金を表示する投影。会計台帳ではない。</t>
+          <t xml:space="preserve">外部明細と通貨を明確化し、既存スナップショットを維持する。</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -856,17 +856,17 @@
     <row r="15" ht="34" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">配送開始</t>
+          <t xml:space="preserve">決済接続</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">受取配送</t>
+          <t xml:space="preserve">決済返金投影</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_fulfillments</t>
+          <t xml:space="preserve">order_transaction_projections</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院受け取り・配送・部分引き渡しの単位。</t>
+          <t xml:space="preserve">Shopify上の決済・返金を表示する投影。会計台帳ではない。</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">受取配送明細</t>
+          <t xml:space="preserve">受取配送</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_fulfillment_items</t>
+          <t xml:space="preserve">patient_fulfillments</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">部分受け取り・部分配送時の対象明細と数量。</t>
+          <t xml:space="preserve">医院受け取り・配送・部分引き渡しの単位。</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -920,17 +920,17 @@
     <row r="17" ht="34" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">定期購入接続</t>
+          <t xml:space="preserve">配送開始</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者定期購入</t>
+          <t xml:space="preserve">受取配送明細</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_subscriptions</t>
+          <t xml:space="preserve">patient_fulfillment_items</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -940,7 +940,7 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shopify上の定期購入契約を患者ポータルへ表示する投影。</t>
+          <t xml:space="preserve">部分受け取り・部分配送時の対象明細と数量。</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -957,12 +957,12 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">定期購入明細</t>
+          <t xml:space="preserve">患者定期購入</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_subscription_items</t>
+          <t xml:space="preserve">patient_subscriptions</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">契約時点の商品・数量・単価の投影。</t>
+          <t xml:space="preserve">Shopify上の定期購入契約を患者ポータルへ表示する投影。</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -984,17 +984,17 @@
     <row r="19" ht="34" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shopify接続</t>
+          <t xml:space="preserve">定期購入接続</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部受信イベント</t>
+          <t xml:space="preserve">定期購入明細</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_webhook_events</t>
+          <t xml:space="preserve">patient_subscription_items</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Webhookを先に永続化し、重複排除・再試行するInbox。</t>
+          <t xml:space="preserve">契約時点の商品・数量・単価の投影。</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
@@ -1021,57 +1021,89 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">外部受信イベント</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">commerce_webhook_events</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">将来案</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Webhookを先に永続化し、重複排除・再試行するInbox。</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="34" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shopify接続</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">外部送信キュー</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">commerce_outbox</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">将来案</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">外部APIへ送る処理を永続化するOutbox。</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">別ドメイン</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">医院仕入注文</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr">
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">clinic_orders</t>
         </is>
       </c>
-      <c r="D21" s="8" t="inlineStr">
+      <c r="D22" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">実装済み</t>
         </is>
       </c>
-      <c r="E21" s="8" t="inlineStr">
+      <c r="E22" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">BGJから医院へのB2B仕入・売上履歴</t>
         </is>
       </c>
-      <c r="F21" s="8" t="inlineStr">
+      <c r="F22" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">患者注文系列へ統合しない</t>
         </is>
@@ -1082,7 +1114,7 @@
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
   </mergeCells>
-  <autoFilter ref="A4:F21"/>
+  <autoFilter ref="A4:F22"/>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0" paperSize="9"/>
 </worksheet>
@@ -1090,7 +1122,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K44"/>
+  <dimension ref="A1:K62"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -2335,12 +2367,12 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部注文ID</t>
+          <t xml:space="preserve">登録経路</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">external_order_id</t>
+          <t xml:space="preserve">created_via</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
@@ -2348,24 +2380,24 @@
           <t xml:space="preserve">text</t>
         </is>
       </c>
-      <c r="G25" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UK1構成</t>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">YES</t>
+          <t xml:space="preserve">NO</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">clinic_portal</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">clinic_portal / bgj_portal / shopify</t>
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr">
@@ -2392,12 +2424,12 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">同期状態</t>
+          <t xml:space="preserve">外部注文ID</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">sync_status</t>
+          <t xml:space="preserve">external_order_id</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -2405,24 +2437,24 @@
           <t xml:space="preserve">text</t>
         </is>
       </c>
-      <c r="G26" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UK1構成</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO</t>
+          <t xml:space="preserve">YES</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">local</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">local / pending / synced / error</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr">
@@ -2449,12 +2481,12 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">同期エラー</t>
+          <t xml:space="preserve">同期状態</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">sync_error</t>
+          <t xml:space="preserve">sync_status</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -2469,17 +2501,17 @@
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">YES</t>
+          <t xml:space="preserve">NO</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">local</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">local / pending / synced / error</t>
         </is>
       </c>
       <c r="K27" s="4" t="inlineStr">
@@ -2506,22 +2538,22 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">冪等キー</t>
+          <t xml:space="preserve">同期エラー</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">idempotency_key</t>
+          <t xml:space="preserve">sync_error</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">uuid</t>
-        </is>
-      </c>
-      <c r="G28" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UK2構成</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
@@ -2563,22 +2595,22 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部更新日時</t>
+          <t xml:space="preserve">冪等キー</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">external_updated_at</t>
+          <t xml:space="preserve">idempotency_key</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">timestamptz</t>
-        </is>
-      </c>
-      <c r="G29" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">uuid</t>
+        </is>
+      </c>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UK2構成</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
@@ -2620,12 +2652,12 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">作成日時</t>
+          <t xml:space="preserve">外部更新日時</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">created_at</t>
+          <t xml:space="preserve">external_updated_at</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
@@ -2640,12 +2672,12 @@
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO</t>
+          <t xml:space="preserve">YES</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">now()</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
@@ -2677,12 +2709,12 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">更新日時</t>
+          <t xml:space="preserve">作成日時</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">updated_at</t>
+          <t xml:space="preserve">created_at</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -2724,32 +2756,32 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文明細</t>
+          <t xml:space="preserve">患者注文</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_order_items</t>
+          <t xml:space="preserve">patient_orders</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文明細ID</t>
+          <t xml:space="preserve">更新日時</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">updated_at</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">uuid</t>
-        </is>
-      </c>
-      <c r="G32" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PK</t>
+          <t xml:space="preserve">timestamptz</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
@@ -2759,7 +2791,7 @@
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">gen_random_uuid()</t>
+          <t xml:space="preserve">now()</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
@@ -2791,12 +2823,12 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">内部注文ID</t>
+          <t xml:space="preserve">注文明細ID</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">order_id</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -2804,9 +2836,9 @@
           <t xml:space="preserve">uuid</t>
         </is>
       </c>
-      <c r="G33" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FK</t>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
@@ -2816,12 +2848,12 @@
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">gen_random_uuid()</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders.id ON DELETE CASCADE</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K33" s="4" t="inlineStr">
@@ -2848,12 +2880,12 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">商品ID</t>
+          <t xml:space="preserve">内部注文ID</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">product_id</t>
+          <t xml:space="preserve">order_id</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -2868,7 +2900,7 @@
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">YES</t>
+          <t xml:space="preserve">NO</t>
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr">
@@ -2878,7 +2910,7 @@
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">products.id ON DELETE SET NULL</t>
+          <t xml:space="preserve">patient_orders.id ON DELETE CASCADE</t>
         </is>
       </c>
       <c r="K34" s="4" t="inlineStr">
@@ -2905,27 +2937,27 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文時商品名</t>
+          <t xml:space="preserve">商品ID</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">product_name</t>
+          <t xml:space="preserve">product_id</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="G35" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">uuid</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO</t>
+          <t xml:space="preserve">YES</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
@@ -2935,7 +2967,7 @@
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">products.id ON DELETE SET NULL</t>
         </is>
       </c>
       <c r="K35" s="4" t="inlineStr">
@@ -2962,17 +2994,17 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文時単価</t>
+          <t xml:space="preserve">注文時商品名</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">unit_price</t>
+          <t xml:space="preserve">product_name</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">integer</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
@@ -2992,7 +3024,7 @@
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">&gt;= 0</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K36" s="4" t="inlineStr">
@@ -3019,12 +3051,12 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">数量</t>
+          <t xml:space="preserve">注文時単価</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">quantity</t>
+          <t xml:space="preserve">unit_price</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
@@ -3044,12 +3076,12 @@
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">&gt; 0</t>
+          <t xml:space="preserve">&gt;= 0</t>
         </is>
       </c>
       <c r="K37" s="4" t="inlineStr">
@@ -3076,17 +3108,17 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">単位スナップショット</t>
+          <t xml:space="preserve">数量</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">unit_snapshot</t>
+          <t xml:space="preserve">quantity</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">integer</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
@@ -3096,17 +3128,17 @@
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">YES</t>
+          <t xml:space="preserve">NO</t>
         </is>
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">&gt; 0</t>
         </is>
       </c>
       <c r="K38" s="4" t="inlineStr">
@@ -3133,12 +3165,12 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">画像種別スナップショット</t>
+          <t xml:space="preserve">単位スナップショット</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">image_type_snapshot</t>
+          <t xml:space="preserve">unit_snapshot</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
@@ -3153,17 +3185,17 @@
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO</t>
+          <t xml:space="preserve">YES</t>
         </is>
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">supplement</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">supplement / yogurt / toothbrush / oral</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K39" s="4" t="inlineStr">
@@ -3190,12 +3222,12 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">用量スナップショット</t>
+          <t xml:space="preserve">画像種別スナップショット</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">daily_amount_snapshot</t>
+          <t xml:space="preserve">image_type_snapshot</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
@@ -3210,17 +3242,17 @@
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">YES</t>
+          <t xml:space="preserve">NO</t>
         </is>
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">supplement</t>
         </is>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">supplement / yogurt / toothbrush / oral</t>
         </is>
       </c>
       <c r="K40" s="4" t="inlineStr">
@@ -3247,12 +3279,12 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">内容量スナップショット</t>
+          <t xml:space="preserve">用量スナップショット</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">volume_snapshot</t>
+          <t xml:space="preserve">daily_amount_snapshot</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
@@ -3304,12 +3336,12 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注意事項スナップショット</t>
+          <t xml:space="preserve">内容量スナップショット</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">caution_snapshot</t>
+          <t xml:space="preserve">volume_snapshot</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
@@ -3361,12 +3393,12 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部明細ID</t>
+          <t xml:space="preserve">注意事項スナップショット</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">external_line_item_id</t>
+          <t xml:space="preserve">caution_snapshot</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
@@ -3418,40 +3450,1066 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">外部明細ID</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">external_line_item_id</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YES</t>
+        </is>
+      </c>
+      <c r="I44" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K44" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="30" customHeight="1">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">患者注文明細</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_order_items</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">作成日時</t>
         </is>
       </c>
-      <c r="E44" s="4" t="inlineStr">
+      <c r="E45" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">created_at</t>
         </is>
       </c>
-      <c r="F44" s="4" t="inlineStr">
+      <c r="F45" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">timestamptz</t>
         </is>
       </c>
-      <c r="G44" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H44" s="4" t="inlineStr">
+      <c r="G45" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H45" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">NO</t>
         </is>
       </c>
-      <c r="I44" s="4" t="inlineStr">
+      <c r="I45" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">now()</t>
         </is>
       </c>
-      <c r="J44" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="K44" s="4" t="inlineStr">
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K45" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="30" customHeight="1">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">注文配送先</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">order_shipping_addresses</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">内部注文ID</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">order_id</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">uuid</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK / FK</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I46" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_orders.id ON DELETE CASCADE</t>
+        </is>
+      </c>
+      <c r="K46" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="30" customHeight="1">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">注文配送先</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">order_shipping_addresses</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">郵便番号</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">postal_code</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I47" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">^[0-9]{3}-[0-9]{4}$</t>
+        </is>
+      </c>
+      <c r="K47" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="30" customHeight="1">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">注文配送先</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">order_shipping_addresses</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">都道府県</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prefecture</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I48" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2〜4文字</t>
+        </is>
+      </c>
+      <c r="K48" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="30" customHeight="1">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">注文配送先</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">order_shipping_addresses</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">市区町村</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">city</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H49" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I49" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1〜100文字</t>
+        </is>
+      </c>
+      <c r="K49" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="30" customHeight="1">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">注文配送先</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">order_shipping_addresses</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">住所1</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">address_line1</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I50" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1〜200文字</t>
+        </is>
+      </c>
+      <c r="K50" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="30" customHeight="1">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">注文配送先</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">order_shipping_addresses</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">住所2</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">address_line2</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H51" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YES</t>
+        </is>
+      </c>
+      <c r="I51" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">200文字以内</t>
+        </is>
+      </c>
+      <c r="K51" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="30" customHeight="1">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">注文配送先</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">order_shipping_addresses</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">受取人名</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">recipient_name</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G52" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I52" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1〜100文字</t>
+        </is>
+      </c>
+      <c r="K52" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="30" customHeight="1">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">注文配送先</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">order_shipping_addresses</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">電話番号</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">phone</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">数字10〜15桁</t>
+        </is>
+      </c>
+      <c r="K53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="30" customHeight="1">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">注文配送先</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">order_shipping_addresses</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">作成日時</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">created_at</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">timestamptz</t>
+        </is>
+      </c>
+      <c r="G54" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I54" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">now()</t>
+        </is>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K54" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="30" customHeight="1">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">注文操作履歴</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_order_events</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">イベントID</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">id</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">uuid</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK</t>
+        </is>
+      </c>
+      <c r="H55" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I55" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gen_random_uuid()</t>
+        </is>
+      </c>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K55" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="30" customHeight="1">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">注文操作履歴</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_order_events</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">内部注文ID</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">order_id</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">uuid</t>
+        </is>
+      </c>
+      <c r="G56" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I56" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_orders.id ON DELETE CASCADE</t>
+        </is>
+      </c>
+      <c r="K56" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="30" customHeight="1">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">注文操作履歴</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_order_events</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">イベント種別</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">event_type</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="30" customHeight="1">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">注文操作履歴</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_order_events</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">操作者種別</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actor_type</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I58" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K58" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="30" customHeight="1">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">注文操作履歴</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_order_events</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">操作者識別子</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actor_identifier</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H59" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I59" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K59" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="30" customHeight="1">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">注文操作履歴</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_order_events</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">変更前状態</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">from_status</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G60" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YES</t>
+        </is>
+      </c>
+      <c r="I60" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K60" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="30" customHeight="1">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">注文操作履歴</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_order_events</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">変更後状態</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">to_status</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H61" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YES</t>
+        </is>
+      </c>
+      <c r="I61" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K61" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="30" customHeight="1">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">注文操作履歴</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_order_events</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">発生日時</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">created_at</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">timestamptz</t>
+        </is>
+      </c>
+      <c r="G62" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H62" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I62" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">now()</t>
+        </is>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K62" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -3462,7 +4520,7 @@
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A2:K2"/>
   </mergeCells>
-  <autoFilter ref="A4:K44"/>
+  <autoFilter ref="A4:K62"/>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0" paperSize="9"/>
 </worksheet>
@@ -3470,7 +4528,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K95"/>
+  <dimension ref="A1:K85"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -3560,22 +4618,22 @@
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Phase 1</t>
+          <t xml:space="preserve">Shopify接続</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文操作履歴</t>
+          <t xml:space="preserve">外部コマース接続</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_order_events</t>
+          <t xml:space="preserve">commerce_accounts</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">イベントID</t>
+          <t xml:space="preserve">接続ID</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -3617,37 +4675,37 @@
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Phase 1</t>
+          <t xml:space="preserve">Shopify接続</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文操作履歴</t>
+          <t xml:space="preserve">外部コマース接続</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_order_events</t>
+          <t xml:space="preserve">commerce_accounts</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">内部注文ID</t>
+          <t xml:space="preserve">プロバイダー</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">order_id</t>
+          <t xml:space="preserve">provider</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">uuid</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FK</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UK1構成</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
@@ -3662,7 +4720,7 @@
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders.id ON DELETE RESTRICT</t>
+          <t xml:space="preserve">shopify 等</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
@@ -3674,27 +4732,27 @@
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Phase 1</t>
+          <t xml:space="preserve">Shopify接続</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文操作履歴</t>
+          <t xml:space="preserve">外部コマース接続</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_order_events</t>
+          <t xml:space="preserve">commerce_accounts</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">イベント種別</t>
+          <t xml:space="preserve">外部アカウントID</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">event_type</t>
+          <t xml:space="preserve">external_account_id</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -3702,9 +4760,9 @@
           <t xml:space="preserve">text</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UK1構成</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -3731,27 +4789,27 @@
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Phase 1</t>
+          <t xml:space="preserve">Shopify接続</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文操作履歴</t>
+          <t xml:space="preserve">外部コマース接続</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_order_events</t>
+          <t xml:space="preserve">commerce_accounts</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">変更前状態</t>
+          <t xml:space="preserve">接続状態</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">before_status</t>
+          <t xml:space="preserve">status</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -3766,12 +4824,12 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">YES</t>
+          <t xml:space="preserve">NO</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">active</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -3788,32 +4846,32 @@
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Phase 1</t>
+          <t xml:space="preserve">Shopify接続</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文操作履歴</t>
+          <t xml:space="preserve">外部コマース接続</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_order_events</t>
+          <t xml:space="preserve">commerce_accounts</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">変更後状態</t>
+          <t xml:space="preserve">作成日時</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">after_status</t>
+          <t xml:space="preserve">created_at</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">timestamptz</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
@@ -3823,12 +4881,12 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">YES</t>
+          <t xml:space="preserve">NO</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">now()</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -3845,32 +4903,32 @@
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Phase 1</t>
+          <t xml:space="preserve">Shopify接続</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文操作履歴</t>
+          <t xml:space="preserve">外部コマース接続</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_order_events</t>
+          <t xml:space="preserve">commerce_accounts</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">操作者ロール</t>
+          <t xml:space="preserve">更新日時</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">actor_role</t>
+          <t xml:space="preserve">updated_at</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">timestamptz</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
@@ -3885,7 +4943,7 @@
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">now()</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -3902,37 +4960,37 @@
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Phase 1</t>
+          <t xml:space="preserve">Shopify接続</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文操作履歴</t>
+          <t xml:space="preserve">患者注文拡張</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_order_events</t>
+          <t xml:space="preserve">patient_orders</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">操作者ID</t>
+          <t xml:space="preserve">定期購入契約ID</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">actor_id</t>
+          <t xml:space="preserve">subscription_id</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">uuid</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -3947,7 +5005,7 @@
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">patient_subscriptions.id</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr">
@@ -3959,37 +5017,37 @@
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Phase 1</t>
+          <t xml:space="preserve">Shopify接続</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文操作履歴</t>
+          <t xml:space="preserve">患者注文拡張</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_order_events</t>
+          <t xml:space="preserve">patient_orders</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">変更理由</t>
+          <t xml:space="preserve">外部接続ID</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">reason</t>
+          <t xml:space="preserve">commerce_account_id</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">uuid</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK / UK5構成</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -4004,7 +5062,7 @@
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">commerce_accounts.id</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
@@ -4016,47 +5074,47 @@
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Phase 1</t>
+          <t xml:space="preserve">Shopify接続</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文操作履歴</t>
+          <t xml:space="preserve">患者注文拡張</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_order_events</t>
+          <t xml:space="preserve">patient_orders</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">補足情報</t>
+          <t xml:space="preserve">外部注文ID</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">metadata</t>
+          <t xml:space="preserve">external_order_id</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">jsonb</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UK5構成</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO</t>
+          <t xml:space="preserve">YES</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">{}</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -4073,32 +5131,32 @@
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Phase 1</t>
+          <t xml:space="preserve">Shopify接続</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文操作履歴</t>
+          <t xml:space="preserve">患者注文拡張</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_order_events</t>
+          <t xml:space="preserve">patient_orders</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">発生日時</t>
+          <t xml:space="preserve">医院業務状態</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">created_at</t>
+          <t xml:space="preserve">clinic_fulfillment_status</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">timestamptz</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
@@ -4113,7 +5171,7 @@
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">now()</t>
+          <t xml:space="preserve">received</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -4135,42 +5193,42 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部コマース接続</t>
+          <t xml:space="preserve">患者注文拡張</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_accounts</t>
+          <t xml:space="preserve">patient_orders</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">接続ID</t>
+          <t xml:space="preserve">外部注文状態</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">external_order_status</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">uuid</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PK</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO</t>
+          <t xml:space="preserve">YES</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">gen_random_uuid()</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -4192,22 +5250,22 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部コマース接続</t>
+          <t xml:space="preserve">患者注文拡張</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_accounts</t>
+          <t xml:space="preserve">patient_orders</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">プロバイダー</t>
+          <t xml:space="preserve">決済状態</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">provider</t>
+          <t xml:space="preserve">payment_status</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -4215,14 +5273,14 @@
           <t xml:space="preserve">text</t>
         </is>
       </c>
-      <c r="G16" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UK1構成</t>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO</t>
+          <t xml:space="preserve">YES</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
@@ -4232,7 +5290,7 @@
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">shopify 等</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
@@ -4249,22 +5307,22 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部コマース接続</t>
+          <t xml:space="preserve">患者注文拡張</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_accounts</t>
+          <t xml:space="preserve">patient_orders</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部アカウントID</t>
+          <t xml:space="preserve">外部配送状態</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">external_account_id</t>
+          <t xml:space="preserve">external_fulfillment_status</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -4272,14 +5330,14 @@
           <t xml:space="preserve">text</t>
         </is>
       </c>
-      <c r="G17" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UK1構成</t>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO</t>
+          <t xml:space="preserve">YES</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
@@ -4306,27 +5364,27 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部コマース接続</t>
+          <t xml:space="preserve">患者注文拡張</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_accounts</t>
+          <t xml:space="preserve">patient_orders</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">接続状態</t>
+          <t xml:space="preserve">通貨コード</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">status</t>
+          <t xml:space="preserve">currency</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">char(3)</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
@@ -4341,7 +5399,7 @@
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">active</t>
+          <t xml:space="preserve">JPY</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -4363,27 +5421,27 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部コマース接続</t>
+          <t xml:space="preserve">患者注文拡張</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_accounts</t>
+          <t xml:space="preserve">patient_orders</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">作成日時</t>
+          <t xml:space="preserve">参考注文金額</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">created_at</t>
+          <t xml:space="preserve">reference_amount</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">timestamptz</t>
+          <t xml:space="preserve">bigint</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
@@ -4393,12 +5451,12 @@
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO</t>
+          <t xml:space="preserve">YES</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">now()</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -4420,27 +5478,27 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部コマース接続</t>
+          <t xml:space="preserve">患者注文拡張</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_accounts</t>
+          <t xml:space="preserve">patient_orders</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">更新日時</t>
+          <t xml:space="preserve">確定総額</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">updated_at</t>
+          <t xml:space="preserve">confirmed_total_amount</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">timestamptz</t>
+          <t xml:space="preserve">bigint</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
@@ -4450,12 +5508,12 @@
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO</t>
+          <t xml:space="preserve">YES</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">now()</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -4487,22 +5545,22 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">定期購入契約ID</t>
+          <t xml:space="preserve">返金額</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">subscription_id</t>
+          <t xml:space="preserve">refunded_amount</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">uuid</t>
-        </is>
-      </c>
-      <c r="G21" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FK</t>
+          <t xml:space="preserve">bigint</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
@@ -4517,7 +5575,7 @@
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_subscriptions.id</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr">
@@ -4544,37 +5602,37 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部接続ID</t>
+          <t xml:space="preserve">排他制御バージョン</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_account_id</t>
+          <t xml:space="preserve">version</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">uuid</t>
-        </is>
-      </c>
-      <c r="G22" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FK / UK5構成</t>
+          <t xml:space="preserve">integer</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">YES</t>
+          <t xml:space="preserve">NO</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_accounts.id</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
@@ -4591,22 +5649,22 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文拡張</t>
+          <t xml:space="preserve">患者注文明細拡張</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders</t>
+          <t xml:space="preserve">patient_order_items</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部注文ID</t>
+          <t xml:space="preserve">外部明細ID</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">external_order_id</t>
+          <t xml:space="preserve">external_line_item_id</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -4614,9 +5672,9 @@
           <t xml:space="preserve">text</t>
         </is>
       </c>
-      <c r="G23" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UK5構成</t>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
@@ -4648,27 +5706,27 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文拡張</t>
+          <t xml:space="preserve">患者注文明細拡張</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders</t>
+          <t xml:space="preserve">patient_order_items</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院業務状態</t>
+          <t xml:space="preserve">通貨コード</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_fulfillment_status</t>
+          <t xml:space="preserve">currency</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">char(3)</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
@@ -4683,7 +5741,7 @@
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">received</t>
+          <t xml:space="preserve">JPY</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -4700,47 +5758,47 @@
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shopify接続</t>
+          <t xml:space="preserve">決済接続</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文拡張</t>
+          <t xml:space="preserve">決済返金投影</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders</t>
+          <t xml:space="preserve">order_transaction_projections</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部注文状態</t>
+          <t xml:space="preserve">取引投影ID</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">external_order_status</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="G25" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">uuid</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">YES</t>
+          <t xml:space="preserve">NO</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">gen_random_uuid()</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -4757,42 +5815,42 @@
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shopify接続</t>
+          <t xml:space="preserve">決済接続</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文拡張</t>
+          <t xml:space="preserve">決済返金投影</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders</t>
+          <t xml:space="preserve">order_transaction_projections</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">決済状態</t>
+          <t xml:space="preserve">内部注文ID</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">payment_status</t>
+          <t xml:space="preserve">order_id</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="G26" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">uuid</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">YES</t>
+          <t xml:space="preserve">NO</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
@@ -4802,7 +5860,7 @@
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">patient_orders.id</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr">
@@ -4814,27 +5872,27 @@
     <row r="27" ht="30" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shopify接続</t>
+          <t xml:space="preserve">決済接続</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文拡張</t>
+          <t xml:space="preserve">決済返金投影</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders</t>
+          <t xml:space="preserve">order_transaction_projections</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部配送状態</t>
+          <t xml:space="preserve">外部取引ID</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">external_fulfillment_status</t>
+          <t xml:space="preserve">external_transaction_id</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -4842,14 +5900,14 @@
           <t xml:space="preserve">text</t>
         </is>
       </c>
-      <c r="G27" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UK</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">YES</t>
+          <t xml:space="preserve">NO</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
@@ -4871,32 +5929,32 @@
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shopify接続</t>
+          <t xml:space="preserve">決済接続</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文拡張</t>
+          <t xml:space="preserve">決済返金投影</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders</t>
+          <t xml:space="preserve">order_transaction_projections</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">通貨コード</t>
+          <t xml:space="preserve">取引種別</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">currency</t>
+          <t xml:space="preserve">transaction_type</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">char(3)</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
@@ -4911,12 +5969,12 @@
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">JPY</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">authorization / capture / refund 等</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr">
@@ -4928,32 +5986,32 @@
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shopify接続</t>
+          <t xml:space="preserve">決済接続</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文拡張</t>
+          <t xml:space="preserve">決済返金投影</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders</t>
+          <t xml:space="preserve">order_transaction_projections</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">参考注文金額</t>
+          <t xml:space="preserve">取引状態</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">reference_amount</t>
+          <t xml:space="preserve">status</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">bigint</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
@@ -4963,7 +6021,7 @@
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">YES</t>
+          <t xml:space="preserve">NO</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
@@ -4985,27 +6043,27 @@
     <row r="30" ht="30" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shopify接続</t>
+          <t xml:space="preserve">決済接続</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文拡張</t>
+          <t xml:space="preserve">決済返金投影</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders</t>
+          <t xml:space="preserve">order_transaction_projections</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">確定総額</t>
+          <t xml:space="preserve">金額</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">confirmed_total_amount</t>
+          <t xml:space="preserve">amount</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
@@ -5020,7 +6078,7 @@
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">YES</t>
+          <t xml:space="preserve">NO</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
@@ -5042,32 +6100,32 @@
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shopify接続</t>
+          <t xml:space="preserve">決済接続</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文拡張</t>
+          <t xml:space="preserve">決済返金投影</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders</t>
+          <t xml:space="preserve">order_transaction_projections</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">返金額</t>
+          <t xml:space="preserve">通貨コード</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">refunded_amount</t>
+          <t xml:space="preserve">currency</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">bigint</t>
+          <t xml:space="preserve">char(3)</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
@@ -5077,7 +6135,7 @@
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">YES</t>
+          <t xml:space="preserve">NO</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
@@ -5099,32 +6157,32 @@
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shopify接続</t>
+          <t xml:space="preserve">決済接続</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文拡張</t>
+          <t xml:space="preserve">決済返金投影</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders</t>
+          <t xml:space="preserve">order_transaction_projections</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">排他制御バージョン</t>
+          <t xml:space="preserve">処理日時</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">version</t>
+          <t xml:space="preserve">processed_at</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">integer</t>
+          <t xml:space="preserve">timestamptz</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
@@ -5134,12 +6192,12 @@
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO</t>
+          <t xml:space="preserve">YES</t>
         </is>
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
@@ -5156,32 +6214,32 @@
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shopify接続</t>
+          <t xml:space="preserve">決済接続</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文明細拡張</t>
+          <t xml:space="preserve">決済返金投影</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_order_items</t>
+          <t xml:space="preserve">order_transaction_projections</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部明細ID</t>
+          <t xml:space="preserve">外部更新日時</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">external_line_item_id</t>
+          <t xml:space="preserve">external_updated_at</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">timestamptz</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
@@ -5191,7 +6249,7 @@
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">YES</t>
+          <t xml:space="preserve">NO</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
@@ -5213,37 +6271,37 @@
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shopify接続</t>
+          <t xml:space="preserve">配送開始</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文明細拡張</t>
+          <t xml:space="preserve">受取配送</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_order_items</t>
+          <t xml:space="preserve">patient_fulfillments</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">通貨コード</t>
+          <t xml:space="preserve">受取配送ID</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">currency</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">char(3)</t>
-        </is>
-      </c>
-      <c r="G34" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">uuid</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
@@ -5253,7 +6311,7 @@
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">JPY</t>
+          <t xml:space="preserve">gen_random_uuid()</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
@@ -5270,27 +6328,27 @@
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">決済接続</t>
+          <t xml:space="preserve">配送開始</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">決済返金投影</t>
+          <t xml:space="preserve">受取配送</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">order_transaction_projections</t>
+          <t xml:space="preserve">patient_fulfillments</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">取引投影ID</t>
+          <t xml:space="preserve">内部注文ID</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">order_id</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
@@ -5298,9 +6356,9 @@
           <t xml:space="preserve">uuid</t>
         </is>
       </c>
-      <c r="G35" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PK</t>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
@@ -5310,12 +6368,12 @@
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">gen_random_uuid()</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">patient_orders.id</t>
         </is>
       </c>
       <c r="K35" s="4" t="inlineStr">
@@ -5327,37 +6385,37 @@
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">決済接続</t>
+          <t xml:space="preserve">配送開始</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">決済返金投影</t>
+          <t xml:space="preserve">受取配送</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">order_transaction_projections</t>
+          <t xml:space="preserve">patient_fulfillments</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">内部注文ID</t>
+          <t xml:space="preserve">受取配送区分</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">order_id</t>
+          <t xml:space="preserve">fulfillment_type</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">uuid</t>
-        </is>
-      </c>
-      <c r="G36" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FK</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
@@ -5372,7 +6430,7 @@
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders.id</t>
+          <t xml:space="preserve">pickup / delivery</t>
         </is>
       </c>
       <c r="K36" s="4" t="inlineStr">
@@ -5384,27 +6442,27 @@
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">決済接続</t>
+          <t xml:space="preserve">配送開始</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">決済返金投影</t>
+          <t xml:space="preserve">受取配送</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">order_transaction_projections</t>
+          <t xml:space="preserve">patient_fulfillments</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部取引ID</t>
+          <t xml:space="preserve">状態</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">external_transaction_id</t>
+          <t xml:space="preserve">status</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
@@ -5412,9 +6470,9 @@
           <t xml:space="preserve">text</t>
         </is>
       </c>
-      <c r="G37" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UK</t>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
@@ -5441,27 +6499,27 @@
     <row r="38" ht="30" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">決済接続</t>
+          <t xml:space="preserve">配送開始</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">決済返金投影</t>
+          <t xml:space="preserve">受取配送</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">order_transaction_projections</t>
+          <t xml:space="preserve">patient_fulfillments</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">取引種別</t>
+          <t xml:space="preserve">受取人スナップショット</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">transaction_type</t>
+          <t xml:space="preserve">recipient_snapshot</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
@@ -5476,7 +6534,7 @@
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO</t>
+          <t xml:space="preserve">YES</t>
         </is>
       </c>
       <c r="I38" s="4" t="inlineStr">
@@ -5486,7 +6544,7 @@
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">authorization / capture / refund 等</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K38" s="4" t="inlineStr">
@@ -5498,32 +6556,32 @@
     <row r="39" ht="30" customHeight="1">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">決済接続</t>
+          <t xml:space="preserve">配送開始</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">決済返金投影</t>
+          <t xml:space="preserve">受取配送</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">order_transaction_projections</t>
+          <t xml:space="preserve">patient_fulfillments</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">取引状態</t>
+          <t xml:space="preserve">住所スナップショット</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">status</t>
+          <t xml:space="preserve">address_snapshot</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">jsonb</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr">
@@ -5533,7 +6591,7 @@
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO</t>
+          <t xml:space="preserve">YES</t>
         </is>
       </c>
       <c r="I39" s="4" t="inlineStr">
@@ -5555,32 +6613,32 @@
     <row r="40" ht="30" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">決済接続</t>
+          <t xml:space="preserve">配送開始</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">決済返金投影</t>
+          <t xml:space="preserve">受取配送</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">order_transaction_projections</t>
+          <t xml:space="preserve">patient_fulfillments</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">金額</t>
+          <t xml:space="preserve">配送会社</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">amount</t>
+          <t xml:space="preserve">carrier</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">bigint</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
@@ -5590,7 +6648,7 @@
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO</t>
+          <t xml:space="preserve">YES</t>
         </is>
       </c>
       <c r="I40" s="4" t="inlineStr">
@@ -5612,32 +6670,32 @@
     <row r="41" ht="30" customHeight="1">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">決済接続</t>
+          <t xml:space="preserve">配送開始</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">決済返金投影</t>
+          <t xml:space="preserve">受取配送</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">order_transaction_projections</t>
+          <t xml:space="preserve">patient_fulfillments</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">通貨コード</t>
+          <t xml:space="preserve">追跡番号</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">currency</t>
+          <t xml:space="preserve">tracking_number</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">char(3)</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr">
@@ -5647,7 +6705,7 @@
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO</t>
+          <t xml:space="preserve">YES</t>
         </is>
       </c>
       <c r="I41" s="4" t="inlineStr">
@@ -5669,27 +6727,27 @@
     <row r="42" ht="30" customHeight="1">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">決済接続</t>
+          <t xml:space="preserve">配送開始</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">決済返金投影</t>
+          <t xml:space="preserve">受取配送</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">order_transaction_projections</t>
+          <t xml:space="preserve">patient_fulfillments</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">処理日時</t>
+          <t xml:space="preserve">準備完了日時</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">processed_at</t>
+          <t xml:space="preserve">ready_at</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
@@ -5726,27 +6784,27 @@
     <row r="43" ht="30" customHeight="1">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">決済接続</t>
+          <t xml:space="preserve">配送開始</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">決済返金投影</t>
+          <t xml:space="preserve">受取配送</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">order_transaction_projections</t>
+          <t xml:space="preserve">patient_fulfillments</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部更新日時</t>
+          <t xml:space="preserve">出荷日時</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">external_updated_at</t>
+          <t xml:space="preserve">shipped_at</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
@@ -5761,7 +6819,7 @@
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO</t>
+          <t xml:space="preserve">YES</t>
         </is>
       </c>
       <c r="I43" s="4" t="inlineStr">
@@ -5798,32 +6856,32 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">受取配送ID</t>
+          <t xml:space="preserve">完了日時</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">completed_at</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">uuid</t>
-        </is>
-      </c>
-      <c r="G44" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PK</t>
+          <t xml:space="preserve">timestamptz</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO</t>
+          <t xml:space="preserve">YES</t>
         </is>
       </c>
       <c r="I44" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">gen_random_uuid()</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J44" s="4" t="inlineStr">
@@ -5845,22 +6903,22 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">受取配送</t>
+          <t xml:space="preserve">受取配送明細</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_fulfillments</t>
+          <t xml:space="preserve">patient_fulfillment_items</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">内部注文ID</t>
+          <t xml:space="preserve">受取配送明細ID</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">order_id</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
@@ -5868,9 +6926,9 @@
           <t xml:space="preserve">uuid</t>
         </is>
       </c>
-      <c r="G45" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FK</t>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
@@ -5880,12 +6938,12 @@
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">gen_random_uuid()</t>
         </is>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders.id</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K45" s="4" t="inlineStr">
@@ -5902,32 +6960,32 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">受取配送</t>
+          <t xml:space="preserve">受取配送明細</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_fulfillments</t>
+          <t xml:space="preserve">patient_fulfillment_items</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">受取配送区分</t>
+          <t xml:space="preserve">受取配送ID</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">fulfillment_type</t>
+          <t xml:space="preserve">fulfillment_id</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="G46" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">uuid</t>
+        </is>
+      </c>
+      <c r="G46" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK / UK2構成</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
@@ -5942,7 +7000,7 @@
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">pickup / delivery</t>
+          <t xml:space="preserve">patient_fulfillments.id</t>
         </is>
       </c>
       <c r="K46" s="4" t="inlineStr">
@@ -5959,32 +7017,32 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">受取配送</t>
+          <t xml:space="preserve">受取配送明細</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_fulfillments</t>
+          <t xml:space="preserve">patient_fulfillment_items</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">状態</t>
+          <t xml:space="preserve">注文明細ID</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">status</t>
+          <t xml:space="preserve">order_item_id</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="G47" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">uuid</t>
+        </is>
+      </c>
+      <c r="G47" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK / UK2構成</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
@@ -5999,7 +7057,7 @@
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">patient_order_items.id</t>
         </is>
       </c>
       <c r="K47" s="4" t="inlineStr">
@@ -6016,27 +7074,27 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">受取配送</t>
+          <t xml:space="preserve">受取配送明細</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_fulfillments</t>
+          <t xml:space="preserve">patient_fulfillment_items</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">受取人スナップショット</t>
+          <t xml:space="preserve">対象数量</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">recipient_snapshot</t>
+          <t xml:space="preserve">quantity</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">integer</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
@@ -6046,7 +7104,7 @@
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">YES</t>
+          <t xml:space="preserve">NO</t>
         </is>
       </c>
       <c r="I48" s="4" t="inlineStr">
@@ -6056,7 +7114,7 @@
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">&gt; 0</t>
         </is>
       </c>
       <c r="K48" s="4" t="inlineStr">
@@ -6068,47 +7126,47 @@
     <row r="49" ht="30" customHeight="1">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">配送開始</t>
+          <t xml:space="preserve">定期購入接続</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">受取配送</t>
+          <t xml:space="preserve">患者定期購入</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_fulfillments</t>
+          <t xml:space="preserve">patient_subscriptions</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">住所スナップショット</t>
+          <t xml:space="preserve">内部契約ID</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">address_snapshot</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">jsonb</t>
-        </is>
-      </c>
-      <c r="G49" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">uuid</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">YES</t>
+          <t xml:space="preserve">NO</t>
         </is>
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">gen_random_uuid()</t>
         </is>
       </c>
       <c r="J49" s="4" t="inlineStr">
@@ -6125,42 +7183,42 @@
     <row r="50" ht="30" customHeight="1">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">配送開始</t>
+          <t xml:space="preserve">定期購入接続</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">受取配送</t>
+          <t xml:space="preserve">患者定期購入</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_fulfillments</t>
+          <t xml:space="preserve">patient_subscriptions</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">配送会社</t>
+          <t xml:space="preserve">患者ID</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">carrier</t>
+          <t xml:space="preserve">patient_id</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="G50" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">uuid</t>
+        </is>
+      </c>
+      <c r="G50" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">YES</t>
+          <t xml:space="preserve">NO</t>
         </is>
       </c>
       <c r="I50" s="4" t="inlineStr">
@@ -6170,7 +7228,7 @@
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">patients.id</t>
         </is>
       </c>
       <c r="K50" s="4" t="inlineStr">
@@ -6182,42 +7240,42 @@
     <row r="51" ht="30" customHeight="1">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">配送開始</t>
+          <t xml:space="preserve">定期購入接続</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">受取配送</t>
+          <t xml:space="preserve">患者定期購入</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_fulfillments</t>
+          <t xml:space="preserve">patient_subscriptions</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">追跡番号</t>
+          <t xml:space="preserve">外部接続ID</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">tracking_number</t>
+          <t xml:space="preserve">commerce_account_id</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="G51" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">uuid</t>
+        </is>
+      </c>
+      <c r="G51" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK / UK3構成</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">YES</t>
+          <t xml:space="preserve">NO</t>
         </is>
       </c>
       <c r="I51" s="4" t="inlineStr">
@@ -6227,7 +7285,7 @@
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">commerce_accounts.id</t>
         </is>
       </c>
       <c r="K51" s="4" t="inlineStr">
@@ -6239,42 +7297,42 @@
     <row r="52" ht="30" customHeight="1">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">配送開始</t>
+          <t xml:space="preserve">定期購入接続</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">受取配送</t>
+          <t xml:space="preserve">患者定期購入</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_fulfillments</t>
+          <t xml:space="preserve">patient_subscriptions</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">準備完了日時</t>
+          <t xml:space="preserve">外部契約ID</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ready_at</t>
+          <t xml:space="preserve">external_subscription_id</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">timestamptz</t>
-        </is>
-      </c>
-      <c r="G52" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G52" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UK3構成</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">YES</t>
+          <t xml:space="preserve">NO</t>
         </is>
       </c>
       <c r="I52" s="4" t="inlineStr">
@@ -6296,32 +7354,32 @@
     <row r="53" ht="30" customHeight="1">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">配送開始</t>
+          <t xml:space="preserve">定期購入接続</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">受取配送</t>
+          <t xml:space="preserve">患者定期購入</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_fulfillments</t>
+          <t xml:space="preserve">patient_subscriptions</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">出荷日時</t>
+          <t xml:space="preserve">契約状態</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">shipped_at</t>
+          <t xml:space="preserve">status</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">timestamptz</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
@@ -6331,7 +7389,7 @@
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">YES</t>
+          <t xml:space="preserve">NO</t>
         </is>
       </c>
       <c r="I53" s="4" t="inlineStr">
@@ -6353,32 +7411,32 @@
     <row r="54" ht="30" customHeight="1">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">配送開始</t>
+          <t xml:space="preserve">定期購入接続</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">受取配送</t>
+          <t xml:space="preserve">患者定期購入</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_fulfillments</t>
+          <t xml:space="preserve">patient_subscriptions</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">完了日時</t>
+          <t xml:space="preserve">次回課金日</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">completed_at</t>
+          <t xml:space="preserve">next_billing_date</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">timestamptz</t>
+          <t xml:space="preserve">date</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
@@ -6410,47 +7468,47 @@
     <row r="55" ht="30" customHeight="1">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">配送開始</t>
+          <t xml:space="preserve">定期購入接続</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">受取配送明細</t>
+          <t xml:space="preserve">患者定期購入</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_fulfillment_items</t>
+          <t xml:space="preserve">patient_subscriptions</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">受取配送明細ID</t>
+          <t xml:space="preserve">次回提供予定日</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">next_fulfillment_date</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">uuid</t>
-        </is>
-      </c>
-      <c r="G55" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PK</t>
+          <t xml:space="preserve">date</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO</t>
+          <t xml:space="preserve">YES</t>
         </is>
       </c>
       <c r="I55" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">gen_random_uuid()</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J55" s="4" t="inlineStr">
@@ -6467,37 +7525,37 @@
     <row r="56" ht="30" customHeight="1">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">配送開始</t>
+          <t xml:space="preserve">定期購入接続</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">受取配送明細</t>
+          <t xml:space="preserve">患者定期購入</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_fulfillment_items</t>
+          <t xml:space="preserve">patient_subscriptions</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">受取配送ID</t>
+          <t xml:space="preserve">同期状態</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">fulfillment_id</t>
+          <t xml:space="preserve">sync_status</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">uuid</t>
-        </is>
-      </c>
-      <c r="G56" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FK / UK2構成</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G56" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
@@ -6507,12 +7565,12 @@
       </c>
       <c r="I56" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pending</t>
         </is>
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_fulfillments.id</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K56" s="4" t="inlineStr">
@@ -6524,37 +7582,37 @@
     <row r="57" ht="30" customHeight="1">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">配送開始</t>
+          <t xml:space="preserve">定期購入接続</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">受取配送明細</t>
+          <t xml:space="preserve">患者定期購入</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_fulfillment_items</t>
+          <t xml:space="preserve">patient_subscriptions</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文明細ID</t>
+          <t xml:space="preserve">外部更新日時</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">order_item_id</t>
+          <t xml:space="preserve">external_updated_at</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">uuid</t>
-        </is>
-      </c>
-      <c r="G57" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FK / UK2構成</t>
+          <t xml:space="preserve">timestamptz</t>
+        </is>
+      </c>
+      <c r="G57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
@@ -6569,7 +7627,7 @@
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_order_items.id</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K57" s="4" t="inlineStr">
@@ -6581,37 +7639,37 @@
     <row r="58" ht="30" customHeight="1">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">配送開始</t>
+          <t xml:space="preserve">定期購入接続</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">受取配送明細</t>
+          <t xml:space="preserve">定期購入明細</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_fulfillment_items</t>
+          <t xml:space="preserve">patient_subscription_items</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">対象数量</t>
+          <t xml:space="preserve">契約明細ID</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">quantity</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">integer</t>
-        </is>
-      </c>
-      <c r="G58" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">uuid</t>
+        </is>
+      </c>
+      <c r="G58" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
@@ -6621,12 +7679,12 @@
       </c>
       <c r="I58" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">gen_random_uuid()</t>
         </is>
       </c>
       <c r="J58" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">&gt; 0</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K58" s="4" t="inlineStr">
@@ -6643,12 +7701,12 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者定期購入</t>
+          <t xml:space="preserve">定期購入明細</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_subscriptions</t>
+          <t xml:space="preserve">patient_subscription_items</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -6658,7 +7716,7 @@
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">subscription_id</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
@@ -6666,9 +7724,9 @@
           <t xml:space="preserve">uuid</t>
         </is>
       </c>
-      <c r="G59" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PK</t>
+      <c r="G59" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr">
@@ -6678,12 +7736,12 @@
       </c>
       <c r="I59" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">gen_random_uuid()</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">patient_subscriptions.id</t>
         </is>
       </c>
       <c r="K59" s="4" t="inlineStr">
@@ -6700,22 +7758,22 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者定期購入</t>
+          <t xml:space="preserve">定期購入明細</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_subscriptions</t>
+          <t xml:space="preserve">patient_subscription_items</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者ID</t>
+          <t xml:space="preserve">商品ID</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_id</t>
+          <t xml:space="preserve">product_id</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
@@ -6730,7 +7788,7 @@
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO</t>
+          <t xml:space="preserve">YES</t>
         </is>
       </c>
       <c r="I60" s="4" t="inlineStr">
@@ -6740,7 +7798,7 @@
       </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patients.id</t>
+          <t xml:space="preserve">products.id</t>
         </is>
       </c>
       <c r="K60" s="4" t="inlineStr">
@@ -6757,37 +7815,37 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者定期購入</t>
+          <t xml:space="preserve">定期購入明細</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_subscriptions</t>
+          <t xml:space="preserve">patient_subscription_items</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部接続ID</t>
+          <t xml:space="preserve">外部契約明細ID</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_account_id</t>
+          <t xml:space="preserve">external_line_item_id</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">uuid</t>
-        </is>
-      </c>
-      <c r="G61" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FK / UK3構成</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO</t>
+          <t xml:space="preserve">YES</t>
         </is>
       </c>
       <c r="I61" s="4" t="inlineStr">
@@ -6797,7 +7855,7 @@
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_accounts.id</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K61" s="4" t="inlineStr">
@@ -6814,32 +7872,32 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者定期購入</t>
+          <t xml:space="preserve">定期購入明細</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_subscriptions</t>
+          <t xml:space="preserve">patient_subscription_items</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部契約ID</t>
+          <t xml:space="preserve">数量</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">external_subscription_id</t>
+          <t xml:space="preserve">quantity</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="G62" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UK3構成</t>
+          <t xml:space="preserve">integer</t>
+        </is>
+      </c>
+      <c r="G62" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr">
@@ -6854,7 +7912,7 @@
       </c>
       <c r="J62" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">&gt; 0</t>
         </is>
       </c>
       <c r="K62" s="4" t="inlineStr">
@@ -6871,27 +7929,27 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者定期購入</t>
+          <t xml:space="preserve">定期購入明細</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_subscriptions</t>
+          <t xml:space="preserve">patient_subscription_items</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">契約状態</t>
+          <t xml:space="preserve">契約時単価</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">status</t>
+          <t xml:space="preserve">unit_price_snapshot</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">bigint</t>
         </is>
       </c>
       <c r="G63" s="4" t="inlineStr">
@@ -6928,27 +7986,27 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者定期購入</t>
+          <t xml:space="preserve">定期購入明細</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_subscriptions</t>
+          <t xml:space="preserve">patient_subscription_items</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">次回課金日</t>
+          <t xml:space="preserve">通貨コード</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">next_billing_date</t>
+          <t xml:space="preserve">currency</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">date</t>
+          <t xml:space="preserve">char(3)</t>
         </is>
       </c>
       <c r="G64" s="4" t="inlineStr">
@@ -6958,7 +8016,7 @@
       </c>
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">YES</t>
+          <t xml:space="preserve">NO</t>
         </is>
       </c>
       <c r="I64" s="4" t="inlineStr">
@@ -6980,47 +8038,47 @@
     <row r="65" ht="30" customHeight="1">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">定期購入接続</t>
+          <t xml:space="preserve">Shopify接続</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者定期購入</t>
+          <t xml:space="preserve">外部受信イベント</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_subscriptions</t>
+          <t xml:space="preserve">commerce_webhook_events</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">次回提供予定日</t>
+          <t xml:space="preserve">受信イベントID</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">next_fulfillment_date</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">date</t>
-        </is>
-      </c>
-      <c r="G65" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">uuid</t>
+        </is>
+      </c>
+      <c r="G65" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">YES</t>
+          <t xml:space="preserve">NO</t>
         </is>
       </c>
       <c r="I65" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">gen_random_uuid()</t>
         </is>
       </c>
       <c r="J65" s="4" t="inlineStr">
@@ -7037,37 +8095,37 @@
     <row r="66" ht="30" customHeight="1">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">定期購入接続</t>
+          <t xml:space="preserve">Shopify接続</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者定期購入</t>
+          <t xml:space="preserve">外部受信イベント</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_subscriptions</t>
+          <t xml:space="preserve">commerce_webhook_events</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">同期状態</t>
+          <t xml:space="preserve">外部接続ID</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">sync_status</t>
+          <t xml:space="preserve">commerce_account_id</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="G66" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">uuid</t>
+        </is>
+      </c>
+      <c r="G66" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK / UK4構成</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr">
@@ -7077,12 +8135,12 @@
       </c>
       <c r="I66" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">pending</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J66" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">commerce_accounts.id</t>
         </is>
       </c>
       <c r="K66" s="4" t="inlineStr">
@@ -7094,37 +8152,37 @@
     <row r="67" ht="30" customHeight="1">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">定期購入接続</t>
+          <t xml:space="preserve">Shopify接続</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者定期購入</t>
+          <t xml:space="preserve">外部受信イベント</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_subscriptions</t>
+          <t xml:space="preserve">commerce_webhook_events</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部更新日時</t>
+          <t xml:space="preserve">外部イベントID</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">external_updated_at</t>
+          <t xml:space="preserve">external_event_id</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">timestamptz</t>
-        </is>
-      </c>
-      <c r="G67" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G67" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UK4構成</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr">
@@ -7151,37 +8209,37 @@
     <row r="68" ht="30" customHeight="1">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">定期購入接続</t>
+          <t xml:space="preserve">Shopify接続</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">定期購入明細</t>
+          <t xml:space="preserve">外部受信イベント</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_subscription_items</t>
+          <t xml:space="preserve">commerce_webhook_events</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">契約明細ID</t>
+          <t xml:space="preserve">トピック</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">topic</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">uuid</t>
-        </is>
-      </c>
-      <c r="G68" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PK</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G68" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr">
@@ -7191,7 +8249,7 @@
       </c>
       <c r="I68" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">gen_random_uuid()</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J68" s="4" t="inlineStr">
@@ -7208,37 +8266,37 @@
     <row r="69" ht="30" customHeight="1">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">定期購入接続</t>
+          <t xml:space="preserve">Shopify接続</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">定期購入明細</t>
+          <t xml:space="preserve">外部受信イベント</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_subscription_items</t>
+          <t xml:space="preserve">commerce_webhook_events</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">内部契約ID</t>
+          <t xml:space="preserve">処理状態</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">subscription_id</t>
+          <t xml:space="preserve">status</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">uuid</t>
-        </is>
-      </c>
-      <c r="G69" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FK</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G69" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr">
@@ -7248,12 +8306,12 @@
       </c>
       <c r="I69" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">received</t>
         </is>
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_subscriptions.id</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K69" s="4" t="inlineStr">
@@ -7265,42 +8323,42 @@
     <row r="70" ht="30" customHeight="1">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">定期購入接続</t>
+          <t xml:space="preserve">Shopify接続</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">定期購入明細</t>
+          <t xml:space="preserve">外部受信イベント</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_subscription_items</t>
+          <t xml:space="preserve">commerce_webhook_events</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">商品ID</t>
+          <t xml:space="preserve">受信内容</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">product_id</t>
+          <t xml:space="preserve">payload</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">uuid</t>
-        </is>
-      </c>
-      <c r="G70" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FK</t>
+          <t xml:space="preserve">jsonb</t>
+        </is>
+      </c>
+      <c r="G70" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">YES</t>
+          <t xml:space="preserve">NO</t>
         </is>
       </c>
       <c r="I70" s="4" t="inlineStr">
@@ -7310,7 +8368,7 @@
       </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">products.id</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K70" s="4" t="inlineStr">
@@ -7322,32 +8380,32 @@
     <row r="71" ht="30" customHeight="1">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">定期購入接続</t>
+          <t xml:space="preserve">Shopify接続</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">定期購入明細</t>
+          <t xml:space="preserve">外部受信イベント</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_subscription_items</t>
+          <t xml:space="preserve">commerce_webhook_events</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部契約明細ID</t>
+          <t xml:space="preserve">再試行回数</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">external_line_item_id</t>
+          <t xml:space="preserve">retry_count</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">integer</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr">
@@ -7357,12 +8415,12 @@
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">YES</t>
+          <t xml:space="preserve">NO</t>
         </is>
       </c>
       <c r="I71" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="J71" s="4" t="inlineStr">
@@ -7379,32 +8437,32 @@
     <row r="72" ht="30" customHeight="1">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">定期購入接続</t>
+          <t xml:space="preserve">Shopify接続</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">定期購入明細</t>
+          <t xml:space="preserve">外部受信イベント</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_subscription_items</t>
+          <t xml:space="preserve">commerce_webhook_events</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">数量</t>
+          <t xml:space="preserve">最終エラー</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">quantity</t>
+          <t xml:space="preserve">last_error</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">integer</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="G72" s="4" t="inlineStr">
@@ -7414,7 +8472,7 @@
       </c>
       <c r="H72" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO</t>
+          <t xml:space="preserve">YES</t>
         </is>
       </c>
       <c r="I72" s="4" t="inlineStr">
@@ -7424,7 +8482,7 @@
       </c>
       <c r="J72" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">&gt; 0</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K72" s="4" t="inlineStr">
@@ -7436,32 +8494,32 @@
     <row r="73" ht="30" customHeight="1">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">定期購入接続</t>
+          <t xml:space="preserve">Shopify接続</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">定期購入明細</t>
+          <t xml:space="preserve">外部受信イベント</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_subscription_items</t>
+          <t xml:space="preserve">commerce_webhook_events</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">契約時単価</t>
+          <t xml:space="preserve">受信日時</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">unit_price_snapshot</t>
+          <t xml:space="preserve">received_at</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">bigint</t>
+          <t xml:space="preserve">timestamptz</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr">
@@ -7476,7 +8534,7 @@
       </c>
       <c r="I73" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">now()</t>
         </is>
       </c>
       <c r="J73" s="4" t="inlineStr">
@@ -7493,32 +8551,32 @@
     <row r="74" ht="30" customHeight="1">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">定期購入接続</t>
+          <t xml:space="preserve">Shopify接続</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">定期購入明細</t>
+          <t xml:space="preserve">外部受信イベント</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_subscription_items</t>
+          <t xml:space="preserve">commerce_webhook_events</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">通貨コード</t>
+          <t xml:space="preserve">処理完了日時</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">currency</t>
+          <t xml:space="preserve">processed_at</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">char(3)</t>
+          <t xml:space="preserve">timestamptz</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr">
@@ -7528,7 +8586,7 @@
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO</t>
+          <t xml:space="preserve">YES</t>
         </is>
       </c>
       <c r="I74" s="4" t="inlineStr">
@@ -7555,17 +8613,17 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部受信イベント</t>
+          <t xml:space="preserve">外部送信キュー</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_webhook_events</t>
+          <t xml:space="preserve">commerce_outbox</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">受信イベントID</t>
+          <t xml:space="preserve">送信キューID</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
@@ -7612,12 +8670,12 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部受信イベント</t>
+          <t xml:space="preserve">外部送信キュー</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_webhook_events</t>
+          <t xml:space="preserve">commerce_outbox</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -7637,7 +8695,7 @@
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK / UK4構成</t>
+          <t xml:space="preserve">FK</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr">
@@ -7669,37 +8727,37 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部受信イベント</t>
+          <t xml:space="preserve">外部送信キュー</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_webhook_events</t>
+          <t xml:space="preserve">commerce_outbox</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部イベントID</t>
+          <t xml:space="preserve">内部注文ID</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">external_event_id</t>
+          <t xml:space="preserve">order_id</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="G77" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UK4構成</t>
+          <t xml:space="preserve">uuid</t>
+        </is>
+      </c>
+      <c r="G77" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO</t>
+          <t xml:space="preserve">YES</t>
         </is>
       </c>
       <c r="I77" s="4" t="inlineStr">
@@ -7709,7 +8767,7 @@
       </c>
       <c r="J77" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">patient_orders.id</t>
         </is>
       </c>
       <c r="K77" s="4" t="inlineStr">
@@ -7726,22 +8784,22 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部受信イベント</t>
+          <t xml:space="preserve">外部送信キュー</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_webhook_events</t>
+          <t xml:space="preserve">commerce_outbox</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">トピック</t>
+          <t xml:space="preserve">送信処理種別</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">topic</t>
+          <t xml:space="preserve">command_type</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
@@ -7783,32 +8841,32 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部受信イベント</t>
+          <t xml:space="preserve">外部送信キュー</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_webhook_events</t>
+          <t xml:space="preserve">commerce_outbox</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">処理状態</t>
+          <t xml:space="preserve">送信冪等キー</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">status</t>
+          <t xml:space="preserve">idempotency_key</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="G79" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">uuid</t>
+        </is>
+      </c>
+      <c r="G79" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UK</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr">
@@ -7818,7 +8876,7 @@
       </c>
       <c r="I79" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">received</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J79" s="4" t="inlineStr">
@@ -7840,17 +8898,17 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部受信イベント</t>
+          <t xml:space="preserve">外部送信キュー</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_webhook_events</t>
+          <t xml:space="preserve">commerce_outbox</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">受信内容</t>
+          <t xml:space="preserve">送信内容</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
@@ -7897,27 +8955,27 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部受信イベント</t>
+          <t xml:space="preserve">外部送信キュー</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_webhook_events</t>
+          <t xml:space="preserve">commerce_outbox</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">再試行回数</t>
+          <t xml:space="preserve">送信状態</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">retry_count</t>
+          <t xml:space="preserve">status</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">integer</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="G81" s="4" t="inlineStr">
@@ -7932,7 +8990,7 @@
       </c>
       <c r="I81" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">pending</t>
         </is>
       </c>
       <c r="J81" s="4" t="inlineStr">
@@ -7954,27 +9012,27 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部受信イベント</t>
+          <t xml:space="preserve">外部送信キュー</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_webhook_events</t>
+          <t xml:space="preserve">commerce_outbox</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">最終エラー</t>
+          <t xml:space="preserve">再試行回数</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">last_error</t>
+          <t xml:space="preserve">retry_count</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">integer</t>
         </is>
       </c>
       <c r="G82" s="4" t="inlineStr">
@@ -7984,12 +9042,12 @@
       </c>
       <c r="H82" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">YES</t>
+          <t xml:space="preserve">NO</t>
         </is>
       </c>
       <c r="I82" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="J82" s="4" t="inlineStr">
@@ -8011,22 +9069,22 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部受信イベント</t>
+          <t xml:space="preserve">外部送信キュー</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_webhook_events</t>
+          <t xml:space="preserve">commerce_outbox</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">受信日時</t>
+          <t xml:space="preserve">次回再試行日時</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">received_at</t>
+          <t xml:space="preserve">next_retry_at</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
@@ -8041,12 +9099,12 @@
       </c>
       <c r="H83" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO</t>
+          <t xml:space="preserve">YES</t>
         </is>
       </c>
       <c r="I83" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">now()</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J83" s="4" t="inlineStr">
@@ -8068,22 +9126,22 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部受信イベント</t>
+          <t xml:space="preserve">外部送信キュー</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_webhook_events</t>
+          <t xml:space="preserve">commerce_outbox</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">処理完了日時</t>
+          <t xml:space="preserve">作成日時</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">processed_at</t>
+          <t xml:space="preserve">created_at</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
@@ -8098,12 +9156,12 @@
       </c>
       <c r="H84" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">YES</t>
+          <t xml:space="preserve">NO</t>
         </is>
       </c>
       <c r="I84" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">now()</t>
         </is>
       </c>
       <c r="J84" s="4" t="inlineStr">
@@ -8135,32 +9193,32 @@
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">送信キューID</t>
+          <t xml:space="preserve">処理完了日時</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">processed_at</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">uuid</t>
-        </is>
-      </c>
-      <c r="G85" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PK</t>
+          <t xml:space="preserve">timestamptz</t>
+        </is>
+      </c>
+      <c r="G85" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO</t>
+          <t xml:space="preserve">YES</t>
         </is>
       </c>
       <c r="I85" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">gen_random_uuid()</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J85" s="4" t="inlineStr">
@@ -8169,576 +9227,6 @@
         </is>
       </c>
       <c r="K85" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="30" customHeight="1">
-      <c r="A86" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Shopify接続</t>
-        </is>
-      </c>
-      <c r="B86" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">外部送信キュー</t>
-        </is>
-      </c>
-      <c r="C86" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">commerce_outbox</t>
-        </is>
-      </c>
-      <c r="D86" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">外部接続ID</t>
-        </is>
-      </c>
-      <c r="E86" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">commerce_account_id</t>
-        </is>
-      </c>
-      <c r="F86" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">uuid</t>
-        </is>
-      </c>
-      <c r="G86" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FK</t>
-        </is>
-      </c>
-      <c r="H86" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NO</t>
-        </is>
-      </c>
-      <c r="I86" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J86" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">commerce_accounts.id</t>
-        </is>
-      </c>
-      <c r="K86" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="30" customHeight="1">
-      <c r="A87" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Shopify接続</t>
-        </is>
-      </c>
-      <c r="B87" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">外部送信キュー</t>
-        </is>
-      </c>
-      <c r="C87" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">commerce_outbox</t>
-        </is>
-      </c>
-      <c r="D87" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">内部注文ID</t>
-        </is>
-      </c>
-      <c r="E87" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">order_id</t>
-        </is>
-      </c>
-      <c r="F87" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">uuid</t>
-        </is>
-      </c>
-      <c r="G87" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FK</t>
-        </is>
-      </c>
-      <c r="H87" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">YES</t>
-        </is>
-      </c>
-      <c r="I87" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J87" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">patient_orders.id</t>
-        </is>
-      </c>
-      <c r="K87" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="30" customHeight="1">
-      <c r="A88" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Shopify接続</t>
-        </is>
-      </c>
-      <c r="B88" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">外部送信キュー</t>
-        </is>
-      </c>
-      <c r="C88" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">commerce_outbox</t>
-        </is>
-      </c>
-      <c r="D88" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">送信処理種別</t>
-        </is>
-      </c>
-      <c r="E88" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">command_type</t>
-        </is>
-      </c>
-      <c r="F88" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="G88" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H88" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NO</t>
-        </is>
-      </c>
-      <c r="I88" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J88" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="K88" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="30" customHeight="1">
-      <c r="A89" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Shopify接続</t>
-        </is>
-      </c>
-      <c r="B89" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">外部送信キュー</t>
-        </is>
-      </c>
-      <c r="C89" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">commerce_outbox</t>
-        </is>
-      </c>
-      <c r="D89" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">送信冪等キー</t>
-        </is>
-      </c>
-      <c r="E89" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">idempotency_key</t>
-        </is>
-      </c>
-      <c r="F89" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">uuid</t>
-        </is>
-      </c>
-      <c r="G89" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UK</t>
-        </is>
-      </c>
-      <c r="H89" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NO</t>
-        </is>
-      </c>
-      <c r="I89" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J89" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="K89" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="30" customHeight="1">
-      <c r="A90" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Shopify接続</t>
-        </is>
-      </c>
-      <c r="B90" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">外部送信キュー</t>
-        </is>
-      </c>
-      <c r="C90" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">commerce_outbox</t>
-        </is>
-      </c>
-      <c r="D90" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">送信内容</t>
-        </is>
-      </c>
-      <c r="E90" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">payload</t>
-        </is>
-      </c>
-      <c r="F90" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jsonb</t>
-        </is>
-      </c>
-      <c r="G90" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H90" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NO</t>
-        </is>
-      </c>
-      <c r="I90" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J90" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="K90" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="30" customHeight="1">
-      <c r="A91" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Shopify接続</t>
-        </is>
-      </c>
-      <c r="B91" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">外部送信キュー</t>
-        </is>
-      </c>
-      <c r="C91" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">commerce_outbox</t>
-        </is>
-      </c>
-      <c r="D91" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">送信状態</t>
-        </is>
-      </c>
-      <c r="E91" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">status</t>
-        </is>
-      </c>
-      <c r="F91" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="G91" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H91" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NO</t>
-        </is>
-      </c>
-      <c r="I91" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pending</t>
-        </is>
-      </c>
-      <c r="J91" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="K91" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="30" customHeight="1">
-      <c r="A92" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Shopify接続</t>
-        </is>
-      </c>
-      <c r="B92" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">外部送信キュー</t>
-        </is>
-      </c>
-      <c r="C92" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">commerce_outbox</t>
-        </is>
-      </c>
-      <c r="D92" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">再試行回数</t>
-        </is>
-      </c>
-      <c r="E92" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">retry_count</t>
-        </is>
-      </c>
-      <c r="F92" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">integer</t>
-        </is>
-      </c>
-      <c r="G92" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H92" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NO</t>
-        </is>
-      </c>
-      <c r="I92" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
-        </is>
-      </c>
-      <c r="J92" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="K92" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="30" customHeight="1">
-      <c r="A93" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Shopify接続</t>
-        </is>
-      </c>
-      <c r="B93" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">外部送信キュー</t>
-        </is>
-      </c>
-      <c r="C93" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">commerce_outbox</t>
-        </is>
-      </c>
-      <c r="D93" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">次回再試行日時</t>
-        </is>
-      </c>
-      <c r="E93" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">next_retry_at</t>
-        </is>
-      </c>
-      <c r="F93" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">timestamptz</t>
-        </is>
-      </c>
-      <c r="G93" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H93" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">YES</t>
-        </is>
-      </c>
-      <c r="I93" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J93" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="K93" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="30" customHeight="1">
-      <c r="A94" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Shopify接続</t>
-        </is>
-      </c>
-      <c r="B94" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">外部送信キュー</t>
-        </is>
-      </c>
-      <c r="C94" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">commerce_outbox</t>
-        </is>
-      </c>
-      <c r="D94" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">作成日時</t>
-        </is>
-      </c>
-      <c r="E94" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">created_at</t>
-        </is>
-      </c>
-      <c r="F94" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">timestamptz</t>
-        </is>
-      </c>
-      <c r="G94" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H94" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NO</t>
-        </is>
-      </c>
-      <c r="I94" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">now()</t>
-        </is>
-      </c>
-      <c r="J94" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="K94" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="30" customHeight="1">
-      <c r="A95" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Shopify接続</t>
-        </is>
-      </c>
-      <c r="B95" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">外部送信キュー</t>
-        </is>
-      </c>
-      <c r="C95" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">commerce_outbox</t>
-        </is>
-      </c>
-      <c r="D95" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">処理完了日時</t>
-        </is>
-      </c>
-      <c r="E95" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">processed_at</t>
-        </is>
-      </c>
-      <c r="F95" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">timestamptz</t>
-        </is>
-      </c>
-      <c r="G95" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H95" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">YES</t>
-        </is>
-      </c>
-      <c r="I95" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J95" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="K95" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -8749,7 +9237,7 @@
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A2:K2"/>
   </mergeCells>
-  <autoFilter ref="A4:K95"/>
+  <autoFilter ref="A4:K85"/>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0" paperSize="9"/>
 </worksheet>
@@ -8757,7 +9245,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -9326,155 +9814,155 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">患者注文</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_orders.id</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0..1</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">order_shipping_addresses.order_id</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">注文配送先</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK・FK・CASCADE</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">患者注文</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_orders.id</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_order_events.order_id</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">注文操作履歴</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK・CASCADE</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">商品</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">products.id</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">0..1</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="E24" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">patient_order_items.product_id</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr">
+      <c r="F24" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">患者注文明細</t>
         </is>
       </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="G24" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">FK・SET NULL</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">将来リレーション案</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">親DB日本語名</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">親KEY</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">親多重度</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">子多重度</t>
         </is>
       </c>
-      <c r="E25" s="3" t="inlineStr">
+      <c r="E27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">子FK</t>
         </is>
       </c>
-      <c r="F25" s="3" t="inlineStr">
+      <c r="F27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">子DB日本語名</t>
         </is>
       </c>
-      <c r="G25" s="3" t="inlineStr">
+      <c r="G27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">削除・備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">患者注文</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">patient_orders.id</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">patient_order_events.order_id</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">注文操作履歴</t>
-        </is>
-      </c>
-      <c r="G26" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FK</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">患者注文</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">patient_orders.id</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">order_transaction_projections.order_id</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">決済返金投影</t>
-        </is>
-      </c>
-      <c r="G27" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FK</t>
         </is>
       </c>
     </row>
@@ -9501,12 +9989,12 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_fulfillments.order_id</t>
+          <t xml:space="preserve">order_transaction_projections.order_id</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">受取配送</t>
+          <t xml:space="preserve">決済返金投影</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
@@ -9518,32 +10006,32 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">患者注文</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_orders.id</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_fulfillments.order_id</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">受取配送</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">patient_fulfillments.id</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">patient_fulfillment_items.fulfillment_id</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">受取配送明細</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
@@ -9555,12 +10043,12 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文明細</t>
+          <t xml:space="preserve">受取配送</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_order_items.id</t>
+          <t xml:space="preserve">patient_fulfillments.id</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -9575,7 +10063,7 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_fulfillment_items.order_item_id</t>
+          <t xml:space="preserve">patient_fulfillment_items.fulfillment_id</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
@@ -9592,12 +10080,12 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部コマース接続</t>
+          <t xml:space="preserve">注文明細</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_accounts.id</t>
+          <t xml:space="preserve">patient_order_items.id</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -9612,12 +10100,12 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders.commerce_account_id</t>
+          <t xml:space="preserve">patient_fulfillment_items.order_item_id</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文</t>
+          <t xml:space="preserve">受取配送明細</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
@@ -9649,12 +10137,12 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_webhook_events.commerce_account_id</t>
+          <t xml:space="preserve">patient_orders.commerce_account_id</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部受信イベント</t>
+          <t xml:space="preserve">患者注文</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
@@ -9686,12 +10174,12 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_outbox.commerce_account_id</t>
+          <t xml:space="preserve">commerce_webhook_events.commerce_account_id</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部送信キュー</t>
+          <t xml:space="preserve">外部受信イベント</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
@@ -9703,12 +10191,12 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者</t>
+          <t xml:space="preserve">外部コマース接続</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patients.id</t>
+          <t xml:space="preserve">commerce_accounts.id</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -9723,12 +10211,12 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_subscriptions.patient_id</t>
+          <t xml:space="preserve">commerce_outbox.commerce_account_id</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者定期購入</t>
+          <t xml:space="preserve">外部送信キュー</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
@@ -9740,32 +10228,32 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">患者</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patients.id</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscriptions.patient_id</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">患者定期購入</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">patient_subscriptions.id</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="D35" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">patient_subscription_items.subscription_id</t>
-        </is>
-      </c>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">定期購入明細</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr">
@@ -9787,25 +10275,62 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscription_items.subscription_id</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">定期購入明細</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">患者定期購入</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscriptions.id</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">0..1</t>
         </is>
       </c>
-      <c r="D36" s="4" t="inlineStr">
+      <c r="D37" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr">
+      <c r="E37" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">patient_orders.subscription_id</t>
         </is>
       </c>
-      <c r="F36" s="4" t="inlineStr">
+      <c r="F37" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">患者注文</t>
         </is>
       </c>
-      <c r="G36" s="4" t="inlineStr">
+      <c r="G37" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">FK</t>
         </is>
@@ -9816,7 +10341,7 @@
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A17:H17"/>
-    <mergeCell ref="A24:H24"/>
+    <mergeCell ref="A26:H26"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0" paperSize="9"/>
@@ -9825,7 +10350,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Q35"/>
+  <dimension ref="A1:Q53"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -10345,200 +10870,536 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="26">
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">患者注文 1 ─── 0..1 注文配送先</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="23" customHeight="1">
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">注文配送先
+order_shipping_addresses</t>
+        </is>
+      </c>
+      <c r="K29" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">注文操作履歴
+patient_order_events</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">日本語項目</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">物理カラム</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KEY</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">日本語項目</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">物理カラム</t>
+        </is>
+      </c>
+      <c r="O31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">内部注文ID</t>
+        </is>
+      </c>
+      <c r="D32" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">order_id</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK/FK</t>
+        </is>
+      </c>
+      <c r="K32" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">イベントID</t>
+        </is>
+      </c>
+      <c r="M32" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">id</t>
+        </is>
+      </c>
+      <c r="O32" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">郵便番号</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">postal_code</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K33" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">内部注文ID</t>
+        </is>
+      </c>
+      <c r="M33" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">order_id</t>
+        </is>
+      </c>
+      <c r="O33" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">都道府県</t>
+        </is>
+      </c>
+      <c r="D34" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prefecture</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K34" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">イベント種別</t>
+        </is>
+      </c>
+      <c r="M34" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">event_type</t>
+        </is>
+      </c>
+      <c r="O34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">市区町村</t>
+        </is>
+      </c>
+      <c r="D35" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">city</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K35" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">操作者種別</t>
+        </is>
+      </c>
+      <c r="M35" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actor_type</t>
+        </is>
+      </c>
+      <c r="O35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">住所1</t>
+        </is>
+      </c>
+      <c r="D36" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">address_line1</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K36" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">変更前状態</t>
+        </is>
+      </c>
+      <c r="M36" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">from_status</t>
+        </is>
+      </c>
+      <c r="O36" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">受取人名</t>
+        </is>
+      </c>
+      <c r="D37" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">recipient_name</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K37" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">変更後状態</t>
+        </is>
+      </c>
+      <c r="M37" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">to_status</t>
+        </is>
+      </c>
+      <c r="O37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">電話番号</t>
+        </is>
+      </c>
+      <c r="D38" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">phone</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">リレーション一覧</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">親DB</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B47" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">親KEY</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="C47" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">親</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
+      <c r="D47" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">子</t>
         </is>
       </c>
-      <c r="E31" s="3" t="inlineStr">
+      <c r="E47" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">子FK</t>
         </is>
       </c>
-      <c r="F31" s="3" t="inlineStr">
+      <c r="F47" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">子DB</t>
         </is>
       </c>
-      <c r="G31" s="3" t="inlineStr">
+      <c r="G47" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">備考</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">医院</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B48" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">clinics.customer_code</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C48" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="D48" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
+      <c r="E48" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">patient_orders.customer_code</t>
         </is>
       </c>
-      <c r="F32" s="4" t="inlineStr">
+      <c r="F48" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">患者注文</t>
         </is>
       </c>
-      <c r="G32" s="4" t="inlineStr">
+      <c r="G48" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">FK</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">患者</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B49" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">patients.id</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C49" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="D49" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr">
+      <c r="E49" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">patient_orders.patient_id</t>
         </is>
       </c>
-      <c r="F33" s="4" t="inlineStr">
+      <c r="F49" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">患者注文</t>
         </is>
       </c>
-      <c r="G33" s="4" t="inlineStr">
+      <c r="G49" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">FK・現状CASCADE</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">患者注文</t>
         </is>
       </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="B50" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">patient_orders.id</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C50" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="D50" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr">
+      <c r="E50" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">patient_order_items.order_id</t>
         </is>
       </c>
-      <c r="F34" s="4" t="inlineStr">
+      <c r="F50" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">患者注文明細</t>
         </is>
       </c>
-      <c r="G34" s="4" t="inlineStr">
+      <c r="G50" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">FK・CASCADE</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">患者注文</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_orders.id</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0..1</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">order_shipping_addresses.order_id</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">注文配送先</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK・FK・CASCADE</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">患者注文</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_orders.id</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_order_events.order_id</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">注文操作履歴</t>
+        </is>
+      </c>
+      <c r="G52" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK・CASCADE</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">商品</t>
         </is>
       </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="B53" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">products.id</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="C53" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">0..1</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="D53" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
+      <c r="E53" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">patient_order_items.product_id</t>
         </is>
       </c>
-      <c r="F35" s="4" t="inlineStr">
+      <c r="F53" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">患者注文明細</t>
         </is>
       </c>
-      <c r="G35" s="4" t="inlineStr">
+      <c r="G53" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">FK・SET NULL</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="65">
+  <mergeCells count="98">
     <mergeCell ref="A1:Q1"/>
     <mergeCell ref="A2:Q2"/>
     <mergeCell ref="A4:E5"/>
@@ -10603,7 +11464,40 @@
     <mergeCell ref="L23:M23"/>
     <mergeCell ref="N23:O23"/>
     <mergeCell ref="L25:Q26"/>
-    <mergeCell ref="A30:Q30"/>
+    <mergeCell ref="B29:F30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="K29:O30"/>
+    <mergeCell ref="K31:L31"/>
+    <mergeCell ref="M31:N31"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="M32:N32"/>
+    <mergeCell ref="K33:L33"/>
+    <mergeCell ref="M33:N33"/>
+    <mergeCell ref="K34:L34"/>
+    <mergeCell ref="M34:N34"/>
+    <mergeCell ref="K35:L35"/>
+    <mergeCell ref="M35:N35"/>
+    <mergeCell ref="K36:L36"/>
+    <mergeCell ref="M36:N36"/>
+    <mergeCell ref="K37:L37"/>
+    <mergeCell ref="M37:N37"/>
+    <mergeCell ref="B26:J27"/>
+    <mergeCell ref="A46:Q46"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0" paperSize="9"/>
@@ -10612,7 +11506,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:W72"/>
+  <dimension ref="A1:W71"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -11224,7 +12118,7 @@
 patient_order_items</t>
         </is>
       </c>
-      <c r="M31" s="10" t="inlineStr">
+      <c r="M31" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">注文操作履歴
 patient_order_events</t>
@@ -11461,7 +12355,7 @@
       </c>
       <c r="O36" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">before_status</t>
+          <t xml:space="preserve">from_status</t>
         </is>
       </c>
       <c r="Q36" s="4" t="inlineStr">
@@ -11493,7 +12387,7 @@
       </c>
       <c r="O37" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">after_status</t>
+          <t xml:space="preserve">to_status</t>
         </is>
       </c>
       <c r="Q37" s="4" t="inlineStr">
@@ -11510,6 +12404,12 @@
       </c>
     </row>
     <row r="46" ht="23" customHeight="1">
+      <c r="A46" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">注文配送先
+order_shipping_addresses</t>
+        </is>
+      </c>
       <c r="G46" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">受取配送
@@ -11524,6 +12424,21 @@
       </c>
     </row>
     <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">日本語項目</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">物理カラム</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KEY</t>
+        </is>
+      </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">日本語項目</t>
@@ -11556,6 +12471,21 @@
       </c>
     </row>
     <row r="49">
+      <c r="A49" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">内部注文ID</t>
+        </is>
+      </c>
+      <c r="C49" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">order_id</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK/FK</t>
+        </is>
+      </c>
       <c r="G49" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">受取配送ID</t>
@@ -11588,6 +12518,21 @@
       </c>
     </row>
     <row r="50">
+      <c r="A50" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">郵便番号</t>
+        </is>
+      </c>
+      <c r="C50" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">postal_code</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
       <c r="G50" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">内部注文ID</t>
@@ -11620,6 +12565,21 @@
       </c>
     </row>
     <row r="51">
+      <c r="A51" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">住所1</t>
+        </is>
+      </c>
+      <c r="C51" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">address_line1</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
       <c r="G51" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">区分</t>
@@ -11652,6 +12612,21 @@
       </c>
     </row>
     <row r="52">
+      <c r="A52" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">受取人名</t>
+        </is>
+      </c>
+      <c r="C52" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">recipient_name</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
       <c r="G52" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">状態</t>
@@ -11735,12 +12710,12 @@
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_order_events.order_id</t>
+          <t xml:space="preserve">order_transaction_projections.order_id</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文操作履歴</t>
+          <t xml:space="preserve">決済返金投影</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr">
@@ -11772,12 +12747,12 @@
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">order_transaction_projections.order_id</t>
+          <t xml:space="preserve">patient_fulfillments.order_id</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">決済返金投影</t>
+          <t xml:space="preserve">受取配送</t>
         </is>
       </c>
       <c r="G63" s="4" t="inlineStr">
@@ -11789,12 +12764,12 @@
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文</t>
+          <t xml:space="preserve">受取配送</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders.id</t>
+          <t xml:space="preserve">patient_fulfillments.id</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -11809,12 +12784,12 @@
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_fulfillments.order_id</t>
+          <t xml:space="preserve">patient_fulfillment_items.fulfillment_id</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">受取配送</t>
+          <t xml:space="preserve">受取配送明細</t>
         </is>
       </c>
       <c r="G64" s="4" t="inlineStr">
@@ -11826,12 +12801,12 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">受取配送</t>
+          <t xml:space="preserve">注文明細</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_fulfillments.id</t>
+          <t xml:space="preserve">patient_order_items.id</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -11846,7 +12821,7 @@
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_fulfillment_items.fulfillment_id</t>
+          <t xml:space="preserve">patient_fulfillment_items.order_item_id</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
@@ -11863,12 +12838,12 @@
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文明細</t>
+          <t xml:space="preserve">外部コマース接続</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_order_items.id</t>
+          <t xml:space="preserve">commerce_accounts.id</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -11883,12 +12858,12 @@
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_fulfillment_items.order_item_id</t>
+          <t xml:space="preserve">patient_orders.commerce_account_id</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">受取配送明細</t>
+          <t xml:space="preserve">患者注文</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr">
@@ -11920,12 +12895,12 @@
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders.commerce_account_id</t>
+          <t xml:space="preserve">commerce_webhook_events.commerce_account_id</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文</t>
+          <t xml:space="preserve">外部受信イベント</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr">
@@ -11957,12 +12932,12 @@
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_webhook_events.commerce_account_id</t>
+          <t xml:space="preserve">commerce_outbox.commerce_account_id</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部受信イベント</t>
+          <t xml:space="preserve">外部送信キュー</t>
         </is>
       </c>
       <c r="G68" s="4" t="inlineStr">
@@ -11974,12 +12949,12 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部コマース接続</t>
+          <t xml:space="preserve">患者</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_accounts.id</t>
+          <t xml:space="preserve">patients.id</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -11994,12 +12969,12 @@
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_outbox.commerce_account_id</t>
+          <t xml:space="preserve">patient_subscriptions.patient_id</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部送信キュー</t>
+          <t xml:space="preserve">患者定期購入</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr">
@@ -12011,12 +12986,12 @@
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者</t>
+          <t xml:space="preserve">患者定期購入</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patients.id</t>
+          <t xml:space="preserve">patient_subscriptions.id</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -12031,12 +13006,12 @@
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_subscriptions.patient_id</t>
+          <t xml:space="preserve">patient_subscription_items.subscription_id</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者定期購入</t>
+          <t xml:space="preserve">定期購入明細</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr">
@@ -12058,7 +13033,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">0..1</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -12068,12 +13043,12 @@
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_subscription_items.subscription_id</t>
+          <t xml:space="preserve">patient_orders.subscription_id</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">定期購入明細</t>
+          <t xml:space="preserve">患者注文</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr">
@@ -12082,45 +13057,8 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">患者定期購入</t>
-        </is>
-      </c>
-      <c r="B72" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">patient_subscriptions.id</t>
-        </is>
-      </c>
-      <c r="C72" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0..1</t>
-        </is>
-      </c>
-      <c r="D72" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="E72" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">patient_orders.subscription_id</t>
-        </is>
-      </c>
-      <c r="F72" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">患者注文</t>
-        </is>
-      </c>
-      <c r="G72" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FK</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="134">
+  <mergeCells count="145">
     <mergeCell ref="A1:W1"/>
     <mergeCell ref="A2:W2"/>
     <mergeCell ref="A4:E5"/>
@@ -12232,6 +13170,17 @@
     <mergeCell ref="U35:V35"/>
     <mergeCell ref="S36:T36"/>
     <mergeCell ref="U36:V36"/>
+    <mergeCell ref="A46:E47"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="C50:D50"/>
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="C51:D51"/>
+    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="C52:D52"/>
     <mergeCell ref="G46:K47"/>
     <mergeCell ref="G48:H48"/>
     <mergeCell ref="I48:J48"/>
@@ -12385,32 +13334,32 @@
       </c>
     </row>
     <row r="7" ht="42" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Phase 1-2</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">次に実施</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">一部完了</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">patient_order_events</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">状態変更、操作者、理由を記録する。</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">状態変更、操作者、変更前後を記録済み。変更理由の記録は今後追加する。</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">注文更新と同一トランザクション。</t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">未実施</t>
         </is>
@@ -12449,34 +13398,34 @@
       </c>
     </row>
     <row r="9" ht="42" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Phase 1-4</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">次に実施</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">自宅配送</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">住所・責任主体確定までdeliveryを無効化。</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">完了</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">order_shipping_addresses</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">自宅配送を有効化し、注文時点の配送先を保存する。</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">住所なし配送を許可しない。</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">未実施</t>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">実装・動作確認済み</t>
         </is>
       </c>
     </row>

--- a/project_clinic_order_management_db_definition.xlsx
+++ b/project_clinic_order_management_db_definition.xlsx
@@ -290,7 +290,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supabaseのpatient_orders / patient_order_items / order_shipping_addresses / patient_order_events</t>
+          <t xml:space="preserve">Supabaseのpatient_orders / patient_order_items / delivery_destinations / order_delivery_destinations / patient_order_events</t>
         </is>
       </c>
     </row>
@@ -338,7 +338,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">自宅配送時はorder_shipping_addressesへ注文時点の配送先を保存し、住所なし配送を拒否する。</t>
+          <t xml:space="preserve">医院・患者は複数送り先を持ち、order_delivery_destinationsへ注文時点の送り先を保存する。</t>
         </is>
       </c>
     </row>
@@ -476,7 +476,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -701,12 +701,12 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文配送先</t>
+          <t xml:space="preserve">送り先マスタ</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">order_shipping_addresses</t>
+          <t xml:space="preserve">delivery_destinations</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">自宅配送注文に対して、注文時点の配送先を1対1で保存する履歴スナップショット。</t>
+          <t xml:space="preserve">医院または患者が複数所有できる送り先。論理削除と既定送り先を管理する。</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -733,12 +733,12 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文操作履歴</t>
+          <t xml:space="preserve">注文配送先</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_order_events</t>
+          <t xml:space="preserve">order_delivery_destinations</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文登録と状態変更について、操作者と変更前後の状態を保存する監査イベント。</t>
+          <t xml:space="preserve">選択した送り先を注文時点の不変スナップショットとして1対1で保存する。</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -760,27 +760,27 @@
     <row r="12" ht="34" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shopify接続</t>
+          <t xml:space="preserve">現行</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部コマース接続</t>
+          <t xml:space="preserve">注文操作履歴</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_accounts</t>
+          <t xml:space="preserve">patient_order_events</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">将来案</t>
+          <t xml:space="preserve">実装済み</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shopifyストア等の外部接続先。医院との対応方式は接続構成確定後に決定する。</t>
+          <t xml:space="preserve">注文登録と状態変更について、操作者と変更前後の状態を保存する監査イベント。</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -797,22 +797,22 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文拡張</t>
+          <t xml:space="preserve">外部コマース接続</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders</t>
+          <t xml:space="preserve">commerce_accounts</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">既存テーブル拡張案</t>
+          <t xml:space="preserve">将来案</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">既存IDを維持し、外部・金額・排他制御の列を追加する。</t>
+          <t xml:space="preserve">Shopifyストア等の外部接続先。医院との対応方式は接続構成確定後に決定する。</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -829,12 +829,12 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文明細拡張</t>
+          <t xml:space="preserve">患者注文拡張</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_order_items</t>
+          <t xml:space="preserve">patient_orders</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部明細と通貨を明確化し、既存スナップショットを維持する。</t>
+          <t xml:space="preserve">既存IDを維持し、外部・金額・排他制御の列を追加する。</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -856,27 +856,27 @@
     <row r="15" ht="34" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">決済接続</t>
+          <t xml:space="preserve">Shopify接続</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">決済返金投影</t>
+          <t xml:space="preserve">患者注文明細拡張</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">order_transaction_projections</t>
+          <t xml:space="preserve">patient_order_items</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">将来案</t>
+          <t xml:space="preserve">既存テーブル拡張案</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shopify上の決済・返金を表示する投影。会計台帳ではない。</t>
+          <t xml:space="preserve">外部明細と通貨を明確化し、既存スナップショットを維持する。</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -888,17 +888,17 @@
     <row r="16" ht="34" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">配送開始</t>
+          <t xml:space="preserve">決済接続</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">受取配送</t>
+          <t xml:space="preserve">決済返金投影</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_fulfillments</t>
+          <t xml:space="preserve">order_transaction_projections</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院受け取り・配送・部分引き渡しの単位。</t>
+          <t xml:space="preserve">Shopify上の決済・返金を表示する投影。会計台帳ではない。</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -925,12 +925,12 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">受取配送明細</t>
+          <t xml:space="preserve">受取配送</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_fulfillment_items</t>
+          <t xml:space="preserve">patient_fulfillments</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -940,7 +940,7 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">部分受け取り・部分配送時の対象明細と数量。</t>
+          <t xml:space="preserve">医院受け取り・配送・部分引き渡しの単位。</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -952,17 +952,17 @@
     <row r="18" ht="34" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">定期購入接続</t>
+          <t xml:space="preserve">配送開始</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者定期購入</t>
+          <t xml:space="preserve">受取配送明細</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_subscriptions</t>
+          <t xml:space="preserve">patient_fulfillment_items</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shopify上の定期購入契約を患者ポータルへ表示する投影。</t>
+          <t xml:space="preserve">部分受け取り・部分配送時の対象明細と数量。</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -989,12 +989,12 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">定期購入明細</t>
+          <t xml:space="preserve">患者定期購入</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_subscription_items</t>
+          <t xml:space="preserve">patient_subscriptions</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">契約時点の商品・数量・単価の投影。</t>
+          <t xml:space="preserve">Shopify上の定期購入契約を患者ポータルへ表示する投影。</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
@@ -1016,17 +1016,17 @@
     <row r="20" ht="34" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shopify接続</t>
+          <t xml:space="preserve">定期購入接続</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部受信イベント</t>
+          <t xml:space="preserve">定期購入明細</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_webhook_events</t>
+          <t xml:space="preserve">patient_subscription_items</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Webhookを先に永続化し、重複排除・再試行するInbox。</t>
+          <t xml:space="preserve">契約時点の商品・数量・単価の投影。</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -1053,57 +1053,89 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">外部受信イベント</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">commerce_webhook_events</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">将来案</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Webhookを先に永続化し、重複排除・再試行するInbox。</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="34" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shopify接続</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">外部送信キュー</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">commerce_outbox</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">将来案</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">外部APIへ送る処理を永続化するOutbox。</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="8" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">別ドメイン</t>
         </is>
       </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">医院仕入注文</t>
         </is>
       </c>
-      <c r="C22" s="8" t="inlineStr">
+      <c r="C23" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">clinic_orders</t>
         </is>
       </c>
-      <c r="D22" s="8" t="inlineStr">
+      <c r="D23" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">実装済み</t>
         </is>
       </c>
-      <c r="E22" s="8" t="inlineStr">
+      <c r="E23" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">BGJから医院へのB2B仕入・売上履歴</t>
         </is>
       </c>
-      <c r="F22" s="8" t="inlineStr">
+      <c r="F23" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">患者注文系列へ統合しない</t>
         </is>
@@ -1114,7 +1146,7 @@
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
   </mergeCells>
-  <autoFilter ref="A4:F22"/>
+  <autoFilter ref="A4:F23"/>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0" paperSize="9"/>
 </worksheet>
@@ -1122,7 +1154,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K62"/>
+  <dimension ref="A1:K79"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -3554,22 +3586,22 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文配送先</t>
+          <t xml:space="preserve">送り先マスタ</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">order_shipping_addresses</t>
+          <t xml:space="preserve">delivery_destinations</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">内部注文ID</t>
+          <t xml:space="preserve">送り先ID</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">order_id</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
@@ -3579,7 +3611,7 @@
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">PK / FK</t>
+          <t xml:space="preserve">PK</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
@@ -3589,12 +3621,12 @@
       </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">gen_random_uuid()</t>
         </is>
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders.id ON DELETE CASCADE</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K46" s="4" t="inlineStr">
@@ -3611,22 +3643,22 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文配送先</t>
+          <t xml:space="preserve">送り先マスタ</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">order_shipping_addresses</t>
+          <t xml:space="preserve">delivery_destinations</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">郵便番号</t>
+          <t xml:space="preserve">医院得意先コード</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">postal_code</t>
+          <t xml:space="preserve">clinic_customer_code</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
@@ -3634,14 +3666,14 @@
           <t xml:space="preserve">text</t>
         </is>
       </c>
-      <c r="G47" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="G47" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO</t>
+          <t xml:space="preserve">YES</t>
         </is>
       </c>
       <c r="I47" s="4" t="inlineStr">
@@ -3651,7 +3683,7 @@
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">^[0-9]{3}-[0-9]{4}$</t>
+          <t xml:space="preserve">clinics.customer_code ON DELETE RESTRICT</t>
         </is>
       </c>
       <c r="K47" s="4" t="inlineStr">
@@ -3668,37 +3700,37 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文配送先</t>
+          <t xml:space="preserve">送り先マスタ</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">order_shipping_addresses</t>
+          <t xml:space="preserve">delivery_destinations</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">都道府県</t>
+          <t xml:space="preserve">患者ID</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">prefecture</t>
+          <t xml:space="preserve">patient_id</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="G48" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">uuid</t>
+        </is>
+      </c>
+      <c r="G48" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO</t>
+          <t xml:space="preserve">YES</t>
         </is>
       </c>
       <c r="I48" s="4" t="inlineStr">
@@ -3708,7 +3740,7 @@
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2〜4文字</t>
+          <t xml:space="preserve">patients.id ON DELETE RESTRICT</t>
         </is>
       </c>
       <c r="K48" s="4" t="inlineStr">
@@ -3725,22 +3757,22 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文配送先</t>
+          <t xml:space="preserve">送り先マスタ</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">order_shipping_addresses</t>
+          <t xml:space="preserve">delivery_destinations</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">市区町村</t>
+          <t xml:space="preserve">送り先名</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">city</t>
+          <t xml:space="preserve">label</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
@@ -3765,7 +3797,7 @@
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1〜100文字</t>
+          <t xml:space="preserve">1〜50文字</t>
         </is>
       </c>
       <c r="K49" s="4" t="inlineStr">
@@ -3782,22 +3814,22 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文配送先</t>
+          <t xml:space="preserve">送り先マスタ</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">order_shipping_addresses</t>
+          <t xml:space="preserve">delivery_destinations</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">住所1</t>
+          <t xml:space="preserve">郵便番号</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">address_line1</t>
+          <t xml:space="preserve">postal_code</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
@@ -3822,7 +3854,7 @@
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1〜200文字</t>
+          <t xml:space="preserve">^[0-9]{3}-[0-9]{4}$</t>
         </is>
       </c>
       <c r="K50" s="4" t="inlineStr">
@@ -3839,22 +3871,22 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文配送先</t>
+          <t xml:space="preserve">送り先マスタ</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">order_shipping_addresses</t>
+          <t xml:space="preserve">delivery_destinations</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">住所2</t>
+          <t xml:space="preserve">都道府県</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">address_line2</t>
+          <t xml:space="preserve">prefecture</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
@@ -3869,7 +3901,7 @@
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">YES</t>
+          <t xml:space="preserve">NO</t>
         </is>
       </c>
       <c r="I51" s="4" t="inlineStr">
@@ -3879,7 +3911,7 @@
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">200文字以内</t>
+          <t xml:space="preserve">2〜4文字</t>
         </is>
       </c>
       <c r="K51" s="4" t="inlineStr">
@@ -3896,22 +3928,22 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文配送先</t>
+          <t xml:space="preserve">送り先マスタ</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">order_shipping_addresses</t>
+          <t xml:space="preserve">delivery_destinations</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">受取人名</t>
+          <t xml:space="preserve">市区町村</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">recipient_name</t>
+          <t xml:space="preserve">city</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
@@ -3953,22 +3985,22 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文配送先</t>
+          <t xml:space="preserve">送り先マスタ</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">order_shipping_addresses</t>
+          <t xml:space="preserve">delivery_destinations</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">電話番号</t>
+          <t xml:space="preserve">住所1</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">phone</t>
+          <t xml:space="preserve">address_line1</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
@@ -3993,7 +4025,7 @@
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">数字10〜15桁</t>
+          <t xml:space="preserve">1〜200文字</t>
         </is>
       </c>
       <c r="K53" s="4" t="inlineStr">
@@ -4010,27 +4042,27 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文配送先</t>
+          <t xml:space="preserve">送り先マスタ</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">order_shipping_addresses</t>
+          <t xml:space="preserve">delivery_destinations</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">作成日時</t>
+          <t xml:space="preserve">住所2</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">created_at</t>
+          <t xml:space="preserve">address_line2</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">timestamptz</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
@@ -4040,17 +4072,17 @@
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO</t>
+          <t xml:space="preserve">YES</t>
         </is>
       </c>
       <c r="I54" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">now()</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200文字以内</t>
         </is>
       </c>
       <c r="K54" s="4" t="inlineStr">
@@ -4067,32 +4099,32 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文操作履歴</t>
+          <t xml:space="preserve">送り先マスタ</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_order_events</t>
+          <t xml:space="preserve">delivery_destinations</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">イベントID</t>
+          <t xml:space="preserve">受取人名</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">recipient_name</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">uuid</t>
-        </is>
-      </c>
-      <c r="G55" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PK</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
@@ -4102,12 +4134,12 @@
       </c>
       <c r="I55" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">gen_random_uuid()</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">1〜100文字</t>
         </is>
       </c>
       <c r="K55" s="4" t="inlineStr">
@@ -4124,32 +4156,32 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文操作履歴</t>
+          <t xml:space="preserve">送り先マスタ</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_order_events</t>
+          <t xml:space="preserve">delivery_destinations</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">内部注文ID</t>
+          <t xml:space="preserve">電話番号</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">order_id</t>
+          <t xml:space="preserve">phone</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">uuid</t>
-        </is>
-      </c>
-      <c r="G56" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FK</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G56" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
@@ -4164,7 +4196,7 @@
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders.id ON DELETE CASCADE</t>
+          <t xml:space="preserve">数字10〜15桁</t>
         </is>
       </c>
       <c r="K56" s="4" t="inlineStr">
@@ -4181,27 +4213,27 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文操作履歴</t>
+          <t xml:space="preserve">送り先マスタ</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_order_events</t>
+          <t xml:space="preserve">delivery_destinations</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">イベント種別</t>
+          <t xml:space="preserve">既定</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">event_type</t>
+          <t xml:space="preserve">is_default</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">boolean</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr">
@@ -4216,7 +4248,7 @@
       </c>
       <c r="I57" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="J57" s="4" t="inlineStr">
@@ -4238,27 +4270,27 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文操作履歴</t>
+          <t xml:space="preserve">送り先マスタ</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_order_events</t>
+          <t xml:space="preserve">delivery_destinations</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">操作者種別</t>
+          <t xml:space="preserve">削除日時</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">actor_type</t>
+          <t xml:space="preserve">deleted_at</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">timestamptz</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
@@ -4268,7 +4300,7 @@
       </c>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO</t>
+          <t xml:space="preserve">YES</t>
         </is>
       </c>
       <c r="I58" s="4" t="inlineStr">
@@ -4295,27 +4327,27 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文操作履歴</t>
+          <t xml:space="preserve">送り先マスタ</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_order_events</t>
+          <t xml:space="preserve">delivery_destinations</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">操作者識別子</t>
+          <t xml:space="preserve">作成日時</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">actor_identifier</t>
+          <t xml:space="preserve">created_at</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">timestamptz</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr">
@@ -4330,7 +4362,7 @@
       </c>
       <c r="I59" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">now()</t>
         </is>
       </c>
       <c r="J59" s="4" t="inlineStr">
@@ -4352,27 +4384,27 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文操作履歴</t>
+          <t xml:space="preserve">送り先マスタ</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_order_events</t>
+          <t xml:space="preserve">delivery_destinations</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">変更前状態</t>
+          <t xml:space="preserve">更新日時</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">from_status</t>
+          <t xml:space="preserve">updated_at</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">timestamptz</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr">
@@ -4382,12 +4414,12 @@
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">YES</t>
+          <t xml:space="preserve">NO</t>
         </is>
       </c>
       <c r="I60" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">now()</t>
         </is>
       </c>
       <c r="J60" s="4" t="inlineStr">
@@ -4409,37 +4441,37 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文操作履歴</t>
+          <t xml:space="preserve">注文配送先</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_order_events</t>
+          <t xml:space="preserve">order_delivery_destinations</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">変更後状態</t>
+          <t xml:space="preserve">内部注文ID</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">to_status</t>
+          <t xml:space="preserve">order_id</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="G61" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">uuid</t>
+        </is>
+      </c>
+      <c r="G61" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK / FK</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">YES</t>
+          <t xml:space="preserve">NO</t>
         </is>
       </c>
       <c r="I61" s="4" t="inlineStr">
@@ -4449,7 +4481,7 @@
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">patient_orders.id ON DELETE CASCADE</t>
         </is>
       </c>
       <c r="K61" s="4" t="inlineStr">
@@ -4466,50 +4498,1019 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">注文配送先</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">order_delivery_destinations</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">送り先ID</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">delivery_destination_id</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">uuid</t>
+        </is>
+      </c>
+      <c r="G62" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
+        </is>
+      </c>
+      <c r="H62" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I62" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">delivery_destinations.id ON DELETE RESTRICT</t>
+        </is>
+      </c>
+      <c r="K62" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="30" customHeight="1">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">注文配送先</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">order_delivery_destinations</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">送り先名</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">label</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G63" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H63" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I63" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J63" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K63" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="30" customHeight="1">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">注文配送先</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">order_delivery_destinations</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">郵便番号</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">postal_code</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G64" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I64" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K64" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="30" customHeight="1">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">注文配送先</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">order_delivery_destinations</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">都道府県</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prefecture</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G65" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H65" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I65" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K65" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="30" customHeight="1">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">注文配送先</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">order_delivery_destinations</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">市区町村</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">city</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G66" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I66" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K66" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="30" customHeight="1">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">注文配送先</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">order_delivery_destinations</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">住所1</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">address_line1</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G67" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H67" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I67" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J67" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K67" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="30" customHeight="1">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">注文配送先</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">order_delivery_destinations</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">住所2</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">address_line2</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G68" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YES</t>
+        </is>
+      </c>
+      <c r="I68" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K68" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="30" customHeight="1">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">注文配送先</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">order_delivery_destinations</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">受取人名</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">recipient_name</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G69" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H69" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I69" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J69" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K69" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="30" customHeight="1">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">注文配送先</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">order_delivery_destinations</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">電話番号</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">phone</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G70" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I70" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K70" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="30" customHeight="1">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">注文配送先</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">order_delivery_destinations</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">作成日時</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">created_at</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">timestamptz</t>
+        </is>
+      </c>
+      <c r="G71" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H71" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I71" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">now()</t>
+        </is>
+      </c>
+      <c r="J71" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K71" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="30" customHeight="1">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">注文操作履歴</t>
         </is>
       </c>
-      <c r="C62" s="4" t="inlineStr">
+      <c r="C72" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">patient_order_events</t>
         </is>
       </c>
-      <c r="D62" s="4" t="inlineStr">
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">イベントID</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">id</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">uuid</t>
+        </is>
+      </c>
+      <c r="G72" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK</t>
+        </is>
+      </c>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I72" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gen_random_uuid()</t>
+        </is>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K72" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="30" customHeight="1">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">注文操作履歴</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_order_events</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">内部注文ID</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">order_id</t>
+        </is>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">uuid</t>
+        </is>
+      </c>
+      <c r="G73" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
+        </is>
+      </c>
+      <c r="H73" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I73" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_orders.id ON DELETE CASCADE</t>
+        </is>
+      </c>
+      <c r="K73" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="30" customHeight="1">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">注文操作履歴</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_order_events</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">イベント種別</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">event_type</t>
+        </is>
+      </c>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G74" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H74" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I74" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K74" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="30" customHeight="1">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">注文操作履歴</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_order_events</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">操作者種別</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actor_type</t>
+        </is>
+      </c>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G75" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H75" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I75" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J75" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K75" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="30" customHeight="1">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">注文操作履歴</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_order_events</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">操作者識別子</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actor_identifier</t>
+        </is>
+      </c>
+      <c r="F76" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G76" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H76" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I76" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K76" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="30" customHeight="1">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">注文操作履歴</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_order_events</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">変更前状態</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">from_status</t>
+        </is>
+      </c>
+      <c r="F77" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G77" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H77" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YES</t>
+        </is>
+      </c>
+      <c r="I77" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J77" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K77" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="30" customHeight="1">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">注文操作履歴</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_order_events</t>
+        </is>
+      </c>
+      <c r="D78" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">変更後状態</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">to_status</t>
+        </is>
+      </c>
+      <c r="F78" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G78" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H78" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YES</t>
+        </is>
+      </c>
+      <c r="I78" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K78" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="30" customHeight="1">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">注文操作履歴</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_order_events</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">発生日時</t>
         </is>
       </c>
-      <c r="E62" s="4" t="inlineStr">
+      <c r="E79" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">created_at</t>
         </is>
       </c>
-      <c r="F62" s="4" t="inlineStr">
+      <c r="F79" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">timestamptz</t>
         </is>
       </c>
-      <c r="G62" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H62" s="4" t="inlineStr">
+      <c r="G79" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H79" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">NO</t>
         </is>
       </c>
-      <c r="I62" s="4" t="inlineStr">
+      <c r="I79" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">now()</t>
         </is>
       </c>
-      <c r="J62" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="K62" s="4" t="inlineStr">
+      <c r="J79" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K79" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -4520,7 +5521,7 @@
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A2:K2"/>
   </mergeCells>
-  <autoFilter ref="A4:K62"/>
+  <autoFilter ref="A4:K79"/>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0" paperSize="9"/>
 </worksheet>
@@ -9245,7 +10246,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -9467,96 +10468,96 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">将来案</t>
+          <t xml:space="preserve">現行</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">UK1</t>
+          <t xml:space="preserve">UK3</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_accounts</t>
+          <t xml:space="preserve">delivery_destinations</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">provider, external_account_id</t>
+          <t xml:space="preserve">clinic_customer_code WHERE is_default AND deleted_at IS NULL</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNIQUE</t>
+          <t xml:space="preserve">PARTIAL UNIQUE</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部接続先の重複防止。</t>
+          <t xml:space="preserve">医院ごとの有効な既定送り先を1件に限定。</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">将来案</t>
+          <t xml:space="preserve">現行</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">UK2</t>
+          <t xml:space="preserve">UK4</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_fulfillment_items</t>
+          <t xml:space="preserve">delivery_destinations</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">fulfillment_id, order_item_id</t>
+          <t xml:space="preserve">patient_id WHERE is_default AND deleted_at IS NULL</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNIQUE</t>
+          <t xml:space="preserve">PARTIAL UNIQUE</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">同一配送への明細重複防止。</t>
+          <t xml:space="preserve">患者ごとの有効な既定送り先を1件に限定。</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">将来案</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UK3</t>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IDX4</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_subscriptions</t>
+          <t xml:space="preserve">order_delivery_destinations</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_account_id, external_subscription_id</t>
+          <t xml:space="preserve">delivery_destination_id</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNIQUE</t>
+          <t xml:space="preserve">INDEX</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部契約の重複防止。</t>
+          <t xml:space="preserve">使用中送り先の削除可否判定。</t>
         </is>
       </c>
     </row>
@@ -9568,17 +10569,17 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">UK4</t>
+          <t xml:space="preserve">UK1</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_webhook_events</t>
+          <t xml:space="preserve">commerce_accounts</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_account_id, external_event_id</t>
+          <t xml:space="preserve">provider, external_account_id</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -9588,7 +10589,7 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Webhook重複配信の無害化。</t>
+          <t xml:space="preserve">外部接続先の重複防止。</t>
         </is>
       </c>
     </row>
@@ -9600,17 +10601,17 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">UK5</t>
+          <t xml:space="preserve">UK2</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders</t>
+          <t xml:space="preserve">patient_fulfillment_items</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_account_id, external_order_id</t>
+          <t xml:space="preserve">fulfillment_id, order_item_id</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -9620,7 +10621,7 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">複数ストアを考慮した外部注文の一意性。</t>
+          <t xml:space="preserve">同一配送への明細重複防止。</t>
         </is>
       </c>
     </row>
@@ -9632,273 +10633,258 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">UK3</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscriptions</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">commerce_account_id, external_subscription_id</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UNIQUE</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">外部契約の重複防止。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">将来案</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UK4</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">commerce_webhook_events</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">commerce_account_id, external_event_id</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UNIQUE</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Webhook重複配信の無害化。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">将来案</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UK5</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_orders</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">commerce_account_id, external_order_id</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UNIQUE</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">複数ストアを考慮した外部注文の一意性。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">将来案</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">UK6</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">commerce_outbox</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">idempotency_key</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">UNIQUE</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="F18" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">外部送信コマンドの二重実行防止。</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">現行リレーション</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">親DB日本語名</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">親KEY</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">親多重度</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">子多重度</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">子FK</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="F21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">子DB日本語名</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="G21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">削除・備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">医院</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">clinics.customer_code</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">patient_orders.customer_code</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">患者注文</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FK</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">患者</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">patients.id</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">patient_orders.patient_id</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">患者注文</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FK・現状CASCADE</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">患者注文</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">patient_orders.id</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">patient_order_items.order_id</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">患者注文明細</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FK・CASCADE</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">医院</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinics.customer_code</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_orders.customer_code</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">患者注文</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">patient_orders.id</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0..1</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">order_shipping_addresses.order_id</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">注文配送先</t>
-        </is>
-      </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">PK・FK・CASCADE</t>
+          <t xml:space="preserve">FK</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">患者</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patients.id</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_orders.patient_id</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">患者注文</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">patient_orders.id</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">patient_order_events.order_id</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">注文操作履歴</t>
-        </is>
-      </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK・CASCADE</t>
+          <t xml:space="preserve">FK・現状CASCADE</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">商品</t>
+          <t xml:space="preserve">患者注文</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">products.id</t>
+          <t xml:space="preserve">patient_orders.id</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">0..1</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -9908,7 +10894,7 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_order_items.product_id</t>
+          <t xml:space="preserve">patient_order_items.order_id</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
@@ -9918,51 +10904,118 @@
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK・SET NULL</t>
+          <t xml:space="preserve">FK・CASCADE</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">医院</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinics.customer_code</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">delivery_destinations.clinic_customer_code</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">送り先マスタ</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK・RESTRICT</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">将来リレーション案</t>
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">患者</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patients.id</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">delivery_destinations.patient_id</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">送り先マスタ</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK・RESTRICT</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">親DB日本語名</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">親KEY</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">親多重度</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">子多重度</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">子FK</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">子DB日本語名</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">削除・備考</t>
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">送り先マスタ</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">delivery_destinations.id</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">order_delivery_destinations.delivery_destination_id</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">注文配送先</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK・RESTRICT</t>
         </is>
       </c>
     </row>
@@ -9984,22 +11037,22 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">N</t>
+          <t xml:space="preserve">0..1</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">order_transaction_projections.order_id</t>
+          <t xml:space="preserve">order_delivery_destinations.order_id</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">決済返金投影</t>
+          <t xml:space="preserve">注文配送先</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK</t>
+          <t xml:space="preserve">PK・FK・CASCADE</t>
         </is>
       </c>
     </row>
@@ -10026,34 +11079,34 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_fulfillments.order_id</t>
+          <t xml:space="preserve">patient_order_events.order_id</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">受取配送</t>
+          <t xml:space="preserve">注文操作履歴</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK</t>
+          <t xml:space="preserve">FK・CASCADE</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">受取配送</t>
+          <t xml:space="preserve">商品</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_fulfillments.id</t>
+          <t xml:space="preserve">products.id</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">0..1</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -10063,140 +11116,73 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_fulfillment_items.fulfillment_id</t>
+          <t xml:space="preserve">patient_order_items.product_id</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">受取配送明細</t>
+          <t xml:space="preserve">患者注文明細</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">注文明細</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">patient_order_items.id</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">patient_fulfillment_items.order_item_id</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">受取配送明細</t>
-        </is>
-      </c>
-      <c r="G31" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FK</t>
+          <t xml:space="preserve">FK・SET NULL</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">外部コマース接続</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">commerce_accounts.id</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">patient_orders.commerce_account_id</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">患者注文</t>
-        </is>
-      </c>
-      <c r="G32" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FK</t>
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">将来リレーション案</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">外部コマース接続</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">commerce_accounts.id</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">commerce_webhook_events.commerce_account_id</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">外部受信イベント</t>
-        </is>
-      </c>
-      <c r="G33" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FK</t>
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">親DB日本語名</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">親KEY</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">親多重度</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">子多重度</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">子FK</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">子DB日本語名</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">削除・備考</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部コマース接続</t>
+          <t xml:space="preserve">患者注文</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_accounts.id</t>
+          <t xml:space="preserve">patient_orders.id</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -10211,12 +11197,12 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_outbox.commerce_account_id</t>
+          <t xml:space="preserve">order_transaction_projections.order_id</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部送信キュー</t>
+          <t xml:space="preserve">決済返金投影</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
@@ -10228,12 +11214,12 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者</t>
+          <t xml:space="preserve">患者注文</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patients.id</t>
+          <t xml:space="preserve">patient_orders.id</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -10248,12 +11234,12 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_subscriptions.patient_id</t>
+          <t xml:space="preserve">patient_fulfillments.order_id</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者定期購入</t>
+          <t xml:space="preserve">受取配送</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr">
@@ -10265,12 +11251,12 @@
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者定期購入</t>
+          <t xml:space="preserve">受取配送</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_subscriptions.id</t>
+          <t xml:space="preserve">patient_fulfillments.id</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -10285,12 +11271,12 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_subscription_items.subscription_id</t>
+          <t xml:space="preserve">patient_fulfillment_items.fulfillment_id</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">定期購入明細</t>
+          <t xml:space="preserve">受取配送明細</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
@@ -10302,35 +11288,257 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">注文明細</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_order_items.id</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_fulfillment_items.order_item_id</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">受取配送明細</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">外部コマース接続</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">commerce_accounts.id</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_orders.commerce_account_id</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">患者注文</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">外部コマース接続</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">commerce_accounts.id</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">commerce_webhook_events.commerce_account_id</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">外部受信イベント</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">外部コマース接続</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">commerce_accounts.id</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">commerce_outbox.commerce_account_id</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">外部送信キュー</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">患者</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patients.id</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscriptions.patient_id</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">患者定期購入</t>
         </is>
       </c>
-      <c r="B37" s="4" t="inlineStr">
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">患者定期購入</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">patient_subscriptions.id</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscription_items.subscription_id</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">定期購入明細</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">患者定期購入</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscriptions.id</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">0..1</t>
         </is>
       </c>
-      <c r="D37" s="4" t="inlineStr">
+      <c r="D43" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr">
+      <c r="E43" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">patient_orders.subscription_id</t>
         </is>
       </c>
-      <c r="F37" s="4" t="inlineStr">
+      <c r="F43" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">患者注文</t>
         </is>
       </c>
-      <c r="G37" s="4" t="inlineStr">
+      <c r="G43" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">FK</t>
         </is>
@@ -10340,8 +11548,8 @@
   <mergeCells count="4">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A17:H17"/>
-    <mergeCell ref="A26:H26"/>
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A32:H32"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0" paperSize="9"/>
@@ -10350,7 +11558,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Q53"/>
+  <dimension ref="A1:Q68"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -10878,528 +12086,749 @@
       </c>
     </row>
     <row r="29" ht="23" customHeight="1">
-      <c r="B29" s="9" t="inlineStr">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">送り先マスタ
+delivery_destinations</t>
+        </is>
+      </c>
+      <c r="J29" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">注文配送先
-order_shipping_addresses</t>
-        </is>
-      </c>
-      <c r="K29" s="9" t="inlineStr">
+order_delivery_destinations</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">日本語項目</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">物理カラム</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KEY</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">日本語項目</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">物理カラム</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">送り先ID</t>
+        </is>
+      </c>
+      <c r="C32" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">id</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK</t>
+        </is>
+      </c>
+      <c r="J32" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">内部注文ID</t>
+        </is>
+      </c>
+      <c r="L32" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">order_id</t>
+        </is>
+      </c>
+      <c r="N32" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK/FK</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">医院得意先コード</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_customer_code</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
+        </is>
+      </c>
+      <c r="J33" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">送り先ID</t>
+        </is>
+      </c>
+      <c r="L33" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">delivery_destination_id</t>
+        </is>
+      </c>
+      <c r="N33" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">患者ID</t>
+        </is>
+      </c>
+      <c r="C34" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_id</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
+        </is>
+      </c>
+      <c r="J34" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">送り先名</t>
+        </is>
+      </c>
+      <c r="L34" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">label</t>
+        </is>
+      </c>
+      <c r="N34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">送り先名</t>
+        </is>
+      </c>
+      <c r="C35" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">label</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J35" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">郵便番号</t>
+        </is>
+      </c>
+      <c r="L35" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">postal_code</t>
+        </is>
+      </c>
+      <c r="N35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">既定</t>
+        </is>
+      </c>
+      <c r="C36" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">is_default</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J36" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">住所1</t>
+        </is>
+      </c>
+      <c r="L36" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">address_line1</t>
+        </is>
+      </c>
+      <c r="N36" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">削除日時</t>
+        </is>
+      </c>
+      <c r="C37" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">deleted_at</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J37" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">受取人名</t>
+        </is>
+      </c>
+      <c r="L37" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">recipient_name</t>
+        </is>
+      </c>
+      <c r="N37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="23" customHeight="1">
+      <c r="F44" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">注文操作履歴
 patient_order_events</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="B31" s="3" t="inlineStr">
+    <row r="46">
+      <c r="F46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">日本語項目</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
+      <c r="H46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">物理カラム</t>
         </is>
       </c>
-      <c r="F31" s="3" t="inlineStr">
+      <c r="J46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">KEY</t>
         </is>
       </c>
-      <c r="K31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">日本語項目</t>
-        </is>
-      </c>
-      <c r="M31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">物理カラム</t>
-        </is>
-      </c>
-      <c r="O31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">KEY</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="11" t="inlineStr">
+    </row>
+    <row r="47">
+      <c r="F47" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">イベントID</t>
+        </is>
+      </c>
+      <c r="H47" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">id</t>
+        </is>
+      </c>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="F48" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">内部注文ID</t>
         </is>
       </c>
-      <c r="D32" s="11" t="inlineStr">
+      <c r="H48" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">order_id</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PK/FK</t>
-        </is>
-      </c>
-      <c r="K32" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">イベントID</t>
-        </is>
-      </c>
-      <c r="M32" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">id</t>
-        </is>
-      </c>
-      <c r="O32" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PK</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">郵便番号</t>
-        </is>
-      </c>
-      <c r="D33" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">postal_code</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="K33" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">内部注文ID</t>
-        </is>
-      </c>
-      <c r="M33" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">order_id</t>
-        </is>
-      </c>
-      <c r="O33" s="6" t="inlineStr">
+      <c r="J48" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">FK</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="B34" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">都道府県</t>
-        </is>
-      </c>
-      <c r="D34" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">prefecture</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="K34" s="11" t="inlineStr">
+    <row r="49">
+      <c r="F49" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">イベント種別</t>
         </is>
       </c>
-      <c r="M34" s="11" t="inlineStr">
+      <c r="H49" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">event_type</t>
         </is>
       </c>
-      <c r="O34" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">市区町村</t>
-        </is>
-      </c>
-      <c r="D35" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">city</t>
-        </is>
-      </c>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="K35" s="11" t="inlineStr">
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="F50" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">操作者種別</t>
         </is>
       </c>
-      <c r="M35" s="11" t="inlineStr">
+      <c r="H50" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">actor_type</t>
         </is>
       </c>
-      <c r="O35" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">住所1</t>
-        </is>
-      </c>
-      <c r="D36" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">address_line1</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="K36" s="11" t="inlineStr">
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="F51" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">変更前状態</t>
         </is>
       </c>
-      <c r="M36" s="11" t="inlineStr">
+      <c r="H51" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">from_status</t>
         </is>
       </c>
-      <c r="O36" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">受取人名</t>
-        </is>
-      </c>
-      <c r="D37" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">recipient_name</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="K37" s="11" t="inlineStr">
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="F52" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">変更後状態</t>
         </is>
       </c>
-      <c r="M37" s="11" t="inlineStr">
+      <c r="H52" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">to_status</t>
         </is>
       </c>
-      <c r="O37" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">電話番号</t>
-        </is>
-      </c>
-      <c r="D38" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">phone</t>
-        </is>
-      </c>
-      <c r="F38" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">リレーション一覧</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="3" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">親DB</t>
         </is>
       </c>
-      <c r="B47" s="3" t="inlineStr">
+      <c r="B59" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">親KEY</t>
         </is>
       </c>
-      <c r="C47" s="3" t="inlineStr">
+      <c r="C59" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">親</t>
         </is>
       </c>
-      <c r="D47" s="3" t="inlineStr">
+      <c r="D59" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">子</t>
         </is>
       </c>
-      <c r="E47" s="3" t="inlineStr">
+      <c r="E59" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">子FK</t>
         </is>
       </c>
-      <c r="F47" s="3" t="inlineStr">
+      <c r="F59" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">子DB</t>
         </is>
       </c>
-      <c r="G47" s="3" t="inlineStr">
+      <c r="G59" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">備考</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="4" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">医院</t>
         </is>
       </c>
-      <c r="B48" s="4" t="inlineStr">
+      <c r="B60" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">clinics.customer_code</t>
         </is>
       </c>
-      <c r="C48" s="4" t="inlineStr">
+      <c r="C60" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="D48" s="4" t="inlineStr">
+      <c r="D60" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="E48" s="4" t="inlineStr">
+      <c r="E60" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">patient_orders.customer_code</t>
         </is>
       </c>
-      <c r="F48" s="4" t="inlineStr">
+      <c r="F60" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">患者注文</t>
         </is>
       </c>
-      <c r="G48" s="4" t="inlineStr">
+      <c r="G60" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">FK</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="4" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">患者</t>
         </is>
       </c>
-      <c r="B49" s="4" t="inlineStr">
+      <c r="B61" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">patients.id</t>
         </is>
       </c>
-      <c r="C49" s="4" t="inlineStr">
+      <c r="C61" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="D49" s="4" t="inlineStr">
+      <c r="D61" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="E49" s="4" t="inlineStr">
+      <c r="E61" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">patient_orders.patient_id</t>
         </is>
       </c>
-      <c r="F49" s="4" t="inlineStr">
+      <c r="F61" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">患者注文</t>
         </is>
       </c>
-      <c r="G49" s="4" t="inlineStr">
+      <c r="G61" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">FK・現状CASCADE</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="4" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">患者注文</t>
         </is>
       </c>
-      <c r="B50" s="4" t="inlineStr">
+      <c r="B62" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">patient_orders.id</t>
         </is>
       </c>
-      <c r="C50" s="4" t="inlineStr">
+      <c r="C62" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="D50" s="4" t="inlineStr">
+      <c r="D62" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="E50" s="4" t="inlineStr">
+      <c r="E62" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">patient_order_items.order_id</t>
         </is>
       </c>
-      <c r="F50" s="4" t="inlineStr">
+      <c r="F62" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">患者注文明細</t>
         </is>
       </c>
-      <c r="G50" s="4" t="inlineStr">
+      <c r="G62" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">FK・CASCADE</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="4" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">医院</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinics.customer_code</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">delivery_destinations.clinic_customer_code</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">送り先マスタ</t>
+        </is>
+      </c>
+      <c r="G63" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK・RESTRICT</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">患者</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patients.id</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">delivery_destinations.patient_id</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">送り先マスタ</t>
+        </is>
+      </c>
+      <c r="G64" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK・RESTRICT</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">送り先マスタ</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">delivery_destinations.id</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">order_delivery_destinations.delivery_destination_id</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">注文配送先</t>
+        </is>
+      </c>
+      <c r="G65" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK・RESTRICT</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">患者注文</t>
         </is>
       </c>
-      <c r="B51" s="4" t="inlineStr">
+      <c r="B66" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">patient_orders.id</t>
         </is>
       </c>
-      <c r="C51" s="4" t="inlineStr">
+      <c r="C66" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="D51" s="4" t="inlineStr">
+      <c r="D66" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">0..1</t>
         </is>
       </c>
-      <c r="E51" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">order_shipping_addresses.order_id</t>
-        </is>
-      </c>
-      <c r="F51" s="4" t="inlineStr">
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">order_delivery_destinations.order_id</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">注文配送先</t>
         </is>
       </c>
-      <c r="G51" s="4" t="inlineStr">
+      <c r="G66" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">PK・FK・CASCADE</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="4" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">患者注文</t>
         </is>
       </c>
-      <c r="B52" s="4" t="inlineStr">
+      <c r="B67" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">patient_orders.id</t>
         </is>
       </c>
-      <c r="C52" s="4" t="inlineStr">
+      <c r="C67" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="D52" s="4" t="inlineStr">
+      <c r="D67" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="E52" s="4" t="inlineStr">
+      <c r="E67" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">patient_order_events.order_id</t>
         </is>
       </c>
-      <c r="F52" s="4" t="inlineStr">
+      <c r="F67" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">注文操作履歴</t>
         </is>
       </c>
-      <c r="G52" s="4" t="inlineStr">
+      <c r="G67" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">FK・CASCADE</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="4" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">商品</t>
         </is>
       </c>
-      <c r="B53" s="4" t="inlineStr">
+      <c r="B68" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">products.id</t>
         </is>
       </c>
-      <c r="C53" s="4" t="inlineStr">
+      <c r="C68" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">0..1</t>
         </is>
       </c>
-      <c r="D53" s="4" t="inlineStr">
+      <c r="D68" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="E53" s="4" t="inlineStr">
+      <c r="E68" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">patient_order_items.product_id</t>
         </is>
       </c>
-      <c r="F53" s="4" t="inlineStr">
+      <c r="F68" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">患者注文明細</t>
         </is>
       </c>
-      <c r="G53" s="4" t="inlineStr">
+      <c r="G68" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">FK・SET NULL</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="98">
+  <mergeCells count="111">
     <mergeCell ref="A1:Q1"/>
     <mergeCell ref="A2:Q2"/>
     <mergeCell ref="A4:E5"/>
@@ -11464,40 +12893,53 @@
     <mergeCell ref="L23:M23"/>
     <mergeCell ref="N23:O23"/>
     <mergeCell ref="L25:Q26"/>
-    <mergeCell ref="B29:F30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="D37:E37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="D38:E38"/>
-    <mergeCell ref="K29:O30"/>
-    <mergeCell ref="K31:L31"/>
-    <mergeCell ref="M31:N31"/>
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="M32:N32"/>
-    <mergeCell ref="K33:L33"/>
-    <mergeCell ref="M33:N33"/>
-    <mergeCell ref="K34:L34"/>
-    <mergeCell ref="M34:N34"/>
-    <mergeCell ref="K35:L35"/>
-    <mergeCell ref="M35:N35"/>
-    <mergeCell ref="K36:L36"/>
-    <mergeCell ref="M36:N36"/>
-    <mergeCell ref="K37:L37"/>
-    <mergeCell ref="M37:N37"/>
+    <mergeCell ref="A29:E30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="J29:N30"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="L31:M31"/>
+    <mergeCell ref="J32:K32"/>
+    <mergeCell ref="L32:M32"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="L33:M33"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="L34:M34"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="L35:M35"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="L36:M36"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="L37:M37"/>
+    <mergeCell ref="F44:J45"/>
+    <mergeCell ref="F46:G46"/>
+    <mergeCell ref="H46:I46"/>
+    <mergeCell ref="F47:G47"/>
+    <mergeCell ref="H47:I47"/>
+    <mergeCell ref="F48:G48"/>
+    <mergeCell ref="H48:I48"/>
+    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="H49:I49"/>
+    <mergeCell ref="F50:G50"/>
+    <mergeCell ref="H50:I50"/>
+    <mergeCell ref="F51:G51"/>
+    <mergeCell ref="H51:I51"/>
+    <mergeCell ref="F52:G52"/>
+    <mergeCell ref="H52:I52"/>
     <mergeCell ref="B26:J27"/>
-    <mergeCell ref="A46:Q46"/>
+    <mergeCell ref="A58:Q58"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0" paperSize="9"/>
@@ -12407,7 +13849,7 @@
       <c r="A46" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">注文配送先
-order_shipping_addresses</t>
+order_delivery_destinations</t>
         </is>
       </c>
       <c r="G46" s="10" t="inlineStr">
@@ -12520,17 +13962,17 @@
     <row r="50">
       <c r="A50" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">郵便番号</t>
+          <t xml:space="preserve">送り先ID</t>
         </is>
       </c>
       <c r="C50" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">postal_code</t>
-        </is>
-      </c>
-      <c r="E50" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">delivery_destination_id</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
         </is>
       </c>
       <c r="G50" s="11" t="inlineStr">
@@ -12567,12 +14009,12 @@
     <row r="51">
       <c r="A51" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">住所1</t>
+          <t xml:space="preserve">郵便番号</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">address_line1</t>
+          <t xml:space="preserve">postal_code</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
@@ -12614,12 +14056,12 @@
     <row r="52">
       <c r="A52" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">受取人名</t>
+          <t xml:space="preserve">住所1</t>
         </is>
       </c>
       <c r="C52" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">recipient_name</t>
+          <t xml:space="preserve">address_line1</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
@@ -13410,17 +14852,17 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">order_shipping_addresses</t>
+          <t xml:space="preserve">delivery_destinations / order_delivery_destinations</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">自宅配送を有効化し、注文時点の配送先を保存する。</t>
+          <t xml:space="preserve">医院・患者の複数送り先と注文時スナップショットを運用する。</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">住所なし配送を許可しない。</t>
+          <t xml:space="preserve">進行中注文の送り先は論理削除不可。</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">

--- a/project_clinic_order_management_db_definition.xlsx
+++ b/project_clinic_order_management_db_definition.xlsx
@@ -476,7 +476,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -637,22 +637,22 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文</t>
+          <t xml:space="preserve">医院契約情報</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders</t>
+          <t xml:space="preserve">clinic_terms</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">実装済み</t>
+          <t xml:space="preserve">実装済み・価格計算元</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院が管理する患者注文ヘッダー。内部注文IDは将来も維持する。</t>
+          <t xml:space="preserve">医院ごとの契約仕切値率。仕切値は基準価格×仕切値率を1円単位で四捨五入し、保存しない。</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -669,22 +669,22 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文明細</t>
+          <t xml:space="preserve">医院商品設定</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_order_items</t>
+          <t xml:space="preserve">clinic_product_settings</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">実装済み</t>
+          <t xml:space="preserve">実装済み・患者表示価格</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">商品変更後も過去注文を保持するため、注文時点の値を保存する。</t>
+          <t xml:space="preserve">医院×商品の表示設定と医院価格。clinic_priceがNULLならproducts.priceを患者表示価格にする。</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -701,12 +701,12 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">送り先マスタ</t>
+          <t xml:space="preserve">患者注文</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery_destinations</t>
+          <t xml:space="preserve">patient_orders</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院または患者が複数所有できる送り先。論理削除と既定送り先を管理する。</t>
+          <t xml:space="preserve">医院が管理する患者注文ヘッダー。内部注文IDは将来も維持する。</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -733,12 +733,12 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文配送先</t>
+          <t xml:space="preserve">患者注文明細</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">order_delivery_destinations</t>
+          <t xml:space="preserve">patient_order_items</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">選択した送り先を注文時点の不変スナップショットとして1対1で保存する。</t>
+          <t xml:space="preserve">商品変更後も過去注文を保持するため、注文時点の値を保存する。</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文操作履歴</t>
+          <t xml:space="preserve">送り先マスタ</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_order_events</t>
+          <t xml:space="preserve">delivery_destinations</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文登録と状態変更について、操作者と変更前後の状態を保存する監査イベント。</t>
+          <t xml:space="preserve">医院または患者が複数所有できる送り先。論理削除と既定送り先を管理する。</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -792,27 +792,27 @@
     <row r="13" ht="34" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shopify接続</t>
+          <t xml:space="preserve">現行</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部コマース接続</t>
+          <t xml:space="preserve">注文配送先</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_accounts</t>
+          <t xml:space="preserve">order_delivery_destinations</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">将来案</t>
+          <t xml:space="preserve">実装済み</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shopifyストア等の外部接続先。医院との対応方式は接続構成確定後に決定する。</t>
+          <t xml:space="preserve">選択した送り先を注文時点の不変スナップショットとして1対1で保存する。</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -824,27 +824,27 @@
     <row r="14" ht="34" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shopify接続</t>
+          <t xml:space="preserve">現行</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文拡張</t>
+          <t xml:space="preserve">注文操作履歴</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders</t>
+          <t xml:space="preserve">patient_order_events</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">既存テーブル拡張案</t>
+          <t xml:space="preserve">実装済み</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">既存IDを維持し、外部・金額・排他制御の列を追加する。</t>
+          <t xml:space="preserve">注文登録と状態変更について、操作者と変更前後の状態を保存する監査イベント。</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -861,22 +861,22 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文明細拡張</t>
+          <t xml:space="preserve">外部コマース接続</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_order_items</t>
+          <t xml:space="preserve">commerce_accounts</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">既存テーブル拡張案</t>
+          <t xml:space="preserve">将来案</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部明細と通貨を明確化し、既存スナップショットを維持する。</t>
+          <t xml:space="preserve">Shopifyストア等の外部接続先。医院との対応方式は接続構成確定後に決定する。</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -888,27 +888,27 @@
     <row r="16" ht="34" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">決済接続</t>
+          <t xml:space="preserve">Shopify接続</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">決済返金投影</t>
+          <t xml:space="preserve">患者注文拡張</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">order_transaction_projections</t>
+          <t xml:space="preserve">patient_orders</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">将来案</t>
+          <t xml:space="preserve">既存テーブル拡張案</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shopify上の決済・返金を表示する投影。会計台帳ではない。</t>
+          <t xml:space="preserve">既存IDを維持し、外部・金額・排他制御の列を追加する。</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -920,27 +920,27 @@
     <row r="17" ht="34" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">配送開始</t>
+          <t xml:space="preserve">Shopify接続</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">受取配送</t>
+          <t xml:space="preserve">患者注文明細拡張</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_fulfillments</t>
+          <t xml:space="preserve">patient_order_items</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">将来案</t>
+          <t xml:space="preserve">既存テーブル拡張案</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院受け取り・配送・部分引き渡しの単位。</t>
+          <t xml:space="preserve">外部明細と通貨を明確化し、既存スナップショットを維持する。</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -952,17 +952,17 @@
     <row r="18" ht="34" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">配送開始</t>
+          <t xml:space="preserve">決済接続</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">受取配送明細</t>
+          <t xml:space="preserve">決済返金投影</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_fulfillment_items</t>
+          <t xml:space="preserve">order_transaction_projections</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">部分受け取り・部分配送時の対象明細と数量。</t>
+          <t xml:space="preserve">Shopify上の決済・返金を表示する投影。会計台帳ではない。</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -984,17 +984,17 @@
     <row r="19" ht="34" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">定期購入接続</t>
+          <t xml:space="preserve">配送開始</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者定期購入</t>
+          <t xml:space="preserve">受取配送</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_subscriptions</t>
+          <t xml:space="preserve">patient_fulfillments</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shopify上の定期購入契約を患者ポータルへ表示する投影。</t>
+          <t xml:space="preserve">医院受け取り・配送・部分引き渡しの単位。</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
@@ -1016,17 +1016,17 @@
     <row r="20" ht="34" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">定期購入接続</t>
+          <t xml:space="preserve">配送開始</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">定期購入明細</t>
+          <t xml:space="preserve">受取配送明細</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_subscription_items</t>
+          <t xml:space="preserve">patient_fulfillment_items</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">契約時点の商品・数量・単価の投影。</t>
+          <t xml:space="preserve">部分受け取り・部分配送時の対象明細と数量。</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -1048,17 +1048,17 @@
     <row r="21" ht="34" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shopify接続</t>
+          <t xml:space="preserve">定期購入接続</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部受信イベント</t>
+          <t xml:space="preserve">患者定期購入</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_webhook_events</t>
+          <t xml:space="preserve">patient_subscriptions</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Webhookを先に永続化し、重複排除・再試行するInbox。</t>
+          <t xml:space="preserve">Shopify上の定期購入契約を患者ポータルへ表示する投影。</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
@@ -1080,62 +1080,126 @@
     <row r="22" ht="34" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">定期購入接続</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">定期購入明細</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscription_items</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">将来案</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">契約時点の商品・数量・単価の投影。</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="34" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">Shopify接続</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">外部受信イベント</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">commerce_webhook_events</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">将来案</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Webhookを先に永続化し、重複排除・再試行するInbox。</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="34" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shopify接続</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">外部送信キュー</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">commerce_outbox</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">将来案</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="E24" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">外部APIへ送る処理を永続化するOutbox。</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="8" t="inlineStr">
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">別ドメイン</t>
         </is>
       </c>
-      <c r="B23" s="8" t="inlineStr">
+      <c r="B25" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">医院仕入注文</t>
         </is>
       </c>
-      <c r="C23" s="8" t="inlineStr">
+      <c r="C25" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">clinic_orders</t>
         </is>
       </c>
-      <c r="D23" s="8" t="inlineStr">
+      <c r="D25" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">実装済み</t>
         </is>
       </c>
-      <c r="E23" s="8" t="inlineStr">
+      <c r="E25" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">BGJから医院へのB2B仕入・売上履歴</t>
         </is>
       </c>
-      <c r="F23" s="8" t="inlineStr">
+      <c r="F25" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">患者注文系列へ統合しない</t>
         </is>
@@ -1146,7 +1210,7 @@
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
   </mergeCells>
-  <autoFilter ref="A4:F23"/>
+  <autoFilter ref="A4:F25"/>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0" paperSize="9"/>
 </worksheet>
@@ -1154,7 +1218,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K79"/>
+  <dimension ref="A1:K95"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1772,7 +1836,7 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">参考価格</t>
+          <t xml:space="preserve">基準価格</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -1829,12 +1893,12 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">公開状態</t>
+          <t xml:space="preserve">商品画像URL</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">status</t>
+          <t xml:space="preserve">image_url</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -1849,22 +1913,22 @@
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO</t>
+          <t xml:space="preserve">YES</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">下書き</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">公開 / 下書き</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Supabase Storage公開URL</t>
         </is>
       </c>
     </row>
@@ -1876,32 +1940,32 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文</t>
+          <t xml:space="preserve">商品</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders</t>
+          <t xml:space="preserve">products</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">内部注文ID</t>
+          <t xml:space="preserve">公開状態</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">status</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">uuid</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PK</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
@@ -1911,12 +1975,12 @@
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">gen_random_uuid()</t>
+          <t xml:space="preserve">下書き</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">公開 / 下書き</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
@@ -1933,12 +1997,12 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文</t>
+          <t xml:space="preserve">医院契約情報</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders</t>
+          <t xml:space="preserve">clinic_terms</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -1956,9 +2020,9 @@
           <t xml:space="preserve">text</t>
         </is>
       </c>
-      <c r="G17" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FK / UK2構成</t>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK / FK</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
@@ -1973,7 +2037,7 @@
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinics.customer_code</t>
+          <t xml:space="preserve">clinics.customer_code ON DELETE CASCADE</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
@@ -1990,32 +2054,32 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文</t>
+          <t xml:space="preserve">医院契約情報</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders</t>
+          <t xml:space="preserve">clinic_terms</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者ID</t>
+          <t xml:space="preserve">コミッション率</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_id</t>
+          <t xml:space="preserve">commission_rate</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">uuid</t>
-        </is>
-      </c>
-      <c r="G18" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FK</t>
+          <t xml:space="preserve">numeric(5,2)</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
@@ -2025,17 +2089,17 @@
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patients.id ON DELETE CASCADE</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">本番前にRESTRICT等へ変更予定</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
@@ -2047,27 +2111,27 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文</t>
+          <t xml:space="preserve">医院契約情報</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders</t>
+          <t xml:space="preserve">clinic_terms</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文区分</t>
+          <t xml:space="preserve">仕切値率</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">order_type</t>
+          <t xml:space="preserve">wholesale_rate</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">numeric(5,2)</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
@@ -2082,12 +2146,12 @@
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">one_time</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">one_time / subscription</t>
+          <t xml:space="preserve">0〜100</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
@@ -2104,22 +2168,22 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文</t>
+          <t xml:space="preserve">医院契約情報</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders</t>
+          <t xml:space="preserve">clinic_terms</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">受取方法</t>
+          <t xml:space="preserve">支払条件</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">fulfillment_method</t>
+          <t xml:space="preserve">payment_terms_site</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -2134,17 +2198,17 @@
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO</t>
+          <t xml:space="preserve">YES</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">pickup</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">pickup / delivery</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
@@ -2161,22 +2225,22 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文</t>
+          <t xml:space="preserve">医院契約情報</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders</t>
+          <t xml:space="preserve">clinic_terms</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院業務状態</t>
+          <t xml:space="preserve">支払方法</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">status</t>
+          <t xml:space="preserve">payment_method</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
@@ -2191,17 +2255,17 @@
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO</t>
+          <t xml:space="preserve">YES</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">received</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">received / preparing / ready / shipped / completed / canceled</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr">
@@ -2218,27 +2282,27 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文</t>
+          <t xml:space="preserve">医院契約情報</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders</t>
+          <t xml:space="preserve">clinic_terms</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文日時</t>
+          <t xml:space="preserve">契約開始日</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ordered_at</t>
+          <t xml:space="preserve">contract_started_at</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">timestamptz</t>
+          <t xml:space="preserve">date</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
@@ -2248,12 +2312,12 @@
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO</t>
+          <t xml:space="preserve">YES</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">now()</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -2275,22 +2339,22 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文</t>
+          <t xml:space="preserve">医院契約情報</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders</t>
+          <t xml:space="preserve">clinic_terms</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">次回提供予定日</t>
+          <t xml:space="preserve">契約更新日</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">next_fulfillment_date</t>
+          <t xml:space="preserve">contract_renewal_at</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -2332,32 +2396,32 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文</t>
+          <t xml:space="preserve">医院契約情報</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders</t>
+          <t xml:space="preserve">clinic_terms</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">作成元</t>
+          <t xml:space="preserve">更新日時</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">source</t>
+          <t xml:space="preserve">updated_at</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="G24" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UK1構成</t>
+          <t xml:space="preserve">timestamptz</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
@@ -2367,12 +2431,12 @@
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">internal</t>
+          <t xml:space="preserve">now()</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">internal / shopify</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
@@ -2389,22 +2453,22 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文</t>
+          <t xml:space="preserve">医院契約情報</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders</t>
+          <t xml:space="preserve">clinic_terms</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">登録経路</t>
+          <t xml:space="preserve">更新者</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">created_via</t>
+          <t xml:space="preserve">updated_by</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
@@ -2419,17 +2483,17 @@
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO</t>
+          <t xml:space="preserve">YES</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_portal</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_portal / bgj_portal / shopify</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr">
@@ -2446,22 +2510,22 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文</t>
+          <t xml:space="preserve">医院商品設定</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders</t>
+          <t xml:space="preserve">clinic_product_settings</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部注文ID</t>
+          <t xml:space="preserve">得意先コード</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">external_order_id</t>
+          <t xml:space="preserve">customer_code</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -2469,14 +2533,14 @@
           <t xml:space="preserve">text</t>
         </is>
       </c>
-      <c r="G26" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UK1構成</t>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK / FK</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">YES</t>
+          <t xml:space="preserve">NO</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
@@ -2486,7 +2550,7 @@
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">clinics.customer_code ON DELETE CASCADE</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr">
@@ -2503,32 +2567,32 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文</t>
+          <t xml:space="preserve">医院商品設定</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders</t>
+          <t xml:space="preserve">clinic_product_settings</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">同期状態</t>
+          <t xml:space="preserve">商品ID</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">sync_status</t>
+          <t xml:space="preserve">product_id</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="G27" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">uuid</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK / FK</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
@@ -2538,12 +2602,12 @@
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">local</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">local / pending / synced / error</t>
+          <t xml:space="preserve">products.id ON DELETE CASCADE</t>
         </is>
       </c>
       <c r="K27" s="4" t="inlineStr">
@@ -2560,27 +2624,27 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文</t>
+          <t xml:space="preserve">医院商品設定</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders</t>
+          <t xml:space="preserve">clinic_product_settings</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">同期エラー</t>
+          <t xml:space="preserve">表示可否</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">sync_error</t>
+          <t xml:space="preserve">is_visible</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">boolean</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
@@ -2590,12 +2654,12 @@
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">YES</t>
+          <t xml:space="preserve">NO</t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">true</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -2617,32 +2681,32 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文</t>
+          <t xml:space="preserve">医院商品設定</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders</t>
+          <t xml:space="preserve">clinic_product_settings</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">冪等キー</t>
+          <t xml:space="preserve">医院価格</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">idempotency_key</t>
+          <t xml:space="preserve">clinic_price</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">uuid</t>
-        </is>
-      </c>
-      <c r="G29" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UK2構成</t>
+          <t xml:space="preserve">integer</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
@@ -2657,7 +2721,7 @@
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">&gt;= 0。NULLは基準価格を使用</t>
         </is>
       </c>
       <c r="K29" s="4" t="inlineStr">
@@ -2674,22 +2738,22 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文</t>
+          <t xml:space="preserve">医院商品設定</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders</t>
+          <t xml:space="preserve">clinic_product_settings</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部更新日時</t>
+          <t xml:space="preserve">更新日時</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">external_updated_at</t>
+          <t xml:space="preserve">updated_at</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
@@ -2704,12 +2768,12 @@
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">YES</t>
+          <t xml:space="preserve">NO</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">now()</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
@@ -2741,22 +2805,22 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">作成日時</t>
+          <t xml:space="preserve">内部注文ID</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">created_at</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">timestamptz</t>
-        </is>
-      </c>
-      <c r="G31" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">uuid</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
@@ -2766,7 +2830,7 @@
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">now()</t>
+          <t xml:space="preserve">gen_random_uuid()</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
@@ -2798,22 +2862,22 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">更新日時</t>
+          <t xml:space="preserve">得意先コード</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">updated_at</t>
+          <t xml:space="preserve">customer_code</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">timestamptz</t>
-        </is>
-      </c>
-      <c r="G32" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK / UK2構成</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
@@ -2823,12 +2887,12 @@
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">now()</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">clinics.customer_code</t>
         </is>
       </c>
       <c r="K32" s="4" t="inlineStr">
@@ -2845,22 +2909,22 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文明細</t>
+          <t xml:space="preserve">患者注文</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_order_items</t>
+          <t xml:space="preserve">patient_orders</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文明細ID</t>
+          <t xml:space="preserve">患者ID</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">patient_id</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -2868,9 +2932,9 @@
           <t xml:space="preserve">uuid</t>
         </is>
       </c>
-      <c r="G33" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PK</t>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
@@ -2880,17 +2944,17 @@
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">gen_random_uuid()</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">patients.id ON DELETE CASCADE</t>
         </is>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">本番前にRESTRICT等へ変更予定</t>
         </is>
       </c>
     </row>
@@ -2902,32 +2966,32 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文明細</t>
+          <t xml:space="preserve">患者注文</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_order_items</t>
+          <t xml:space="preserve">patient_orders</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">内部注文ID</t>
+          <t xml:space="preserve">注文区分</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">order_id</t>
+          <t xml:space="preserve">order_type</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">uuid</t>
-        </is>
-      </c>
-      <c r="G34" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FK</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
@@ -2937,12 +3001,12 @@
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">one_time</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders.id ON DELETE CASCADE</t>
+          <t xml:space="preserve">one_time / subscription</t>
         </is>
       </c>
       <c r="K34" s="4" t="inlineStr">
@@ -2959,47 +3023,47 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文明細</t>
+          <t xml:space="preserve">患者注文</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_order_items</t>
+          <t xml:space="preserve">patient_orders</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">商品ID</t>
+          <t xml:space="preserve">受取方法</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">product_id</t>
+          <t xml:space="preserve">fulfillment_method</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">uuid</t>
-        </is>
-      </c>
-      <c r="G35" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FK</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">YES</t>
+          <t xml:space="preserve">NO</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pickup</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">products.id ON DELETE SET NULL</t>
+          <t xml:space="preserve">pickup / delivery</t>
         </is>
       </c>
       <c r="K35" s="4" t="inlineStr">
@@ -3016,22 +3080,22 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文明細</t>
+          <t xml:space="preserve">患者注文</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_order_items</t>
+          <t xml:space="preserve">patient_orders</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文時商品名</t>
+          <t xml:space="preserve">医院業務状態</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">product_name</t>
+          <t xml:space="preserve">status</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
@@ -3051,12 +3115,12 @@
       </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">received</t>
         </is>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">received / preparing / ready / shipped / completed / canceled</t>
         </is>
       </c>
       <c r="K36" s="4" t="inlineStr">
@@ -3073,27 +3137,27 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文明細</t>
+          <t xml:space="preserve">患者注文</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_order_items</t>
+          <t xml:space="preserve">patient_orders</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文時単価</t>
+          <t xml:space="preserve">注文日時</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">unit_price</t>
+          <t xml:space="preserve">ordered_at</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">integer</t>
+          <t xml:space="preserve">timestamptz</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr">
@@ -3108,12 +3172,12 @@
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">now()</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">&gt;= 0</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K37" s="4" t="inlineStr">
@@ -3130,27 +3194,27 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文明細</t>
+          <t xml:space="preserve">患者注文</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_order_items</t>
+          <t xml:space="preserve">patient_orders</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">数量</t>
+          <t xml:space="preserve">次回提供予定日</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">quantity</t>
+          <t xml:space="preserve">next_fulfillment_date</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">integer</t>
+          <t xml:space="preserve">date</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
@@ -3160,17 +3224,17 @@
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO</t>
+          <t xml:space="preserve">YES</t>
         </is>
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">&gt; 0</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K38" s="4" t="inlineStr">
@@ -3187,22 +3251,22 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文明細</t>
+          <t xml:space="preserve">患者注文</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_order_items</t>
+          <t xml:space="preserve">patient_orders</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">単位スナップショット</t>
+          <t xml:space="preserve">作成元</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">unit_snapshot</t>
+          <t xml:space="preserve">source</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
@@ -3210,24 +3274,24 @@
           <t xml:space="preserve">text</t>
         </is>
       </c>
-      <c r="G39" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UK1構成</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">YES</t>
+          <t xml:space="preserve">NO</t>
         </is>
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">internal</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">internal / shopify</t>
         </is>
       </c>
       <c r="K39" s="4" t="inlineStr">
@@ -3244,22 +3308,22 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文明細</t>
+          <t xml:space="preserve">患者注文</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_order_items</t>
+          <t xml:space="preserve">patient_orders</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">画像種別スナップショット</t>
+          <t xml:space="preserve">登録経路</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">image_type_snapshot</t>
+          <t xml:space="preserve">created_via</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
@@ -3279,12 +3343,12 @@
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">supplement</t>
+          <t xml:space="preserve">clinic_portal</t>
         </is>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">supplement / yogurt / toothbrush / oral</t>
+          <t xml:space="preserve">clinic_portal / bgj_portal / shopify</t>
         </is>
       </c>
       <c r="K40" s="4" t="inlineStr">
@@ -3301,22 +3365,22 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文明細</t>
+          <t xml:space="preserve">患者注文</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_order_items</t>
+          <t xml:space="preserve">patient_orders</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">用量スナップショット</t>
+          <t xml:space="preserve">外部注文ID</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">daily_amount_snapshot</t>
+          <t xml:space="preserve">external_order_id</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
@@ -3324,9 +3388,9 @@
           <t xml:space="preserve">text</t>
         </is>
       </c>
-      <c r="G41" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="G41" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UK1構成</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
@@ -3358,22 +3422,22 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文明細</t>
+          <t xml:space="preserve">患者注文</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_order_items</t>
+          <t xml:space="preserve">patient_orders</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">内容量スナップショット</t>
+          <t xml:space="preserve">同期状態</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">volume_snapshot</t>
+          <t xml:space="preserve">sync_status</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
@@ -3388,17 +3452,17 @@
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">YES</t>
+          <t xml:space="preserve">NO</t>
         </is>
       </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">local</t>
         </is>
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">local / pending / synced / error</t>
         </is>
       </c>
       <c r="K42" s="4" t="inlineStr">
@@ -3415,22 +3479,22 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文明細</t>
+          <t xml:space="preserve">患者注文</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_order_items</t>
+          <t xml:space="preserve">patient_orders</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注意事項スナップショット</t>
+          <t xml:space="preserve">同期エラー</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">caution_snapshot</t>
+          <t xml:space="preserve">sync_error</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
@@ -3472,32 +3536,32 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文明細</t>
+          <t xml:space="preserve">患者注文</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_order_items</t>
+          <t xml:space="preserve">patient_orders</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部明細ID</t>
+          <t xml:space="preserve">冪等キー</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">external_line_item_id</t>
+          <t xml:space="preserve">idempotency_key</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="G44" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">uuid</t>
+        </is>
+      </c>
+      <c r="G44" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UK2構成</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
@@ -3529,22 +3593,22 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文明細</t>
+          <t xml:space="preserve">患者注文</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_order_items</t>
+          <t xml:space="preserve">patient_orders</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">作成日時</t>
+          <t xml:space="preserve">外部更新日時</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">created_at</t>
+          <t xml:space="preserve">external_updated_at</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
@@ -3559,12 +3623,12 @@
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO</t>
+          <t xml:space="preserve">YES</t>
         </is>
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">now()</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J45" s="4" t="inlineStr">
@@ -3586,32 +3650,32 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">送り先マスタ</t>
+          <t xml:space="preserve">患者注文</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery_destinations</t>
+          <t xml:space="preserve">patient_orders</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">送り先ID</t>
+          <t xml:space="preserve">作成日時</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">created_at</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">uuid</t>
-        </is>
-      </c>
-      <c r="G46" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PK</t>
+          <t xml:space="preserve">timestamptz</t>
+        </is>
+      </c>
+      <c r="G46" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
@@ -3621,7 +3685,7 @@
       </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">gen_random_uuid()</t>
+          <t xml:space="preserve">now()</t>
         </is>
       </c>
       <c r="J46" s="4" t="inlineStr">
@@ -3643,47 +3707,47 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">送り先マスタ</t>
+          <t xml:space="preserve">患者注文</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery_destinations</t>
+          <t xml:space="preserve">patient_orders</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院得意先コード</t>
+          <t xml:space="preserve">更新日時</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_customer_code</t>
+          <t xml:space="preserve">updated_at</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="G47" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FK</t>
+          <t xml:space="preserve">timestamptz</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">YES</t>
+          <t xml:space="preserve">NO</t>
         </is>
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">now()</t>
         </is>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinics.customer_code ON DELETE RESTRICT</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K47" s="4" t="inlineStr">
@@ -3700,22 +3764,22 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">送り先マスタ</t>
+          <t xml:space="preserve">患者注文明細</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery_destinations</t>
+          <t xml:space="preserve">patient_order_items</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者ID</t>
+          <t xml:space="preserve">注文明細ID</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_id</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
@@ -3723,24 +3787,24 @@
           <t xml:space="preserve">uuid</t>
         </is>
       </c>
-      <c r="G48" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FK</t>
+      <c r="G48" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">YES</t>
+          <t xml:space="preserve">NO</t>
         </is>
       </c>
       <c r="I48" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">gen_random_uuid()</t>
         </is>
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patients.id ON DELETE RESTRICT</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K48" s="4" t="inlineStr">
@@ -3757,32 +3821,32 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">送り先マスタ</t>
+          <t xml:space="preserve">患者注文明細</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery_destinations</t>
+          <t xml:space="preserve">patient_order_items</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">送り先名</t>
+          <t xml:space="preserve">内部注文ID</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">label</t>
+          <t xml:space="preserve">order_id</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="G49" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">uuid</t>
+        </is>
+      </c>
+      <c r="G49" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
@@ -3797,7 +3861,7 @@
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1〜50文字</t>
+          <t xml:space="preserve">patient_orders.id ON DELETE CASCADE</t>
         </is>
       </c>
       <c r="K49" s="4" t="inlineStr">
@@ -3814,37 +3878,37 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">送り先マスタ</t>
+          <t xml:space="preserve">患者注文明細</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery_destinations</t>
+          <t xml:space="preserve">patient_order_items</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">郵便番号</t>
+          <t xml:space="preserve">商品ID</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">postal_code</t>
+          <t xml:space="preserve">product_id</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="G50" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">uuid</t>
+        </is>
+      </c>
+      <c r="G50" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO</t>
+          <t xml:space="preserve">YES</t>
         </is>
       </c>
       <c r="I50" s="4" t="inlineStr">
@@ -3854,7 +3918,7 @@
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">^[0-9]{3}-[0-9]{4}$</t>
+          <t xml:space="preserve">products.id ON DELETE SET NULL</t>
         </is>
       </c>
       <c r="K50" s="4" t="inlineStr">
@@ -3871,22 +3935,22 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">送り先マスタ</t>
+          <t xml:space="preserve">患者注文明細</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery_destinations</t>
+          <t xml:space="preserve">patient_order_items</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">都道府県</t>
+          <t xml:space="preserve">注文時商品名</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">prefecture</t>
+          <t xml:space="preserve">product_name</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
@@ -3911,7 +3975,7 @@
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2〜4文字</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K51" s="4" t="inlineStr">
@@ -3928,27 +3992,27 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">送り先マスタ</t>
+          <t xml:space="preserve">患者注文明細</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery_destinations</t>
+          <t xml:space="preserve">patient_order_items</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">市区町村</t>
+          <t xml:space="preserve">注文時単価</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">city</t>
+          <t xml:space="preserve">unit_price</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">integer</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
@@ -3968,7 +4032,7 @@
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1〜100文字</t>
+          <t xml:space="preserve">&gt;= 0</t>
         </is>
       </c>
       <c r="K52" s="4" t="inlineStr">
@@ -3985,27 +4049,27 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">送り先マスタ</t>
+          <t xml:space="preserve">患者注文明細</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery_destinations</t>
+          <t xml:space="preserve">patient_order_items</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">住所1</t>
+          <t xml:space="preserve">数量</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">address_line1</t>
+          <t xml:space="preserve">quantity</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">integer</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
@@ -4020,12 +4084,12 @@
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1〜200文字</t>
+          <t xml:space="preserve">&gt; 0</t>
         </is>
       </c>
       <c r="K53" s="4" t="inlineStr">
@@ -4042,22 +4106,22 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">送り先マスタ</t>
+          <t xml:space="preserve">患者注文明細</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery_destinations</t>
+          <t xml:space="preserve">patient_order_items</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">住所2</t>
+          <t xml:space="preserve">単位スナップショット</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">address_line2</t>
+          <t xml:space="preserve">unit_snapshot</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
@@ -4082,7 +4146,7 @@
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">200文字以内</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K54" s="4" t="inlineStr">
@@ -4099,22 +4163,22 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">送り先マスタ</t>
+          <t xml:space="preserve">患者注文明細</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery_destinations</t>
+          <t xml:space="preserve">patient_order_items</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">受取人名</t>
+          <t xml:space="preserve">画像種別スナップショット</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">recipient_name</t>
+          <t xml:space="preserve">image_type_snapshot</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
@@ -4134,12 +4198,12 @@
       </c>
       <c r="I55" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">supplement</t>
         </is>
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1〜100文字</t>
+          <t xml:space="preserve">supplement / yogurt / toothbrush / oral</t>
         </is>
       </c>
       <c r="K55" s="4" t="inlineStr">
@@ -4156,22 +4220,22 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">送り先マスタ</t>
+          <t xml:space="preserve">患者注文明細</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery_destinations</t>
+          <t xml:space="preserve">patient_order_items</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">電話番号</t>
+          <t xml:space="preserve">画像URLスナップショット</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">phone</t>
+          <t xml:space="preserve">image_url_snapshot</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
@@ -4186,7 +4250,7 @@
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO</t>
+          <t xml:space="preserve">YES</t>
         </is>
       </c>
       <c r="I56" s="4" t="inlineStr">
@@ -4196,7 +4260,7 @@
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">数字10〜15桁</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K56" s="4" t="inlineStr">
@@ -4213,27 +4277,27 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">送り先マスタ</t>
+          <t xml:space="preserve">患者注文明細</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery_destinations</t>
+          <t xml:space="preserve">patient_order_items</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">既定</t>
+          <t xml:space="preserve">用量スナップショット</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">is_default</t>
+          <t xml:space="preserve">daily_amount_snapshot</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">boolean</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr">
@@ -4243,12 +4307,12 @@
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO</t>
+          <t xml:space="preserve">YES</t>
         </is>
       </c>
       <c r="I57" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J57" s="4" t="inlineStr">
@@ -4270,27 +4334,27 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">送り先マスタ</t>
+          <t xml:space="preserve">患者注文明細</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery_destinations</t>
+          <t xml:space="preserve">patient_order_items</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">削除日時</t>
+          <t xml:space="preserve">内容量スナップショット</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">deleted_at</t>
+          <t xml:space="preserve">volume_snapshot</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">timestamptz</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
@@ -4327,27 +4391,27 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">送り先マスタ</t>
+          <t xml:space="preserve">患者注文明細</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery_destinations</t>
+          <t xml:space="preserve">patient_order_items</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">作成日時</t>
+          <t xml:space="preserve">注意事項スナップショット</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">created_at</t>
+          <t xml:space="preserve">caution_snapshot</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">timestamptz</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr">
@@ -4357,12 +4421,12 @@
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO</t>
+          <t xml:space="preserve">YES</t>
         </is>
       </c>
       <c r="I59" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">now()</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J59" s="4" t="inlineStr">
@@ -4384,27 +4448,27 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">送り先マスタ</t>
+          <t xml:space="preserve">患者注文明細</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery_destinations</t>
+          <t xml:space="preserve">patient_order_items</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">更新日時</t>
+          <t xml:space="preserve">外部明細ID</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">updated_at</t>
+          <t xml:space="preserve">external_line_item_id</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">timestamptz</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr">
@@ -4414,12 +4478,12 @@
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO</t>
+          <t xml:space="preserve">YES</t>
         </is>
       </c>
       <c r="I60" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">now()</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J60" s="4" t="inlineStr">
@@ -4441,32 +4505,32 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文配送先</t>
+          <t xml:space="preserve">患者注文明細</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">order_delivery_destinations</t>
+          <t xml:space="preserve">patient_order_items</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">内部注文ID</t>
+          <t xml:space="preserve">作成日時</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">order_id</t>
+          <t xml:space="preserve">created_at</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">uuid</t>
-        </is>
-      </c>
-      <c r="G61" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PK / FK</t>
+          <t xml:space="preserve">timestamptz</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr">
@@ -4476,12 +4540,12 @@
       </c>
       <c r="I61" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">now()</t>
         </is>
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders.id ON DELETE CASCADE</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K61" s="4" t="inlineStr">
@@ -4498,12 +4562,12 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文配送先</t>
+          <t xml:space="preserve">送り先マスタ</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">order_delivery_destinations</t>
+          <t xml:space="preserve">delivery_destinations</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -4513,7 +4577,7 @@
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery_destination_id</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
@@ -4521,9 +4585,9 @@
           <t xml:space="preserve">uuid</t>
         </is>
       </c>
-      <c r="G62" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FK</t>
+      <c r="G62" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr">
@@ -4533,12 +4597,12 @@
       </c>
       <c r="I62" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">gen_random_uuid()</t>
         </is>
       </c>
       <c r="J62" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery_destinations.id ON DELETE RESTRICT</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K62" s="4" t="inlineStr">
@@ -4555,22 +4619,22 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文配送先</t>
+          <t xml:space="preserve">送り先マスタ</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">order_delivery_destinations</t>
+          <t xml:space="preserve">delivery_destinations</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">送り先名</t>
+          <t xml:space="preserve">医院得意先コード</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">label</t>
+          <t xml:space="preserve">clinic_customer_code</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
@@ -4578,14 +4642,14 @@
           <t xml:space="preserve">text</t>
         </is>
       </c>
-      <c r="G63" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="G63" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO</t>
+          <t xml:space="preserve">YES</t>
         </is>
       </c>
       <c r="I63" s="4" t="inlineStr">
@@ -4595,7 +4659,7 @@
       </c>
       <c r="J63" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">clinics.customer_code ON DELETE RESTRICT</t>
         </is>
       </c>
       <c r="K63" s="4" t="inlineStr">
@@ -4612,37 +4676,37 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文配送先</t>
+          <t xml:space="preserve">送り先マスタ</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">order_delivery_destinations</t>
+          <t xml:space="preserve">delivery_destinations</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">郵便番号</t>
+          <t xml:space="preserve">患者ID</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">postal_code</t>
+          <t xml:space="preserve">patient_id</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="G64" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">uuid</t>
+        </is>
+      </c>
+      <c r="G64" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO</t>
+          <t xml:space="preserve">YES</t>
         </is>
       </c>
       <c r="I64" s="4" t="inlineStr">
@@ -4652,7 +4716,7 @@
       </c>
       <c r="J64" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">patients.id ON DELETE RESTRICT</t>
         </is>
       </c>
       <c r="K64" s="4" t="inlineStr">
@@ -4669,22 +4733,22 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文配送先</t>
+          <t xml:space="preserve">送り先マスタ</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">order_delivery_destinations</t>
+          <t xml:space="preserve">delivery_destinations</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">都道府県</t>
+          <t xml:space="preserve">送り先名</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">prefecture</t>
+          <t xml:space="preserve">label</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
@@ -4709,7 +4773,7 @@
       </c>
       <c r="J65" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">1〜50文字</t>
         </is>
       </c>
       <c r="K65" s="4" t="inlineStr">
@@ -4726,22 +4790,22 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文配送先</t>
+          <t xml:space="preserve">送り先マスタ</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">order_delivery_destinations</t>
+          <t xml:space="preserve">delivery_destinations</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">市区町村</t>
+          <t xml:space="preserve">郵便番号</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">city</t>
+          <t xml:space="preserve">postal_code</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
@@ -4766,7 +4830,7 @@
       </c>
       <c r="J66" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">^[0-9]{3}-[0-9]{4}$</t>
         </is>
       </c>
       <c r="K66" s="4" t="inlineStr">
@@ -4783,22 +4847,22 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文配送先</t>
+          <t xml:space="preserve">送り先マスタ</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">order_delivery_destinations</t>
+          <t xml:space="preserve">delivery_destinations</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">住所1</t>
+          <t xml:space="preserve">都道府県</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">address_line1</t>
+          <t xml:space="preserve">prefecture</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
@@ -4823,7 +4887,7 @@
       </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2〜4文字</t>
         </is>
       </c>
       <c r="K67" s="4" t="inlineStr">
@@ -4840,22 +4904,22 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文配送先</t>
+          <t xml:space="preserve">送り先マスタ</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">order_delivery_destinations</t>
+          <t xml:space="preserve">delivery_destinations</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">住所2</t>
+          <t xml:space="preserve">市区町村</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">address_line2</t>
+          <t xml:space="preserve">city</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
@@ -4870,7 +4934,7 @@
       </c>
       <c r="H68" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">YES</t>
+          <t xml:space="preserve">NO</t>
         </is>
       </c>
       <c r="I68" s="4" t="inlineStr">
@@ -4880,7 +4944,7 @@
       </c>
       <c r="J68" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">1〜100文字</t>
         </is>
       </c>
       <c r="K68" s="4" t="inlineStr">
@@ -4897,22 +4961,22 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文配送先</t>
+          <t xml:space="preserve">送り先マスタ</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">order_delivery_destinations</t>
+          <t xml:space="preserve">delivery_destinations</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">受取人名</t>
+          <t xml:space="preserve">住所1</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">recipient_name</t>
+          <t xml:space="preserve">address_line1</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
@@ -4937,7 +5001,7 @@
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">1〜200文字</t>
         </is>
       </c>
       <c r="K69" s="4" t="inlineStr">
@@ -4954,22 +5018,22 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文配送先</t>
+          <t xml:space="preserve">送り先マスタ</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">order_delivery_destinations</t>
+          <t xml:space="preserve">delivery_destinations</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">電話番号</t>
+          <t xml:space="preserve">住所2</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">phone</t>
+          <t xml:space="preserve">address_line2</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
@@ -4984,7 +5048,7 @@
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO</t>
+          <t xml:space="preserve">YES</t>
         </is>
       </c>
       <c r="I70" s="4" t="inlineStr">
@@ -4994,7 +5058,7 @@
       </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200文字以内</t>
         </is>
       </c>
       <c r="K70" s="4" t="inlineStr">
@@ -5011,27 +5075,27 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文配送先</t>
+          <t xml:space="preserve">送り先マスタ</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">order_delivery_destinations</t>
+          <t xml:space="preserve">delivery_destinations</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">作成日時</t>
+          <t xml:space="preserve">受取人名</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">created_at</t>
+          <t xml:space="preserve">recipient_name</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">timestamptz</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr">
@@ -5046,12 +5110,12 @@
       </c>
       <c r="I71" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">now()</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J71" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">1〜100文字</t>
         </is>
       </c>
       <c r="K71" s="4" t="inlineStr">
@@ -5068,32 +5132,32 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文操作履歴</t>
+          <t xml:space="preserve">送り先マスタ</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_order_events</t>
+          <t xml:space="preserve">delivery_destinations</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">イベントID</t>
+          <t xml:space="preserve">電話番号</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">phone</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">uuid</t>
-        </is>
-      </c>
-      <c r="G72" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PK</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G72" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr">
@@ -5103,12 +5167,12 @@
       </c>
       <c r="I72" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">gen_random_uuid()</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J72" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">数字10〜15桁</t>
         </is>
       </c>
       <c r="K72" s="4" t="inlineStr">
@@ -5125,32 +5189,32 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文操作履歴</t>
+          <t xml:space="preserve">送り先マスタ</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_order_events</t>
+          <t xml:space="preserve">delivery_destinations</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">内部注文ID</t>
+          <t xml:space="preserve">既定</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">order_id</t>
+          <t xml:space="preserve">is_default</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">uuid</t>
-        </is>
-      </c>
-      <c r="G73" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FK</t>
+          <t xml:space="preserve">boolean</t>
+        </is>
+      </c>
+      <c r="G73" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr">
@@ -5160,12 +5224,12 @@
       </c>
       <c r="I73" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="J73" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders.id ON DELETE CASCADE</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K73" s="4" t="inlineStr">
@@ -5182,27 +5246,27 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文操作履歴</t>
+          <t xml:space="preserve">送り先マスタ</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_order_events</t>
+          <t xml:space="preserve">delivery_destinations</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">イベント種別</t>
+          <t xml:space="preserve">削除日時</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">event_type</t>
+          <t xml:space="preserve">deleted_at</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">timestamptz</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr">
@@ -5212,7 +5276,7 @@
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO</t>
+          <t xml:space="preserve">YES</t>
         </is>
       </c>
       <c r="I74" s="4" t="inlineStr">
@@ -5239,27 +5303,27 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文操作履歴</t>
+          <t xml:space="preserve">送り先マスタ</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_order_events</t>
+          <t xml:space="preserve">delivery_destinations</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">操作者種別</t>
+          <t xml:space="preserve">作成日時</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">actor_type</t>
+          <t xml:space="preserve">created_at</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">timestamptz</t>
         </is>
       </c>
       <c r="G75" s="4" t="inlineStr">
@@ -5274,7 +5338,7 @@
       </c>
       <c r="I75" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">now()</t>
         </is>
       </c>
       <c r="J75" s="4" t="inlineStr">
@@ -5296,27 +5360,27 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文操作履歴</t>
+          <t xml:space="preserve">送り先マスタ</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_order_events</t>
+          <t xml:space="preserve">delivery_destinations</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">操作者識別子</t>
+          <t xml:space="preserve">更新日時</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">actor_identifier</t>
+          <t xml:space="preserve">updated_at</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">timestamptz</t>
         </is>
       </c>
       <c r="G76" s="4" t="inlineStr">
@@ -5331,7 +5395,7 @@
       </c>
       <c r="I76" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">now()</t>
         </is>
       </c>
       <c r="J76" s="4" t="inlineStr">
@@ -5353,37 +5417,37 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文操作履歴</t>
+          <t xml:space="preserve">注文配送先</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_order_events</t>
+          <t xml:space="preserve">order_delivery_destinations</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">変更前状態</t>
+          <t xml:space="preserve">内部注文ID</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">from_status</t>
+          <t xml:space="preserve">order_id</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="G77" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">uuid</t>
+        </is>
+      </c>
+      <c r="G77" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK / FK</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">YES</t>
+          <t xml:space="preserve">NO</t>
         </is>
       </c>
       <c r="I77" s="4" t="inlineStr">
@@ -5393,7 +5457,7 @@
       </c>
       <c r="J77" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">patient_orders.id ON DELETE CASCADE</t>
         </is>
       </c>
       <c r="K77" s="4" t="inlineStr">
@@ -5410,37 +5474,37 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文操作履歴</t>
+          <t xml:space="preserve">注文配送先</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_order_events</t>
+          <t xml:space="preserve">order_delivery_destinations</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">変更後状態</t>
+          <t xml:space="preserve">送り先ID</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">to_status</t>
+          <t xml:space="preserve">delivery_destination_id</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="G78" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">uuid</t>
+        </is>
+      </c>
+      <c r="G78" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">YES</t>
+          <t xml:space="preserve">NO</t>
         </is>
       </c>
       <c r="I78" s="4" t="inlineStr">
@@ -5450,7 +5514,7 @@
       </c>
       <c r="J78" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">delivery_destinations.id ON DELETE RESTRICT</t>
         </is>
       </c>
       <c r="K78" s="4" t="inlineStr">
@@ -5467,50 +5531,962 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">注文配送先</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">order_delivery_destinations</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">送り先名</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">label</t>
+        </is>
+      </c>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G79" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H79" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I79" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J79" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K79" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="30" customHeight="1">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">注文配送先</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">order_delivery_destinations</t>
+        </is>
+      </c>
+      <c r="D80" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">郵便番号</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">postal_code</t>
+        </is>
+      </c>
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G80" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H80" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I80" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K80" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="30" customHeight="1">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">注文配送先</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">order_delivery_destinations</t>
+        </is>
+      </c>
+      <c r="D81" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">都道府県</t>
+        </is>
+      </c>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prefecture</t>
+        </is>
+      </c>
+      <c r="F81" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G81" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H81" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I81" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J81" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K81" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="30" customHeight="1">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B82" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">注文配送先</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">order_delivery_destinations</t>
+        </is>
+      </c>
+      <c r="D82" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">市区町村</t>
+        </is>
+      </c>
+      <c r="E82" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">city</t>
+        </is>
+      </c>
+      <c r="F82" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G82" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H82" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I82" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K82" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="30" customHeight="1">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">注文配送先</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">order_delivery_destinations</t>
+        </is>
+      </c>
+      <c r="D83" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">住所1</t>
+        </is>
+      </c>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">address_line1</t>
+        </is>
+      </c>
+      <c r="F83" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G83" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H83" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I83" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J83" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K83" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="30" customHeight="1">
+      <c r="A84" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">注文配送先</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">order_delivery_destinations</t>
+        </is>
+      </c>
+      <c r="D84" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">住所2</t>
+        </is>
+      </c>
+      <c r="E84" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">address_line2</t>
+        </is>
+      </c>
+      <c r="F84" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G84" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H84" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YES</t>
+        </is>
+      </c>
+      <c r="I84" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K84" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="30" customHeight="1">
+      <c r="A85" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">注文配送先</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">order_delivery_destinations</t>
+        </is>
+      </c>
+      <c r="D85" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">受取人名</t>
+        </is>
+      </c>
+      <c r="E85" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">recipient_name</t>
+        </is>
+      </c>
+      <c r="F85" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G85" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H85" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I85" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J85" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K85" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="30" customHeight="1">
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">注文配送先</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">order_delivery_destinations</t>
+        </is>
+      </c>
+      <c r="D86" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">電話番号</t>
+        </is>
+      </c>
+      <c r="E86" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">phone</t>
+        </is>
+      </c>
+      <c r="F86" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G86" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H86" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I86" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J86" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K86" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="30" customHeight="1">
+      <c r="A87" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">注文配送先</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">order_delivery_destinations</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">作成日時</t>
+        </is>
+      </c>
+      <c r="E87" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">created_at</t>
+        </is>
+      </c>
+      <c r="F87" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">timestamptz</t>
+        </is>
+      </c>
+      <c r="G87" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H87" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I87" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">now()</t>
+        </is>
+      </c>
+      <c r="J87" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K87" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="30" customHeight="1">
+      <c r="A88" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B88" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">注文操作履歴</t>
         </is>
       </c>
-      <c r="C79" s="4" t="inlineStr">
+      <c r="C88" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">patient_order_events</t>
         </is>
       </c>
-      <c r="D79" s="4" t="inlineStr">
+      <c r="D88" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">イベントID</t>
+        </is>
+      </c>
+      <c r="E88" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">id</t>
+        </is>
+      </c>
+      <c r="F88" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">uuid</t>
+        </is>
+      </c>
+      <c r="G88" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK</t>
+        </is>
+      </c>
+      <c r="H88" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I88" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gen_random_uuid()</t>
+        </is>
+      </c>
+      <c r="J88" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K88" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="30" customHeight="1">
+      <c r="A89" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">注文操作履歴</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_order_events</t>
+        </is>
+      </c>
+      <c r="D89" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">内部注文ID</t>
+        </is>
+      </c>
+      <c r="E89" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">order_id</t>
+        </is>
+      </c>
+      <c r="F89" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">uuid</t>
+        </is>
+      </c>
+      <c r="G89" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
+        </is>
+      </c>
+      <c r="H89" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I89" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J89" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_orders.id ON DELETE CASCADE</t>
+        </is>
+      </c>
+      <c r="K89" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="30" customHeight="1">
+      <c r="A90" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B90" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">注文操作履歴</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_order_events</t>
+        </is>
+      </c>
+      <c r="D90" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">イベント種別</t>
+        </is>
+      </c>
+      <c r="E90" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">event_type</t>
+        </is>
+      </c>
+      <c r="F90" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G90" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H90" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I90" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J90" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K90" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="30" customHeight="1">
+      <c r="A91" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">注文操作履歴</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_order_events</t>
+        </is>
+      </c>
+      <c r="D91" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">操作者種別</t>
+        </is>
+      </c>
+      <c r="E91" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actor_type</t>
+        </is>
+      </c>
+      <c r="F91" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G91" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H91" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I91" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J91" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K91" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="30" customHeight="1">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B92" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">注文操作履歴</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_order_events</t>
+        </is>
+      </c>
+      <c r="D92" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">操作者識別子</t>
+        </is>
+      </c>
+      <c r="E92" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actor_identifier</t>
+        </is>
+      </c>
+      <c r="F92" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G92" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H92" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I92" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J92" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K92" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="30" customHeight="1">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">注文操作履歴</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_order_events</t>
+        </is>
+      </c>
+      <c r="D93" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">変更前状態</t>
+        </is>
+      </c>
+      <c r="E93" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">from_status</t>
+        </is>
+      </c>
+      <c r="F93" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G93" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H93" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YES</t>
+        </is>
+      </c>
+      <c r="I93" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J93" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K93" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="30" customHeight="1">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">注文操作履歴</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_order_events</t>
+        </is>
+      </c>
+      <c r="D94" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">変更後状態</t>
+        </is>
+      </c>
+      <c r="E94" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">to_status</t>
+        </is>
+      </c>
+      <c r="F94" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G94" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H94" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YES</t>
+        </is>
+      </c>
+      <c r="I94" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J94" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K94" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="30" customHeight="1">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">注文操作履歴</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_order_events</t>
+        </is>
+      </c>
+      <c r="D95" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">発生日時</t>
         </is>
       </c>
-      <c r="E79" s="4" t="inlineStr">
+      <c r="E95" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">created_at</t>
         </is>
       </c>
-      <c r="F79" s="4" t="inlineStr">
+      <c r="F95" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">timestamptz</t>
         </is>
       </c>
-      <c r="G79" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H79" s="4" t="inlineStr">
+      <c r="G95" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H95" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">NO</t>
         </is>
       </c>
-      <c r="I79" s="4" t="inlineStr">
+      <c r="I95" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">now()</t>
         </is>
       </c>
-      <c r="J79" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="K79" s="4" t="inlineStr">
+      <c r="J95" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K95" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -5521,7 +6497,7 @@
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A2:K2"/>
   </mergeCells>
-  <autoFilter ref="A4:K79"/>
+  <autoFilter ref="A4:K95"/>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0" paperSize="9"/>
 </worksheet>
@@ -10246,7 +11222,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -10815,34 +11791,34 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">N</t>
+          <t xml:space="preserve">0..1</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders.customer_code</t>
+          <t xml:space="preserve">clinic_terms.customer_code</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文</t>
+          <t xml:space="preserve">医院契約情報</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK</t>
+          <t xml:space="preserve">PK・FK・CASCADE</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者</t>
+          <t xml:space="preserve">医院</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patients.id</t>
+          <t xml:space="preserve">clinics.customer_code</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -10857,29 +11833,29 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders.patient_id</t>
+          <t xml:space="preserve">clinic_product_settings.customer_code</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文</t>
+          <t xml:space="preserve">医院商品設定</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK・現状CASCADE</t>
+          <t xml:space="preserve">PK・FK・CASCADE</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文</t>
+          <t xml:space="preserve">商品</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders.id</t>
+          <t xml:space="preserve">products.id</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -10894,17 +11870,17 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_order_items.order_id</t>
+          <t xml:space="preserve">clinic_product_settings.product_id</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文明細</t>
+          <t xml:space="preserve">医院商品設定</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK・CASCADE</t>
+          <t xml:space="preserve">PK・FK・CASCADE</t>
         </is>
       </c>
     </row>
@@ -10931,17 +11907,17 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery_destinations.clinic_customer_code</t>
+          <t xml:space="preserve">patient_orders.customer_code</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">送り先マスタ</t>
+          <t xml:space="preserve">患者注文</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK・RESTRICT</t>
+          <t xml:space="preserve">FK</t>
         </is>
       </c>
     </row>
@@ -10968,29 +11944,29 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery_destinations.patient_id</t>
+          <t xml:space="preserve">patient_orders.patient_id</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">送り先マスタ</t>
+          <t xml:space="preserve">患者注文</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK・RESTRICT</t>
+          <t xml:space="preserve">FK・現状CASCADE</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">送り先マスタ</t>
+          <t xml:space="preserve">患者注文</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery_destinations.id</t>
+          <t xml:space="preserve">patient_orders.id</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -11005,29 +11981,29 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">order_delivery_destinations.delivery_destination_id</t>
+          <t xml:space="preserve">patient_order_items.order_id</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文配送先</t>
+          <t xml:space="preserve">患者注文明細</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK・RESTRICT</t>
+          <t xml:space="preserve">FK・CASCADE</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文</t>
+          <t xml:space="preserve">医院</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders.id</t>
+          <t xml:space="preserve">clinics.customer_code</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -11037,34 +12013,34 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">0..1</t>
+          <t xml:space="preserve">N</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">order_delivery_destinations.order_id</t>
+          <t xml:space="preserve">delivery_destinations.clinic_customer_code</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文配送先</t>
+          <t xml:space="preserve">送り先マスタ</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">PK・FK・CASCADE</t>
+          <t xml:space="preserve">FK・RESTRICT</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文</t>
+          <t xml:space="preserve">患者</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders.id</t>
+          <t xml:space="preserve">patients.id</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -11079,221 +12055,221 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_order_events.order_id</t>
+          <t xml:space="preserve">delivery_destinations.patient_id</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文操作履歴</t>
+          <t xml:space="preserve">送り先マスタ</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK・CASCADE</t>
+          <t xml:space="preserve">FK・RESTRICT</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">送り先マスタ</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">delivery_destinations.id</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">order_delivery_destinations.delivery_destination_id</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">注文配送先</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK・RESTRICT</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">患者注文</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_orders.id</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0..1</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">order_delivery_destinations.order_id</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">注文配送先</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK・FK・CASCADE</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">患者注文</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_orders.id</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_order_events.order_id</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">注文操作履歴</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK・CASCADE</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">商品</t>
         </is>
       </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">products.id</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">0..1</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D33" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
+      <c r="E33" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">patient_order_items.product_id</t>
         </is>
       </c>
-      <c r="F30" s="4" t="inlineStr">
+      <c r="F33" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">患者注文明細</t>
         </is>
       </c>
-      <c r="G30" s="4" t="inlineStr">
+      <c r="G33" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">FK・SET NULL</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">将来リレーション案</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">親DB日本語名</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">親KEY</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="C36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">親多重度</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr">
+      <c r="D36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">子多重度</t>
         </is>
       </c>
-      <c r="E33" s="3" t="inlineStr">
+      <c r="E36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">子FK</t>
         </is>
       </c>
-      <c r="F33" s="3" t="inlineStr">
+      <c r="F36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">子DB日本語名</t>
         </is>
       </c>
-      <c r="G33" s="3" t="inlineStr">
+      <c r="G36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">削除・備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">患者注文</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">patient_orders.id</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">order_transaction_projections.order_id</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">決済返金投影</t>
-        </is>
-      </c>
-      <c r="G34" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FK</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">患者注文</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">patient_orders.id</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="D35" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">patient_fulfillments.order_id</t>
-        </is>
-      </c>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">受取配送</t>
-        </is>
-      </c>
-      <c r="G35" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FK</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">受取配送</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">patient_fulfillments.id</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="D36" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">patient_fulfillment_items.fulfillment_id</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">受取配送明細</t>
-        </is>
-      </c>
-      <c r="G36" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FK</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文明細</t>
+          <t xml:space="preserve">患者注文</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_order_items.id</t>
+          <t xml:space="preserve">patient_orders.id</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -11308,12 +12284,12 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_fulfillment_items.order_item_id</t>
+          <t xml:space="preserve">order_transaction_projections.order_id</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">受取配送明細</t>
+          <t xml:space="preserve">決済返金投影</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr">
@@ -11325,12 +12301,12 @@
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部コマース接続</t>
+          <t xml:space="preserve">患者注文</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_accounts.id</t>
+          <t xml:space="preserve">patient_orders.id</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -11345,12 +12321,12 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders.commerce_account_id</t>
+          <t xml:space="preserve">patient_fulfillments.order_id</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文</t>
+          <t xml:space="preserve">受取配送</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
@@ -11362,12 +12338,12 @@
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部コマース接続</t>
+          <t xml:space="preserve">受取配送</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_accounts.id</t>
+          <t xml:space="preserve">patient_fulfillments.id</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -11382,12 +12358,12 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_webhook_events.commerce_account_id</t>
+          <t xml:space="preserve">patient_fulfillment_items.fulfillment_id</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部受信イベント</t>
+          <t xml:space="preserve">受取配送明細</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr">
@@ -11399,12 +12375,12 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部コマース接続</t>
+          <t xml:space="preserve">注文明細</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_accounts.id</t>
+          <t xml:space="preserve">patient_order_items.id</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -11419,12 +12395,12 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_outbox.commerce_account_id</t>
+          <t xml:space="preserve">patient_fulfillment_items.order_item_id</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部送信キュー</t>
+          <t xml:space="preserve">受取配送明細</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
@@ -11436,12 +12412,12 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者</t>
+          <t xml:space="preserve">外部コマース接続</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patients.id</t>
+          <t xml:space="preserve">commerce_accounts.id</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -11456,12 +12432,12 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_subscriptions.patient_id</t>
+          <t xml:space="preserve">patient_orders.commerce_account_id</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者定期購入</t>
+          <t xml:space="preserve">患者注文</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr">
@@ -11473,12 +12449,12 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者定期購入</t>
+          <t xml:space="preserve">外部コマース接続</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_subscriptions.id</t>
+          <t xml:space="preserve">commerce_accounts.id</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -11493,12 +12469,12 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_subscription_items.subscription_id</t>
+          <t xml:space="preserve">commerce_webhook_events.commerce_account_id</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">定期購入明細</t>
+          <t xml:space="preserve">外部受信イベント</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
@@ -11510,35 +12486,146 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">外部コマース接続</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">commerce_accounts.id</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">commerce_outbox.commerce_account_id</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">外部送信キュー</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">患者</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patients.id</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscriptions.patient_id</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">患者定期購入</t>
         </is>
       </c>
-      <c r="B43" s="4" t="inlineStr">
+      <c r="G44" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">患者定期購入</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">patient_subscriptions.id</t>
         </is>
       </c>
-      <c r="C43" s="4" t="inlineStr">
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscription_items.subscription_id</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">定期購入明細</t>
+        </is>
+      </c>
+      <c r="G45" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">患者定期購入</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscriptions.id</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">0..1</t>
         </is>
       </c>
-      <c r="D43" s="4" t="inlineStr">
+      <c r="D46" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="E43" s="4" t="inlineStr">
+      <c r="E46" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">patient_orders.subscription_id</t>
         </is>
       </c>
-      <c r="F43" s="4" t="inlineStr">
+      <c r="F46" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">患者注文</t>
         </is>
       </c>
-      <c r="G43" s="4" t="inlineStr">
+      <c r="G46" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">FK</t>
         </is>
@@ -11549,7 +12636,7 @@
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A20:H20"/>
-    <mergeCell ref="A32:H32"/>
+    <mergeCell ref="A35:H35"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0" paperSize="9"/>
@@ -11558,7 +12645,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Q68"/>
+  <dimension ref="A1:Q85"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -11773,7 +12860,7 @@
       </c>
       <c r="M9" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">参考価格</t>
+          <t xml:space="preserve">基準価格</t>
         </is>
       </c>
       <c r="O9" s="11" t="inlineStr">
@@ -12070,6 +13157,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="L24" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">画像URL</t>
+        </is>
+      </c>
+      <c r="N24" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">image_url_snapshot</t>
+        </is>
+      </c>
+      <c r="P24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="L25" s="12" t="inlineStr">
@@ -12324,6 +13426,12 @@
       </c>
     </row>
     <row r="44" ht="23" customHeight="1">
+      <c r="A44" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">医院契約情報
+clinic_terms</t>
+        </is>
+      </c>
       <c r="F44" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">注文操作履歴
@@ -12332,6 +13440,21 @@
       </c>
     </row>
     <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">日本語項目</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">物理カラム</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KEY</t>
+        </is>
+      </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">日本語項目</t>
@@ -12349,6 +13472,21 @@
       </c>
     </row>
     <row r="47">
+      <c r="A47" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">得意先コード</t>
+        </is>
+      </c>
+      <c r="C47" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">customer_code</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK/FK</t>
+        </is>
+      </c>
       <c r="F47" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">イベントID</t>
@@ -12366,6 +13504,21 @@
       </c>
     </row>
     <row r="48">
+      <c r="A48" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仕切値率</t>
+        </is>
+      </c>
+      <c r="C48" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wholesale_rate</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
       <c r="F48" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">内部注文ID</t>
@@ -12450,385 +13603,589 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="58" ht="23" customHeight="1">
+      <c r="A58" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">医院商品設定
+clinic_product_settings</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">日本語項目</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">物理カラム</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">得意先コード</t>
+        </is>
+      </c>
+      <c r="C61" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">customer_code</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK/FK</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">商品ID</t>
+        </is>
+      </c>
+      <c r="C62" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">product_id</t>
+        </is>
+      </c>
+      <c r="E62" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK/FK</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">表示可否</t>
+        </is>
+      </c>
+      <c r="C63" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">is_visible</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">医院価格</t>
+        </is>
+      </c>
+      <c r="C64" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_price</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">リレーション一覧</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="3" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">親DB</t>
         </is>
       </c>
-      <c r="B59" s="3" t="inlineStr">
+      <c r="B73" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">親KEY</t>
         </is>
       </c>
-      <c r="C59" s="3" t="inlineStr">
+      <c r="C73" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">親</t>
         </is>
       </c>
-      <c r="D59" s="3" t="inlineStr">
+      <c r="D73" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">子</t>
         </is>
       </c>
-      <c r="E59" s="3" t="inlineStr">
+      <c r="E73" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">子FK</t>
         </is>
       </c>
-      <c r="F59" s="3" t="inlineStr">
+      <c r="F73" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">子DB</t>
         </is>
       </c>
-      <c r="G59" s="3" t="inlineStr">
+      <c r="G73" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">備考</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="4" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">医院</t>
         </is>
       </c>
-      <c r="B60" s="4" t="inlineStr">
+      <c r="B74" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">clinics.customer_code</t>
         </is>
       </c>
-      <c r="C60" s="4" t="inlineStr">
+      <c r="C74" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="D60" s="4" t="inlineStr">
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0..1</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_terms.customer_code</t>
+        </is>
+      </c>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">医院契約情報</t>
+        </is>
+      </c>
+      <c r="G74" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK・FK・CASCADE</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">医院</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinics.customer_code</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="E60" s="4" t="inlineStr">
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_product_settings.customer_code</t>
+        </is>
+      </c>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">医院商品設定</t>
+        </is>
+      </c>
+      <c r="G75" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK・FK・CASCADE</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">商品</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">products.id</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_product_settings.product_id</t>
+        </is>
+      </c>
+      <c r="F76" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">医院商品設定</t>
+        </is>
+      </c>
+      <c r="G76" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK・FK・CASCADE</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">医院</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinics.customer_code</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">patient_orders.customer_code</t>
         </is>
       </c>
-      <c r="F60" s="4" t="inlineStr">
+      <c r="F77" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">患者注文</t>
         </is>
       </c>
-      <c r="G60" s="4" t="inlineStr">
+      <c r="G77" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">FK</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="4" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">患者</t>
         </is>
       </c>
-      <c r="B61" s="4" t="inlineStr">
+      <c r="B78" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">patients.id</t>
         </is>
       </c>
-      <c r="C61" s="4" t="inlineStr">
+      <c r="C78" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="D61" s="4" t="inlineStr">
+      <c r="D78" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="E61" s="4" t="inlineStr">
+      <c r="E78" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">patient_orders.patient_id</t>
         </is>
       </c>
-      <c r="F61" s="4" t="inlineStr">
+      <c r="F78" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">患者注文</t>
         </is>
       </c>
-      <c r="G61" s="4" t="inlineStr">
+      <c r="G78" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">FK・現状CASCADE</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="4" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">患者注文</t>
         </is>
       </c>
-      <c r="B62" s="4" t="inlineStr">
+      <c r="B79" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">patient_orders.id</t>
         </is>
       </c>
-      <c r="C62" s="4" t="inlineStr">
+      <c r="C79" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="D62" s="4" t="inlineStr">
+      <c r="D79" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="E62" s="4" t="inlineStr">
+      <c r="E79" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">patient_order_items.order_id</t>
         </is>
       </c>
-      <c r="F62" s="4" t="inlineStr">
+      <c r="F79" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">患者注文明細</t>
         </is>
       </c>
-      <c r="G62" s="4" t="inlineStr">
+      <c r="G79" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">FK・CASCADE</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="4" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">医院</t>
         </is>
       </c>
-      <c r="B63" s="4" t="inlineStr">
+      <c r="B80" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">clinics.customer_code</t>
         </is>
       </c>
-      <c r="C63" s="4" t="inlineStr">
+      <c r="C80" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="D63" s="4" t="inlineStr">
+      <c r="D80" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="E63" s="4" t="inlineStr">
+      <c r="E80" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">delivery_destinations.clinic_customer_code</t>
         </is>
       </c>
-      <c r="F63" s="4" t="inlineStr">
+      <c r="F80" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">送り先マスタ</t>
         </is>
       </c>
-      <c r="G63" s="4" t="inlineStr">
+      <c r="G80" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">FK・RESTRICT</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="4" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">患者</t>
         </is>
       </c>
-      <c r="B64" s="4" t="inlineStr">
+      <c r="B81" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">patients.id</t>
         </is>
       </c>
-      <c r="C64" s="4" t="inlineStr">
+      <c r="C81" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="D64" s="4" t="inlineStr">
+      <c r="D81" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="E64" s="4" t="inlineStr">
+      <c r="E81" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">delivery_destinations.patient_id</t>
         </is>
       </c>
-      <c r="F64" s="4" t="inlineStr">
+      <c r="F81" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">送り先マスタ</t>
         </is>
       </c>
-      <c r="G64" s="4" t="inlineStr">
+      <c r="G81" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">FK・RESTRICT</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="4" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">送り先マスタ</t>
         </is>
       </c>
-      <c r="B65" s="4" t="inlineStr">
+      <c r="B82" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">delivery_destinations.id</t>
         </is>
       </c>
-      <c r="C65" s="4" t="inlineStr">
+      <c r="C82" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="D65" s="4" t="inlineStr">
+      <c r="D82" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="E65" s="4" t="inlineStr">
+      <c r="E82" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">order_delivery_destinations.delivery_destination_id</t>
         </is>
       </c>
-      <c r="F65" s="4" t="inlineStr">
+      <c r="F82" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">注文配送先</t>
         </is>
       </c>
-      <c r="G65" s="4" t="inlineStr">
+      <c r="G82" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">FK・RESTRICT</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="4" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">患者注文</t>
         </is>
       </c>
-      <c r="B66" s="4" t="inlineStr">
+      <c r="B83" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">patient_orders.id</t>
         </is>
       </c>
-      <c r="C66" s="4" t="inlineStr">
+      <c r="C83" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="D66" s="4" t="inlineStr">
+      <c r="D83" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">0..1</t>
         </is>
       </c>
-      <c r="E66" s="4" t="inlineStr">
+      <c r="E83" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">order_delivery_destinations.order_id</t>
         </is>
       </c>
-      <c r="F66" s="4" t="inlineStr">
+      <c r="F83" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">注文配送先</t>
         </is>
       </c>
-      <c r="G66" s="4" t="inlineStr">
+      <c r="G83" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">PK・FK・CASCADE</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="4" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">患者注文</t>
         </is>
       </c>
-      <c r="B67" s="4" t="inlineStr">
+      <c r="B84" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">patient_orders.id</t>
         </is>
       </c>
-      <c r="C67" s="4" t="inlineStr">
+      <c r="C84" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="D67" s="4" t="inlineStr">
+      <c r="D84" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="E67" s="4" t="inlineStr">
+      <c r="E84" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">patient_order_events.order_id</t>
         </is>
       </c>
-      <c r="F67" s="4" t="inlineStr">
+      <c r="F84" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">注文操作履歴</t>
         </is>
       </c>
-      <c r="G67" s="4" t="inlineStr">
+      <c r="G84" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">FK・CASCADE</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="4" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">商品</t>
         </is>
       </c>
-      <c r="B68" s="4" t="inlineStr">
+      <c r="B85" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">products.id</t>
         </is>
       </c>
-      <c r="C68" s="4" t="inlineStr">
+      <c r="C85" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">0..1</t>
         </is>
       </c>
-      <c r="D68" s="4" t="inlineStr">
+      <c r="D85" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="E68" s="4" t="inlineStr">
+      <c r="E85" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">patient_order_items.product_id</t>
         </is>
       </c>
-      <c r="F68" s="4" t="inlineStr">
+      <c r="F85" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">患者注文明細</t>
         </is>
       </c>
-      <c r="G68" s="4" t="inlineStr">
+      <c r="G85" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">FK・SET NULL</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="111">
+  <mergeCells count="131">
     <mergeCell ref="A1:Q1"/>
     <mergeCell ref="A2:Q2"/>
     <mergeCell ref="A4:E5"/>
@@ -12892,6 +14249,8 @@
     <mergeCell ref="N22:O22"/>
     <mergeCell ref="L23:M23"/>
     <mergeCell ref="N23:O23"/>
+    <mergeCell ref="L24:M24"/>
+    <mergeCell ref="N24:O24"/>
     <mergeCell ref="L25:Q26"/>
     <mergeCell ref="A29:E30"/>
     <mergeCell ref="A31:B31"/>
@@ -12938,8 +14297,26 @@
     <mergeCell ref="H51:I51"/>
     <mergeCell ref="F52:G52"/>
     <mergeCell ref="H52:I52"/>
+    <mergeCell ref="A44:E45"/>
+    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="A58:E59"/>
+    <mergeCell ref="A60:B60"/>
+    <mergeCell ref="C60:D60"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="C61:D61"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="C62:D62"/>
+    <mergeCell ref="A63:B63"/>
+    <mergeCell ref="C63:D63"/>
+    <mergeCell ref="A64:B64"/>
+    <mergeCell ref="C64:D64"/>
     <mergeCell ref="B26:J27"/>
-    <mergeCell ref="A58:Q58"/>
+    <mergeCell ref="A72:Q72"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0" paperSize="9"/>
@@ -14654,7 +16031,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -14874,39 +16251,39 @@
     <row r="10" ht="42" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Phase 2-1</t>
+          <t xml:space="preserve">Phase 1-5</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">仕様確定後</t>
+          <t xml:space="preserve">完了</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_accounts / Inbox / Outbox</t>
+          <t xml:space="preserve">clinic_product_settings / patient_order_items</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shopify接続・Webhook受信・外部送信を分離する。</t>
+          <t xml:space="preserve">医院価格と注文時商品画像を運用する。</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部仕様確定前に作り込まない。</t>
+          <t xml:space="preserve">仕切値は導出し、重複保存しない。</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">未実施</t>
+          <t xml:space="preserve">実装・動作確認済み</t>
         </is>
       </c>
     </row>
     <row r="11" ht="42" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Phase 2-2</t>
+          <t xml:space="preserve">Phase 2-1</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -14916,17 +16293,17 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">決済・返金・配送投影</t>
+          <t xml:space="preserve">commerce_accounts / Inbox / Outbox</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shopify状態を医院業務状態と別軸で保持する。</t>
+          <t xml:space="preserve">Shopify接続・Webhook受信・外部送信を分離する。</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">確定額と参考額を混同しない。</t>
+          <t xml:space="preserve">外部仕様確定前に作り込まない。</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -14938,7 +16315,7 @@
     <row r="12" ht="42" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Phase 2-3</t>
+          <t xml:space="preserve">Phase 2-2</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -14948,17 +16325,17 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_subscriptions</t>
+          <t xml:space="preserve">決済・返金・配送投影</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">定期購入契約を読み取り用投影として追加する。</t>
+          <t xml:space="preserve">Shopify状態を医院業務状態と別軸で保持する。</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">変更・解約はShopify正本。</t>
+          <t xml:space="preserve">確定額と参考額を混同しない。</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -14970,72 +16347,104 @@
     <row r="13" ht="42" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">Phase 2-3</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仕様確定後</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscriptions</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">定期購入契約を読み取り用投影として追加する。</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">変更・解約はShopify正本。</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未実施</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="42" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">Phase 3</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">仕様確定後</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Salesforce外部ID対応</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">医院・患者・活動の同期方向を定義する。</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">CRM正本はSalesforce。</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">未実施</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">共通実行ルール</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">・本番書き込み前にバックアップと確認SQLを用意する。</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">・新規テーブルはRLS有効・ポリシーなし・service role経由のみとする。</t>
+          <t xml:space="preserve">・本番書き込み前にバックアップと確認SQLを用意する。</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">・schema.sql、増分migration、TypeScript型、APIテスト、BGJマニュアルを同じ作業単位で更新する。</t>
+          <t xml:space="preserve">・新規テーブルはRLS有効・ポリシーなし・service role経由のみとする。</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">・列・テーブル削除は新構造へ切替後も最低1リリース待ち、同一リリースで追加と削除を行わない。</t>
+          <t xml:space="preserve">・schema.sql、増分migration、TypeScript型、APIテスト、BGJマニュアルを同じ作業単位で更新する。</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">・列・テーブル削除は新構造へ切替後も最低1リリース待ち、同一リリースで追加と削除を行わない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">・Shopify・Salesforce仕様確定前に外部契約・決済・CRMをローカルだけで成立させない。</t>
         </is>
@@ -15045,12 +16454,12 @@
   <mergeCells count="8">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A15:F15"/>
     <mergeCell ref="A16:F16"/>
     <mergeCell ref="A17:F17"/>
     <mergeCell ref="A18:F18"/>
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A21:F21"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0" paperSize="9"/>

--- a/project_clinic_order_management_db_definition.xlsx
+++ b/project_clinic_order_management_db_definition.xlsx
@@ -679,12 +679,12 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">実装済み・患者表示価格</t>
+          <t xml:space="preserve">実装済み・患者表示／定期価格</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院×商品の表示設定と医院価格。clinic_priceがNULLならproducts.priceを患者表示価格にする。</t>
+          <t xml:space="preserve">医院×商品の表示設定、医院通常価格、3ヶ月／6ヶ月定期価格。期間別価格がNULLなら医院通常価格を使用する。</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -1218,7 +1218,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K95"/>
+  <dimension ref="A1:K97"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院価格</t>
+          <t xml:space="preserve">医院通常価格</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
@@ -2748,17 +2748,17 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">更新日時</t>
+          <t xml:space="preserve">3ヶ月価格</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">updated_at</t>
+          <t xml:space="preserve">subscription_3_month_price</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">timestamptz</t>
+          <t xml:space="preserve">integer</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
@@ -2768,17 +2768,17 @@
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO</t>
+          <t xml:space="preserve">YES</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">now()</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">&gt;= 0。NULLは医院通常価格を使用</t>
         </is>
       </c>
       <c r="K30" s="4" t="inlineStr">
@@ -2795,47 +2795,47 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文</t>
+          <t xml:space="preserve">医院商品設定</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders</t>
+          <t xml:space="preserve">clinic_product_settings</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">内部注文ID</t>
+          <t xml:space="preserve">6ヶ月価格</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">subscription_6_month_price</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">uuid</t>
-        </is>
-      </c>
-      <c r="G31" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PK</t>
+          <t xml:space="preserve">integer</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO</t>
+          <t xml:space="preserve">YES</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">gen_random_uuid()</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">&gt;= 0。NULLは医院通常価格を使用</t>
         </is>
       </c>
       <c r="K31" s="4" t="inlineStr">
@@ -2852,32 +2852,32 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文</t>
+          <t xml:space="preserve">医院商品設定</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders</t>
+          <t xml:space="preserve">clinic_product_settings</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">得意先コード</t>
+          <t xml:space="preserve">更新日時</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">customer_code</t>
+          <t xml:space="preserve">updated_at</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="G32" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FK / UK2構成</t>
+          <t xml:space="preserve">timestamptz</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
@@ -2887,12 +2887,12 @@
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">now()</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinics.customer_code</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K32" s="4" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者ID</t>
+          <t xml:space="preserve">内部注文ID</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_id</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -2932,9 +2932,9 @@
           <t xml:space="preserve">uuid</t>
         </is>
       </c>
-      <c r="G33" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FK</t>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
@@ -2944,17 +2944,17 @@
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">gen_random_uuid()</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patients.id ON DELETE CASCADE</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">本番前にRESTRICT等へ変更予定</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
@@ -2976,12 +2976,12 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文区分</t>
+          <t xml:space="preserve">得意先コード</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">order_type</t>
+          <t xml:space="preserve">customer_code</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -2989,9 +2989,9 @@
           <t xml:space="preserve">text</t>
         </is>
       </c>
-      <c r="G34" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK / UK2構成</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
@@ -3001,12 +3001,12 @@
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">one_time</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">one_time / subscription</t>
+          <t xml:space="preserve">clinics.customer_code</t>
         </is>
       </c>
       <c r="K34" s="4" t="inlineStr">
@@ -3033,22 +3033,22 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">受取方法</t>
+          <t xml:space="preserve">患者ID</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">fulfillment_method</t>
+          <t xml:space="preserve">patient_id</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="G35" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">uuid</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">pickup</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">pickup / delivery</t>
+          <t xml:space="preserve">patients.id ON DELETE CASCADE</t>
         </is>
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">本番前にRESTRICT等へ変更予定</t>
         </is>
       </c>
     </row>
@@ -3090,12 +3090,12 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院業務状態</t>
+          <t xml:space="preserve">注文区分</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">status</t>
+          <t xml:space="preserve">order_type</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
@@ -3115,12 +3115,12 @@
       </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">received</t>
+          <t xml:space="preserve">one_time</t>
         </is>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">received / preparing / ready / shipped / completed / canceled</t>
+          <t xml:space="preserve">one_time / subscription</t>
         </is>
       </c>
       <c r="K36" s="4" t="inlineStr">
@@ -3147,17 +3147,17 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文日時</t>
+          <t xml:space="preserve">受取方法</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ordered_at</t>
+          <t xml:space="preserve">fulfillment_method</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">timestamptz</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">now()</t>
+          <t xml:space="preserve">pickup</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pickup / delivery</t>
         </is>
       </c>
       <c r="K37" s="4" t="inlineStr">
@@ -3204,17 +3204,17 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">次回提供予定日</t>
+          <t xml:space="preserve">医院業務状態</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">next_fulfillment_date</t>
+          <t xml:space="preserve">status</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">date</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
@@ -3224,17 +3224,17 @@
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">YES</t>
+          <t xml:space="preserve">NO</t>
         </is>
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">received</t>
         </is>
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">received / preparing / ready / shipped / completed / canceled</t>
         </is>
       </c>
       <c r="K38" s="4" t="inlineStr">
@@ -3261,22 +3261,22 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">作成元</t>
+          <t xml:space="preserve">注文日時</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">source</t>
+          <t xml:space="preserve">ordered_at</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="G39" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UK1構成</t>
+          <t xml:space="preserve">timestamptz</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
@@ -3286,12 +3286,12 @@
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">internal</t>
+          <t xml:space="preserve">now()</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">internal / shopify</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K39" s="4" t="inlineStr">
@@ -3318,17 +3318,17 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">登録経路</t>
+          <t xml:space="preserve">次回提供予定日</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">created_via</t>
+          <t xml:space="preserve">next_fulfillment_date</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">date</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
@@ -3338,17 +3338,17 @@
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO</t>
+          <t xml:space="preserve">YES</t>
         </is>
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_portal</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_portal / bgj_portal / shopify</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K40" s="4" t="inlineStr">
@@ -3375,12 +3375,12 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部注文ID</t>
+          <t xml:space="preserve">作成元</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">external_order_id</t>
+          <t xml:space="preserve">source</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
@@ -3395,17 +3395,17 @@
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">YES</t>
+          <t xml:space="preserve">NO</t>
         </is>
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">internal</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">internal / shopify</t>
         </is>
       </c>
       <c r="K41" s="4" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">同期状態</t>
+          <t xml:space="preserve">登録経路</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">sync_status</t>
+          <t xml:space="preserve">created_via</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
@@ -3457,12 +3457,12 @@
       </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">local</t>
+          <t xml:space="preserve">clinic_portal</t>
         </is>
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">local / pending / synced / error</t>
+          <t xml:space="preserve">clinic_portal / bgj_portal / shopify</t>
         </is>
       </c>
       <c r="K42" s="4" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">同期エラー</t>
+          <t xml:space="preserve">外部注文ID</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">sync_error</t>
+          <t xml:space="preserve">external_order_id</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
@@ -3502,9 +3502,9 @@
           <t xml:space="preserve">text</t>
         </is>
       </c>
-      <c r="G43" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="G43" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UK1構成</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
@@ -3546,37 +3546,37 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">冪等キー</t>
+          <t xml:space="preserve">同期状態</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">idempotency_key</t>
+          <t xml:space="preserve">sync_status</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">uuid</t>
-        </is>
-      </c>
-      <c r="G44" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UK2構成</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">YES</t>
+          <t xml:space="preserve">NO</t>
         </is>
       </c>
       <c r="I44" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">local</t>
         </is>
       </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">local / pending / synced / error</t>
         </is>
       </c>
       <c r="K44" s="4" t="inlineStr">
@@ -3603,17 +3603,17 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部更新日時</t>
+          <t xml:space="preserve">同期エラー</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">external_updated_at</t>
+          <t xml:space="preserve">sync_error</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">timestamptz</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr">
@@ -3660,32 +3660,32 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">作成日時</t>
+          <t xml:space="preserve">冪等キー</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">created_at</t>
+          <t xml:space="preserve">idempotency_key</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">timestamptz</t>
-        </is>
-      </c>
-      <c r="G46" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">uuid</t>
+        </is>
+      </c>
+      <c r="G46" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UK2構成</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO</t>
+          <t xml:space="preserve">YES</t>
         </is>
       </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">now()</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J46" s="4" t="inlineStr">
@@ -3717,12 +3717,12 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">更新日時</t>
+          <t xml:space="preserve">外部更新日時</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">updated_at</t>
+          <t xml:space="preserve">external_updated_at</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
@@ -3737,12 +3737,12 @@
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO</t>
+          <t xml:space="preserve">YES</t>
         </is>
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">now()</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J47" s="4" t="inlineStr">
@@ -3764,32 +3764,32 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文明細</t>
+          <t xml:space="preserve">患者注文</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_order_items</t>
+          <t xml:space="preserve">patient_orders</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文明細ID</t>
+          <t xml:space="preserve">作成日時</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">created_at</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">uuid</t>
-        </is>
-      </c>
-      <c r="G48" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PK</t>
+          <t xml:space="preserve">timestamptz</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
@@ -3799,7 +3799,7 @@
       </c>
       <c r="I48" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">gen_random_uuid()</t>
+          <t xml:space="preserve">now()</t>
         </is>
       </c>
       <c r="J48" s="4" t="inlineStr">
@@ -3821,32 +3821,32 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文明細</t>
+          <t xml:space="preserve">患者注文</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_order_items</t>
+          <t xml:space="preserve">patient_orders</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">内部注文ID</t>
+          <t xml:space="preserve">更新日時</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">order_id</t>
+          <t xml:space="preserve">updated_at</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">uuid</t>
-        </is>
-      </c>
-      <c r="G49" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FK</t>
+          <t xml:space="preserve">timestamptz</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
@@ -3856,12 +3856,12 @@
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">now()</t>
         </is>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders.id ON DELETE CASCADE</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K49" s="4" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">商品ID</t>
+          <t xml:space="preserve">注文明細ID</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">product_id</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
@@ -3901,24 +3901,24 @@
           <t xml:space="preserve">uuid</t>
         </is>
       </c>
-      <c r="G50" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FK</t>
+      <c r="G50" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">YES</t>
+          <t xml:space="preserve">NO</t>
         </is>
       </c>
       <c r="I50" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">gen_random_uuid()</t>
         </is>
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">products.id ON DELETE SET NULL</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K50" s="4" t="inlineStr">
@@ -3945,22 +3945,22 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文時商品名</t>
+          <t xml:space="preserve">内部注文ID</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">product_name</t>
+          <t xml:space="preserve">order_id</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="G51" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">uuid</t>
+        </is>
+      </c>
+      <c r="G51" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
@@ -3975,7 +3975,7 @@
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">patient_orders.id ON DELETE CASCADE</t>
         </is>
       </c>
       <c r="K51" s="4" t="inlineStr">
@@ -4002,27 +4002,27 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文時単価</t>
+          <t xml:space="preserve">商品ID</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">unit_price</t>
+          <t xml:space="preserve">product_id</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">integer</t>
-        </is>
-      </c>
-      <c r="G52" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">uuid</t>
+        </is>
+      </c>
+      <c r="G52" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO</t>
+          <t xml:space="preserve">YES</t>
         </is>
       </c>
       <c r="I52" s="4" t="inlineStr">
@@ -4032,7 +4032,7 @@
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">&gt;= 0</t>
+          <t xml:space="preserve">products.id ON DELETE SET NULL</t>
         </is>
       </c>
       <c r="K52" s="4" t="inlineStr">
@@ -4059,17 +4059,17 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">数量</t>
+          <t xml:space="preserve">注文時商品名</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">quantity</t>
+          <t xml:space="preserve">product_name</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">integer</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">&gt; 0</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K53" s="4" t="inlineStr">
@@ -4116,17 +4116,17 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">単位スナップショット</t>
+          <t xml:space="preserve">注文時単価</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">unit_snapshot</t>
+          <t xml:space="preserve">unit_price</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">integer</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">YES</t>
+          <t xml:space="preserve">NO</t>
         </is>
       </c>
       <c r="I54" s="4" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">&gt;= 0</t>
         </is>
       </c>
       <c r="K54" s="4" t="inlineStr">
@@ -4173,17 +4173,17 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">画像種別スナップショット</t>
+          <t xml:space="preserve">数量</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">image_type_snapshot</t>
+          <t xml:space="preserve">quantity</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">integer</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="I55" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">supplement</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">supplement / yogurt / toothbrush / oral</t>
+          <t xml:space="preserve">&gt; 0</t>
         </is>
       </c>
       <c r="K55" s="4" t="inlineStr">
@@ -4230,12 +4230,12 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">画像URLスナップショット</t>
+          <t xml:space="preserve">単位スナップショット</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">image_url_snapshot</t>
+          <t xml:space="preserve">unit_snapshot</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
@@ -4287,12 +4287,12 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">用量スナップショット</t>
+          <t xml:space="preserve">画像種別スナップショット</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">daily_amount_snapshot</t>
+          <t xml:space="preserve">image_type_snapshot</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
@@ -4307,17 +4307,17 @@
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">YES</t>
+          <t xml:space="preserve">NO</t>
         </is>
       </c>
       <c r="I57" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">supplement</t>
         </is>
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">supplement / yogurt / toothbrush / oral</t>
         </is>
       </c>
       <c r="K57" s="4" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">内容量スナップショット</t>
+          <t xml:space="preserve">画像URLスナップショット</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">volume_snapshot</t>
+          <t xml:space="preserve">image_url_snapshot</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注意事項スナップショット</t>
+          <t xml:space="preserve">用量スナップショット</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">caution_snapshot</t>
+          <t xml:space="preserve">daily_amount_snapshot</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部明細ID</t>
+          <t xml:space="preserve">内容量スナップショット</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">external_line_item_id</t>
+          <t xml:space="preserve">volume_snapshot</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
@@ -4515,17 +4515,17 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">作成日時</t>
+          <t xml:space="preserve">注意事項スナップショット</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">created_at</t>
+          <t xml:space="preserve">caution_snapshot</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">timestamptz</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="G61" s="4" t="inlineStr">
@@ -4535,12 +4535,12 @@
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO</t>
+          <t xml:space="preserve">YES</t>
         </is>
       </c>
       <c r="I61" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">now()</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J61" s="4" t="inlineStr">
@@ -4562,42 +4562,42 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">送り先マスタ</t>
+          <t xml:space="preserve">患者注文明細</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery_destinations</t>
+          <t xml:space="preserve">patient_order_items</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">送り先ID</t>
+          <t xml:space="preserve">外部明細ID</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">external_line_item_id</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">uuid</t>
-        </is>
-      </c>
-      <c r="G62" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PK</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G62" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO</t>
+          <t xml:space="preserve">YES</t>
         </is>
       </c>
       <c r="I62" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">gen_random_uuid()</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J62" s="4" t="inlineStr">
@@ -4619,47 +4619,47 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">送り先マスタ</t>
+          <t xml:space="preserve">患者注文明細</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery_destinations</t>
+          <t xml:space="preserve">patient_order_items</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院得意先コード</t>
+          <t xml:space="preserve">作成日時</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_customer_code</t>
+          <t xml:space="preserve">created_at</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="G63" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FK</t>
+          <t xml:space="preserve">timestamptz</t>
+        </is>
+      </c>
+      <c r="G63" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">YES</t>
+          <t xml:space="preserve">NO</t>
         </is>
       </c>
       <c r="I63" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">now()</t>
         </is>
       </c>
       <c r="J63" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinics.customer_code ON DELETE RESTRICT</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K63" s="4" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者ID</t>
+          <t xml:space="preserve">送り先ID</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_id</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
@@ -4699,24 +4699,24 @@
           <t xml:space="preserve">uuid</t>
         </is>
       </c>
-      <c r="G64" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FK</t>
+      <c r="G64" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">YES</t>
+          <t xml:space="preserve">NO</t>
         </is>
       </c>
       <c r="I64" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">gen_random_uuid()</t>
         </is>
       </c>
       <c r="J64" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patients.id ON DELETE RESTRICT</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K64" s="4" t="inlineStr">
@@ -4743,12 +4743,12 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">送り先名</t>
+          <t xml:space="preserve">医院得意先コード</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">label</t>
+          <t xml:space="preserve">clinic_customer_code</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
@@ -4756,14 +4756,14 @@
           <t xml:space="preserve">text</t>
         </is>
       </c>
-      <c r="G65" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="G65" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO</t>
+          <t xml:space="preserve">YES</t>
         </is>
       </c>
       <c r="I65" s="4" t="inlineStr">
@@ -4773,7 +4773,7 @@
       </c>
       <c r="J65" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1〜50文字</t>
+          <t xml:space="preserve">clinics.customer_code ON DELETE RESTRICT</t>
         </is>
       </c>
       <c r="K65" s="4" t="inlineStr">
@@ -4800,27 +4800,27 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">郵便番号</t>
+          <t xml:space="preserve">患者ID</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">postal_code</t>
+          <t xml:space="preserve">patient_id</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="G66" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">uuid</t>
+        </is>
+      </c>
+      <c r="G66" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO</t>
+          <t xml:space="preserve">YES</t>
         </is>
       </c>
       <c r="I66" s="4" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="J66" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">^[0-9]{3}-[0-9]{4}$</t>
+          <t xml:space="preserve">patients.id ON DELETE RESTRICT</t>
         </is>
       </c>
       <c r="K66" s="4" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">都道府県</t>
+          <t xml:space="preserve">送り先名</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">prefecture</t>
+          <t xml:space="preserve">label</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
@@ -4887,7 +4887,7 @@
       </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2〜4文字</t>
+          <t xml:space="preserve">1〜50文字</t>
         </is>
       </c>
       <c r="K67" s="4" t="inlineStr">
@@ -4914,12 +4914,12 @@
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">市区町村</t>
+          <t xml:space="preserve">郵便番号</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">city</t>
+          <t xml:space="preserve">postal_code</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="J68" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1〜100文字</t>
+          <t xml:space="preserve">^[0-9]{3}-[0-9]{4}$</t>
         </is>
       </c>
       <c r="K68" s="4" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">住所1</t>
+          <t xml:space="preserve">都道府県</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">address_line1</t>
+          <t xml:space="preserve">prefecture</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1〜200文字</t>
+          <t xml:space="preserve">2〜4文字</t>
         </is>
       </c>
       <c r="K69" s="4" t="inlineStr">
@@ -5028,12 +5028,12 @@
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">住所2</t>
+          <t xml:space="preserve">市区町村</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">address_line2</t>
+          <t xml:space="preserve">city</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
@@ -5048,7 +5048,7 @@
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">YES</t>
+          <t xml:space="preserve">NO</t>
         </is>
       </c>
       <c r="I70" s="4" t="inlineStr">
@@ -5058,7 +5058,7 @@
       </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">200文字以内</t>
+          <t xml:space="preserve">1〜100文字</t>
         </is>
       </c>
       <c r="K70" s="4" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">受取人名</t>
+          <t xml:space="preserve">住所1</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">recipient_name</t>
+          <t xml:space="preserve">address_line1</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
@@ -5115,7 +5115,7 @@
       </c>
       <c r="J71" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1〜100文字</t>
+          <t xml:space="preserve">1〜200文字</t>
         </is>
       </c>
       <c r="K71" s="4" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">電話番号</t>
+          <t xml:space="preserve">住所2</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">phone</t>
+          <t xml:space="preserve">address_line2</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
@@ -5162,7 +5162,7 @@
       </c>
       <c r="H72" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO</t>
+          <t xml:space="preserve">YES</t>
         </is>
       </c>
       <c r="I72" s="4" t="inlineStr">
@@ -5172,7 +5172,7 @@
       </c>
       <c r="J72" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">数字10〜15桁</t>
+          <t xml:space="preserve">200文字以内</t>
         </is>
       </c>
       <c r="K72" s="4" t="inlineStr">
@@ -5199,17 +5199,17 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">既定</t>
+          <t xml:space="preserve">受取人名</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">is_default</t>
+          <t xml:space="preserve">recipient_name</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">boolean</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr">
@@ -5224,12 +5224,12 @@
       </c>
       <c r="I73" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J73" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">1〜100文字</t>
         </is>
       </c>
       <c r="K73" s="4" t="inlineStr">
@@ -5256,17 +5256,17 @@
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">削除日時</t>
+          <t xml:space="preserve">電話番号</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">deleted_at</t>
+          <t xml:space="preserve">phone</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">timestamptz</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr">
@@ -5276,7 +5276,7 @@
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">YES</t>
+          <t xml:space="preserve">NO</t>
         </is>
       </c>
       <c r="I74" s="4" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="J74" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">数字10〜15桁</t>
         </is>
       </c>
       <c r="K74" s="4" t="inlineStr">
@@ -5313,17 +5313,17 @@
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">作成日時</t>
+          <t xml:space="preserve">既定</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">created_at</t>
+          <t xml:space="preserve">is_default</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">timestamptz</t>
+          <t xml:space="preserve">boolean</t>
         </is>
       </c>
       <c r="G75" s="4" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="I75" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">now()</t>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="J75" s="4" t="inlineStr">
@@ -5370,12 +5370,12 @@
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">更新日時</t>
+          <t xml:space="preserve">削除日時</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">updated_at</t>
+          <t xml:space="preserve">deleted_at</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
@@ -5390,12 +5390,12 @@
       </c>
       <c r="H76" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO</t>
+          <t xml:space="preserve">YES</t>
         </is>
       </c>
       <c r="I76" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">now()</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J76" s="4" t="inlineStr">
@@ -5417,32 +5417,32 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文配送先</t>
+          <t xml:space="preserve">送り先マスタ</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">order_delivery_destinations</t>
+          <t xml:space="preserve">delivery_destinations</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">内部注文ID</t>
+          <t xml:space="preserve">作成日時</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">order_id</t>
+          <t xml:space="preserve">created_at</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">uuid</t>
-        </is>
-      </c>
-      <c r="G77" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PK / FK</t>
+          <t xml:space="preserve">timestamptz</t>
+        </is>
+      </c>
+      <c r="G77" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr">
@@ -5452,12 +5452,12 @@
       </c>
       <c r="I77" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">now()</t>
         </is>
       </c>
       <c r="J77" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders.id ON DELETE CASCADE</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K77" s="4" t="inlineStr">
@@ -5474,32 +5474,32 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文配送先</t>
+          <t xml:space="preserve">送り先マスタ</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">order_delivery_destinations</t>
+          <t xml:space="preserve">delivery_destinations</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">送り先ID</t>
+          <t xml:space="preserve">更新日時</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery_destination_id</t>
+          <t xml:space="preserve">updated_at</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">uuid</t>
-        </is>
-      </c>
-      <c r="G78" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FK</t>
+          <t xml:space="preserve">timestamptz</t>
+        </is>
+      </c>
+      <c r="G78" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr">
@@ -5509,12 +5509,12 @@
       </c>
       <c r="I78" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">now()</t>
         </is>
       </c>
       <c r="J78" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery_destinations.id ON DELETE RESTRICT</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K78" s="4" t="inlineStr">
@@ -5541,22 +5541,22 @@
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">送り先名</t>
+          <t xml:space="preserve">内部注文ID</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">label</t>
+          <t xml:space="preserve">order_id</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="G79" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">uuid</t>
+        </is>
+      </c>
+      <c r="G79" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK / FK</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="J79" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">patient_orders.id ON DELETE CASCADE</t>
         </is>
       </c>
       <c r="K79" s="4" t="inlineStr">
@@ -5598,22 +5598,22 @@
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">郵便番号</t>
+          <t xml:space="preserve">送り先ID</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">postal_code</t>
+          <t xml:space="preserve">delivery_destination_id</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="G80" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">uuid</t>
+        </is>
+      </c>
+      <c r="G80" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="J80" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">delivery_destinations.id ON DELETE RESTRICT</t>
         </is>
       </c>
       <c r="K80" s="4" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">都道府県</t>
+          <t xml:space="preserve">送り先名</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">prefecture</t>
+          <t xml:space="preserve">label</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
@@ -5712,12 +5712,12 @@
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">市区町村</t>
+          <t xml:space="preserve">郵便番号</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">city</t>
+          <t xml:space="preserve">postal_code</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">住所1</t>
+          <t xml:space="preserve">都道府県</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">address_line1</t>
+          <t xml:space="preserve">prefecture</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
@@ -5826,12 +5826,12 @@
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">住所2</t>
+          <t xml:space="preserve">市区町村</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">address_line2</t>
+          <t xml:space="preserve">city</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
@@ -5846,7 +5846,7 @@
       </c>
       <c r="H84" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">YES</t>
+          <t xml:space="preserve">NO</t>
         </is>
       </c>
       <c r="I84" s="4" t="inlineStr">
@@ -5883,12 +5883,12 @@
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">受取人名</t>
+          <t xml:space="preserve">住所1</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">recipient_name</t>
+          <t xml:space="preserve">address_line1</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">電話番号</t>
+          <t xml:space="preserve">住所2</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">phone</t>
+          <t xml:space="preserve">address_line2</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
@@ -5960,7 +5960,7 @@
       </c>
       <c r="H86" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO</t>
+          <t xml:space="preserve">YES</t>
         </is>
       </c>
       <c r="I86" s="4" t="inlineStr">
@@ -5997,17 +5997,17 @@
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">作成日時</t>
+          <t xml:space="preserve">受取人名</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">created_at</t>
+          <t xml:space="preserve">recipient_name</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">timestamptz</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="G87" s="4" t="inlineStr">
@@ -6022,7 +6022,7 @@
       </c>
       <c r="I87" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">now()</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J87" s="4" t="inlineStr">
@@ -6044,32 +6044,32 @@
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文操作履歴</t>
+          <t xml:space="preserve">注文配送先</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_order_events</t>
+          <t xml:space="preserve">order_delivery_destinations</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">イベントID</t>
+          <t xml:space="preserve">電話番号</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">phone</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">uuid</t>
-        </is>
-      </c>
-      <c r="G88" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PK</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G88" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H88" s="4" t="inlineStr">
@@ -6079,7 +6079,7 @@
       </c>
       <c r="I88" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">gen_random_uuid()</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J88" s="4" t="inlineStr">
@@ -6101,32 +6101,32 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文操作履歴</t>
+          <t xml:space="preserve">注文配送先</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_order_events</t>
+          <t xml:space="preserve">order_delivery_destinations</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">内部注文ID</t>
+          <t xml:space="preserve">作成日時</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">order_id</t>
+          <t xml:space="preserve">created_at</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">uuid</t>
-        </is>
-      </c>
-      <c r="G89" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FK</t>
+          <t xml:space="preserve">timestamptz</t>
+        </is>
+      </c>
+      <c r="G89" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="I89" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">now()</t>
         </is>
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders.id ON DELETE CASCADE</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K89" s="4" t="inlineStr">
@@ -6168,22 +6168,22 @@
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">イベント種別</t>
+          <t xml:space="preserve">イベントID</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">event_type</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="G90" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">uuid</t>
+        </is>
+      </c>
+      <c r="G90" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK</t>
         </is>
       </c>
       <c r="H90" s="4" t="inlineStr">
@@ -6193,7 +6193,7 @@
       </c>
       <c r="I90" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">gen_random_uuid()</t>
         </is>
       </c>
       <c r="J90" s="4" t="inlineStr">
@@ -6225,22 +6225,22 @@
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">操作者種別</t>
+          <t xml:space="preserve">内部注文ID</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">actor_type</t>
+          <t xml:space="preserve">order_id</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="G91" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">uuid</t>
+        </is>
+      </c>
+      <c r="G91" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr">
@@ -6255,7 +6255,7 @@
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">patient_orders.id ON DELETE CASCADE</t>
         </is>
       </c>
       <c r="K91" s="4" t="inlineStr">
@@ -6282,12 +6282,12 @@
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">操作者識別子</t>
+          <t xml:space="preserve">イベント種別</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">actor_identifier</t>
+          <t xml:space="preserve">event_type</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
@@ -6339,12 +6339,12 @@
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">変更前状態</t>
+          <t xml:space="preserve">操作者種別</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">from_status</t>
+          <t xml:space="preserve">actor_type</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
@@ -6359,7 +6359,7 @@
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">YES</t>
+          <t xml:space="preserve">NO</t>
         </is>
       </c>
       <c r="I93" s="4" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">変更後状態</t>
+          <t xml:space="preserve">操作者識別子</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">to_status</t>
+          <t xml:space="preserve">actor_identifier</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="H94" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">YES</t>
+          <t xml:space="preserve">NO</t>
         </is>
       </c>
       <c r="I94" s="4" t="inlineStr">
@@ -6453,40 +6453,154 @@
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">変更前状態</t>
+        </is>
+      </c>
+      <c r="E95" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">from_status</t>
+        </is>
+      </c>
+      <c r="F95" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G95" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H95" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YES</t>
+        </is>
+      </c>
+      <c r="I95" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J95" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K95" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="30" customHeight="1">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B96" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">注文操作履歴</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_order_events</t>
+        </is>
+      </c>
+      <c r="D96" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">変更後状態</t>
+        </is>
+      </c>
+      <c r="E96" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">to_status</t>
+        </is>
+      </c>
+      <c r="F96" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G96" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H96" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YES</t>
+        </is>
+      </c>
+      <c r="I96" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J96" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K96" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="30" customHeight="1">
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">注文操作履歴</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_order_events</t>
+        </is>
+      </c>
+      <c r="D97" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">発生日時</t>
         </is>
       </c>
-      <c r="E95" s="4" t="inlineStr">
+      <c r="E97" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">created_at</t>
         </is>
       </c>
-      <c r="F95" s="4" t="inlineStr">
+      <c r="F97" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">timestamptz</t>
         </is>
       </c>
-      <c r="G95" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H95" s="4" t="inlineStr">
+      <c r="G97" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H97" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">NO</t>
         </is>
       </c>
-      <c r="I95" s="4" t="inlineStr">
+      <c r="I97" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">now()</t>
         </is>
       </c>
-      <c r="J95" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="K95" s="4" t="inlineStr">
+      <c r="J97" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K97" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -6497,7 +6611,7 @@
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A2:K2"/>
   </mergeCells>
-  <autoFilter ref="A4:K95"/>
+  <autoFilter ref="A4:K97"/>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0" paperSize="9"/>
 </worksheet>
@@ -13682,7 +13796,7 @@
     <row r="64">
       <c r="A64" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院価格</t>
+          <t xml:space="preserve">医院通常価格</t>
         </is>
       </c>
       <c r="C64" s="11" t="inlineStr">
@@ -13691,6 +13805,40 @@
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3ヶ月価格</t>
+        </is>
+      </c>
+      <c r="C65" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">subscription_3_month_price</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6ヶ月価格</t>
+        </is>
+      </c>
+      <c r="C66" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">subscription_6_month_price</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -14185,7 +14333,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="131">
+  <mergeCells count="135">
     <mergeCell ref="A1:Q1"/>
     <mergeCell ref="A2:Q2"/>
     <mergeCell ref="A4:E5"/>
@@ -14315,6 +14463,10 @@
     <mergeCell ref="C63:D63"/>
     <mergeCell ref="A64:B64"/>
     <mergeCell ref="C64:D64"/>
+    <mergeCell ref="A65:B65"/>
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="A66:B66"/>
+    <mergeCell ref="C66:D66"/>
     <mergeCell ref="B26:J27"/>
     <mergeCell ref="A72:Q72"/>
   </mergeCells>
@@ -16266,12 +16418,12 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院価格と注文時商品画像を運用する。</t>
+          <t xml:space="preserve">医院通常・期間別価格と注文時商品画像を運用する。</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">仕切値は導出し、重複保存しない。</t>
+          <t xml:space="preserve">仕切値と価格既定値は重複保存しない。</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">

--- a/project_clinic_order_management_db_definition.xlsx
+++ b/project_clinic_order_management_db_definition.xlsx
@@ -254,7 +254,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-22</t>
+          <t xml:space="preserve">2026-07-23</t>
         </is>
       </c>
     </row>
@@ -266,7 +266,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院が患者向け商品を管理するpatient_orders系列</t>
+          <t xml:space="preserve">医院が患者向け商品を管理するpatient_orders系列、およびウェビナー管理</t>
         </is>
       </c>
     </row>
@@ -290,7 +290,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supabaseのpatient_orders / patient_order_items / delivery_destinations / order_delivery_destinations / patient_order_events</t>
+          <t xml:space="preserve">Supabaseの患者注文・定期購入申込・送り先・ウェビナー各テーブル</t>
         </is>
       </c>
     </row>
@@ -476,7 +476,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -856,27 +856,27 @@
     <row r="15" ht="34" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shopify接続</t>
+          <t xml:space="preserve">現行</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部コマース接続</t>
+          <t xml:space="preserve">定期購入申込</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_accounts</t>
+          <t xml:space="preserve">patient_subscription_requests</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">将来案</t>
+          <t xml:space="preserve">実装済み</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shopifyストア等の外部接続先。医院との対応方式は接続構成確定後に決定する。</t>
+          <t xml:space="preserve">患者が送信しBGJが審査する申込。Shopify契約・実受注とは分離する。</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -888,27 +888,27 @@
     <row r="16" ht="34" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shopify接続</t>
+          <t xml:space="preserve">現行</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文拡張</t>
+          <t xml:space="preserve">定期購入申込明細</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders</t>
+          <t xml:space="preserve">patient_subscription_request_items</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">既存テーブル拡張案</t>
+          <t xml:space="preserve">実装済み</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">既存IDを維持し、外部・金額・排他制御の列を追加する。</t>
+          <t xml:space="preserve">申込時点の商品名・期間別月額・画像と数量を保存する。</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -920,27 +920,27 @@
     <row r="17" ht="34" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shopify接続</t>
+          <t xml:space="preserve">現行</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文明細拡張</t>
+          <t xml:space="preserve">定期購入申込配送先</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_order_items</t>
+          <t xml:space="preserve">patient_subscription_request_destinations</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">既存テーブル拡張案</t>
+          <t xml:space="preserve">実装済み</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部明細と通貨を明確化し、既存スナップショットを維持する。</t>
+          <t xml:space="preserve">申込時点の医院または患者送り先を1対1で不変保存する。</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -952,27 +952,27 @@
     <row r="18" ht="34" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">決済接続</t>
+          <t xml:space="preserve">現行</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">決済返金投影</t>
+          <t xml:space="preserve">定期購入申込履歴</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">order_transaction_projections</t>
+          <t xml:space="preserve">patient_subscription_request_events</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">将来案</t>
+          <t xml:space="preserve">実装済み</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shopify上の決済・返金を表示する投影。会計台帳ではない。</t>
+          <t xml:space="preserve">申込・承認・却下・取消の操作者、変更前後、理由を監査保存する。</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -984,27 +984,27 @@
     <row r="19" ht="34" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">配送開始</t>
+          <t xml:space="preserve">現行</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">受取配送</t>
+          <t xml:space="preserve">ウェビナー</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_fulfillments</t>
+          <t xml:space="preserve">webinars</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">将来案</t>
+          <t xml:space="preserve">実装済み・Phase 1</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院受け取り・配送・部分引き渡しの単位。</t>
+          <t xml:space="preserve">BGJが管理するプロバイダー非依存のウェビナー本体。</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
@@ -1016,27 +1016,27 @@
     <row r="20" ht="34" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">配送開始</t>
+          <t xml:space="preserve">現行</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">受取配送明細</t>
+          <t xml:space="preserve">ウェビナー開催枠</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_fulfillment_items</t>
+          <t xml:space="preserve">webinar_sessions</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">将来案</t>
+          <t xml:space="preserve">実装済み・Phase 1</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">部分受け取り・部分配送時の対象明細と数量。</t>
+          <t xml:space="preserve">開催日時、Google Meet／Zoomと参加URLを本体から分離する。</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -1048,27 +1048,27 @@
     <row r="21" ht="34" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">定期購入接続</t>
+          <t xml:space="preserve">現行</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者定期購入</t>
+          <t xml:space="preserve">ウェビナー対象医院</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_subscriptions</t>
+          <t xml:space="preserve">webinar_target_clinics</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">将来案</t>
+          <t xml:space="preserve">実装済み・Phase 1</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shopify上の定期購入契約を患者ポータルへ表示する投影。</t>
+          <t xml:space="preserve">公開対象となる医院をウェビナーとの多対多中間表で管理する。</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
@@ -1080,27 +1080,27 @@
     <row r="22" ht="34" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">定期購入接続</t>
+          <t xml:space="preserve">現行</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">定期購入明細</t>
+          <t xml:space="preserve">ウェビナー操作履歴</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_subscription_items</t>
+          <t xml:space="preserve">webinar_events</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">将来案</t>
+          <t xml:space="preserve">実装済み・Phase 1</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">契約時点の商品・数量・単価の投影。</t>
+          <t xml:space="preserve">作成・編集・公開・中止を監査保存する。</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -1117,12 +1117,12 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部受信イベント</t>
+          <t xml:space="preserve">外部コマース接続</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_webhook_events</t>
+          <t xml:space="preserve">commerce_accounts</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Webhookを先に永続化し、重複排除・再試行するInbox。</t>
+          <t xml:space="preserve">Shopifyストア等の外部接続先。医院との対応方式は接続構成確定後に決定する。</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -1149,57 +1149,313 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">患者注文拡張</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_orders</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">既存テーブル拡張案</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">既存IDを維持し、外部・金額・排他制御の列を追加する。</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="34" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shopify接続</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">患者注文明細拡張</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_order_items</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">既存テーブル拡張案</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">外部明細と通貨を明確化し、既存スナップショットを維持する。</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="34" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">決済接続</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">決済返金投影</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">order_transaction_projections</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">将来案</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shopify上の決済・返金を表示する投影。会計台帳ではない。</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="34" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">配送開始</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">受取配送</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_fulfillments</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">将来案</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">医院受け取り・配送・部分引き渡しの単位。</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="34" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">配送開始</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">受取配送明細</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_fulfillment_items</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">将来案</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">部分受け取り・部分配送時の対象明細と数量。</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="34" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">定期購入接続</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">患者定期購入</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscriptions</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">将来案</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shopify上の定期購入契約を患者ポータルへ表示する投影。</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="34" customHeight="1">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">定期購入接続</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">定期購入明細</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscription_items</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">将来案</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">契約時点の商品・数量・単価の投影。</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="34" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shopify接続</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">外部受信イベント</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">commerce_webhook_events</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">将来案</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Webhookを先に永続化し、重複排除・再試行するInbox。</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="34" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shopify接続</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">外部送信キュー</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">commerce_outbox</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D32" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">将来案</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="E32" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">外部APIへ送る処理を永続化するOutbox。</t>
         </is>
       </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="8" t="inlineStr">
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">別ドメイン</t>
         </is>
       </c>
-      <c r="B25" s="8" t="inlineStr">
+      <c r="B33" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">医院仕入注文</t>
         </is>
       </c>
-      <c r="C25" s="8" t="inlineStr">
+      <c r="C33" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">clinic_orders</t>
         </is>
       </c>
-      <c r="D25" s="8" t="inlineStr">
+      <c r="D33" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">実装済み</t>
         </is>
       </c>
-      <c r="E25" s="8" t="inlineStr">
+      <c r="E33" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">BGJから医院へのB2B仕入・売上履歴</t>
         </is>
       </c>
-      <c r="F25" s="8" t="inlineStr">
+      <c r="F33" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">患者注文系列へ統合しない</t>
         </is>
@@ -1210,7 +1466,7 @@
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
   </mergeCells>
-  <autoFilter ref="A4:F25"/>
+  <autoFilter ref="A4:F33"/>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0" paperSize="9"/>
 </worksheet>
@@ -1218,7 +1474,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K97"/>
+  <dimension ref="A1:K169"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -6606,12 +6862,4116 @@
         </is>
       </c>
     </row>
+    <row r="98" ht="30" customHeight="1">
+      <c r="A98" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B98" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">定期購入申込</t>
+        </is>
+      </c>
+      <c r="C98" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscription_requests</t>
+        </is>
+      </c>
+      <c r="D98" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">申込ID</t>
+        </is>
+      </c>
+      <c r="E98" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">id</t>
+        </is>
+      </c>
+      <c r="F98" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">uuid</t>
+        </is>
+      </c>
+      <c r="G98" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK</t>
+        </is>
+      </c>
+      <c r="H98" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I98" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gen_random_uuid()</t>
+        </is>
+      </c>
+      <c r="J98" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K98" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="30" customHeight="1">
+      <c r="A99" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">定期購入申込</t>
+        </is>
+      </c>
+      <c r="C99" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscription_requests</t>
+        </is>
+      </c>
+      <c r="D99" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">申込番号</t>
+        </is>
+      </c>
+      <c r="E99" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">request_number</t>
+        </is>
+      </c>
+      <c r="F99" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bigint</t>
+        </is>
+      </c>
+      <c r="G99" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UK</t>
+        </is>
+      </c>
+      <c r="H99" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I99" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">identity</t>
+        </is>
+      </c>
+      <c r="J99" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K99" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="30" customHeight="1">
+      <c r="A100" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B100" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">定期購入申込</t>
+        </is>
+      </c>
+      <c r="C100" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscription_requests</t>
+        </is>
+      </c>
+      <c r="D100" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">得意先コード</t>
+        </is>
+      </c>
+      <c r="E100" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">customer_code</t>
+        </is>
+      </c>
+      <c r="F100" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G100" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK / UK2構成</t>
+        </is>
+      </c>
+      <c r="H100" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I100" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J100" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinics.customer_code ON DELETE RESTRICT</t>
+        </is>
+      </c>
+      <c r="K100" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="30" customHeight="1">
+      <c r="A101" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B101" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">定期購入申込</t>
+        </is>
+      </c>
+      <c r="C101" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscription_requests</t>
+        </is>
+      </c>
+      <c r="D101" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">患者ID</t>
+        </is>
+      </c>
+      <c r="E101" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_id</t>
+        </is>
+      </c>
+      <c r="F101" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">uuid</t>
+        </is>
+      </c>
+      <c r="G101" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
+        </is>
+      </c>
+      <c r="H101" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I101" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J101" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patients.id ON DELETE RESTRICT</t>
+        </is>
+      </c>
+      <c r="K101" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="30" customHeight="1">
+      <c r="A102" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B102" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">定期購入申込</t>
+        </is>
+      </c>
+      <c r="C102" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscription_requests</t>
+        </is>
+      </c>
+      <c r="D102" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">契約期間月数</t>
+        </is>
+      </c>
+      <c r="E102" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">term_months</t>
+        </is>
+      </c>
+      <c r="F102" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">smallint</t>
+        </is>
+      </c>
+      <c r="G102" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H102" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I102" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J102" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3 / 6</t>
+        </is>
+      </c>
+      <c r="K102" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="30" customHeight="1">
+      <c r="A103" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B103" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">定期購入申込</t>
+        </is>
+      </c>
+      <c r="C103" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscription_requests</t>
+        </is>
+      </c>
+      <c r="D103" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">受け取り方法</t>
+        </is>
+      </c>
+      <c r="E103" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fulfillment_method</t>
+        </is>
+      </c>
+      <c r="F103" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G103" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H103" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I103" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J103" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pickup / delivery</t>
+        </is>
+      </c>
+      <c r="K103" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="30" customHeight="1">
+      <c r="A104" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B104" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">定期購入申込</t>
+        </is>
+      </c>
+      <c r="C104" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscription_requests</t>
+        </is>
+      </c>
+      <c r="D104" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">申込状態</t>
+        </is>
+      </c>
+      <c r="E104" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">status</t>
+        </is>
+      </c>
+      <c r="F104" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G104" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H104" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I104" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">submitted</t>
+        </is>
+      </c>
+      <c r="J104" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">submitted / approved / rejected / canceled</t>
+        </is>
+      </c>
+      <c r="K104" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="30" customHeight="1">
+      <c r="A105" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B105" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">定期購入申込</t>
+        </is>
+      </c>
+      <c r="C105" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscription_requests</t>
+        </is>
+      </c>
+      <c r="D105" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">冪等キー</t>
+        </is>
+      </c>
+      <c r="E105" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">idempotency_key</t>
+        </is>
+      </c>
+      <c r="F105" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">uuid</t>
+        </is>
+      </c>
+      <c r="G105" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UK2構成</t>
+        </is>
+      </c>
+      <c r="H105" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I105" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J105" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K105" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="30" customHeight="1">
+      <c r="A106" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B106" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">定期購入申込</t>
+        </is>
+      </c>
+      <c r="C106" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscription_requests</t>
+        </is>
+      </c>
+      <c r="D106" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">排他バージョン</t>
+        </is>
+      </c>
+      <c r="E106" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">version</t>
+        </is>
+      </c>
+      <c r="F106" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">integer</t>
+        </is>
+      </c>
+      <c r="G106" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H106" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I106" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="J106" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K106" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="30" customHeight="1">
+      <c r="A107" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B107" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">定期購入申込</t>
+        </is>
+      </c>
+      <c r="C107" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscription_requests</t>
+        </is>
+      </c>
+      <c r="D107" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">申込日時</t>
+        </is>
+      </c>
+      <c r="E107" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">submitted_at</t>
+        </is>
+      </c>
+      <c r="F107" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">timestamptz</t>
+        </is>
+      </c>
+      <c r="G107" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H107" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I107" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">now()</t>
+        </is>
+      </c>
+      <c r="J107" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K107" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="30" customHeight="1">
+      <c r="A108" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B108" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">定期購入申込</t>
+        </is>
+      </c>
+      <c r="C108" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscription_requests</t>
+        </is>
+      </c>
+      <c r="D108" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">審査日時</t>
+        </is>
+      </c>
+      <c r="E108" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reviewed_at</t>
+        </is>
+      </c>
+      <c r="F108" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">timestamptz</t>
+        </is>
+      </c>
+      <c r="G108" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H108" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YES</t>
+        </is>
+      </c>
+      <c r="I108" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J108" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K108" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="30" customHeight="1">
+      <c r="A109" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B109" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">定期購入申込</t>
+        </is>
+      </c>
+      <c r="C109" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscription_requests</t>
+        </is>
+      </c>
+      <c r="D109" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">取消日時</t>
+        </is>
+      </c>
+      <c r="E109" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">canceled_at</t>
+        </is>
+      </c>
+      <c r="F109" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">timestamptz</t>
+        </is>
+      </c>
+      <c r="G109" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H109" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YES</t>
+        </is>
+      </c>
+      <c r="I109" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J109" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K109" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="30" customHeight="1">
+      <c r="A110" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B110" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">定期購入申込</t>
+        </is>
+      </c>
+      <c r="C110" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscription_requests</t>
+        </is>
+      </c>
+      <c r="D110" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">作成日時</t>
+        </is>
+      </c>
+      <c r="E110" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">created_at</t>
+        </is>
+      </c>
+      <c r="F110" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">timestamptz</t>
+        </is>
+      </c>
+      <c r="G110" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H110" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I110" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">now()</t>
+        </is>
+      </c>
+      <c r="J110" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K110" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="30" customHeight="1">
+      <c r="A111" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B111" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">定期購入申込</t>
+        </is>
+      </c>
+      <c r="C111" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscription_requests</t>
+        </is>
+      </c>
+      <c r="D111" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">更新日時</t>
+        </is>
+      </c>
+      <c r="E111" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">updated_at</t>
+        </is>
+      </c>
+      <c r="F111" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">timestamptz</t>
+        </is>
+      </c>
+      <c r="G111" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H111" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I111" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">now()</t>
+        </is>
+      </c>
+      <c r="J111" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K111" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="30" customHeight="1">
+      <c r="A112" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B112" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">定期購入申込明細</t>
+        </is>
+      </c>
+      <c r="C112" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscription_request_items</t>
+        </is>
+      </c>
+      <c r="D112" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明細ID</t>
+        </is>
+      </c>
+      <c r="E112" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">id</t>
+        </is>
+      </c>
+      <c r="F112" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">uuid</t>
+        </is>
+      </c>
+      <c r="G112" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK</t>
+        </is>
+      </c>
+      <c r="H112" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I112" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gen_random_uuid()</t>
+        </is>
+      </c>
+      <c r="J112" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K112" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="30" customHeight="1">
+      <c r="A113" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B113" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">定期購入申込明細</t>
+        </is>
+      </c>
+      <c r="C113" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscription_request_items</t>
+        </is>
+      </c>
+      <c r="D113" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">申込ID</t>
+        </is>
+      </c>
+      <c r="E113" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">request_id</t>
+        </is>
+      </c>
+      <c r="F113" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">uuid</t>
+        </is>
+      </c>
+      <c r="G113" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK / UK1構成</t>
+        </is>
+      </c>
+      <c r="H113" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I113" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J113" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscription_requests.id ON DELETE CASCADE</t>
+        </is>
+      </c>
+      <c r="K113" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="30" customHeight="1">
+      <c r="A114" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B114" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">定期購入申込明細</t>
+        </is>
+      </c>
+      <c r="C114" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscription_request_items</t>
+        </is>
+      </c>
+      <c r="D114" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">商品ID</t>
+        </is>
+      </c>
+      <c r="E114" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">product_id</t>
+        </is>
+      </c>
+      <c r="F114" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">uuid</t>
+        </is>
+      </c>
+      <c r="G114" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK / UK1構成</t>
+        </is>
+      </c>
+      <c r="H114" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YES</t>
+        </is>
+      </c>
+      <c r="I114" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J114" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">products.id ON DELETE SET NULL</t>
+        </is>
+      </c>
+      <c r="K114" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="30" customHeight="1">
+      <c r="A115" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B115" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">定期購入申込明細</t>
+        </is>
+      </c>
+      <c r="C115" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscription_request_items</t>
+        </is>
+      </c>
+      <c r="D115" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">申込時商品名</t>
+        </is>
+      </c>
+      <c r="E115" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">product_name</t>
+        </is>
+      </c>
+      <c r="F115" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G115" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H115" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I115" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J115" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K115" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="30" customHeight="1">
+      <c r="A116" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B116" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">定期購入申込明細</t>
+        </is>
+      </c>
+      <c r="C116" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscription_request_items</t>
+        </is>
+      </c>
+      <c r="D116" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">申込時月額</t>
+        </is>
+      </c>
+      <c r="E116" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unit_price</t>
+        </is>
+      </c>
+      <c r="F116" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">integer</t>
+        </is>
+      </c>
+      <c r="G116" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H116" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I116" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J116" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&gt;= 0</t>
+        </is>
+      </c>
+      <c r="K116" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="30" customHeight="1">
+      <c r="A117" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B117" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">定期購入申込明細</t>
+        </is>
+      </c>
+      <c r="C117" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscription_request_items</t>
+        </is>
+      </c>
+      <c r="D117" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">数量</t>
+        </is>
+      </c>
+      <c r="E117" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">quantity</t>
+        </is>
+      </c>
+      <c r="F117" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">integer</t>
+        </is>
+      </c>
+      <c r="G117" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H117" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I117" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J117" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1〜100</t>
+        </is>
+      </c>
+      <c r="K117" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="30" customHeight="1">
+      <c r="A118" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B118" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">定期購入申込明細</t>
+        </is>
+      </c>
+      <c r="C118" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscription_request_items</t>
+        </is>
+      </c>
+      <c r="D118" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">申込時画像URL</t>
+        </is>
+      </c>
+      <c r="E118" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">image_url_snapshot</t>
+        </is>
+      </c>
+      <c r="F118" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G118" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H118" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YES</t>
+        </is>
+      </c>
+      <c r="I118" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J118" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K118" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="30" customHeight="1">
+      <c r="A119" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B119" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">定期購入申込明細</t>
+        </is>
+      </c>
+      <c r="C119" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscription_request_items</t>
+        </is>
+      </c>
+      <c r="D119" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">作成日時</t>
+        </is>
+      </c>
+      <c r="E119" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">created_at</t>
+        </is>
+      </c>
+      <c r="F119" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">timestamptz</t>
+        </is>
+      </c>
+      <c r="G119" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H119" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I119" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">now()</t>
+        </is>
+      </c>
+      <c r="J119" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K119" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="30" customHeight="1">
+      <c r="A120" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B120" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">定期購入申込配送先</t>
+        </is>
+      </c>
+      <c r="C120" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscription_request_destinations</t>
+        </is>
+      </c>
+      <c r="D120" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">申込ID</t>
+        </is>
+      </c>
+      <c r="E120" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">request_id</t>
+        </is>
+      </c>
+      <c r="F120" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">uuid</t>
+        </is>
+      </c>
+      <c r="G120" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK / FK</t>
+        </is>
+      </c>
+      <c r="H120" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I120" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J120" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscription_requests.id ON DELETE CASCADE</t>
+        </is>
+      </c>
+      <c r="K120" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="30" customHeight="1">
+      <c r="A121" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B121" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">定期購入申込配送先</t>
+        </is>
+      </c>
+      <c r="C121" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscription_request_destinations</t>
+        </is>
+      </c>
+      <c r="D121" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">送り先ID</t>
+        </is>
+      </c>
+      <c r="E121" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">delivery_destination_id</t>
+        </is>
+      </c>
+      <c r="F121" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">uuid</t>
+        </is>
+      </c>
+      <c r="G121" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
+        </is>
+      </c>
+      <c r="H121" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I121" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J121" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">delivery_destinations.id ON DELETE RESTRICT</t>
+        </is>
+      </c>
+      <c r="K121" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="30" customHeight="1">
+      <c r="A122" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B122" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">定期購入申込配送先</t>
+        </is>
+      </c>
+      <c r="C122" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscription_request_destinations</t>
+        </is>
+      </c>
+      <c r="D122" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">送り先名</t>
+        </is>
+      </c>
+      <c r="E122" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">label</t>
+        </is>
+      </c>
+      <c r="F122" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G122" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H122" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I122" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J122" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K122" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="30" customHeight="1">
+      <c r="A123" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B123" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">定期購入申込配送先</t>
+        </is>
+      </c>
+      <c r="C123" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscription_request_destinations</t>
+        </is>
+      </c>
+      <c r="D123" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">郵便番号</t>
+        </is>
+      </c>
+      <c r="E123" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">postal_code</t>
+        </is>
+      </c>
+      <c r="F123" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G123" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H123" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I123" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J123" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K123" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="30" customHeight="1">
+      <c r="A124" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B124" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">定期購入申込配送先</t>
+        </is>
+      </c>
+      <c r="C124" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscription_request_destinations</t>
+        </is>
+      </c>
+      <c r="D124" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">都道府県</t>
+        </is>
+      </c>
+      <c r="E124" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prefecture</t>
+        </is>
+      </c>
+      <c r="F124" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G124" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H124" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I124" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J124" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K124" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="30" customHeight="1">
+      <c r="A125" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B125" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">定期購入申込配送先</t>
+        </is>
+      </c>
+      <c r="C125" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscription_request_destinations</t>
+        </is>
+      </c>
+      <c r="D125" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">市区町村</t>
+        </is>
+      </c>
+      <c r="E125" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">city</t>
+        </is>
+      </c>
+      <c r="F125" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G125" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H125" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I125" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J125" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K125" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="30" customHeight="1">
+      <c r="A126" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B126" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">定期購入申込配送先</t>
+        </is>
+      </c>
+      <c r="C126" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscription_request_destinations</t>
+        </is>
+      </c>
+      <c r="D126" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">住所1</t>
+        </is>
+      </c>
+      <c r="E126" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">address_line1</t>
+        </is>
+      </c>
+      <c r="F126" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G126" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H126" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I126" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J126" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K126" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="30" customHeight="1">
+      <c r="A127" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B127" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">定期購入申込配送先</t>
+        </is>
+      </c>
+      <c r="C127" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscription_request_destinations</t>
+        </is>
+      </c>
+      <c r="D127" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">住所2</t>
+        </is>
+      </c>
+      <c r="E127" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">address_line2</t>
+        </is>
+      </c>
+      <c r="F127" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G127" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H127" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YES</t>
+        </is>
+      </c>
+      <c r="I127" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J127" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K127" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="30" customHeight="1">
+      <c r="A128" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B128" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">定期購入申込配送先</t>
+        </is>
+      </c>
+      <c r="C128" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscription_request_destinations</t>
+        </is>
+      </c>
+      <c r="D128" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">受取人名</t>
+        </is>
+      </c>
+      <c r="E128" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">recipient_name</t>
+        </is>
+      </c>
+      <c r="F128" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G128" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H128" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I128" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J128" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K128" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="30" customHeight="1">
+      <c r="A129" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B129" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">定期購入申込配送先</t>
+        </is>
+      </c>
+      <c r="C129" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscription_request_destinations</t>
+        </is>
+      </c>
+      <c r="D129" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">電話番号</t>
+        </is>
+      </c>
+      <c r="E129" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">phone</t>
+        </is>
+      </c>
+      <c r="F129" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G129" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H129" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I129" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J129" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K129" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="30" customHeight="1">
+      <c r="A130" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B130" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">定期購入申込配送先</t>
+        </is>
+      </c>
+      <c r="C130" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscription_request_destinations</t>
+        </is>
+      </c>
+      <c r="D130" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">作成日時</t>
+        </is>
+      </c>
+      <c r="E130" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">created_at</t>
+        </is>
+      </c>
+      <c r="F130" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">timestamptz</t>
+        </is>
+      </c>
+      <c r="G130" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H130" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I130" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">now()</t>
+        </is>
+      </c>
+      <c r="J130" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K130" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="30" customHeight="1">
+      <c r="A131" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B131" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">定期購入申込履歴</t>
+        </is>
+      </c>
+      <c r="C131" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscription_request_events</t>
+        </is>
+      </c>
+      <c r="D131" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">イベントID</t>
+        </is>
+      </c>
+      <c r="E131" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">id</t>
+        </is>
+      </c>
+      <c r="F131" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">uuid</t>
+        </is>
+      </c>
+      <c r="G131" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK</t>
+        </is>
+      </c>
+      <c r="H131" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I131" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gen_random_uuid()</t>
+        </is>
+      </c>
+      <c r="J131" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K131" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="30" customHeight="1">
+      <c r="A132" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B132" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">定期購入申込履歴</t>
+        </is>
+      </c>
+      <c r="C132" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscription_request_events</t>
+        </is>
+      </c>
+      <c r="D132" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">申込ID</t>
+        </is>
+      </c>
+      <c r="E132" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">request_id</t>
+        </is>
+      </c>
+      <c r="F132" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">uuid</t>
+        </is>
+      </c>
+      <c r="G132" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
+        </is>
+      </c>
+      <c r="H132" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I132" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J132" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscription_requests.id ON DELETE CASCADE</t>
+        </is>
+      </c>
+      <c r="K132" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="30" customHeight="1">
+      <c r="A133" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B133" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">定期購入申込履歴</t>
+        </is>
+      </c>
+      <c r="C133" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscription_request_events</t>
+        </is>
+      </c>
+      <c r="D133" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">イベント種別</t>
+        </is>
+      </c>
+      <c r="E133" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">event_type</t>
+        </is>
+      </c>
+      <c r="F133" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G133" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H133" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I133" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J133" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K133" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="30" customHeight="1">
+      <c r="A134" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B134" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">定期購入申込履歴</t>
+        </is>
+      </c>
+      <c r="C134" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscription_request_events</t>
+        </is>
+      </c>
+      <c r="D134" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">操作者種別</t>
+        </is>
+      </c>
+      <c r="E134" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actor_type</t>
+        </is>
+      </c>
+      <c r="F134" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G134" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H134" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I134" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J134" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K134" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="30" customHeight="1">
+      <c r="A135" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B135" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">定期購入申込履歴</t>
+        </is>
+      </c>
+      <c r="C135" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscription_request_events</t>
+        </is>
+      </c>
+      <c r="D135" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">操作者識別子</t>
+        </is>
+      </c>
+      <c r="E135" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actor_identifier</t>
+        </is>
+      </c>
+      <c r="F135" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G135" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H135" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I135" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J135" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K135" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="30" customHeight="1">
+      <c r="A136" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B136" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">定期購入申込履歴</t>
+        </is>
+      </c>
+      <c r="C136" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscription_request_events</t>
+        </is>
+      </c>
+      <c r="D136" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">変更前状態</t>
+        </is>
+      </c>
+      <c r="E136" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">from_status</t>
+        </is>
+      </c>
+      <c r="F136" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G136" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H136" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YES</t>
+        </is>
+      </c>
+      <c r="I136" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J136" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K136" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="30" customHeight="1">
+      <c r="A137" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B137" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">定期購入申込履歴</t>
+        </is>
+      </c>
+      <c r="C137" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscription_request_events</t>
+        </is>
+      </c>
+      <c r="D137" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">変更後状態</t>
+        </is>
+      </c>
+      <c r="E137" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">to_status</t>
+        </is>
+      </c>
+      <c r="F137" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G137" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H137" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I137" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J137" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K137" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="30" customHeight="1">
+      <c r="A138" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B138" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">定期購入申込履歴</t>
+        </is>
+      </c>
+      <c r="C138" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscription_request_events</t>
+        </is>
+      </c>
+      <c r="D138" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">理由</t>
+        </is>
+      </c>
+      <c r="E138" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reason</t>
+        </is>
+      </c>
+      <c r="F138" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G138" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H138" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YES</t>
+        </is>
+      </c>
+      <c r="I138" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J138" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K138" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="30" customHeight="1">
+      <c r="A139" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B139" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">定期購入申込履歴</t>
+        </is>
+      </c>
+      <c r="C139" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscription_request_events</t>
+        </is>
+      </c>
+      <c r="D139" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">発生日時</t>
+        </is>
+      </c>
+      <c r="E139" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">created_at</t>
+        </is>
+      </c>
+      <c r="F139" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">timestamptz</t>
+        </is>
+      </c>
+      <c r="G139" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H139" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I139" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">now()</t>
+        </is>
+      </c>
+      <c r="J139" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K139" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="30" customHeight="1">
+      <c r="A140" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B140" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ウェビナー</t>
+        </is>
+      </c>
+      <c r="C140" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">webinars</t>
+        </is>
+      </c>
+      <c r="D140" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ウェビナーID</t>
+        </is>
+      </c>
+      <c r="E140" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">id</t>
+        </is>
+      </c>
+      <c r="F140" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">uuid</t>
+        </is>
+      </c>
+      <c r="G140" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK</t>
+        </is>
+      </c>
+      <c r="H140" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I140" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gen_random_uuid()</t>
+        </is>
+      </c>
+      <c r="J140" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K140" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="30" customHeight="1">
+      <c r="A141" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B141" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ウェビナー</t>
+        </is>
+      </c>
+      <c r="C141" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">webinars</t>
+        </is>
+      </c>
+      <c r="D141" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">タイトル</t>
+        </is>
+      </c>
+      <c r="E141" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">title</t>
+        </is>
+      </c>
+      <c r="F141" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G141" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H141" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I141" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J141" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1〜200文字</t>
+        </is>
+      </c>
+      <c r="K141" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="30" customHeight="1">
+      <c r="A142" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B142" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ウェビナー</t>
+        </is>
+      </c>
+      <c r="C142" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">webinars</t>
+        </is>
+      </c>
+      <c r="D142" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">説明</t>
+        </is>
+      </c>
+      <c r="E142" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">description</t>
+        </is>
+      </c>
+      <c r="F142" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G142" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H142" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YES</t>
+        </is>
+      </c>
+      <c r="I142" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J142" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K142" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="30" customHeight="1">
+      <c r="A143" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B143" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ウェビナー</t>
+        </is>
+      </c>
+      <c r="C143" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">webinars</t>
+        </is>
+      </c>
+      <c r="D143" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">公開状態</t>
+        </is>
+      </c>
+      <c r="E143" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">status</t>
+        </is>
+      </c>
+      <c r="F143" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G143" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H143" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I143" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">draft</t>
+        </is>
+      </c>
+      <c r="J143" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">draft / published / canceled</t>
+        </is>
+      </c>
+      <c r="K143" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="30" customHeight="1">
+      <c r="A144" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B144" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ウェビナー</t>
+        </is>
+      </c>
+      <c r="C144" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">webinars</t>
+        </is>
+      </c>
+      <c r="D144" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主催者メール</t>
+        </is>
+      </c>
+      <c r="E144" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">organizer_email</t>
+        </is>
+      </c>
+      <c r="F144" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G144" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H144" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I144" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J144" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K144" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="30" customHeight="1">
+      <c r="A145" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B145" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ウェビナー</t>
+        </is>
+      </c>
+      <c r="C145" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">webinars</t>
+        </is>
+      </c>
+      <c r="D145" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">排他バージョン</t>
+        </is>
+      </c>
+      <c r="E145" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">version</t>
+        </is>
+      </c>
+      <c r="F145" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">integer</t>
+        </is>
+      </c>
+      <c r="G145" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H145" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I145" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="J145" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K145" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="30" customHeight="1">
+      <c r="A146" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B146" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ウェビナー</t>
+        </is>
+      </c>
+      <c r="C146" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">webinars</t>
+        </is>
+      </c>
+      <c r="D146" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">公開日時</t>
+        </is>
+      </c>
+      <c r="E146" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">published_at</t>
+        </is>
+      </c>
+      <c r="F146" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">timestamptz</t>
+        </is>
+      </c>
+      <c r="G146" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H146" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YES</t>
+        </is>
+      </c>
+      <c r="I146" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J146" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K146" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="30" customHeight="1">
+      <c r="A147" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B147" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ウェビナー</t>
+        </is>
+      </c>
+      <c r="C147" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">webinars</t>
+        </is>
+      </c>
+      <c r="D147" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中止日時</t>
+        </is>
+      </c>
+      <c r="E147" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">canceled_at</t>
+        </is>
+      </c>
+      <c r="F147" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">timestamptz</t>
+        </is>
+      </c>
+      <c r="G147" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H147" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YES</t>
+        </is>
+      </c>
+      <c r="I147" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J147" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K147" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="30" customHeight="1">
+      <c r="A148" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B148" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ウェビナー</t>
+        </is>
+      </c>
+      <c r="C148" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">webinars</t>
+        </is>
+      </c>
+      <c r="D148" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">作成日時</t>
+        </is>
+      </c>
+      <c r="E148" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">created_at</t>
+        </is>
+      </c>
+      <c r="F148" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">timestamptz</t>
+        </is>
+      </c>
+      <c r="G148" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H148" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I148" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">now()</t>
+        </is>
+      </c>
+      <c r="J148" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K148" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="30" customHeight="1">
+      <c r="A149" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B149" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ウェビナー</t>
+        </is>
+      </c>
+      <c r="C149" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">webinars</t>
+        </is>
+      </c>
+      <c r="D149" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">更新日時</t>
+        </is>
+      </c>
+      <c r="E149" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">updated_at</t>
+        </is>
+      </c>
+      <c r="F149" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">timestamptz</t>
+        </is>
+      </c>
+      <c r="G149" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H149" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I149" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">now()</t>
+        </is>
+      </c>
+      <c r="J149" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K149" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="30" customHeight="1">
+      <c r="A150" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B150" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ウェビナー開催枠</t>
+        </is>
+      </c>
+      <c r="C150" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">webinar_sessions</t>
+        </is>
+      </c>
+      <c r="D150" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">開催枠ID</t>
+        </is>
+      </c>
+      <c r="E150" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">id</t>
+        </is>
+      </c>
+      <c r="F150" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">uuid</t>
+        </is>
+      </c>
+      <c r="G150" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK</t>
+        </is>
+      </c>
+      <c r="H150" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I150" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gen_random_uuid()</t>
+        </is>
+      </c>
+      <c r="J150" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K150" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="30" customHeight="1">
+      <c r="A151" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B151" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ウェビナー開催枠</t>
+        </is>
+      </c>
+      <c r="C151" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">webinar_sessions</t>
+        </is>
+      </c>
+      <c r="D151" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ウェビナーID</t>
+        </is>
+      </c>
+      <c r="E151" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">webinar_id</t>
+        </is>
+      </c>
+      <c r="F151" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">uuid</t>
+        </is>
+      </c>
+      <c r="G151" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK / UK1構成</t>
+        </is>
+      </c>
+      <c r="H151" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I151" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J151" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">webinars.id ON DELETE CASCADE</t>
+        </is>
+      </c>
+      <c r="K151" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="30" customHeight="1">
+      <c r="A152" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B152" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ウェビナー開催枠</t>
+        </is>
+      </c>
+      <c r="C152" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">webinar_sessions</t>
+        </is>
+      </c>
+      <c r="D152" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">配信サービス</t>
+        </is>
+      </c>
+      <c r="E152" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">provider</t>
+        </is>
+      </c>
+      <c r="F152" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G152" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H152" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I152" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J152" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">google_meet / zoom</t>
+        </is>
+      </c>
+      <c r="K152" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="30" customHeight="1">
+      <c r="A153" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B153" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ウェビナー開催枠</t>
+        </is>
+      </c>
+      <c r="C153" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">webinar_sessions</t>
+        </is>
+      </c>
+      <c r="D153" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">開始日時</t>
+        </is>
+      </c>
+      <c r="E153" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">starts_at</t>
+        </is>
+      </c>
+      <c r="F153" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">timestamptz</t>
+        </is>
+      </c>
+      <c r="G153" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UK1構成</t>
+        </is>
+      </c>
+      <c r="H153" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I153" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J153" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K153" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="30" customHeight="1">
+      <c r="A154" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B154" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ウェビナー開催枠</t>
+        </is>
+      </c>
+      <c r="C154" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">webinar_sessions</t>
+        </is>
+      </c>
+      <c r="D154" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">終了日時</t>
+        </is>
+      </c>
+      <c r="E154" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ends_at</t>
+        </is>
+      </c>
+      <c r="F154" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">timestamptz</t>
+        </is>
+      </c>
+      <c r="G154" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H154" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I154" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J154" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">開始より後</t>
+        </is>
+      </c>
+      <c r="K154" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="30" customHeight="1">
+      <c r="A155" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B155" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ウェビナー開催枠</t>
+        </is>
+      </c>
+      <c r="C155" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">webinar_sessions</t>
+        </is>
+      </c>
+      <c r="D155" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">タイムゾーン</t>
+        </is>
+      </c>
+      <c r="E155" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">timezone</t>
+        </is>
+      </c>
+      <c r="F155" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G155" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H155" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I155" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Asia/Tokyo</t>
+        </is>
+      </c>
+      <c r="J155" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K155" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="30" customHeight="1">
+      <c r="A156" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B156" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ウェビナー開催枠</t>
+        </is>
+      </c>
+      <c r="C156" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">webinar_sessions</t>
+        </is>
+      </c>
+      <c r="D156" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">参加URL</t>
+        </is>
+      </c>
+      <c r="E156" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">join_url</t>
+        </is>
+      </c>
+      <c r="F156" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G156" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H156" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I156" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J156" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://</t>
+        </is>
+      </c>
+      <c r="K156" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="30" customHeight="1">
+      <c r="A157" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B157" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ウェビナー開催枠</t>
+        </is>
+      </c>
+      <c r="C157" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">webinar_sessions</t>
+        </is>
+      </c>
+      <c r="D157" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">外部スペースID</t>
+        </is>
+      </c>
+      <c r="E157" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">external_space_id</t>
+        </is>
+      </c>
+      <c r="F157" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G157" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H157" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YES</t>
+        </is>
+      </c>
+      <c r="I157" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J157" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K157" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API連携後に使用</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="30" customHeight="1">
+      <c r="A158" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B158" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ウェビナー開催枠</t>
+        </is>
+      </c>
+      <c r="C158" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">webinar_sessions</t>
+        </is>
+      </c>
+      <c r="D158" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">作成日時</t>
+        </is>
+      </c>
+      <c r="E158" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">created_at</t>
+        </is>
+      </c>
+      <c r="F158" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">timestamptz</t>
+        </is>
+      </c>
+      <c r="G158" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H158" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I158" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">now()</t>
+        </is>
+      </c>
+      <c r="J158" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K158" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="30" customHeight="1">
+      <c r="A159" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B159" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ウェビナー開催枠</t>
+        </is>
+      </c>
+      <c r="C159" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">webinar_sessions</t>
+        </is>
+      </c>
+      <c r="D159" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">更新日時</t>
+        </is>
+      </c>
+      <c r="E159" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">updated_at</t>
+        </is>
+      </c>
+      <c r="F159" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">timestamptz</t>
+        </is>
+      </c>
+      <c r="G159" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H159" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I159" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">now()</t>
+        </is>
+      </c>
+      <c r="J159" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K159" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="30" customHeight="1">
+      <c r="A160" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B160" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ウェビナー対象医院</t>
+        </is>
+      </c>
+      <c r="C160" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">webinar_target_clinics</t>
+        </is>
+      </c>
+      <c r="D160" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ウェビナーID</t>
+        </is>
+      </c>
+      <c r="E160" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">webinar_id</t>
+        </is>
+      </c>
+      <c r="F160" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">uuid</t>
+        </is>
+      </c>
+      <c r="G160" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK / FK</t>
+        </is>
+      </c>
+      <c r="H160" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I160" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J160" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">webinars.id ON DELETE CASCADE</t>
+        </is>
+      </c>
+      <c r="K160" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="30" customHeight="1">
+      <c r="A161" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B161" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ウェビナー対象医院</t>
+        </is>
+      </c>
+      <c r="C161" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">webinar_target_clinics</t>
+        </is>
+      </c>
+      <c r="D161" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">得意先コード</t>
+        </is>
+      </c>
+      <c r="E161" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">customer_code</t>
+        </is>
+      </c>
+      <c r="F161" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G161" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK / FK</t>
+        </is>
+      </c>
+      <c r="H161" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I161" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J161" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinics.customer_code ON DELETE RESTRICT</t>
+        </is>
+      </c>
+      <c r="K161" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="30" customHeight="1">
+      <c r="A162" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B162" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ウェビナー対象医院</t>
+        </is>
+      </c>
+      <c r="C162" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">webinar_target_clinics</t>
+        </is>
+      </c>
+      <c r="D162" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">作成日時</t>
+        </is>
+      </c>
+      <c r="E162" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">created_at</t>
+        </is>
+      </c>
+      <c r="F162" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">timestamptz</t>
+        </is>
+      </c>
+      <c r="G162" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H162" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I162" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">now()</t>
+        </is>
+      </c>
+      <c r="J162" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K162" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="30" customHeight="1">
+      <c r="A163" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B163" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ウェビナー操作履歴</t>
+        </is>
+      </c>
+      <c r="C163" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">webinar_events</t>
+        </is>
+      </c>
+      <c r="D163" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">イベントID</t>
+        </is>
+      </c>
+      <c r="E163" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">id</t>
+        </is>
+      </c>
+      <c r="F163" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">uuid</t>
+        </is>
+      </c>
+      <c r="G163" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK</t>
+        </is>
+      </c>
+      <c r="H163" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I163" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gen_random_uuid()</t>
+        </is>
+      </c>
+      <c r="J163" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K163" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="30" customHeight="1">
+      <c r="A164" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B164" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ウェビナー操作履歴</t>
+        </is>
+      </c>
+      <c r="C164" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">webinar_events</t>
+        </is>
+      </c>
+      <c r="D164" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ウェビナーID</t>
+        </is>
+      </c>
+      <c r="E164" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">webinar_id</t>
+        </is>
+      </c>
+      <c r="F164" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">uuid</t>
+        </is>
+      </c>
+      <c r="G164" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
+        </is>
+      </c>
+      <c r="H164" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I164" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J164" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">webinars.id ON DELETE CASCADE</t>
+        </is>
+      </c>
+      <c r="K164" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="30" customHeight="1">
+      <c r="A165" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B165" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ウェビナー操作履歴</t>
+        </is>
+      </c>
+      <c r="C165" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">webinar_events</t>
+        </is>
+      </c>
+      <c r="D165" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">イベント種別</t>
+        </is>
+      </c>
+      <c r="E165" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">event_type</t>
+        </is>
+      </c>
+      <c r="F165" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G165" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H165" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I165" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J165" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K165" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="30" customHeight="1">
+      <c r="A166" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B166" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ウェビナー操作履歴</t>
+        </is>
+      </c>
+      <c r="C166" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">webinar_events</t>
+        </is>
+      </c>
+      <c r="D166" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">操作者メール</t>
+        </is>
+      </c>
+      <c r="E166" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actor_email</t>
+        </is>
+      </c>
+      <c r="F166" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G166" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H166" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I166" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J166" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K166" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="30" customHeight="1">
+      <c r="A167" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B167" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ウェビナー操作履歴</t>
+        </is>
+      </c>
+      <c r="C167" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">webinar_events</t>
+        </is>
+      </c>
+      <c r="D167" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">変更前状態</t>
+        </is>
+      </c>
+      <c r="E167" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">from_status</t>
+        </is>
+      </c>
+      <c r="F167" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G167" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H167" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YES</t>
+        </is>
+      </c>
+      <c r="I167" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J167" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K167" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="30" customHeight="1">
+      <c r="A168" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B168" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ウェビナー操作履歴</t>
+        </is>
+      </c>
+      <c r="C168" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">webinar_events</t>
+        </is>
+      </c>
+      <c r="D168" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">変更後状態</t>
+        </is>
+      </c>
+      <c r="E168" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">to_status</t>
+        </is>
+      </c>
+      <c r="F168" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G168" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H168" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I168" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J168" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K168" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="30" customHeight="1">
+      <c r="A169" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B169" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ウェビナー操作履歴</t>
+        </is>
+      </c>
+      <c r="C169" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">webinar_events</t>
+        </is>
+      </c>
+      <c r="D169" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">発生日時</t>
+        </is>
+      </c>
+      <c r="E169" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">created_at</t>
+        </is>
+      </c>
+      <c r="F169" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">timestamptz</t>
+        </is>
+      </c>
+      <c r="G169" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H169" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I169" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">now()</t>
+        </is>
+      </c>
+      <c r="J169" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K169" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A2:K2"/>
   </mergeCells>
-  <autoFilter ref="A4:K97"/>
+  <autoFilter ref="A4:K169"/>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0" paperSize="9"/>
 </worksheet>
@@ -11336,7 +15696,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:G63"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -11654,22 +16014,22 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">将来案</t>
+          <t xml:space="preserve">現行</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">UK1</t>
+          <t xml:space="preserve">UK5</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_accounts</t>
+          <t xml:space="preserve">patient_subscription_requests</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">provider, external_account_id</t>
+          <t xml:space="preserve">request_number</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -11679,29 +16039,29 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部接続先の重複防止。</t>
+          <t xml:space="preserve">表示用申込番号の一意性。</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">将来案</t>
+          <t xml:space="preserve">現行</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">UK2</t>
+          <t xml:space="preserve">UK6</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_fulfillment_items</t>
+          <t xml:space="preserve">patient_subscription_requests</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">fulfillment_id, order_item_id</t>
+          <t xml:space="preserve">customer_code, idempotency_key</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -11711,29 +16071,29 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">同一配送への明細重複防止。</t>
+          <t xml:space="preserve">申込再送時の二重登録防止。</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">将来案</t>
+          <t xml:space="preserve">現行</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">UK3</t>
+          <t xml:space="preserve">UK7</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_subscriptions</t>
+          <t xml:space="preserve">patient_subscription_request_items</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_account_id, external_subscription_id</t>
+          <t xml:space="preserve">request_id, product_id</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -11743,61 +16103,61 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部契約の重複防止。</t>
+          <t xml:space="preserve">同じ申込内の商品重複防止。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">将来案</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UK4</t>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IDX5</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_webhook_events</t>
+          <t xml:space="preserve">patient_subscription_requests</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_account_id, external_event_id</t>
+          <t xml:space="preserve">status, submitted_at DESC</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNIQUE</t>
+          <t xml:space="preserve">INDEX</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Webhook重複配信の無害化。</t>
+          <t xml:space="preserve">BGJ申込一覧。</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">将来案</t>
+          <t xml:space="preserve">現行</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">UK5</t>
+          <t xml:space="preserve">UK8</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders</t>
+          <t xml:space="preserve">webinar_sessions</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_account_id, external_order_id</t>
+          <t xml:space="preserve">webinar_id, starts_at</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
@@ -11807,354 +16167,319 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">複数ストアを考慮した外部注文の一意性。</t>
+          <t xml:space="preserve">同一ウェビナーの開催日時重複防止。</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UK9</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">webinar_target_clinics</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">webinar_id, customer_code</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PRIMARY KEY</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">対象医院の重複防止。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IDX6</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">webinar_target_clinics</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">customer_code, webinar_id</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">INDEX</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">医院別公開ウェビナー取得。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">将来案</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UK6</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">commerce_outbox</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">idempotency_key</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UK1</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">commerce_accounts</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">provider, external_account_id</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">UNIQUE</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">外部送信コマンドの二重実行防止。</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">現行リレーション</t>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">外部接続先の重複防止。</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">親DB日本語名</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">親KEY</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">親多重度</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">子多重度</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">子FK</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">子DB日本語名</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">削除・備考</t>
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">将来案</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UK2</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_fulfillment_items</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fulfillment_id, order_item_id</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UNIQUE</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">同一配送への明細重複防止。</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">clinics.customer_code</t>
+          <t xml:space="preserve">将来案</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UK3</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">patient_subscriptions</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">0..1</t>
+          <t xml:space="preserve">commerce_account_id, external_subscription_id</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_terms.customer_code</t>
+          <t xml:space="preserve">UNIQUE</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院契約情報</t>
-        </is>
-      </c>
-      <c r="G22" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PK・FK・CASCADE</t>
+          <t xml:space="preserve">外部契約の重複防止。</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">clinics.customer_code</t>
+          <t xml:space="preserve">将来案</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UK4</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">commerce_webhook_events</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">N</t>
+          <t xml:space="preserve">commerce_account_id, external_event_id</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_product_settings.customer_code</t>
+          <t xml:space="preserve">UNIQUE</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院商品設定</t>
-        </is>
-      </c>
-      <c r="G23" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PK・FK・CASCADE</t>
+          <t xml:space="preserve">Webhook重複配信の無害化。</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">商品</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">products.id</t>
+          <t xml:space="preserve">将来案</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UK5</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">patient_orders</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">N</t>
+          <t xml:space="preserve">commerce_account_id, external_order_id</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_product_settings.product_id</t>
+          <t xml:space="preserve">UNIQUE</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院商品設定</t>
-        </is>
-      </c>
-      <c r="G24" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PK・FK・CASCADE</t>
+          <t xml:space="preserve">複数ストアを考慮した外部注文の一意性。</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">clinics.customer_code</t>
+          <t xml:space="preserve">将来案</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UK6</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">commerce_outbox</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">N</t>
+          <t xml:space="preserve">idempotency_key</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders.customer_code</t>
+          <t xml:space="preserve">UNIQUE</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文</t>
-        </is>
-      </c>
-      <c r="G25" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FK</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">患者</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">patients.id</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">patient_orders.patient_id</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">患者注文</t>
-        </is>
-      </c>
-      <c r="G26" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FK・現状CASCADE</t>
+          <t xml:space="preserve">外部送信コマンドの二重実行防止。</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">患者注文</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">patient_orders.id</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">patient_order_items.order_id</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">患者注文明細</t>
-        </is>
-      </c>
-      <c r="G27" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FK・CASCADE</t>
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行リレーション</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">医院</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">clinics.customer_code</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">delivery_destinations.clinic_customer_code</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">送り先マスタ</t>
-        </is>
-      </c>
-      <c r="G28" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FK・RESTRICT</t>
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">親DB日本語名</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">親KEY</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">親多重度</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">子多重度</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">子FK</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">子DB日本語名</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">削除・備考</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者</t>
+          <t xml:space="preserve">医院</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patients.id</t>
+          <t xml:space="preserve">clinics.customer_code</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -12164,34 +16489,34 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">N</t>
+          <t xml:space="preserve">0..1</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery_destinations.patient_id</t>
+          <t xml:space="preserve">clinic_terms.customer_code</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">送り先マスタ</t>
+          <t xml:space="preserve">医院契約情報</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK・RESTRICT</t>
+          <t xml:space="preserve">PK・FK・CASCADE</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">送り先マスタ</t>
+          <t xml:space="preserve">医院</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery_destinations.id</t>
+          <t xml:space="preserve">clinics.customer_code</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -12206,29 +16531,29 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">order_delivery_destinations.delivery_destination_id</t>
+          <t xml:space="preserve">clinic_product_settings.customer_code</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文配送先</t>
+          <t xml:space="preserve">医院商品設定</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK・RESTRICT</t>
+          <t xml:space="preserve">PK・FK・CASCADE</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文</t>
+          <t xml:space="preserve">商品</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders.id</t>
+          <t xml:space="preserve">products.id</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -12238,17 +16563,17 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">0..1</t>
+          <t xml:space="preserve">N</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">order_delivery_destinations.order_id</t>
+          <t xml:space="preserve">clinic_product_settings.product_id</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文配送先</t>
+          <t xml:space="preserve">医院商品設定</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
@@ -12260,54 +16585,54 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">医院</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinics.customer_code</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_orders.customer_code</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">患者注文</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">patient_orders.id</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">patient_order_events.order_id</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">注文操作履歴</t>
-        </is>
-      </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK・CASCADE</t>
+          <t xml:space="preserve">FK</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">商品</t>
+          <t xml:space="preserve">患者</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">products.id</t>
+          <t xml:space="preserve">patients.id</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">0..1</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -12317,73 +16642,140 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_order_items.product_id</t>
+          <t xml:space="preserve">patient_orders.patient_id</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">患者注文</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK・現状CASCADE</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">患者注文</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_orders.id</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_order_items.order_id</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">患者注文明細</t>
         </is>
       </c>
-      <c r="G33" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FK・SET NULL</t>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK・CASCADE</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">将来リレーション案</t>
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">医院</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinics.customer_code</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">delivery_destinations.clinic_customer_code</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">送り先マスタ</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK・RESTRICT</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">親DB日本語名</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">親KEY</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">親多重度</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">子多重度</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">子FK</t>
-        </is>
-      </c>
-      <c r="F36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">子DB日本語名</t>
-        </is>
-      </c>
-      <c r="G36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">削除・備考</t>
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">患者</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patients.id</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">delivery_destinations.patient_id</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">送り先マスタ</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK・RESTRICT</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文</t>
+          <t xml:space="preserve">送り先マスタ</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders.id</t>
+          <t xml:space="preserve">delivery_destinations.id</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -12398,17 +16790,17 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">order_transaction_projections.order_id</t>
+          <t xml:space="preserve">order_delivery_destinations.delivery_destination_id</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">決済返金投影</t>
+          <t xml:space="preserve">注文配送先</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK</t>
+          <t xml:space="preserve">FK・RESTRICT</t>
         </is>
       </c>
     </row>
@@ -12430,34 +16822,34 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">N</t>
+          <t xml:space="preserve">0..1</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_fulfillments.order_id</t>
+          <t xml:space="preserve">order_delivery_destinations.order_id</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">受取配送</t>
+          <t xml:space="preserve">注文配送先</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK</t>
+          <t xml:space="preserve">PK・FK・CASCADE</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">受取配送</t>
+          <t xml:space="preserve">患者注文</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_fulfillments.id</t>
+          <t xml:space="preserve">patient_orders.id</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -12472,34 +16864,34 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_fulfillment_items.fulfillment_id</t>
+          <t xml:space="preserve">patient_order_events.order_id</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">受取配送明細</t>
+          <t xml:space="preserve">注文操作履歴</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK</t>
+          <t xml:space="preserve">FK・CASCADE</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文明細</t>
+          <t xml:space="preserve">商品</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_order_items.id</t>
+          <t xml:space="preserve">products.id</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">0..1</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -12509,29 +16901,29 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_fulfillment_items.order_item_id</t>
+          <t xml:space="preserve">patient_order_items.product_id</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">受取配送明細</t>
+          <t xml:space="preserve">患者注文明細</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK</t>
+          <t xml:space="preserve">FK・SET NULL</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部コマース接続</t>
+          <t xml:space="preserve">医院</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_accounts.id</t>
+          <t xml:space="preserve">clinics.customer_code</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -12546,29 +16938,29 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders.commerce_account_id</t>
+          <t xml:space="preserve">patient_subscription_requests.customer_code</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文</t>
+          <t xml:space="preserve">定期購入申込</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK</t>
+          <t xml:space="preserve">FK・RESTRICT</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部コマース接続</t>
+          <t xml:space="preserve">患者</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_accounts.id</t>
+          <t xml:space="preserve">patients.id</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -12583,29 +16975,29 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_webhook_events.commerce_account_id</t>
+          <t xml:space="preserve">patient_subscription_requests.patient_id</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部受信イベント</t>
+          <t xml:space="preserve">定期購入申込</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK</t>
+          <t xml:space="preserve">FK・RESTRICT</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部コマース接続</t>
+          <t xml:space="preserve">定期購入申込</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_accounts.id</t>
+          <t xml:space="preserve">patient_subscription_requests.id</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -12620,29 +17012,29 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_outbox.commerce_account_id</t>
+          <t xml:space="preserve">patient_subscription_request_items.request_id</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部送信キュー</t>
+          <t xml:space="preserve">定期購入申込明細</t>
         </is>
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK</t>
+          <t xml:space="preserve">FK・CASCADE</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者</t>
+          <t xml:space="preserve">定期購入申込</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patients.id</t>
+          <t xml:space="preserve">patient_subscription_requests.id</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -12652,34 +17044,34 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">N</t>
+          <t xml:space="preserve">0..1</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_subscriptions.patient_id</t>
+          <t xml:space="preserve">patient_subscription_request_destinations.request_id</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者定期購入</t>
+          <t xml:space="preserve">定期購入申込配送先</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK</t>
+          <t xml:space="preserve">PK・FK・CASCADE</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者定期購入</t>
+          <t xml:space="preserve">定期購入申込</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_subscriptions.id</t>
+          <t xml:space="preserve">patient_subscription_requests.id</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -12694,52 +17086,614 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_subscription_items.subscription_id</t>
+          <t xml:space="preserve">patient_subscription_request_events.request_id</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">定期購入明細</t>
+          <t xml:space="preserve">定期購入申込履歴</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK</t>
+          <t xml:space="preserve">FK・CASCADE</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">送り先マスタ</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">delivery_destinations.id</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscription_request_destinations.delivery_destination_id</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">定期購入申込配送先</t>
+        </is>
+      </c>
+      <c r="G46" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK・RESTRICT</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ウェビナー</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">webinars.id</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">webinar_sessions.webinar_id</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ウェビナー開催枠</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK・CASCADE</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ウェビナー</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">webinars.id</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">webinar_target_clinics.webinar_id</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ウェビナー対象医院</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK・FK・CASCADE</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">医院</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinics.customer_code</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">webinar_target_clinics.customer_code</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ウェビナー対象医院</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK・FK・RESTRICT</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ウェビナー</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">webinars.id</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">webinar_events.webinar_id</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ウェビナー操作履歴</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK・CASCADE</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">将来リレーション案</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">親DB日本語名</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">親KEY</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">親多重度</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">子多重度</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">子FK</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">子DB日本語名</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">削除・備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">患者注文</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_orders.id</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">order_transaction_projections.order_id</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">決済返金投影</t>
+        </is>
+      </c>
+      <c r="G54" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">患者注文</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_orders.id</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_fulfillments.order_id</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">受取配送</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">受取配送</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_fulfillments.id</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_fulfillment_items.fulfillment_id</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">受取配送明細</t>
+        </is>
+      </c>
+      <c r="G56" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">注文明細</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_order_items.id</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_fulfillment_items.order_item_id</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">受取配送明細</t>
+        </is>
+      </c>
+      <c r="G57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">外部コマース接続</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">commerce_accounts.id</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_orders.commerce_account_id</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">患者注文</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">外部コマース接続</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">commerce_accounts.id</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">commerce_webhook_events.commerce_account_id</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">外部受信イベント</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">外部コマース接続</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">commerce_accounts.id</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">commerce_outbox.commerce_account_id</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">外部送信キュー</t>
+        </is>
+      </c>
+      <c r="G60" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">患者</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patients.id</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscriptions.patient_id</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">患者定期購入</t>
         </is>
       </c>
-      <c r="B46" s="4" t="inlineStr">
+      <c r="G61" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">患者定期購入</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">patient_subscriptions.id</t>
         </is>
       </c>
-      <c r="C46" s="4" t="inlineStr">
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscription_items.subscription_id</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">定期購入明細</t>
+        </is>
+      </c>
+      <c r="G62" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">患者定期購入</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscriptions.id</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">0..1</t>
         </is>
       </c>
-      <c r="D46" s="4" t="inlineStr">
+      <c r="D63" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="E46" s="4" t="inlineStr">
+      <c r="E63" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">patient_orders.subscription_id</t>
         </is>
       </c>
-      <c r="F46" s="4" t="inlineStr">
+      <c r="F63" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">患者注文</t>
         </is>
       </c>
-      <c r="G46" s="4" t="inlineStr">
+      <c r="G63" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">FK</t>
         </is>
@@ -12749,8 +17703,8 @@
   <mergeCells count="4">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A20:H20"/>
-    <mergeCell ref="A35:H35"/>
+    <mergeCell ref="A27:H27"/>
+    <mergeCell ref="A52:H52"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0" paperSize="9"/>
@@ -12759,7 +17713,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Q85"/>
+  <dimension ref="A1:Q95"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -14329,6 +19283,376 @@
       <c r="G85" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">FK・SET NULL</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">医院</t>
+        </is>
+      </c>
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinics.customer_code</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D86" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E86" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscription_requests.customer_code</t>
+        </is>
+      </c>
+      <c r="F86" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">定期購入申込</t>
+        </is>
+      </c>
+      <c r="G86" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK・RESTRICT</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">患者</t>
+        </is>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patients.id</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E87" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscription_requests.patient_id</t>
+        </is>
+      </c>
+      <c r="F87" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">定期購入申込</t>
+        </is>
+      </c>
+      <c r="G87" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK・RESTRICT</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">定期購入申込</t>
+        </is>
+      </c>
+      <c r="B88" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscription_requests.id</t>
+        </is>
+      </c>
+      <c r="C88" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D88" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E88" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscription_request_items.request_id</t>
+        </is>
+      </c>
+      <c r="F88" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">定期購入申込明細</t>
+        </is>
+      </c>
+      <c r="G88" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK・CASCADE</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">定期購入申込</t>
+        </is>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscription_requests.id</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D89" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0..1</t>
+        </is>
+      </c>
+      <c r="E89" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscription_request_destinations.request_id</t>
+        </is>
+      </c>
+      <c r="F89" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">定期購入申込配送先</t>
+        </is>
+      </c>
+      <c r="G89" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK・FK・CASCADE</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">定期購入申込</t>
+        </is>
+      </c>
+      <c r="B90" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscription_requests.id</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D90" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E90" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscription_request_events.request_id</t>
+        </is>
+      </c>
+      <c r="F90" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">定期購入申込履歴</t>
+        </is>
+      </c>
+      <c r="G90" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK・CASCADE</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">送り先マスタ</t>
+        </is>
+      </c>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">delivery_destinations.id</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D91" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E91" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscription_request_destinations.delivery_destination_id</t>
+        </is>
+      </c>
+      <c r="F91" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">定期購入申込配送先</t>
+        </is>
+      </c>
+      <c r="G91" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK・RESTRICT</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ウェビナー</t>
+        </is>
+      </c>
+      <c r="B92" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">webinars.id</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D92" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E92" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">webinar_sessions.webinar_id</t>
+        </is>
+      </c>
+      <c r="F92" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ウェビナー開催枠</t>
+        </is>
+      </c>
+      <c r="G92" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK・CASCADE</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ウェビナー</t>
+        </is>
+      </c>
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">webinars.id</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D93" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E93" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">webinar_target_clinics.webinar_id</t>
+        </is>
+      </c>
+      <c r="F93" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ウェビナー対象医院</t>
+        </is>
+      </c>
+      <c r="G93" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK・FK・CASCADE</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">医院</t>
+        </is>
+      </c>
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinics.customer_code</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D94" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E94" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">webinar_target_clinics.customer_code</t>
+        </is>
+      </c>
+      <c r="F94" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ウェビナー対象医院</t>
+        </is>
+      </c>
+      <c r="G94" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK・FK・RESTRICT</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ウェビナー</t>
+        </is>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">webinars.id</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D95" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E95" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">webinar_events.webinar_id</t>
+        </is>
+      </c>
+      <c r="F95" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ウェビナー操作履歴</t>
+        </is>
+      </c>
+      <c r="G95" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK・CASCADE</t>
         </is>
       </c>
     </row>

--- a/project_clinic_order_management_db_definition.xlsx
+++ b/project_clinic_order_management_db_definition.xlsx
@@ -266,7 +266,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院が患者向け商品を管理するpatient_orders系列、およびウェビナー管理</t>
+          <t xml:space="preserve">医院が患者向け商品を管理するpatient_orders系列、ウェビナー、医院業務連絡担当者</t>
         </is>
       </c>
     </row>
@@ -290,7 +290,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supabaseの患者注文・定期購入申込・送り先・ウェビナー各テーブル</t>
+          <t xml:space="preserve">Supabaseの患者注文・定期購入申込・送り先・ウェビナー・医院担当者各テーブル</t>
         </is>
       </c>
     </row>
@@ -476,7 +476,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -1112,27 +1112,27 @@
     <row r="23" ht="34" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shopify接続</t>
+          <t xml:space="preserve">現行</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部コマース接続</t>
+          <t xml:space="preserve">医院業務連絡担当者</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_accounts</t>
+          <t xml:space="preserve">clinic_contacts</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">将来案</t>
+          <t xml:space="preserve">実装済み</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shopifyストア等の外部接続先。医院との対応方式は接続構成確定後に決定する。</t>
+          <t xml:space="preserve">医院ごとに複数の業務連絡担当者と主担当、論理削除、排他制御を管理する。</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -1144,27 +1144,27 @@
     <row r="24" ht="34" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shopify接続</t>
+          <t xml:space="preserve">現行</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文拡張</t>
+          <t xml:space="preserve">担当者通知設定</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders</t>
+          <t xml:space="preserve">clinic_contact_notification_preferences</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">既存テーブル拡張案</t>
+          <t xml:space="preserve">実装済み</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">既存IDを維持し、外部・金額・排他制御の列を追加する。</t>
+          <t xml:space="preserve">担当者ごとの連絡内容と方法を多値属性として分離する。</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
@@ -1176,27 +1176,27 @@
     <row r="25" ht="34" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shopify接続</t>
+          <t xml:space="preserve">現行</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文明細拡張</t>
+          <t xml:space="preserve">担当者操作履歴</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_order_items</t>
+          <t xml:space="preserve">clinic_contact_events</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">既存テーブル拡張案</t>
+          <t xml:space="preserve">実装済み</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部明細と通貨を明確化し、既存スナップショットを維持する。</t>
+          <t xml:space="preserve">登録・更新・無効化・主担当変更・論理削除を監査保存する。</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
@@ -1208,17 +1208,17 @@
     <row r="26" ht="34" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">決済接続</t>
+          <t xml:space="preserve">Shopify接続</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">決済返金投影</t>
+          <t xml:space="preserve">外部コマース接続</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">order_transaction_projections</t>
+          <t xml:space="preserve">commerce_accounts</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shopify上の決済・返金を表示する投影。会計台帳ではない。</t>
+          <t xml:space="preserve">Shopifyストア等の外部接続先。医院との対応方式は接続構成確定後に決定する。</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -1240,27 +1240,27 @@
     <row r="27" ht="34" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">配送開始</t>
+          <t xml:space="preserve">Shopify接続</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">受取配送</t>
+          <t xml:space="preserve">患者注文拡張</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_fulfillments</t>
+          <t xml:space="preserve">patient_orders</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">将来案</t>
+          <t xml:space="preserve">既存テーブル拡張案</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院受け取り・配送・部分引き渡しの単位。</t>
+          <t xml:space="preserve">既存IDを維持し、外部・金額・排他制御の列を追加する。</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -1272,27 +1272,27 @@
     <row r="28" ht="34" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">配送開始</t>
+          <t xml:space="preserve">Shopify接続</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">受取配送明細</t>
+          <t xml:space="preserve">患者注文明細拡張</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_fulfillment_items</t>
+          <t xml:space="preserve">patient_order_items</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">将来案</t>
+          <t xml:space="preserve">既存テーブル拡張案</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">部分受け取り・部分配送時の対象明細と数量。</t>
+          <t xml:space="preserve">外部明細と通貨を明確化し、既存スナップショットを維持する。</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
@@ -1304,17 +1304,17 @@
     <row r="29" ht="34" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">定期購入接続</t>
+          <t xml:space="preserve">決済接続</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者定期購入</t>
+          <t xml:space="preserve">決済返金投影</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_subscriptions</t>
+          <t xml:space="preserve">order_transaction_projections</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shopify上の定期購入契約を患者ポータルへ表示する投影。</t>
+          <t xml:space="preserve">Shopify上の決済・返金を表示する投影。会計台帳ではない。</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
@@ -1336,17 +1336,17 @@
     <row r="30" ht="34" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">定期購入接続</t>
+          <t xml:space="preserve">配送開始</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">定期購入明細</t>
+          <t xml:space="preserve">受取配送</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_subscription_items</t>
+          <t xml:space="preserve">patient_fulfillments</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">契約時点の商品・数量・単価の投影。</t>
+          <t xml:space="preserve">医院受け取り・配送・部分引き渡しの単位。</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
@@ -1368,17 +1368,17 @@
     <row r="31" ht="34" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shopify接続</t>
+          <t xml:space="preserve">配送開始</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部受信イベント</t>
+          <t xml:space="preserve">受取配送明細</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_webhook_events</t>
+          <t xml:space="preserve">patient_fulfillment_items</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Webhookを先に永続化し、重複排除・再試行するInbox。</t>
+          <t xml:space="preserve">部分受け取り・部分配送時の対象明細と数量。</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -1400,62 +1400,158 @@
     <row r="32" ht="34" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">定期購入接続</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">患者定期購入</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscriptions</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">将来案</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shopify上の定期購入契約を患者ポータルへ表示する投影。</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="34" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">定期購入接続</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">定期購入明細</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscription_items</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">将来案</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">契約時点の商品・数量・単価の投影。</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="34" customHeight="1">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">Shopify接続</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">外部受信イベント</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">commerce_webhook_events</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">将来案</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Webhookを先に永続化し、重複排除・再試行するInbox。</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="34" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shopify接続</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">外部送信キュー</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">commerce_outbox</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="D35" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">将来案</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
+      <c r="E35" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">外部APIへ送る処理を永続化するOutbox。</t>
         </is>
       </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="8" t="inlineStr">
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">別ドメイン</t>
         </is>
       </c>
-      <c r="B33" s="8" t="inlineStr">
+      <c r="B36" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">医院仕入注文</t>
         </is>
       </c>
-      <c r="C33" s="8" t="inlineStr">
+      <c r="C36" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">clinic_orders</t>
         </is>
       </c>
-      <c r="D33" s="8" t="inlineStr">
+      <c r="D36" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">実装済み</t>
         </is>
       </c>
-      <c r="E33" s="8" t="inlineStr">
+      <c r="E36" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">BGJから医院へのB2B仕入・売上履歴</t>
         </is>
       </c>
-      <c r="F33" s="8" t="inlineStr">
+      <c r="F36" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">患者注文系列へ統合しない</t>
         </is>
@@ -1466,7 +1562,7 @@
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
   </mergeCells>
-  <autoFilter ref="A4:F33"/>
+  <autoFilter ref="A4:F36"/>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0" paperSize="9"/>
 </worksheet>
@@ -1474,7 +1570,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K169"/>
+  <dimension ref="A1:K196"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -10966,12 +11062,1551 @@
         </is>
       </c>
     </row>
+    <row r="170" ht="30" customHeight="1">
+      <c r="A170" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B170" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">医院業務連絡担当者</t>
+        </is>
+      </c>
+      <c r="C170" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_contacts</t>
+        </is>
+      </c>
+      <c r="D170" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">担当者ID</t>
+        </is>
+      </c>
+      <c r="E170" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">id</t>
+        </is>
+      </c>
+      <c r="F170" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">uuid</t>
+        </is>
+      </c>
+      <c r="G170" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK</t>
+        </is>
+      </c>
+      <c r="H170" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I170" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gen_random_uuid()</t>
+        </is>
+      </c>
+      <c r="J170" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K170" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="30" customHeight="1">
+      <c r="A171" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B171" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">医院業務連絡担当者</t>
+        </is>
+      </c>
+      <c r="C171" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_contacts</t>
+        </is>
+      </c>
+      <c r="D171" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">得意先コード</t>
+        </is>
+      </c>
+      <c r="E171" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">customer_code</t>
+        </is>
+      </c>
+      <c r="F171" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G171" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
+        </is>
+      </c>
+      <c r="H171" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I171" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J171" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinics.customer_code ON DELETE RESTRICT</t>
+        </is>
+      </c>
+      <c r="K171" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="30" customHeight="1">
+      <c r="A172" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B172" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">医院業務連絡担当者</t>
+        </is>
+      </c>
+      <c r="C172" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_contacts</t>
+        </is>
+      </c>
+      <c r="D172" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">医院ログインID</t>
+        </is>
+      </c>
+      <c r="E172" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_user_id</t>
+        </is>
+      </c>
+      <c r="F172" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">uuid</t>
+        </is>
+      </c>
+      <c r="G172" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
+        </is>
+      </c>
+      <c r="H172" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YES</t>
+        </is>
+      </c>
+      <c r="I172" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J172" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_users.id ON DELETE SET NULL</t>
+        </is>
+      </c>
+      <c r="K172" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="30" customHeight="1">
+      <c r="A173" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B173" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">医院業務連絡担当者</t>
+        </is>
+      </c>
+      <c r="C173" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_contacts</t>
+        </is>
+      </c>
+      <c r="D173" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">氏名</t>
+        </is>
+      </c>
+      <c r="E173" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">name</t>
+        </is>
+      </c>
+      <c r="F173" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G173" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H173" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I173" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J173" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K173" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="30" customHeight="1">
+      <c r="A174" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B174" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">医院業務連絡担当者</t>
+        </is>
+      </c>
+      <c r="C174" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_contacts</t>
+        </is>
+      </c>
+      <c r="D174" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">部署</t>
+        </is>
+      </c>
+      <c r="E174" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">department</t>
+        </is>
+      </c>
+      <c r="F174" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G174" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H174" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YES</t>
+        </is>
+      </c>
+      <c r="I174" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J174" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K174" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="30" customHeight="1">
+      <c r="A175" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B175" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">医院業務連絡担当者</t>
+        </is>
+      </c>
+      <c r="C175" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_contacts</t>
+        </is>
+      </c>
+      <c r="D175" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">役職</t>
+        </is>
+      </c>
+      <c r="E175" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">title</t>
+        </is>
+      </c>
+      <c r="F175" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G175" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H175" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YES</t>
+        </is>
+      </c>
+      <c r="I175" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J175" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K175" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="30" customHeight="1">
+      <c r="A176" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B176" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">医院業務連絡担当者</t>
+        </is>
+      </c>
+      <c r="C176" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_contacts</t>
+        </is>
+      </c>
+      <c r="D176" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">メールアドレス</t>
+        </is>
+      </c>
+      <c r="E176" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">email</t>
+        </is>
+      </c>
+      <c r="F176" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G176" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H176" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YES</t>
+        </is>
+      </c>
+      <c r="I176" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J176" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K176" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="30" customHeight="1">
+      <c r="A177" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B177" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">医院業務連絡担当者</t>
+        </is>
+      </c>
+      <c r="C177" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_contacts</t>
+        </is>
+      </c>
+      <c r="D177" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">電話番号</t>
+        </is>
+      </c>
+      <c r="E177" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">phone</t>
+        </is>
+      </c>
+      <c r="F177" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G177" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H177" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YES</t>
+        </is>
+      </c>
+      <c r="I177" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J177" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K177" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="30" customHeight="1">
+      <c r="A178" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B178" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">医院業務連絡担当者</t>
+        </is>
+      </c>
+      <c r="C178" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_contacts</t>
+        </is>
+      </c>
+      <c r="D178" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主担当</t>
+        </is>
+      </c>
+      <c r="E178" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">is_primary</t>
+        </is>
+      </c>
+      <c r="F178" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">boolean</t>
+        </is>
+      </c>
+      <c r="G178" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H178" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I178" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="J178" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K178" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="30" customHeight="1">
+      <c r="A179" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B179" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">医院業務連絡担当者</t>
+        </is>
+      </c>
+      <c r="C179" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_contacts</t>
+        </is>
+      </c>
+      <c r="D179" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">状態</t>
+        </is>
+      </c>
+      <c r="E179" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">status</t>
+        </is>
+      </c>
+      <c r="F179" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G179" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H179" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I179" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active</t>
+        </is>
+      </c>
+      <c r="J179" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">active / inactive</t>
+        </is>
+      </c>
+      <c r="K179" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="180" ht="30" customHeight="1">
+      <c r="A180" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B180" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">医院業務連絡担当者</t>
+        </is>
+      </c>
+      <c r="C180" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_contacts</t>
+        </is>
+      </c>
+      <c r="D180" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">備考</t>
+        </is>
+      </c>
+      <c r="E180" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">notes</t>
+        </is>
+      </c>
+      <c r="F180" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G180" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H180" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YES</t>
+        </is>
+      </c>
+      <c r="I180" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J180" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K180" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="181" ht="30" customHeight="1">
+      <c r="A181" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B181" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">医院業務連絡担当者</t>
+        </is>
+      </c>
+      <c r="C181" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_contacts</t>
+        </is>
+      </c>
+      <c r="D181" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">排他バージョン</t>
+        </is>
+      </c>
+      <c r="E181" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">version</t>
+        </is>
+      </c>
+      <c r="F181" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">integer</t>
+        </is>
+      </c>
+      <c r="G181" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H181" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I181" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="J181" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K181" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="182" ht="30" customHeight="1">
+      <c r="A182" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B182" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">医院業務連絡担当者</t>
+        </is>
+      </c>
+      <c r="C182" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_contacts</t>
+        </is>
+      </c>
+      <c r="D182" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">論理削除日時</t>
+        </is>
+      </c>
+      <c r="E182" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">deleted_at</t>
+        </is>
+      </c>
+      <c r="F182" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">timestamptz</t>
+        </is>
+      </c>
+      <c r="G182" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H182" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YES</t>
+        </is>
+      </c>
+      <c r="I182" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J182" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K182" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="183" ht="30" customHeight="1">
+      <c r="A183" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B183" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">医院業務連絡担当者</t>
+        </is>
+      </c>
+      <c r="C183" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_contacts</t>
+        </is>
+      </c>
+      <c r="D183" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">作成日時</t>
+        </is>
+      </c>
+      <c r="E183" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">created_at</t>
+        </is>
+      </c>
+      <c r="F183" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">timestamptz</t>
+        </is>
+      </c>
+      <c r="G183" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H183" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I183" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">now()</t>
+        </is>
+      </c>
+      <c r="J183" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K183" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="30" customHeight="1">
+      <c r="A184" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B184" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">医院業務連絡担当者</t>
+        </is>
+      </c>
+      <c r="C184" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_contacts</t>
+        </is>
+      </c>
+      <c r="D184" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">更新日時</t>
+        </is>
+      </c>
+      <c r="E184" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">updated_at</t>
+        </is>
+      </c>
+      <c r="F184" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">timestamptz</t>
+        </is>
+      </c>
+      <c r="G184" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H184" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I184" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">now()</t>
+        </is>
+      </c>
+      <c r="J184" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K184" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="30" customHeight="1">
+      <c r="A185" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B185" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">担当者通知設定</t>
+        </is>
+      </c>
+      <c r="C185" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_contact_notification_preferences</t>
+        </is>
+      </c>
+      <c r="D185" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">担当者ID</t>
+        </is>
+      </c>
+      <c r="E185" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">contact_id</t>
+        </is>
+      </c>
+      <c r="F185" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">uuid</t>
+        </is>
+      </c>
+      <c r="G185" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK / FK</t>
+        </is>
+      </c>
+      <c r="H185" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I185" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J185" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_contacts.id ON DELETE RESTRICT</t>
+        </is>
+      </c>
+      <c r="K185" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="186" ht="30" customHeight="1">
+      <c r="A186" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B186" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">担当者通知設定</t>
+        </is>
+      </c>
+      <c r="C186" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_contact_notification_preferences</t>
+        </is>
+      </c>
+      <c r="D186" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">通知種別</t>
+        </is>
+      </c>
+      <c r="E186" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">topic</t>
+        </is>
+      </c>
+      <c r="F186" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G186" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK</t>
+        </is>
+      </c>
+      <c r="H186" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I186" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J186" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">webinar / orders / billing / product / system / sales</t>
+        </is>
+      </c>
+      <c r="K186" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="187" ht="30" customHeight="1">
+      <c r="A187" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B187" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">担当者通知設定</t>
+        </is>
+      </c>
+      <c r="C187" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_contact_notification_preferences</t>
+        </is>
+      </c>
+      <c r="D187" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">連絡方法</t>
+        </is>
+      </c>
+      <c r="E187" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">channel</t>
+        </is>
+      </c>
+      <c r="F187" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G187" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK</t>
+        </is>
+      </c>
+      <c r="H187" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I187" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J187" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">email / phone</t>
+        </is>
+      </c>
+      <c r="K187" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="188" ht="30" customHeight="1">
+      <c r="A188" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B188" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">担当者通知設定</t>
+        </is>
+      </c>
+      <c r="C188" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_contact_notification_preferences</t>
+        </is>
+      </c>
+      <c r="D188" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">有効</t>
+        </is>
+      </c>
+      <c r="E188" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">enabled</t>
+        </is>
+      </c>
+      <c r="F188" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">boolean</t>
+        </is>
+      </c>
+      <c r="G188" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H188" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I188" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">true</t>
+        </is>
+      </c>
+      <c r="J188" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K188" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="189" ht="30" customHeight="1">
+      <c r="A189" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B189" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">担当者通知設定</t>
+        </is>
+      </c>
+      <c r="C189" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_contact_notification_preferences</t>
+        </is>
+      </c>
+      <c r="D189" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">作成日時</t>
+        </is>
+      </c>
+      <c r="E189" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">created_at</t>
+        </is>
+      </c>
+      <c r="F189" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">timestamptz</t>
+        </is>
+      </c>
+      <c r="G189" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H189" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I189" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">now()</t>
+        </is>
+      </c>
+      <c r="J189" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K189" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="30" customHeight="1">
+      <c r="A190" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B190" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">担当者通知設定</t>
+        </is>
+      </c>
+      <c r="C190" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_contact_notification_preferences</t>
+        </is>
+      </c>
+      <c r="D190" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">更新日時</t>
+        </is>
+      </c>
+      <c r="E190" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">updated_at</t>
+        </is>
+      </c>
+      <c r="F190" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">timestamptz</t>
+        </is>
+      </c>
+      <c r="G190" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H190" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I190" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">now()</t>
+        </is>
+      </c>
+      <c r="J190" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K190" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="30" customHeight="1">
+      <c r="A191" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B191" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">担当者操作履歴</t>
+        </is>
+      </c>
+      <c r="C191" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_contact_events</t>
+        </is>
+      </c>
+      <c r="D191" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">イベントID</t>
+        </is>
+      </c>
+      <c r="E191" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">id</t>
+        </is>
+      </c>
+      <c r="F191" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">uuid</t>
+        </is>
+      </c>
+      <c r="G191" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK</t>
+        </is>
+      </c>
+      <c r="H191" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I191" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gen_random_uuid()</t>
+        </is>
+      </c>
+      <c r="J191" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K191" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="192" ht="30" customHeight="1">
+      <c r="A192" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B192" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">担当者操作履歴</t>
+        </is>
+      </c>
+      <c r="C192" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_contact_events</t>
+        </is>
+      </c>
+      <c r="D192" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">担当者ID</t>
+        </is>
+      </c>
+      <c r="E192" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">contact_id</t>
+        </is>
+      </c>
+      <c r="F192" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">uuid</t>
+        </is>
+      </c>
+      <c r="G192" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
+        </is>
+      </c>
+      <c r="H192" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I192" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J192" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_contacts.id ON DELETE RESTRICT</t>
+        </is>
+      </c>
+      <c r="K192" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="30" customHeight="1">
+      <c r="A193" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B193" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">担当者操作履歴</t>
+        </is>
+      </c>
+      <c r="C193" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_contact_events</t>
+        </is>
+      </c>
+      <c r="D193" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">イベント種別</t>
+        </is>
+      </c>
+      <c r="E193" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">event_type</t>
+        </is>
+      </c>
+      <c r="F193" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G193" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H193" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I193" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J193" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K193" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="194" ht="30" customHeight="1">
+      <c r="A194" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B194" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">担当者操作履歴</t>
+        </is>
+      </c>
+      <c r="C194" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_contact_events</t>
+        </is>
+      </c>
+      <c r="D194" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">操作者種別</t>
+        </is>
+      </c>
+      <c r="E194" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actor_type</t>
+        </is>
+      </c>
+      <c r="F194" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G194" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H194" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I194" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J194" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K194" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="195" ht="30" customHeight="1">
+      <c r="A195" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B195" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">担当者操作履歴</t>
+        </is>
+      </c>
+      <c r="C195" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_contact_events</t>
+        </is>
+      </c>
+      <c r="D195" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">操作者識別子</t>
+        </is>
+      </c>
+      <c r="E195" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actor_identifier</t>
+        </is>
+      </c>
+      <c r="F195" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G195" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H195" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I195" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J195" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K195" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="196" ht="30" customHeight="1">
+      <c r="A196" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B196" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">担当者操作履歴</t>
+        </is>
+      </c>
+      <c r="C196" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_contact_events</t>
+        </is>
+      </c>
+      <c r="D196" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">発生日時</t>
+        </is>
+      </c>
+      <c r="E196" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">created_at</t>
+        </is>
+      </c>
+      <c r="F196" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">timestamptz</t>
+        </is>
+      </c>
+      <c r="G196" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H196" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I196" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">now()</t>
+        </is>
+      </c>
+      <c r="J196" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K196" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A2:K2"/>
   </mergeCells>
-  <autoFilter ref="A4:K169"/>
+  <autoFilter ref="A4:K196"/>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0" paperSize="9"/>
 </worksheet>
@@ -15696,7 +17331,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G63"/>
+  <dimension ref="A1:G70"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -16238,96 +17873,96 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">将来案</t>
+          <t xml:space="preserve">現行</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">UK1</t>
+          <t xml:space="preserve">UK10</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_accounts</t>
+          <t xml:space="preserve">clinic_contacts</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">provider, external_account_id</t>
+          <t xml:space="preserve">customer_code WHERE is_primary AND status='active' AND deleted_at IS NULL</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNIQUE</t>
+          <t xml:space="preserve">PARTIAL UNIQUE</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部接続先の重複防止。</t>
+          <t xml:space="preserve">医院ごとの有効な主担当を1人に限定。</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">将来案</t>
+          <t xml:space="preserve">現行</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">UK2</t>
+          <t xml:space="preserve">UK11</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_fulfillment_items</t>
+          <t xml:space="preserve">clinic_contacts</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">fulfillment_id, order_item_id</t>
+          <t xml:space="preserve">customer_code, lower(email) WHERE deleted_at IS NULL</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNIQUE</t>
+          <t xml:space="preserve">PARTIAL UNIQUE</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">同一配送への明細重複防止。</t>
+          <t xml:space="preserve">医院内の担当者メール重複防止。</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">将来案</t>
+          <t xml:space="preserve">現行</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">UK3</t>
+          <t xml:space="preserve">UK12</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_subscriptions</t>
+          <t xml:space="preserve">clinic_contacts</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_account_id, external_subscription_id</t>
+          <t xml:space="preserve">clinic_user_id WHERE deleted_at IS NULL</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNIQUE</t>
+          <t xml:space="preserve">PARTIAL UNIQUE</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部契約の重複防止。</t>
+          <t xml:space="preserve">1ログインと複数担当者の誤関連防止。</t>
         </is>
       </c>
     </row>
@@ -16339,17 +17974,17 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">UK4</t>
+          <t xml:space="preserve">UK1</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_webhook_events</t>
+          <t xml:space="preserve">commerce_accounts</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_account_id, external_event_id</t>
+          <t xml:space="preserve">provider, external_account_id</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
@@ -16359,7 +17994,7 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Webhook重複配信の無害化。</t>
+          <t xml:space="preserve">外部接続先の重複防止。</t>
         </is>
       </c>
     </row>
@@ -16371,17 +18006,17 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">UK5</t>
+          <t xml:space="preserve">UK2</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders</t>
+          <t xml:space="preserve">patient_fulfillment_items</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_account_id, external_order_id</t>
+          <t xml:space="preserve">fulfillment_id, order_item_id</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
@@ -16391,7 +18026,7 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">複数ストアを考慮した外部注文の一意性。</t>
+          <t xml:space="preserve">同一配送への明細重複防止。</t>
         </is>
       </c>
     </row>
@@ -16403,182 +18038,167 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">UK3</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscriptions</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">commerce_account_id, external_subscription_id</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UNIQUE</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">外部契約の重複防止。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">将来案</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UK4</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">commerce_webhook_events</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">commerce_account_id, external_event_id</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UNIQUE</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Webhook重複配信の無害化。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">将来案</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UK5</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_orders</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">commerce_account_id, external_order_id</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UNIQUE</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">複数ストアを考慮した外部注文の一意性。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">将来案</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">UK6</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">commerce_outbox</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D28" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">idempotency_key</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
+      <c r="E28" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">UNIQUE</t>
         </is>
       </c>
-      <c r="F25" s="4" t="inlineStr">
+      <c r="F28" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">外部送信コマンドの二重実行防止。</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">現行リレーション</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">親DB日本語名</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">親KEY</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">親多重度</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">子多重度</t>
         </is>
       </c>
-      <c r="E28" s="3" t="inlineStr">
+      <c r="E31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">子FK</t>
         </is>
       </c>
-      <c r="F28" s="3" t="inlineStr">
+      <c r="F31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">子DB日本語名</t>
         </is>
       </c>
-      <c r="G28" s="3" t="inlineStr">
+      <c r="G31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">削除・備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">医院</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">clinics.customer_code</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0..1</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">clinic_terms.customer_code</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">医院契約情報</t>
-        </is>
-      </c>
-      <c r="G29" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PK・FK・CASCADE</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">医院</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">clinics.customer_code</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">clinic_product_settings.customer_code</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">医院商品設定</t>
-        </is>
-      </c>
-      <c r="G30" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PK・FK・CASCADE</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">商品</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">products.id</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">clinic_product_settings.product_id</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">医院商品設定</t>
-        </is>
-      </c>
-      <c r="G31" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PK・FK・CASCADE</t>
         </is>
       </c>
     </row>
@@ -16600,34 +18220,34 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">N</t>
+          <t xml:space="preserve">0..1</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders.customer_code</t>
+          <t xml:space="preserve">clinic_terms.customer_code</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文</t>
+          <t xml:space="preserve">医院契約情報</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK</t>
+          <t xml:space="preserve">PK・FK・CASCADE</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者</t>
+          <t xml:space="preserve">医院</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patients.id</t>
+          <t xml:space="preserve">clinics.customer_code</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -16642,29 +18262,29 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders.patient_id</t>
+          <t xml:space="preserve">clinic_product_settings.customer_code</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文</t>
+          <t xml:space="preserve">医院商品設定</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK・現状CASCADE</t>
+          <t xml:space="preserve">PK・FK・CASCADE</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文</t>
+          <t xml:space="preserve">商品</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders.id</t>
+          <t xml:space="preserve">products.id</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -16679,17 +18299,17 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_order_items.order_id</t>
+          <t xml:space="preserve">clinic_product_settings.product_id</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文明細</t>
+          <t xml:space="preserve">医院商品設定</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK・CASCADE</t>
+          <t xml:space="preserve">PK・FK・CASCADE</t>
         </is>
       </c>
     </row>
@@ -16716,17 +18336,17 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery_destinations.clinic_customer_code</t>
+          <t xml:space="preserve">patient_orders.customer_code</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">送り先マスタ</t>
+          <t xml:space="preserve">患者注文</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK・RESTRICT</t>
+          <t xml:space="preserve">FK</t>
         </is>
       </c>
     </row>
@@ -16753,29 +18373,29 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery_destinations.patient_id</t>
+          <t xml:space="preserve">patient_orders.patient_id</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">送り先マスタ</t>
+          <t xml:space="preserve">患者注文</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK・RESTRICT</t>
+          <t xml:space="preserve">FK・現状CASCADE</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">送り先マスタ</t>
+          <t xml:space="preserve">患者注文</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery_destinations.id</t>
+          <t xml:space="preserve">patient_orders.id</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -16790,29 +18410,29 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">order_delivery_destinations.delivery_destination_id</t>
+          <t xml:space="preserve">patient_order_items.order_id</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文配送先</t>
+          <t xml:space="preserve">患者注文明細</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK・RESTRICT</t>
+          <t xml:space="preserve">FK・CASCADE</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文</t>
+          <t xml:space="preserve">医院</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders.id</t>
+          <t xml:space="preserve">clinics.customer_code</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -16822,34 +18442,34 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">0..1</t>
+          <t xml:space="preserve">N</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">order_delivery_destinations.order_id</t>
+          <t xml:space="preserve">delivery_destinations.clinic_customer_code</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文配送先</t>
+          <t xml:space="preserve">送り先マスタ</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">PK・FK・CASCADE</t>
+          <t xml:space="preserve">FK・RESTRICT</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文</t>
+          <t xml:space="preserve">患者</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders.id</t>
+          <t xml:space="preserve">patients.id</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -16864,34 +18484,34 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_order_events.order_id</t>
+          <t xml:space="preserve">delivery_destinations.patient_id</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文操作履歴</t>
+          <t xml:space="preserve">送り先マスタ</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK・CASCADE</t>
+          <t xml:space="preserve">FK・RESTRICT</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">商品</t>
+          <t xml:space="preserve">送り先マスタ</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">products.id</t>
+          <t xml:space="preserve">delivery_destinations.id</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">0..1</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -16901,29 +18521,29 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_order_items.product_id</t>
+          <t xml:space="preserve">order_delivery_destinations.delivery_destination_id</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文明細</t>
+          <t xml:space="preserve">注文配送先</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK・SET NULL</t>
+          <t xml:space="preserve">FK・RESTRICT</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院</t>
+          <t xml:space="preserve">患者注文</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinics.customer_code</t>
+          <t xml:space="preserve">patient_orders.id</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -16933,34 +18553,34 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">N</t>
+          <t xml:space="preserve">0..1</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_subscription_requests.customer_code</t>
+          <t xml:space="preserve">order_delivery_destinations.order_id</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">定期購入申込</t>
+          <t xml:space="preserve">注文配送先</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK・RESTRICT</t>
+          <t xml:space="preserve">PK・FK・CASCADE</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者</t>
+          <t xml:space="preserve">患者注文</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patients.id</t>
+          <t xml:space="preserve">patient_orders.id</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -16975,34 +18595,34 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_subscription_requests.patient_id</t>
+          <t xml:space="preserve">patient_order_events.order_id</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">定期購入申込</t>
+          <t xml:space="preserve">注文操作履歴</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK・RESTRICT</t>
+          <t xml:space="preserve">FK・CASCADE</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">定期購入申込</t>
+          <t xml:space="preserve">商品</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_subscription_requests.id</t>
+          <t xml:space="preserve">products.id</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">0..1</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -17012,103 +18632,103 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_subscription_request_items.request_id</t>
+          <t xml:space="preserve">patient_order_items.product_id</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">定期購入申込明細</t>
+          <t xml:space="preserve">患者注文明細</t>
         </is>
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK・CASCADE</t>
+          <t xml:space="preserve">FK・SET NULL</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">医院</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinics.customer_code</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscription_requests.customer_code</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">定期購入申込</t>
         </is>
       </c>
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">patient_subscription_requests.id</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="D44" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0..1</t>
-        </is>
-      </c>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">patient_subscription_request_destinations.request_id</t>
-        </is>
-      </c>
-      <c r="F44" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">定期購入申込配送先</t>
-        </is>
-      </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">PK・FK・CASCADE</t>
+          <t xml:space="preserve">FK・RESTRICT</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">患者</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patients.id</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscription_requests.patient_id</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">定期購入申込</t>
         </is>
       </c>
-      <c r="B45" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">patient_subscription_requests.id</t>
-        </is>
-      </c>
-      <c r="C45" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="D45" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">patient_subscription_request_events.request_id</t>
-        </is>
-      </c>
-      <c r="F45" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">定期購入申込履歴</t>
-        </is>
-      </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK・CASCADE</t>
+          <t xml:space="preserve">FK・RESTRICT</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">送り先マスタ</t>
+          <t xml:space="preserve">定期購入申込</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery_destinations.id</t>
+          <t xml:space="preserve">patient_subscription_requests.id</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -17123,29 +18743,29 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_subscription_request_destinations.delivery_destination_id</t>
+          <t xml:space="preserve">patient_subscription_request_items.request_id</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">定期購入申込配送先</t>
+          <t xml:space="preserve">定期購入申込明細</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK・RESTRICT</t>
+          <t xml:space="preserve">FK・CASCADE</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ウェビナー</t>
+          <t xml:space="preserve">定期購入申込</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">webinars.id</t>
+          <t xml:space="preserve">patient_subscription_requests.id</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -17155,34 +18775,34 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">N</t>
+          <t xml:space="preserve">0..1</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">webinar_sessions.webinar_id</t>
+          <t xml:space="preserve">patient_subscription_request_destinations.request_id</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ウェビナー開催枠</t>
+          <t xml:space="preserve">定期購入申込配送先</t>
         </is>
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK・CASCADE</t>
+          <t xml:space="preserve">PK・FK・CASCADE</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ウェビナー</t>
+          <t xml:space="preserve">定期購入申込</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">webinars.id</t>
+          <t xml:space="preserve">patient_subscription_requests.id</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -17197,29 +18817,29 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">webinar_target_clinics.webinar_id</t>
+          <t xml:space="preserve">patient_subscription_request_events.request_id</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ウェビナー対象医院</t>
+          <t xml:space="preserve">定期購入申込履歴</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">PK・FK・CASCADE</t>
+          <t xml:space="preserve">FK・CASCADE</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院</t>
+          <t xml:space="preserve">送り先マスタ</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinics.customer_code</t>
+          <t xml:space="preserve">delivery_destinations.id</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -17234,17 +18854,17 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">webinar_target_clinics.customer_code</t>
+          <t xml:space="preserve">patient_subscription_request_destinations.delivery_destination_id</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ウェビナー対象医院</t>
+          <t xml:space="preserve">定期購入申込配送先</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">PK・FK・RESTRICT</t>
+          <t xml:space="preserve">FK・RESTRICT</t>
         </is>
       </c>
     </row>
@@ -17271,73 +18891,140 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">webinar_sessions.webinar_id</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ウェビナー開催枠</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK・CASCADE</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ウェビナー</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">webinars.id</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">webinar_target_clinics.webinar_id</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ウェビナー対象医院</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK・FK・CASCADE</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">医院</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinics.customer_code</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">webinar_target_clinics.customer_code</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ウェビナー対象医院</t>
+        </is>
+      </c>
+      <c r="G52" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK・FK・RESTRICT</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ウェビナー</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">webinars.id</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">webinar_events.webinar_id</t>
         </is>
       </c>
-      <c r="F50" s="4" t="inlineStr">
+      <c r="F53" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">ウェビナー操作履歴</t>
         </is>
       </c>
-      <c r="G50" s="4" t="inlineStr">
+      <c r="G53" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">FK・CASCADE</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">将来リレーション案</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">親DB日本語名</t>
-        </is>
-      </c>
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">親KEY</t>
-        </is>
-      </c>
-      <c r="C53" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">親多重度</t>
-        </is>
-      </c>
-      <c r="D53" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">子多重度</t>
-        </is>
-      </c>
-      <c r="E53" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">子FK</t>
-        </is>
-      </c>
-      <c r="F53" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">子DB日本語名</t>
-        </is>
-      </c>
-      <c r="G53" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">削除・備考</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文</t>
+          <t xml:space="preserve">医院</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders.id</t>
+          <t xml:space="preserve">clinics.customer_code</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -17352,29 +19039,29 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">order_transaction_projections.order_id</t>
+          <t xml:space="preserve">clinic_contacts.customer_code</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">決済返金投影</t>
+          <t xml:space="preserve">医院業務連絡担当者</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK</t>
+          <t xml:space="preserve">FK・RESTRICT</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文</t>
+          <t xml:space="preserve">医院ログイン</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders.id</t>
+          <t xml:space="preserve">clinic_users.id</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -17384,34 +19071,34 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">N</t>
+          <t xml:space="preserve">0..1</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_fulfillments.order_id</t>
+          <t xml:space="preserve">clinic_contacts.clinic_user_id</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">受取配送</t>
+          <t xml:space="preserve">医院業務連絡担当者</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK</t>
+          <t xml:space="preserve">FK・SET NULL</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">受取配送</t>
+          <t xml:space="preserve">医院業務連絡担当者</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_fulfillments.id</t>
+          <t xml:space="preserve">clinic_contacts.id</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -17426,29 +19113,29 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_fulfillment_items.fulfillment_id</t>
+          <t xml:space="preserve">clinic_contact_notification_preferences.contact_id</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">受取配送明細</t>
+          <t xml:space="preserve">担当者通知設定</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK</t>
+          <t xml:space="preserve">PK・FK・RESTRICT</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文明細</t>
+          <t xml:space="preserve">医院業務連絡担当者</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_order_items.id</t>
+          <t xml:space="preserve">clinic_contacts.id</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -17463,140 +19150,73 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_fulfillment_items.order_item_id</t>
+          <t xml:space="preserve">clinic_contact_events.contact_id</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">受取配送明細</t>
+          <t xml:space="preserve">担当者操作履歴</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">外部コマース接続</t>
-        </is>
-      </c>
-      <c r="B58" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">commerce_accounts.id</t>
-        </is>
-      </c>
-      <c r="C58" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="D58" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="E58" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">patient_orders.commerce_account_id</t>
-        </is>
-      </c>
-      <c r="F58" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">患者注文</t>
-        </is>
-      </c>
-      <c r="G58" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FK</t>
+          <t xml:space="preserve">FK・RESTRICT</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">外部コマース接続</t>
-        </is>
-      </c>
-      <c r="B59" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">commerce_accounts.id</t>
-        </is>
-      </c>
-      <c r="C59" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="D59" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="E59" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">commerce_webhook_events.commerce_account_id</t>
-        </is>
-      </c>
-      <c r="F59" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">外部受信イベント</t>
-        </is>
-      </c>
-      <c r="G59" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FK</t>
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">将来リレーション案</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">外部コマース接続</t>
-        </is>
-      </c>
-      <c r="B60" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">commerce_accounts.id</t>
-        </is>
-      </c>
-      <c r="C60" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="D60" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="E60" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">commerce_outbox.commerce_account_id</t>
-        </is>
-      </c>
-      <c r="F60" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">外部送信キュー</t>
-        </is>
-      </c>
-      <c r="G60" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FK</t>
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">親DB日本語名</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">親KEY</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">親多重度</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">子多重度</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">子FK</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">子DB日本語名</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">削除・備考</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者</t>
+          <t xml:space="preserve">患者注文</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patients.id</t>
+          <t xml:space="preserve">patient_orders.id</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -17611,12 +19231,12 @@
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_subscriptions.patient_id</t>
+          <t xml:space="preserve">order_transaction_projections.order_id</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者定期購入</t>
+          <t xml:space="preserve">決済返金投影</t>
         </is>
       </c>
       <c r="G61" s="4" t="inlineStr">
@@ -17628,12 +19248,12 @@
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者定期購入</t>
+          <t xml:space="preserve">患者注文</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_subscriptions.id</t>
+          <t xml:space="preserve">patient_orders.id</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -17648,12 +19268,12 @@
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_subscription_items.subscription_id</t>
+          <t xml:space="preserve">patient_fulfillments.order_id</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">定期購入明細</t>
+          <t xml:space="preserve">受取配送</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr">
@@ -17665,35 +19285,294 @@
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">受取配送</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_fulfillments.id</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_fulfillment_items.fulfillment_id</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">受取配送明細</t>
+        </is>
+      </c>
+      <c r="G63" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">注文明細</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_order_items.id</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_fulfillment_items.order_item_id</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">受取配送明細</t>
+        </is>
+      </c>
+      <c r="G64" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">外部コマース接続</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">commerce_accounts.id</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_orders.commerce_account_id</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">患者注文</t>
+        </is>
+      </c>
+      <c r="G65" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">外部コマース接続</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">commerce_accounts.id</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">commerce_webhook_events.commerce_account_id</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">外部受信イベント</t>
+        </is>
+      </c>
+      <c r="G66" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">外部コマース接続</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">commerce_accounts.id</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">commerce_outbox.commerce_account_id</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">外部送信キュー</t>
+        </is>
+      </c>
+      <c r="G67" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">患者</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patients.id</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscriptions.patient_id</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">患者定期購入</t>
         </is>
       </c>
-      <c r="B63" s="4" t="inlineStr">
+      <c r="G68" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">患者定期購入</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">patient_subscriptions.id</t>
         </is>
       </c>
-      <c r="C63" s="4" t="inlineStr">
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscription_items.subscription_id</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">定期購入明細</t>
+        </is>
+      </c>
+      <c r="G69" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">患者定期購入</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscriptions.id</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">0..1</t>
         </is>
       </c>
-      <c r="D63" s="4" t="inlineStr">
+      <c r="D70" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="E63" s="4" t="inlineStr">
+      <c r="E70" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">patient_orders.subscription_id</t>
         </is>
       </c>
-      <c r="F63" s="4" t="inlineStr">
+      <c r="F70" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">患者注文</t>
         </is>
       </c>
-      <c r="G63" s="4" t="inlineStr">
+      <c r="G70" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">FK</t>
         </is>
@@ -17703,8 +19582,8 @@
   <mergeCells count="4">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A27:H27"/>
-    <mergeCell ref="A52:H52"/>
+    <mergeCell ref="A30:H30"/>
+    <mergeCell ref="A59:H59"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0" paperSize="9"/>
@@ -17713,7 +19592,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Q95"/>
+  <dimension ref="A1:Q99"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -19653,6 +21532,154 @@
       <c r="G95" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">FK・CASCADE</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">医院</t>
+        </is>
+      </c>
+      <c r="B96" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinics.customer_code</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D96" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E96" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_contacts.customer_code</t>
+        </is>
+      </c>
+      <c r="F96" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">医院業務連絡担当者</t>
+        </is>
+      </c>
+      <c r="G96" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK・RESTRICT</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">医院ログイン</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_users.id</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D97" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0..1</t>
+        </is>
+      </c>
+      <c r="E97" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_contacts.clinic_user_id</t>
+        </is>
+      </c>
+      <c r="F97" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">医院業務連絡担当者</t>
+        </is>
+      </c>
+      <c r="G97" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK・SET NULL</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">医院業務連絡担当者</t>
+        </is>
+      </c>
+      <c r="B98" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_contacts.id</t>
+        </is>
+      </c>
+      <c r="C98" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D98" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E98" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_contact_notification_preferences.contact_id</t>
+        </is>
+      </c>
+      <c r="F98" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">担当者通知設定</t>
+        </is>
+      </c>
+      <c r="G98" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK・FK・RESTRICT</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">医院業務連絡担当者</t>
+        </is>
+      </c>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_contacts.id</t>
+        </is>
+      </c>
+      <c r="C99" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D99" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E99" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_contact_events.contact_id</t>
+        </is>
+      </c>
+      <c r="F99" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">担当者操作履歴</t>
+        </is>
+      </c>
+      <c r="G99" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK・RESTRICT</t>
         </is>
       </c>
     </row>

--- a/project_clinic_order_management_db_definition.xlsx
+++ b/project_clinic_order_management_db_definition.xlsx
@@ -476,7 +476,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -1149,22 +1149,22 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">担当者通知設定</t>
+          <t xml:space="preserve">医院ポータルログイン</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_contact_notification_preferences</t>
+          <t xml:space="preserve">clinic_users</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">実装済み</t>
+          <t xml:space="preserve">実装済み・Phase 1</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">担当者ごとの連絡内容と方法を多値属性として分離する。</t>
+          <t xml:space="preserve">認証情報とセッション世代を保持する。担当者プロフィールとはclinic_contactsで関連する。</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
@@ -1181,22 +1181,22 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">担当者操作履歴</t>
+          <t xml:space="preserve">医院ポータル権限</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_contact_events</t>
+          <t xml:space="preserve">clinic_portal_roles</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">実装済み</t>
+          <t xml:space="preserve">実装済み・Phase 1</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">登録・更新・無効化・主担当変更・論理削除を監査保存する。</t>
+          <t xml:space="preserve">管理者・一般・閲覧専用の権限マスタ。</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
@@ -1208,27 +1208,27 @@
     <row r="26" ht="34" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shopify接続</t>
+          <t xml:space="preserve">現行</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部コマース接続</t>
+          <t xml:space="preserve">医院ポータル権限機能</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_accounts</t>
+          <t xml:space="preserve">clinic_portal_role_permissions</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">将来案</t>
+          <t xml:space="preserve">実装済み・Phase 1</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shopifyストア等の外部接続先。医院との対応方式は接続構成確定後に決定する。</t>
+          <t xml:space="preserve">権限と操作可能な機能を多対多で管理する。</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -1240,27 +1240,27 @@
     <row r="27" ht="34" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shopify接続</t>
+          <t xml:space="preserve">現行</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文拡張</t>
+          <t xml:space="preserve">医院ログイン権限割当</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders</t>
+          <t xml:space="preserve">clinic_user_role_assignments</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">既存テーブル拡張案</t>
+          <t xml:space="preserve">実装済み・Phase 1</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">既存IDを維持し、外部・金額・排他制御の列を追加する。</t>
+          <t xml:space="preserve">1ログインに1権限を割り当て、認証情報と権限マスタを分離する。</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -1272,27 +1272,27 @@
     <row r="28" ht="34" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shopify接続</t>
+          <t xml:space="preserve">現行</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文明細拡張</t>
+          <t xml:space="preserve">担当者通知設定</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_order_items</t>
+          <t xml:space="preserve">clinic_contact_notification_preferences</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">既存テーブル拡張案</t>
+          <t xml:space="preserve">実装済み</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部明細と通貨を明確化し、既存スナップショットを維持する。</t>
+          <t xml:space="preserve">担当者ごとの連絡内容と方法を多値属性として分離する。</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
@@ -1304,27 +1304,27 @@
     <row r="29" ht="34" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">決済接続</t>
+          <t xml:space="preserve">現行</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">決済返金投影</t>
+          <t xml:space="preserve">担当者操作履歴</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">order_transaction_projections</t>
+          <t xml:space="preserve">clinic_contact_events</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">将来案</t>
+          <t xml:space="preserve">実装済み</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shopify上の決済・返金を表示する投影。会計台帳ではない。</t>
+          <t xml:space="preserve">登録・更新・無効化・主担当変更・論理削除を監査保存する。</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
@@ -1336,17 +1336,17 @@
     <row r="30" ht="34" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">配送開始</t>
+          <t xml:space="preserve">Shopify接続</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">受取配送</t>
+          <t xml:space="preserve">外部コマース接続</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_fulfillments</t>
+          <t xml:space="preserve">commerce_accounts</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院受け取り・配送・部分引き渡しの単位。</t>
+          <t xml:space="preserve">Shopifyストア等の外部接続先。医院との対応方式は接続構成確定後に決定する。</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
@@ -1368,27 +1368,27 @@
     <row r="31" ht="34" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">配送開始</t>
+          <t xml:space="preserve">Shopify接続</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">受取配送明細</t>
+          <t xml:space="preserve">患者注文拡張</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_fulfillment_items</t>
+          <t xml:space="preserve">patient_orders</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">将来案</t>
+          <t xml:space="preserve">既存テーブル拡張案</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">部分受け取り・部分配送時の対象明細と数量。</t>
+          <t xml:space="preserve">既存IDを維持し、外部・金額・排他制御の列を追加する。</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -1400,27 +1400,27 @@
     <row r="32" ht="34" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">定期購入接続</t>
+          <t xml:space="preserve">Shopify接続</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者定期購入</t>
+          <t xml:space="preserve">患者注文明細拡張</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_subscriptions</t>
+          <t xml:space="preserve">patient_order_items</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">将来案</t>
+          <t xml:space="preserve">既存テーブル拡張案</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shopify上の定期購入契約を患者ポータルへ表示する投影。</t>
+          <t xml:space="preserve">外部明細と通貨を明確化し、既存スナップショットを維持する。</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -1432,17 +1432,17 @@
     <row r="33" ht="34" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">定期購入接続</t>
+          <t xml:space="preserve">決済接続</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">定期購入明細</t>
+          <t xml:space="preserve">決済返金投影</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_subscription_items</t>
+          <t xml:space="preserve">order_transaction_projections</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">契約時点の商品・数量・単価の投影。</t>
+          <t xml:space="preserve">Shopify上の決済・返金を表示する投影。会計台帳ではない。</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -1464,17 +1464,17 @@
     <row r="34" ht="34" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shopify接続</t>
+          <t xml:space="preserve">配送開始</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部受信イベント</t>
+          <t xml:space="preserve">受取配送</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_webhook_events</t>
+          <t xml:space="preserve">patient_fulfillments</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Webhookを先に永続化し、重複排除・再試行するInbox。</t>
+          <t xml:space="preserve">医院受け取り・配送・部分引き渡しの単位。</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -1496,62 +1496,190 @@
     <row r="35" ht="34" customHeight="1">
       <c r="A35" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">配送開始</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">受取配送明細</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_fulfillment_items</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">将来案</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">部分受け取り・部分配送時の対象明細と数量。</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="34" customHeight="1">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">定期購入接続</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">患者定期購入</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscriptions</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">将来案</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shopify上の定期購入契約を患者ポータルへ表示する投影。</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="34" customHeight="1">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">定期購入接続</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">定期購入明細</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscription_items</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">将来案</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">契約時点の商品・数量・単価の投影。</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="34" customHeight="1">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">Shopify接続</t>
         </is>
       </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">外部受信イベント</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">commerce_webhook_events</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">将来案</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Webhookを先に永続化し、重複排除・再試行するInbox。</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="34" customHeight="1">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shopify接続</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">外部送信キュー</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">commerce_outbox</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="D39" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">将来案</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
+      <c r="E39" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">外部APIへ送る処理を永続化するOutbox。</t>
         </is>
       </c>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="8" t="inlineStr">
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">別ドメイン</t>
         </is>
       </c>
-      <c r="B36" s="8" t="inlineStr">
+      <c r="B40" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">医院仕入注文</t>
         </is>
       </c>
-      <c r="C36" s="8" t="inlineStr">
+      <c r="C40" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">clinic_orders</t>
         </is>
       </c>
-      <c r="D36" s="8" t="inlineStr">
+      <c r="D40" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">実装済み</t>
         </is>
       </c>
-      <c r="E36" s="8" t="inlineStr">
+      <c r="E40" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">BGJから医院へのB2B仕入・売上履歴</t>
         </is>
       </c>
-      <c r="F36" s="8" t="inlineStr">
+      <c r="F40" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">患者注文系列へ統合しない</t>
         </is>
@@ -1562,7 +1690,7 @@
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
   </mergeCells>
-  <autoFilter ref="A4:F36"/>
+  <autoFilter ref="A4:F40"/>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0" paperSize="9"/>
 </worksheet>
@@ -1570,7 +1698,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K196"/>
+  <dimension ref="A1:K225"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -11925,22 +12053,22 @@
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">担当者通知設定</t>
+          <t xml:space="preserve">医院ポータルログイン</t>
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_contact_notification_preferences</t>
+          <t xml:space="preserve">clinic_users</t>
         </is>
       </c>
       <c r="D185" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">担当者ID</t>
+          <t xml:space="preserve">医院ログインID</t>
         </is>
       </c>
       <c r="E185" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">contact_id</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="F185" s="4" t="inlineStr">
@@ -11950,7 +12078,7 @@
       </c>
       <c r="G185" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">PK / FK</t>
+          <t xml:space="preserve">PK</t>
         </is>
       </c>
       <c r="H185" s="4" t="inlineStr">
@@ -11960,12 +12088,12 @@
       </c>
       <c r="I185" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">gen_random_uuid()</t>
         </is>
       </c>
       <c r="J185" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_contacts.id ON DELETE RESTRICT</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K185" s="4" t="inlineStr">
@@ -11982,22 +12110,22 @@
       </c>
       <c r="B186" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">担当者通知設定</t>
+          <t xml:space="preserve">医院ポータルログイン</t>
         </is>
       </c>
       <c r="C186" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_contact_notification_preferences</t>
+          <t xml:space="preserve">clinic_users</t>
         </is>
       </c>
       <c r="D186" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">通知種別</t>
+          <t xml:space="preserve">得意先コード</t>
         </is>
       </c>
       <c r="E186" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">topic</t>
+          <t xml:space="preserve">customer_code</t>
         </is>
       </c>
       <c r="F186" s="4" t="inlineStr">
@@ -12005,9 +12133,9 @@
           <t xml:space="preserve">text</t>
         </is>
       </c>
-      <c r="G186" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PK</t>
+      <c r="G186" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
         </is>
       </c>
       <c r="H186" s="4" t="inlineStr">
@@ -12022,7 +12150,7 @@
       </c>
       <c r="J186" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">webinar / orders / billing / product / system / sales</t>
+          <t xml:space="preserve">clinics.customer_code ON DELETE CASCADE</t>
         </is>
       </c>
       <c r="K186" s="4" t="inlineStr">
@@ -12039,22 +12167,22 @@
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">担当者通知設定</t>
+          <t xml:space="preserve">医院ポータルログイン</t>
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_contact_notification_preferences</t>
+          <t xml:space="preserve">clinic_users</t>
         </is>
       </c>
       <c r="D187" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">連絡方法</t>
+          <t xml:space="preserve">ログインID</t>
         </is>
       </c>
       <c r="E187" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">channel</t>
+          <t xml:space="preserve">login_id</t>
         </is>
       </c>
       <c r="F187" s="4" t="inlineStr">
@@ -12062,9 +12190,9 @@
           <t xml:space="preserve">text</t>
         </is>
       </c>
-      <c r="G187" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PK</t>
+      <c r="G187" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UK</t>
         </is>
       </c>
       <c r="H187" s="4" t="inlineStr">
@@ -12079,7 +12207,7 @@
       </c>
       <c r="J187" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">email / phone</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K187" s="4" t="inlineStr">
@@ -12096,27 +12224,27 @@
       </c>
       <c r="B188" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">担当者通知設定</t>
+          <t xml:space="preserve">医院ポータルログイン</t>
         </is>
       </c>
       <c r="C188" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_contact_notification_preferences</t>
+          <t xml:space="preserve">clinic_users</t>
         </is>
       </c>
       <c r="D188" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">有効</t>
+          <t xml:space="preserve">パスワードハッシュ</t>
         </is>
       </c>
       <c r="E188" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">enabled</t>
+          <t xml:space="preserve">password_hash</t>
         </is>
       </c>
       <c r="F188" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">boolean</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="G188" s="4" t="inlineStr">
@@ -12131,7 +12259,7 @@
       </c>
       <c r="I188" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">true</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J188" s="4" t="inlineStr">
@@ -12153,27 +12281,27 @@
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">担当者通知設定</t>
+          <t xml:space="preserve">医院ポータルログイン</t>
         </is>
       </c>
       <c r="C189" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_contact_notification_preferences</t>
+          <t xml:space="preserve">clinic_users</t>
         </is>
       </c>
       <c r="D189" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">作成日時</t>
+          <t xml:space="preserve">表示名</t>
         </is>
       </c>
       <c r="E189" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">created_at</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="F189" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">timestamptz</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="G189" s="4" t="inlineStr">
@@ -12183,12 +12311,12 @@
       </c>
       <c r="H189" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO</t>
+          <t xml:space="preserve">YES</t>
         </is>
       </c>
       <c r="I189" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">now()</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J189" s="4" t="inlineStr">
@@ -12210,27 +12338,27 @@
       </c>
       <c r="B190" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">担当者通知設定</t>
+          <t xml:space="preserve">医院ポータルログイン</t>
         </is>
       </c>
       <c r="C190" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_contact_notification_preferences</t>
+          <t xml:space="preserve">clinic_users</t>
         </is>
       </c>
       <c r="D190" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">更新日時</t>
+          <t xml:space="preserve">メールアドレス</t>
         </is>
       </c>
       <c r="E190" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">updated_at</t>
+          <t xml:space="preserve">email</t>
         </is>
       </c>
       <c r="F190" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">timestamptz</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="G190" s="4" t="inlineStr">
@@ -12240,12 +12368,12 @@
       </c>
       <c r="H190" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO</t>
+          <t xml:space="preserve">YES</t>
         </is>
       </c>
       <c r="I190" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">now()</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J190" s="4" t="inlineStr">
@@ -12267,32 +12395,32 @@
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">担当者操作履歴</t>
+          <t xml:space="preserve">医院ポータルログイン</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_contact_events</t>
+          <t xml:space="preserve">clinic_users</t>
         </is>
       </c>
       <c r="D191" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">イベントID</t>
+          <t xml:space="preserve">状態</t>
         </is>
       </c>
       <c r="E191" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">status</t>
         </is>
       </c>
       <c r="F191" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">uuid</t>
-        </is>
-      </c>
-      <c r="G191" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PK</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G191" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H191" s="4" t="inlineStr">
@@ -12302,12 +12430,12 @@
       </c>
       <c r="I191" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">gen_random_uuid()</t>
+          <t xml:space="preserve">有効</t>
         </is>
       </c>
       <c r="J191" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">有効 / 無効</t>
         </is>
       </c>
       <c r="K191" s="4" t="inlineStr">
@@ -12324,32 +12452,32 @@
       </c>
       <c r="B192" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">担当者操作履歴</t>
+          <t xml:space="preserve">医院ポータルログイン</t>
         </is>
       </c>
       <c r="C192" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_contact_events</t>
+          <t xml:space="preserve">clinic_users</t>
         </is>
       </c>
       <c r="D192" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">担当者ID</t>
+          <t xml:space="preserve">作成日時</t>
         </is>
       </c>
       <c r="E192" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">contact_id</t>
+          <t xml:space="preserve">created_at</t>
         </is>
       </c>
       <c r="F192" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">uuid</t>
-        </is>
-      </c>
-      <c r="G192" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FK</t>
+          <t xml:space="preserve">timestamptz</t>
+        </is>
+      </c>
+      <c r="G192" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H192" s="4" t="inlineStr">
@@ -12359,12 +12487,12 @@
       </c>
       <c r="I192" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">now()</t>
         </is>
       </c>
       <c r="J192" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_contacts.id ON DELETE RESTRICT</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K192" s="4" t="inlineStr">
@@ -12381,27 +12509,27 @@
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">担当者操作履歴</t>
+          <t xml:space="preserve">医院ポータルログイン</t>
         </is>
       </c>
       <c r="C193" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_contact_events</t>
+          <t xml:space="preserve">clinic_users</t>
         </is>
       </c>
       <c r="D193" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">イベント種別</t>
+          <t xml:space="preserve">更新日時</t>
         </is>
       </c>
       <c r="E193" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">event_type</t>
+          <t xml:space="preserve">updated_at</t>
         </is>
       </c>
       <c r="F193" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">timestamptz</t>
         </is>
       </c>
       <c r="G193" s="4" t="inlineStr">
@@ -12416,7 +12544,7 @@
       </c>
       <c r="I193" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">now()</t>
         </is>
       </c>
       <c r="J193" s="4" t="inlineStr">
@@ -12438,27 +12566,27 @@
       </c>
       <c r="B194" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">担当者操作履歴</t>
+          <t xml:space="preserve">医院ポータルログイン</t>
         </is>
       </c>
       <c r="C194" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_contact_events</t>
+          <t xml:space="preserve">clinic_users</t>
         </is>
       </c>
       <c r="D194" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">操作者種別</t>
+          <t xml:space="preserve">ログイン失敗回数</t>
         </is>
       </c>
       <c r="E194" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">actor_type</t>
+          <t xml:space="preserve">failed_login_attempts</t>
         </is>
       </c>
       <c r="F194" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">integer</t>
         </is>
       </c>
       <c r="G194" s="4" t="inlineStr">
@@ -12473,7 +12601,7 @@
       </c>
       <c r="I194" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="J194" s="4" t="inlineStr">
@@ -12495,27 +12623,27 @@
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">担当者操作履歴</t>
+          <t xml:space="preserve">医院ポータルログイン</t>
         </is>
       </c>
       <c r="C195" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_contact_events</t>
+          <t xml:space="preserve">clinic_users</t>
         </is>
       </c>
       <c r="D195" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">操作者識別子</t>
+          <t xml:space="preserve">ロック解除日時</t>
         </is>
       </c>
       <c r="E195" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">actor_identifier</t>
+          <t xml:space="preserve">locked_until</t>
         </is>
       </c>
       <c r="F195" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">timestamptz</t>
         </is>
       </c>
       <c r="G195" s="4" t="inlineStr">
@@ -12525,7 +12653,7 @@
       </c>
       <c r="H195" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO</t>
+          <t xml:space="preserve">YES</t>
         </is>
       </c>
       <c r="I195" s="4" t="inlineStr">
@@ -12552,50 +12680,1703 @@
       </c>
       <c r="B196" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">医院ポータルログイン</t>
+        </is>
+      </c>
+      <c r="C196" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_users</t>
+        </is>
+      </c>
+      <c r="D196" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">セッション世代</t>
+        </is>
+      </c>
+      <c r="E196" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">session_version</t>
+        </is>
+      </c>
+      <c r="F196" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">integer</t>
+        </is>
+      </c>
+      <c r="G196" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H196" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I196" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="J196" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&gt; 0</t>
+        </is>
+      </c>
+      <c r="K196" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無効化・パスワード変更時に加算し旧セッションを失効</t>
+        </is>
+      </c>
+    </row>
+    <row r="197" ht="30" customHeight="1">
+      <c r="A197" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B197" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">医院ポータルログイン</t>
+        </is>
+      </c>
+      <c r="C197" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_users</t>
+        </is>
+      </c>
+      <c r="D197" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最終ログイン日時</t>
+        </is>
+      </c>
+      <c r="E197" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">last_login_at</t>
+        </is>
+      </c>
+      <c r="F197" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">timestamptz</t>
+        </is>
+      </c>
+      <c r="G197" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H197" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YES</t>
+        </is>
+      </c>
+      <c r="I197" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J197" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K197" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="198" ht="30" customHeight="1">
+      <c r="A198" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B198" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">医院ポータルログイン</t>
+        </is>
+      </c>
+      <c r="C198" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_users</t>
+        </is>
+      </c>
+      <c r="D198" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">パスワード変更日時</t>
+        </is>
+      </c>
+      <c r="E198" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">password_changed_at</t>
+        </is>
+      </c>
+      <c r="F198" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">timestamptz</t>
+        </is>
+      </c>
+      <c r="G198" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H198" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YES</t>
+        </is>
+      </c>
+      <c r="I198" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J198" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K198" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="199" ht="30" customHeight="1">
+      <c r="A199" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B199" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">医院ポータル権限</t>
+        </is>
+      </c>
+      <c r="C199" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_portal_roles</t>
+        </is>
+      </c>
+      <c r="D199" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">権限キー</t>
+        </is>
+      </c>
+      <c r="E199" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">role_key</t>
+        </is>
+      </c>
+      <c r="F199" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G199" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK</t>
+        </is>
+      </c>
+      <c r="H199" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I199" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J199" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">admin / staff / viewer</t>
+        </is>
+      </c>
+      <c r="K199" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="200" ht="30" customHeight="1">
+      <c r="A200" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B200" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">医院ポータル権限</t>
+        </is>
+      </c>
+      <c r="C200" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_portal_roles</t>
+        </is>
+      </c>
+      <c r="D200" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">権限名</t>
+        </is>
+      </c>
+      <c r="E200" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">label</t>
+        </is>
+      </c>
+      <c r="F200" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G200" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UK</t>
+        </is>
+      </c>
+      <c r="H200" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I200" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J200" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K200" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="201" ht="30" customHeight="1">
+      <c r="A201" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B201" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">医院ポータル権限</t>
+        </is>
+      </c>
+      <c r="C201" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_portal_roles</t>
+        </is>
+      </c>
+      <c r="D201" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">説明</t>
+        </is>
+      </c>
+      <c r="E201" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">description</t>
+        </is>
+      </c>
+      <c r="F201" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G201" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H201" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I201" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J201" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K201" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="202" ht="30" customHeight="1">
+      <c r="A202" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B202" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">医院ポータル権限</t>
+        </is>
+      </c>
+      <c r="C202" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_portal_roles</t>
+        </is>
+      </c>
+      <c r="D202" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">表示順</t>
+        </is>
+      </c>
+      <c r="E202" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sort_order</t>
+        </is>
+      </c>
+      <c r="F202" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">integer</t>
+        </is>
+      </c>
+      <c r="G202" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UK</t>
+        </is>
+      </c>
+      <c r="H202" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I202" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J202" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K202" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="203" ht="30" customHeight="1">
+      <c r="A203" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B203" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">医院ポータル権限</t>
+        </is>
+      </c>
+      <c r="C203" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_portal_roles</t>
+        </is>
+      </c>
+      <c r="D203" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">作成日時</t>
+        </is>
+      </c>
+      <c r="E203" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">created_at</t>
+        </is>
+      </c>
+      <c r="F203" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">timestamptz</t>
+        </is>
+      </c>
+      <c r="G203" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H203" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I203" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">now()</t>
+        </is>
+      </c>
+      <c r="J203" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K203" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="204" ht="30" customHeight="1">
+      <c r="A204" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B204" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">医院ポータル権限</t>
+        </is>
+      </c>
+      <c r="C204" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_portal_roles</t>
+        </is>
+      </c>
+      <c r="D204" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">更新日時</t>
+        </is>
+      </c>
+      <c r="E204" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">updated_at</t>
+        </is>
+      </c>
+      <c r="F204" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">timestamptz</t>
+        </is>
+      </c>
+      <c r="G204" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H204" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I204" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">now()</t>
+        </is>
+      </c>
+      <c r="J204" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K204" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="205" ht="30" customHeight="1">
+      <c r="A205" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B205" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">医院ポータル権限機能</t>
+        </is>
+      </c>
+      <c r="C205" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_portal_role_permissions</t>
+        </is>
+      </c>
+      <c r="D205" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">権限キー</t>
+        </is>
+      </c>
+      <c r="E205" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">role_key</t>
+        </is>
+      </c>
+      <c r="F205" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G205" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK / FK</t>
+        </is>
+      </c>
+      <c r="H205" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I205" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J205" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_portal_roles.role_key ON DELETE RESTRICT</t>
+        </is>
+      </c>
+      <c r="K205" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="206" ht="30" customHeight="1">
+      <c r="A206" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B206" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">医院ポータル権限機能</t>
+        </is>
+      </c>
+      <c r="C206" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_portal_role_permissions</t>
+        </is>
+      </c>
+      <c r="D206" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">機能キー</t>
+        </is>
+      </c>
+      <c r="E206" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">permission_key</t>
+        </is>
+      </c>
+      <c r="F206" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G206" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK</t>
+        </is>
+      </c>
+      <c r="H206" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I206" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J206" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">view_contacts / manage_contacts / manage_logins</t>
+        </is>
+      </c>
+      <c r="K206" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="207" ht="30" customHeight="1">
+      <c r="A207" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B207" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">医院ポータル権限機能</t>
+        </is>
+      </c>
+      <c r="C207" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_portal_role_permissions</t>
+        </is>
+      </c>
+      <c r="D207" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">作成日時</t>
+        </is>
+      </c>
+      <c r="E207" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">created_at</t>
+        </is>
+      </c>
+      <c r="F207" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">timestamptz</t>
+        </is>
+      </c>
+      <c r="G207" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H207" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I207" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">now()</t>
+        </is>
+      </c>
+      <c r="J207" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K207" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="208" ht="30" customHeight="1">
+      <c r="A208" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B208" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">医院ログイン権限割当</t>
+        </is>
+      </c>
+      <c r="C208" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_user_role_assignments</t>
+        </is>
+      </c>
+      <c r="D208" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">医院ログインID</t>
+        </is>
+      </c>
+      <c r="E208" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_user_id</t>
+        </is>
+      </c>
+      <c r="F208" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">uuid</t>
+        </is>
+      </c>
+      <c r="G208" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK / FK</t>
+        </is>
+      </c>
+      <c r="H208" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I208" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J208" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_users.id ON DELETE CASCADE</t>
+        </is>
+      </c>
+      <c r="K208" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="209" ht="30" customHeight="1">
+      <c r="A209" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B209" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">医院ログイン権限割当</t>
+        </is>
+      </c>
+      <c r="C209" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_user_role_assignments</t>
+        </is>
+      </c>
+      <c r="D209" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">権限キー</t>
+        </is>
+      </c>
+      <c r="E209" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">role_key</t>
+        </is>
+      </c>
+      <c r="F209" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G209" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
+        </is>
+      </c>
+      <c r="H209" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I209" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J209" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_portal_roles.role_key ON DELETE RESTRICT</t>
+        </is>
+      </c>
+      <c r="K209" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="210" ht="30" customHeight="1">
+      <c r="A210" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B210" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">医院ログイン権限割当</t>
+        </is>
+      </c>
+      <c r="C210" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_user_role_assignments</t>
+        </is>
+      </c>
+      <c r="D210" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">割当操作者</t>
+        </is>
+      </c>
+      <c r="E210" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">assigned_by</t>
+        </is>
+      </c>
+      <c r="F210" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G210" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H210" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I210" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">system</t>
+        </is>
+      </c>
+      <c r="J210" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K210" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="211" ht="30" customHeight="1">
+      <c r="A211" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B211" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">医院ログイン権限割当</t>
+        </is>
+      </c>
+      <c r="C211" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_user_role_assignments</t>
+        </is>
+      </c>
+      <c r="D211" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">作成日時</t>
+        </is>
+      </c>
+      <c r="E211" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">created_at</t>
+        </is>
+      </c>
+      <c r="F211" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">timestamptz</t>
+        </is>
+      </c>
+      <c r="G211" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H211" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I211" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">now()</t>
+        </is>
+      </c>
+      <c r="J211" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K211" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="212" ht="30" customHeight="1">
+      <c r="A212" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B212" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">医院ログイン権限割当</t>
+        </is>
+      </c>
+      <c r="C212" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_user_role_assignments</t>
+        </is>
+      </c>
+      <c r="D212" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">更新日時</t>
+        </is>
+      </c>
+      <c r="E212" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">updated_at</t>
+        </is>
+      </c>
+      <c r="F212" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">timestamptz</t>
+        </is>
+      </c>
+      <c r="G212" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H212" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I212" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">now()</t>
+        </is>
+      </c>
+      <c r="J212" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K212" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="213" ht="30" customHeight="1">
+      <c r="A213" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B213" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">担当者通知設定</t>
+        </is>
+      </c>
+      <c r="C213" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_contact_notification_preferences</t>
+        </is>
+      </c>
+      <c r="D213" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">担当者ID</t>
+        </is>
+      </c>
+      <c r="E213" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">contact_id</t>
+        </is>
+      </c>
+      <c r="F213" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">uuid</t>
+        </is>
+      </c>
+      <c r="G213" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK / FK</t>
+        </is>
+      </c>
+      <c r="H213" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I213" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J213" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_contacts.id ON DELETE RESTRICT</t>
+        </is>
+      </c>
+      <c r="K213" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="214" ht="30" customHeight="1">
+      <c r="A214" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B214" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">担当者通知設定</t>
+        </is>
+      </c>
+      <c r="C214" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_contact_notification_preferences</t>
+        </is>
+      </c>
+      <c r="D214" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">通知種別</t>
+        </is>
+      </c>
+      <c r="E214" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">topic</t>
+        </is>
+      </c>
+      <c r="F214" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G214" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK</t>
+        </is>
+      </c>
+      <c r="H214" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I214" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J214" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">webinar / orders / billing / product / system / sales</t>
+        </is>
+      </c>
+      <c r="K214" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="215" ht="30" customHeight="1">
+      <c r="A215" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B215" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">担当者通知設定</t>
+        </is>
+      </c>
+      <c r="C215" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_contact_notification_preferences</t>
+        </is>
+      </c>
+      <c r="D215" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">連絡方法</t>
+        </is>
+      </c>
+      <c r="E215" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">channel</t>
+        </is>
+      </c>
+      <c r="F215" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G215" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK</t>
+        </is>
+      </c>
+      <c r="H215" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I215" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J215" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">email / phone</t>
+        </is>
+      </c>
+      <c r="K215" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="216" ht="30" customHeight="1">
+      <c r="A216" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B216" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">担当者通知設定</t>
+        </is>
+      </c>
+      <c r="C216" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_contact_notification_preferences</t>
+        </is>
+      </c>
+      <c r="D216" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">有効</t>
+        </is>
+      </c>
+      <c r="E216" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">enabled</t>
+        </is>
+      </c>
+      <c r="F216" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">boolean</t>
+        </is>
+      </c>
+      <c r="G216" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H216" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I216" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">true</t>
+        </is>
+      </c>
+      <c r="J216" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K216" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="217" ht="30" customHeight="1">
+      <c r="A217" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B217" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">担当者通知設定</t>
+        </is>
+      </c>
+      <c r="C217" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_contact_notification_preferences</t>
+        </is>
+      </c>
+      <c r="D217" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">作成日時</t>
+        </is>
+      </c>
+      <c r="E217" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">created_at</t>
+        </is>
+      </c>
+      <c r="F217" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">timestamptz</t>
+        </is>
+      </c>
+      <c r="G217" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H217" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I217" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">now()</t>
+        </is>
+      </c>
+      <c r="J217" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K217" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="218" ht="30" customHeight="1">
+      <c r="A218" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B218" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">担当者通知設定</t>
+        </is>
+      </c>
+      <c r="C218" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_contact_notification_preferences</t>
+        </is>
+      </c>
+      <c r="D218" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">更新日時</t>
+        </is>
+      </c>
+      <c r="E218" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">updated_at</t>
+        </is>
+      </c>
+      <c r="F218" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">timestamptz</t>
+        </is>
+      </c>
+      <c r="G218" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H218" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I218" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">now()</t>
+        </is>
+      </c>
+      <c r="J218" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K218" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="219" ht="30" customHeight="1">
+      <c r="A219" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B219" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">担当者操作履歴</t>
         </is>
       </c>
-      <c r="C196" s="4" t="inlineStr">
+      <c r="C219" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">clinic_contact_events</t>
         </is>
       </c>
-      <c r="D196" s="4" t="inlineStr">
+      <c r="D219" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">イベントID</t>
+        </is>
+      </c>
+      <c r="E219" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">id</t>
+        </is>
+      </c>
+      <c r="F219" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">uuid</t>
+        </is>
+      </c>
+      <c r="G219" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK</t>
+        </is>
+      </c>
+      <c r="H219" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I219" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gen_random_uuid()</t>
+        </is>
+      </c>
+      <c r="J219" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K219" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="220" ht="30" customHeight="1">
+      <c r="A220" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B220" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">担当者操作履歴</t>
+        </is>
+      </c>
+      <c r="C220" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_contact_events</t>
+        </is>
+      </c>
+      <c r="D220" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">担当者ID</t>
+        </is>
+      </c>
+      <c r="E220" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">contact_id</t>
+        </is>
+      </c>
+      <c r="F220" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">uuid</t>
+        </is>
+      </c>
+      <c r="G220" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
+        </is>
+      </c>
+      <c r="H220" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I220" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J220" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_contacts.id ON DELETE RESTRICT</t>
+        </is>
+      </c>
+      <c r="K220" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="221" ht="30" customHeight="1">
+      <c r="A221" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B221" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">担当者操作履歴</t>
+        </is>
+      </c>
+      <c r="C221" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_contact_events</t>
+        </is>
+      </c>
+      <c r="D221" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">イベント種別</t>
+        </is>
+      </c>
+      <c r="E221" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">event_type</t>
+        </is>
+      </c>
+      <c r="F221" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G221" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H221" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I221" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J221" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K221" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="222" ht="30" customHeight="1">
+      <c r="A222" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B222" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">担当者操作履歴</t>
+        </is>
+      </c>
+      <c r="C222" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_contact_events</t>
+        </is>
+      </c>
+      <c r="D222" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">操作者種別</t>
+        </is>
+      </c>
+      <c r="E222" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actor_type</t>
+        </is>
+      </c>
+      <c r="F222" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G222" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H222" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I222" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J222" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K222" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="223" ht="30" customHeight="1">
+      <c r="A223" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B223" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">担当者操作履歴</t>
+        </is>
+      </c>
+      <c r="C223" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_contact_events</t>
+        </is>
+      </c>
+      <c r="D223" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">操作者識別子</t>
+        </is>
+      </c>
+      <c r="E223" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actor_identifier</t>
+        </is>
+      </c>
+      <c r="F223" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G223" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H223" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I223" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J223" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K223" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="224" ht="30" customHeight="1">
+      <c r="A224" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B224" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">担当者操作履歴</t>
+        </is>
+      </c>
+      <c r="C224" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_contact_events</t>
+        </is>
+      </c>
+      <c r="D224" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">追加情報</t>
+        </is>
+      </c>
+      <c r="E224" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metadata</t>
+        </is>
+      </c>
+      <c r="F224" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jsonb</t>
+        </is>
+      </c>
+      <c r="G224" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H224" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I224" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{}</t>
+        </is>
+      </c>
+      <c r="J224" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K224" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="225" ht="30" customHeight="1">
+      <c r="A225" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B225" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">担当者操作履歴</t>
+        </is>
+      </c>
+      <c r="C225" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_contact_events</t>
+        </is>
+      </c>
+      <c r="D225" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">発生日時</t>
         </is>
       </c>
-      <c r="E196" s="4" t="inlineStr">
+      <c r="E225" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">created_at</t>
         </is>
       </c>
-      <c r="F196" s="4" t="inlineStr">
+      <c r="F225" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">timestamptz</t>
         </is>
       </c>
-      <c r="G196" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H196" s="4" t="inlineStr">
+      <c r="G225" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H225" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">NO</t>
         </is>
       </c>
-      <c r="I196" s="4" t="inlineStr">
+      <c r="I225" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">now()</t>
         </is>
       </c>
-      <c r="J196" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="K196" s="4" t="inlineStr">
+      <c r="J225" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K225" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -12606,7 +14387,7 @@
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A2:K2"/>
   </mergeCells>
-  <autoFilter ref="A4:K196"/>
+  <autoFilter ref="A4:K225"/>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0" paperSize="9"/>
 </worksheet>
@@ -17331,7 +19112,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G70"/>
+  <dimension ref="A1:G76"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -17969,22 +19750,22 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">将来案</t>
+          <t xml:space="preserve">現行</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">UK1</t>
+          <t xml:space="preserve">UK13</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_accounts</t>
+          <t xml:space="preserve">clinic_users</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">provider, external_account_id</t>
+          <t xml:space="preserve">login_id</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
@@ -17994,39 +19775,39 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部接続先の重複防止。</t>
+          <t xml:space="preserve">ログインIDの重複防止。</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">将来案</t>
+          <t xml:space="preserve">現行</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">UK2</t>
+          <t xml:space="preserve">UK14</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_fulfillment_items</t>
+          <t xml:space="preserve">clinic_users</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">fulfillment_id, order_item_id</t>
+          <t xml:space="preserve">email WHERE email IS NOT NULL</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNIQUE</t>
+          <t xml:space="preserve">PARTIAL UNIQUE</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">同一配送への明細重複防止。</t>
+          <t xml:space="preserve">パスワード再設定先の重複防止。</t>
         </is>
       </c>
     </row>
@@ -18038,17 +19819,17 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">UK3</t>
+          <t xml:space="preserve">UK1</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_subscriptions</t>
+          <t xml:space="preserve">commerce_accounts</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_account_id, external_subscription_id</t>
+          <t xml:space="preserve">provider, external_account_id</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
@@ -18058,7 +19839,7 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部契約の重複防止。</t>
+          <t xml:space="preserve">外部接続先の重複防止。</t>
         </is>
       </c>
     </row>
@@ -18070,17 +19851,17 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">UK4</t>
+          <t xml:space="preserve">UK2</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_webhook_events</t>
+          <t xml:space="preserve">patient_fulfillment_items</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_account_id, external_event_id</t>
+          <t xml:space="preserve">fulfillment_id, order_item_id</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
@@ -18090,7 +19871,7 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Webhook重複配信の無害化。</t>
+          <t xml:space="preserve">同一配送への明細重複防止。</t>
         </is>
       </c>
     </row>
@@ -18102,17 +19883,17 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">UK5</t>
+          <t xml:space="preserve">UK3</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders</t>
+          <t xml:space="preserve">patient_subscriptions</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_account_id, external_order_id</t>
+          <t xml:space="preserve">commerce_account_id, external_subscription_id</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -18122,7 +19903,7 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">複数ストアを考慮した外部注文の一意性。</t>
+          <t xml:space="preserve">外部契約の重複防止。</t>
         </is>
       </c>
     </row>
@@ -18134,157 +19915,147 @@
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">UK4</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">commerce_webhook_events</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">commerce_account_id, external_event_id</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UNIQUE</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Webhook重複配信の無害化。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">将来案</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UK5</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_orders</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">commerce_account_id, external_order_id</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UNIQUE</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">複数ストアを考慮した外部注文の一意性。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">将来案</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">UK6</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">commerce_outbox</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="D30" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">idempotency_key</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
+      <c r="E30" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">UNIQUE</t>
         </is>
       </c>
-      <c r="F28" s="4" t="inlineStr">
+      <c r="F30" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">外部送信コマンドの二重実行防止。</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">現行リレーション</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">親DB日本語名</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">親KEY</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">親多重度</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">子多重度</t>
         </is>
       </c>
-      <c r="E31" s="3" t="inlineStr">
+      <c r="E33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">子FK</t>
         </is>
       </c>
-      <c r="F31" s="3" t="inlineStr">
+      <c r="F33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">子DB日本語名</t>
         </is>
       </c>
-      <c r="G31" s="3" t="inlineStr">
+      <c r="G33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">削除・備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">医院</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">clinics.customer_code</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0..1</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">clinic_terms.customer_code</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">医院契約情報</t>
-        </is>
-      </c>
-      <c r="G32" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PK・FK・CASCADE</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">医院</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">clinics.customer_code</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">clinic_product_settings.customer_code</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">医院商品設定</t>
-        </is>
-      </c>
-      <c r="G33" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PK・FK・CASCADE</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">商品</t>
+          <t xml:space="preserve">医院</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">products.id</t>
+          <t xml:space="preserve">clinics.customer_code</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -18294,17 +20065,17 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">N</t>
+          <t xml:space="preserve">0..1</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_product_settings.product_id</t>
+          <t xml:space="preserve">clinic_terms.customer_code</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院商品設定</t>
+          <t xml:space="preserve">医院契約情報</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
@@ -18336,29 +20107,29 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders.customer_code</t>
+          <t xml:space="preserve">clinic_product_settings.customer_code</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文</t>
+          <t xml:space="preserve">医院商品設定</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK</t>
+          <t xml:space="preserve">PK・FK・CASCADE</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者</t>
+          <t xml:space="preserve">商品</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patients.id</t>
+          <t xml:space="preserve">products.id</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -18373,66 +20144,66 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders.patient_id</t>
+          <t xml:space="preserve">clinic_product_settings.product_id</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文</t>
+          <t xml:space="preserve">医院商品設定</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK・現状CASCADE</t>
+          <t xml:space="preserve">PK・FK・CASCADE</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">医院</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinics.customer_code</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_orders.customer_code</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">患者注文</t>
         </is>
       </c>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">patient_orders.id</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="D37" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">patient_order_items.order_id</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">患者注文明細</t>
-        </is>
-      </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK・CASCADE</t>
+          <t xml:space="preserve">FK</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院</t>
+          <t xml:space="preserve">患者</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinics.customer_code</t>
+          <t xml:space="preserve">patients.id</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -18447,29 +20218,29 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery_destinations.clinic_customer_code</t>
+          <t xml:space="preserve">patient_orders.patient_id</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">送り先マスタ</t>
+          <t xml:space="preserve">患者注文</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK・RESTRICT</t>
+          <t xml:space="preserve">FK・現状CASCADE</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者</t>
+          <t xml:space="preserve">患者注文</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patients.id</t>
+          <t xml:space="preserve">patient_orders.id</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -18484,49 +20255,49 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery_destinations.patient_id</t>
+          <t xml:space="preserve">patient_order_items.order_id</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">送り先マスタ</t>
+          <t xml:space="preserve">患者注文明細</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK・RESTRICT</t>
+          <t xml:space="preserve">FK・CASCADE</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">医院</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinics.customer_code</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">delivery_destinations.clinic_customer_code</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">送り先マスタ</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">delivery_destinations.id</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="D40" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">order_delivery_destinations.delivery_destination_id</t>
-        </is>
-      </c>
-      <c r="F40" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">注文配送先</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
@@ -18538,12 +20309,12 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文</t>
+          <t xml:space="preserve">患者</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders.id</t>
+          <t xml:space="preserve">patients.id</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -18553,34 +20324,34 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">0..1</t>
+          <t xml:space="preserve">N</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">order_delivery_destinations.order_id</t>
+          <t xml:space="preserve">delivery_destinations.patient_id</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文配送先</t>
+          <t xml:space="preserve">送り先マスタ</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">PK・FK・CASCADE</t>
+          <t xml:space="preserve">FK・RESTRICT</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文</t>
+          <t xml:space="preserve">送り先マスタ</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders.id</t>
+          <t xml:space="preserve">delivery_destinations.id</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -18595,66 +20366,66 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_order_events.order_id</t>
+          <t xml:space="preserve">order_delivery_destinations.delivery_destination_id</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文操作履歴</t>
+          <t xml:space="preserve">注文配送先</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK・CASCADE</t>
+          <t xml:space="preserve">FK・RESTRICT</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">商品</t>
+          <t xml:space="preserve">患者注文</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">products.id</t>
+          <t xml:space="preserve">patient_orders.id</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">0..1</t>
         </is>
       </c>
-      <c r="D43" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_order_items.product_id</t>
+          <t xml:space="preserve">order_delivery_destinations.order_id</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文明細</t>
+          <t xml:space="preserve">注文配送先</t>
         </is>
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK・SET NULL</t>
+          <t xml:space="preserve">PK・FK・CASCADE</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院</t>
+          <t xml:space="preserve">患者注文</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinics.customer_code</t>
+          <t xml:space="preserve">patient_orders.id</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -18669,34 +20440,34 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_subscription_requests.customer_code</t>
+          <t xml:space="preserve">patient_order_events.order_id</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">定期購入申込</t>
+          <t xml:space="preserve">注文操作履歴</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK・RESTRICT</t>
+          <t xml:space="preserve">FK・CASCADE</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者</t>
+          <t xml:space="preserve">商品</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patients.id</t>
+          <t xml:space="preserve">products.id</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">0..1</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -18706,91 +20477,91 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_subscription_requests.patient_id</t>
+          <t xml:space="preserve">patient_order_items.product_id</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">定期購入申込</t>
+          <t xml:space="preserve">患者注文明細</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK・RESTRICT</t>
+          <t xml:space="preserve">FK・SET NULL</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">医院</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinics.customer_code</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscription_requests.customer_code</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">定期購入申込</t>
         </is>
       </c>
-      <c r="B46" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">patient_subscription_requests.id</t>
-        </is>
-      </c>
-      <c r="C46" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="D46" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="E46" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">patient_subscription_request_items.request_id</t>
-        </is>
-      </c>
-      <c r="F46" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">定期購入申込明細</t>
-        </is>
-      </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK・CASCADE</t>
+          <t xml:space="preserve">FK・RESTRICT</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">患者</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patients.id</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscription_requests.patient_id</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">定期購入申込</t>
         </is>
       </c>
-      <c r="B47" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">patient_subscription_requests.id</t>
-        </is>
-      </c>
-      <c r="C47" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="D47" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0..1</t>
-        </is>
-      </c>
-      <c r="E47" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">patient_subscription_request_destinations.request_id</t>
-        </is>
-      </c>
-      <c r="F47" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">定期購入申込配送先</t>
-        </is>
-      </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">PK・FK・CASCADE</t>
+          <t xml:space="preserve">FK・RESTRICT</t>
         </is>
       </c>
     </row>
@@ -18817,12 +20588,12 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_subscription_request_events.request_id</t>
+          <t xml:space="preserve">patient_subscription_request_items.request_id</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">定期購入申込履歴</t>
+          <t xml:space="preserve">定期購入申込明細</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
@@ -18834,12 +20605,12 @@
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">送り先マスタ</t>
+          <t xml:space="preserve">定期購入申込</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery_destinations.id</t>
+          <t xml:space="preserve">patient_subscription_requests.id</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -18849,12 +20620,12 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">N</t>
+          <t xml:space="preserve">0..1</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_subscription_request_destinations.delivery_destination_id</t>
+          <t xml:space="preserve">patient_subscription_request_destinations.request_id</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
@@ -18864,19 +20635,19 @@
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK・RESTRICT</t>
+          <t xml:space="preserve">PK・FK・CASCADE</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ウェビナー</t>
+          <t xml:space="preserve">定期購入申込</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">webinars.id</t>
+          <t xml:space="preserve">patient_subscription_requests.id</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -18891,12 +20662,12 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">webinar_sessions.webinar_id</t>
+          <t xml:space="preserve">patient_subscription_request_events.request_id</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ウェビナー開催枠</t>
+          <t xml:space="preserve">定期購入申込履歴</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
@@ -18908,12 +20679,12 @@
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ウェビナー</t>
+          <t xml:space="preserve">送り先マスタ</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">webinars.id</t>
+          <t xml:space="preserve">delivery_destinations.id</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -18928,29 +20699,29 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">webinar_target_clinics.webinar_id</t>
+          <t xml:space="preserve">patient_subscription_request_destinations.delivery_destination_id</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ウェビナー対象医院</t>
+          <t xml:space="preserve">定期購入申込配送先</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">PK・FK・CASCADE</t>
+          <t xml:space="preserve">FK・RESTRICT</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院</t>
+          <t xml:space="preserve">ウェビナー</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinics.customer_code</t>
+          <t xml:space="preserve">webinars.id</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -18965,17 +20736,17 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">webinar_target_clinics.customer_code</t>
+          <t xml:space="preserve">webinar_sessions.webinar_id</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ウェビナー対象医院</t>
+          <t xml:space="preserve">ウェビナー開催枠</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">PK・FK・RESTRICT</t>
+          <t xml:space="preserve">FK・CASCADE</t>
         </is>
       </c>
     </row>
@@ -19002,17 +20773,17 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">webinar_events.webinar_id</t>
+          <t xml:space="preserve">webinar_target_clinics.webinar_id</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ウェビナー操作履歴</t>
+          <t xml:space="preserve">ウェビナー対象医院</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK・CASCADE</t>
+          <t xml:space="preserve">PK・FK・CASCADE</t>
         </is>
       </c>
     </row>
@@ -19039,29 +20810,29 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_contacts.customer_code</t>
+          <t xml:space="preserve">webinar_target_clinics.customer_code</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院業務連絡担当者</t>
+          <t xml:space="preserve">ウェビナー対象医院</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK・RESTRICT</t>
+          <t xml:space="preserve">PK・FK・RESTRICT</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院ログイン</t>
+          <t xml:space="preserve">ウェビナー</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_users.id</t>
+          <t xml:space="preserve">webinars.id</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -19071,152 +20842,219 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">0..1</t>
+          <t xml:space="preserve">N</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_contacts.clinic_user_id</t>
+          <t xml:space="preserve">webinar_events.webinar_id</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院業務連絡担当者</t>
+          <t xml:space="preserve">ウェビナー操作履歴</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK・SET NULL</t>
+          <t xml:space="preserve">FK・CASCADE</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">医院</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinics.customer_code</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_contacts.customer_code</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">医院業務連絡担当者</t>
         </is>
       </c>
-      <c r="B56" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">clinic_contacts.id</t>
-        </is>
-      </c>
-      <c r="C56" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="D56" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="E56" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">clinic_contact_notification_preferences.contact_id</t>
-        </is>
-      </c>
-      <c r="F56" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">担当者通知設定</t>
-        </is>
-      </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">PK・FK・RESTRICT</t>
+          <t xml:space="preserve">FK・RESTRICT</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">医院ログイン</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_users.id</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0..1</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_contacts.clinic_user_id</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">医院業務連絡担当者</t>
         </is>
       </c>
-      <c r="B57" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">clinic_contacts.id</t>
-        </is>
-      </c>
-      <c r="C57" s="4" t="inlineStr">
+      <c r="G57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK・SET NULL</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">医院</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinics.customer_code</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="D57" s="4" t="inlineStr">
+      <c r="D58" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="E57" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">clinic_contact_events.contact_id</t>
-        </is>
-      </c>
-      <c r="F57" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">担当者操作履歴</t>
-        </is>
-      </c>
-      <c r="G57" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FK・RESTRICT</t>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_users.customer_code</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">医院ポータルログイン</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK・CASCADE</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">将来リレーション案</t>
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">医院ポータル権限</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_portal_roles.role_key</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_portal_role_permissions.role_key</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">権限機能</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK・FK・RESTRICT</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">親DB日本語名</t>
-        </is>
-      </c>
-      <c r="B60" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">親KEY</t>
-        </is>
-      </c>
-      <c r="C60" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">親多重度</t>
-        </is>
-      </c>
-      <c r="D60" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">子多重度</t>
-        </is>
-      </c>
-      <c r="E60" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">子FK</t>
-        </is>
-      </c>
-      <c r="F60" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">子DB日本語名</t>
-        </is>
-      </c>
-      <c r="G60" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">削除・備考</t>
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">医院ポータルログイン</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_users.id</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0..1</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_user_role_assignments.clinic_user_id</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">権限割当</t>
+        </is>
+      </c>
+      <c r="G60" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK・FK・CASCADE</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文</t>
+          <t xml:space="preserve">医院ポータル権限</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders.id</t>
+          <t xml:space="preserve">clinic_portal_roles.role_key</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -19231,29 +21069,29 @@
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">order_transaction_projections.order_id</t>
+          <t xml:space="preserve">clinic_user_role_assignments.role_key</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">決済返金投影</t>
+          <t xml:space="preserve">権限割当</t>
         </is>
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK</t>
+          <t xml:space="preserve">FK・RESTRICT</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文</t>
+          <t xml:space="preserve">医院業務連絡担当者</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders.id</t>
+          <t xml:space="preserve">clinic_contacts.id</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -19268,29 +21106,29 @@
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_fulfillments.order_id</t>
+          <t xml:space="preserve">clinic_contact_notification_preferences.contact_id</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">受取配送</t>
+          <t xml:space="preserve">担当者通知設定</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK</t>
+          <t xml:space="preserve">PK・FK・RESTRICT</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">受取配送</t>
+          <t xml:space="preserve">医院業務連絡担当者</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_fulfillments.id</t>
+          <t xml:space="preserve">clinic_contacts.id</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -19305,140 +21143,73 @@
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_fulfillment_items.fulfillment_id</t>
+          <t xml:space="preserve">clinic_contact_events.contact_id</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">受取配送明細</t>
+          <t xml:space="preserve">担当者操作履歴</t>
         </is>
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">注文明細</t>
-        </is>
-      </c>
-      <c r="B64" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">patient_order_items.id</t>
-        </is>
-      </c>
-      <c r="C64" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="D64" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="E64" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">patient_fulfillment_items.order_item_id</t>
-        </is>
-      </c>
-      <c r="F64" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">受取配送明細</t>
-        </is>
-      </c>
-      <c r="G64" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FK</t>
+          <t xml:space="preserve">FK・RESTRICT</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">外部コマース接続</t>
-        </is>
-      </c>
-      <c r="B65" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">commerce_accounts.id</t>
-        </is>
-      </c>
-      <c r="C65" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="D65" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="E65" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">patient_orders.commerce_account_id</t>
-        </is>
-      </c>
-      <c r="F65" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">患者注文</t>
-        </is>
-      </c>
-      <c r="G65" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FK</t>
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">将来リレーション案</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">外部コマース接続</t>
-        </is>
-      </c>
-      <c r="B66" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">commerce_accounts.id</t>
-        </is>
-      </c>
-      <c r="C66" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="D66" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="E66" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">commerce_webhook_events.commerce_account_id</t>
-        </is>
-      </c>
-      <c r="F66" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">外部受信イベント</t>
-        </is>
-      </c>
-      <c r="G66" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FK</t>
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">親DB日本語名</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">親KEY</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">親多重度</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">子多重度</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">子FK</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">子DB日本語名</t>
+        </is>
+      </c>
+      <c r="G66" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">削除・備考</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部コマース接続</t>
+          <t xml:space="preserve">患者注文</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_accounts.id</t>
+          <t xml:space="preserve">patient_orders.id</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -19453,12 +21224,12 @@
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_outbox.commerce_account_id</t>
+          <t xml:space="preserve">order_transaction_projections.order_id</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部送信キュー</t>
+          <t xml:space="preserve">決済返金投影</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr">
@@ -19470,12 +21241,12 @@
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者</t>
+          <t xml:space="preserve">患者注文</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patients.id</t>
+          <t xml:space="preserve">patient_orders.id</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -19490,12 +21261,12 @@
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_subscriptions.patient_id</t>
+          <t xml:space="preserve">patient_fulfillments.order_id</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者定期購入</t>
+          <t xml:space="preserve">受取配送</t>
         </is>
       </c>
       <c r="G68" s="4" t="inlineStr">
@@ -19507,12 +21278,12 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者定期購入</t>
+          <t xml:space="preserve">受取配送</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_subscriptions.id</t>
+          <t xml:space="preserve">patient_fulfillments.id</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -19527,12 +21298,12 @@
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_subscription_items.subscription_id</t>
+          <t xml:space="preserve">patient_fulfillment_items.fulfillment_id</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">定期購入明細</t>
+          <t xml:space="preserve">受取配送明細</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr">
@@ -19544,35 +21315,257 @@
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">注文明細</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_order_items.id</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_fulfillment_items.order_item_id</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">受取配送明細</t>
+        </is>
+      </c>
+      <c r="G70" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">外部コマース接続</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">commerce_accounts.id</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_orders.commerce_account_id</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">患者注文</t>
+        </is>
+      </c>
+      <c r="G71" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">外部コマース接続</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">commerce_accounts.id</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">commerce_webhook_events.commerce_account_id</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">外部受信イベント</t>
+        </is>
+      </c>
+      <c r="G72" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">外部コマース接続</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">commerce_accounts.id</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">commerce_outbox.commerce_account_id</t>
+        </is>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">外部送信キュー</t>
+        </is>
+      </c>
+      <c r="G73" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">患者</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patients.id</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscriptions.patient_id</t>
+        </is>
+      </c>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">患者定期購入</t>
         </is>
       </c>
-      <c r="B70" s="4" t="inlineStr">
+      <c r="G74" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">患者定期購入</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">patient_subscriptions.id</t>
         </is>
       </c>
-      <c r="C70" s="4" t="inlineStr">
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscription_items.subscription_id</t>
+        </is>
+      </c>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">定期購入明細</t>
+        </is>
+      </c>
+      <c r="G75" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">患者定期購入</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscriptions.id</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">0..1</t>
         </is>
       </c>
-      <c r="D70" s="4" t="inlineStr">
+      <c r="D76" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="E70" s="4" t="inlineStr">
+      <c r="E76" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">patient_orders.subscription_id</t>
         </is>
       </c>
-      <c r="F70" s="4" t="inlineStr">
+      <c r="F76" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">患者注文</t>
         </is>
       </c>
-      <c r="G70" s="4" t="inlineStr">
+      <c r="G76" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">FK</t>
         </is>
@@ -19582,8 +21575,8 @@
   <mergeCells count="4">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A30:H30"/>
-    <mergeCell ref="A59:H59"/>
+    <mergeCell ref="A32:H32"/>
+    <mergeCell ref="A65:H65"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0" paperSize="9"/>
@@ -19592,7 +21585,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Q99"/>
+  <dimension ref="A1:Q103"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -21612,12 +23605,12 @@
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院業務連絡担当者</t>
+          <t xml:space="preserve">医院</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_contacts.id</t>
+          <t xml:space="preserve">clinics.customer_code</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
@@ -21632,52 +23625,200 @@
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_contact_notification_preferences.contact_id</t>
+          <t xml:space="preserve">clinic_users.customer_code</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">担当者通知設定</t>
+          <t xml:space="preserve">医院ポータルログイン</t>
         </is>
       </c>
       <c r="G98" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">PK・FK・RESTRICT</t>
+          <t xml:space="preserve">FK・CASCADE</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">医院ポータル権限</t>
+        </is>
+      </c>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_portal_roles.role_key</t>
+        </is>
+      </c>
+      <c r="C99" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D99" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E99" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_portal_role_permissions.role_key</t>
+        </is>
+      </c>
+      <c r="F99" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">権限機能</t>
+        </is>
+      </c>
+      <c r="G99" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK・FK・RESTRICT</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">医院ポータルログイン</t>
+        </is>
+      </c>
+      <c r="B100" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_users.id</t>
+        </is>
+      </c>
+      <c r="C100" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D100" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0..1</t>
+        </is>
+      </c>
+      <c r="E100" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_user_role_assignments.clinic_user_id</t>
+        </is>
+      </c>
+      <c r="F100" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">権限割当</t>
+        </is>
+      </c>
+      <c r="G100" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK・FK・CASCADE</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">医院ポータル権限</t>
+        </is>
+      </c>
+      <c r="B101" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_portal_roles.role_key</t>
+        </is>
+      </c>
+      <c r="C101" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D101" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E101" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_user_role_assignments.role_key</t>
+        </is>
+      </c>
+      <c r="F101" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">権限割当</t>
+        </is>
+      </c>
+      <c r="G101" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK・RESTRICT</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">医院業務連絡担当者</t>
         </is>
       </c>
-      <c r="B99" s="4" t="inlineStr">
+      <c r="B102" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">clinic_contacts.id</t>
         </is>
       </c>
-      <c r="C99" s="4" t="inlineStr">
+      <c r="C102" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="D99" s="4" t="inlineStr">
+      <c r="D102" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="E99" s="4" t="inlineStr">
+      <c r="E102" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_contact_notification_preferences.contact_id</t>
+        </is>
+      </c>
+      <c r="F102" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">担当者通知設定</t>
+        </is>
+      </c>
+      <c r="G102" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK・FK・RESTRICT</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">医院業務連絡担当者</t>
+        </is>
+      </c>
+      <c r="B103" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_contacts.id</t>
+        </is>
+      </c>
+      <c r="C103" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D103" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E103" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">clinic_contact_events.contact_id</t>
         </is>
       </c>
-      <c r="F99" s="4" t="inlineStr">
+      <c r="F103" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">担当者操作履歴</t>
         </is>
       </c>
-      <c r="G99" s="4" t="inlineStr">
+      <c r="G103" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">FK・RESTRICT</t>
         </is>

--- a/project_clinic_order_management_db_definition.xlsx
+++ b/project_clinic_order_management_db_definition.xlsx
@@ -476,7 +476,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -1117,12 +1117,12 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院業務連絡担当者</t>
+          <t xml:space="preserve">医院担当者役職</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_contacts</t>
+          <t xml:space="preserve">clinic_contact_roles</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院ごとに複数の業務連絡担当者と主担当、論理削除、排他制御を管理する。</t>
+          <t xml:space="preserve">医院担当者の役職を選択肢として一元管理する。</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -1149,22 +1149,22 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院ポータルログイン</t>
+          <t xml:space="preserve">医院業務連絡担当者</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_users</t>
+          <t xml:space="preserve">clinic_contacts</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">実装済み・Phase 1</t>
+          <t xml:space="preserve">実装済み</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">認証情報とセッション世代を保持する。担当者プロフィールとはclinic_contactsで関連する。</t>
+          <t xml:space="preserve">医院ごとに複数の業務連絡担当者と主担当、論理削除、排他制御を管理する。</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
@@ -1181,12 +1181,12 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院ポータル権限</t>
+          <t xml:space="preserve">医院ポータルログイン</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_portal_roles</t>
+          <t xml:space="preserve">clinic_users</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">管理者・一般・閲覧専用の権限マスタ。</t>
+          <t xml:space="preserve">担当者ID・認証情報・所属得意先・セッション世代を保持する。全担当者が1対1でclinic_contactsを持つ。</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
@@ -1213,12 +1213,12 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院ポータル権限機能</t>
+          <t xml:space="preserve">医院ポータル権限</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_portal_role_permissions</t>
+          <t xml:space="preserve">clinic_portal_roles</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">権限と操作可能な機能を多対多で管理する。</t>
+          <t xml:space="preserve">管理者・一般・閲覧専用の権限マスタ。</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -1245,12 +1245,12 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院ログイン権限割当</t>
+          <t xml:space="preserve">医院ポータル権限機能</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_user_role_assignments</t>
+          <t xml:space="preserve">clinic_portal_role_permissions</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1ログインに1権限を割り当て、認証情報と権限マスタを分離する。</t>
+          <t xml:space="preserve">権限と操作可能な機能を多対多で管理する。</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -1277,22 +1277,22 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">担当者通知設定</t>
+          <t xml:space="preserve">医院ログイン権限割当</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_contact_notification_preferences</t>
+          <t xml:space="preserve">clinic_user_role_assignments</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">実装済み</t>
+          <t xml:space="preserve">実装済み・Phase 1</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">担当者ごとの連絡内容と方法を多値属性として分離する。</t>
+          <t xml:space="preserve">1ログインに1権限を割り当て、認証情報と権限マスタを分離する。</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">担当者操作履歴</t>
+          <t xml:space="preserve">担当者通知設定</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_contact_events</t>
+          <t xml:space="preserve">clinic_contact_notification_preferences</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">登録・更新・無効化・主担当変更・論理削除を監査保存する。</t>
+          <t xml:space="preserve">担当者ごとの連絡内容と方法を多値属性として分離する。</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
@@ -1336,27 +1336,27 @@
     <row r="30" ht="34" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shopify接続</t>
+          <t xml:space="preserve">現行</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部コマース接続</t>
+          <t xml:space="preserve">担当者操作履歴</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_accounts</t>
+          <t xml:space="preserve">clinic_contact_events</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">将来案</t>
+          <t xml:space="preserve">実装済み</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shopifyストア等の外部接続先。医院との対応方式は接続構成確定後に決定する。</t>
+          <t xml:space="preserve">登録・更新・無効化・主担当変更・論理削除を監査保存する。</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
@@ -1373,22 +1373,22 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文拡張</t>
+          <t xml:space="preserve">外部コマース接続</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders</t>
+          <t xml:space="preserve">commerce_accounts</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">既存テーブル拡張案</t>
+          <t xml:space="preserve">将来案</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">既存IDを維持し、外部・金額・排他制御の列を追加する。</t>
+          <t xml:space="preserve">Shopifyストア等の外部接続先。医院との対応方式は接続構成確定後に決定する。</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -1405,12 +1405,12 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文明細拡張</t>
+          <t xml:space="preserve">患者注文拡張</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_order_items</t>
+          <t xml:space="preserve">patient_orders</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部明細と通貨を明確化し、既存スナップショットを維持する。</t>
+          <t xml:space="preserve">既存IDを維持し、外部・金額・排他制御の列を追加する。</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -1432,27 +1432,27 @@
     <row r="33" ht="34" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">決済接続</t>
+          <t xml:space="preserve">Shopify接続</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">決済返金投影</t>
+          <t xml:space="preserve">患者注文明細拡張</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">order_transaction_projections</t>
+          <t xml:space="preserve">patient_order_items</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">将来案</t>
+          <t xml:space="preserve">既存テーブル拡張案</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shopify上の決済・返金を表示する投影。会計台帳ではない。</t>
+          <t xml:space="preserve">外部明細と通貨を明確化し、既存スナップショットを維持する。</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -1464,17 +1464,17 @@
     <row r="34" ht="34" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">配送開始</t>
+          <t xml:space="preserve">決済接続</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">受取配送</t>
+          <t xml:space="preserve">決済返金投影</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_fulfillments</t>
+          <t xml:space="preserve">order_transaction_projections</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院受け取り・配送・部分引き渡しの単位。</t>
+          <t xml:space="preserve">Shopify上の決済・返金を表示する投影。会計台帳ではない。</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">受取配送明細</t>
+          <t xml:space="preserve">受取配送</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_fulfillment_items</t>
+          <t xml:space="preserve">patient_fulfillments</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -1516,7 +1516,7 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">部分受け取り・部分配送時の対象明細と数量。</t>
+          <t xml:space="preserve">医院受け取り・配送・部分引き渡しの単位。</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
@@ -1528,17 +1528,17 @@
     <row r="36" ht="34" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">定期購入接続</t>
+          <t xml:space="preserve">配送開始</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者定期購入</t>
+          <t xml:space="preserve">受取配送明細</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_subscriptions</t>
+          <t xml:space="preserve">patient_fulfillment_items</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shopify上の定期購入契約を患者ポータルへ表示する投影。</t>
+          <t xml:space="preserve">部分受け取り・部分配送時の対象明細と数量。</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">定期購入明細</t>
+          <t xml:space="preserve">患者定期購入</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_subscription_items</t>
+          <t xml:space="preserve">patient_subscriptions</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">契約時点の商品・数量・単価の投影。</t>
+          <t xml:space="preserve">Shopify上の定期購入契約を患者ポータルへ表示する投影。</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
@@ -1592,17 +1592,17 @@
     <row r="38" ht="34" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shopify接続</t>
+          <t xml:space="preserve">定期購入接続</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部受信イベント</t>
+          <t xml:space="preserve">定期購入明細</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_webhook_events</t>
+          <t xml:space="preserve">patient_subscription_items</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Webhookを先に永続化し、重複排除・再試行するInbox。</t>
+          <t xml:space="preserve">契約時点の商品・数量・単価の投影。</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
@@ -1629,57 +1629,89 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">外部受信イベント</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">commerce_webhook_events</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">将来案</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Webhookを先に永続化し、重複排除・再試行するInbox。</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="34" customHeight="1">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shopify接続</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">外部送信キュー</t>
         </is>
       </c>
-      <c r="C39" s="4" t="inlineStr">
+      <c r="C40" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">commerce_outbox</t>
         </is>
       </c>
-      <c r="D39" s="4" t="inlineStr">
+      <c r="D40" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">将来案</t>
         </is>
       </c>
-      <c r="E39" s="4" t="inlineStr">
+      <c r="E40" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">外部APIへ送る処理を永続化するOutbox。</t>
         </is>
       </c>
-      <c r="F39" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="8" t="inlineStr">
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">別ドメイン</t>
         </is>
       </c>
-      <c r="B40" s="8" t="inlineStr">
+      <c r="B41" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">医院仕入注文</t>
         </is>
       </c>
-      <c r="C40" s="8" t="inlineStr">
+      <c r="C41" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">clinic_orders</t>
         </is>
       </c>
-      <c r="D40" s="8" t="inlineStr">
+      <c r="D41" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">実装済み</t>
         </is>
       </c>
-      <c r="E40" s="8" t="inlineStr">
+      <c r="E41" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">BGJから医院へのB2B仕入・売上履歴</t>
         </is>
       </c>
-      <c r="F40" s="8" t="inlineStr">
+      <c r="F41" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">患者注文系列へ統合しない</t>
         </is>
@@ -1690,7 +1722,7 @@
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
   </mergeCells>
-  <autoFilter ref="A4:F40"/>
+  <autoFilter ref="A4:F41"/>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0" paperSize="9"/>
 </worksheet>
@@ -1698,7 +1730,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K225"/>
+  <dimension ref="A1:K231"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -11198,27 +11230,27 @@
       </c>
       <c r="B170" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院業務連絡担当者</t>
+          <t xml:space="preserve">医院担当者役職</t>
         </is>
       </c>
       <c r="C170" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_contacts</t>
+          <t xml:space="preserve">clinic_contact_roles</t>
         </is>
       </c>
       <c r="D170" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">担当者ID</t>
+          <t xml:space="preserve">役職キー</t>
         </is>
       </c>
       <c r="E170" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">role_key</t>
         </is>
       </c>
       <c r="F170" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">uuid</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="G170" s="5" t="inlineStr">
@@ -11233,12 +11265,12 @@
       </c>
       <c r="I170" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">gen_random_uuid()</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J170" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">physician / dentist / nurse / dental_hygienist / receptionist / other</t>
         </is>
       </c>
       <c r="K170" s="4" t="inlineStr">
@@ -11255,22 +11287,22 @@
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院業務連絡担当者</t>
+          <t xml:space="preserve">医院担当者役職</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_contacts</t>
+          <t xml:space="preserve">clinic_contact_roles</t>
         </is>
       </c>
       <c r="D171" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">得意先コード</t>
+          <t xml:space="preserve">役職名</t>
         </is>
       </c>
       <c r="E171" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">customer_code</t>
+          <t xml:space="preserve">label</t>
         </is>
       </c>
       <c r="F171" s="4" t="inlineStr">
@@ -11278,9 +11310,9 @@
           <t xml:space="preserve">text</t>
         </is>
       </c>
-      <c r="G171" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FK</t>
+      <c r="G171" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UK</t>
         </is>
       </c>
       <c r="H171" s="4" t="inlineStr">
@@ -11295,7 +11327,7 @@
       </c>
       <c r="J171" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinics.customer_code ON DELETE RESTRICT</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K171" s="4" t="inlineStr">
@@ -11312,37 +11344,37 @@
       </c>
       <c r="B172" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院業務連絡担当者</t>
+          <t xml:space="preserve">医院担当者役職</t>
         </is>
       </c>
       <c r="C172" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_contacts</t>
+          <t xml:space="preserve">clinic_contact_roles</t>
         </is>
       </c>
       <c r="D172" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院ログインID</t>
+          <t xml:space="preserve">表示順</t>
         </is>
       </c>
       <c r="E172" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_user_id</t>
+          <t xml:space="preserve">sort_order</t>
         </is>
       </c>
       <c r="F172" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">uuid</t>
-        </is>
-      </c>
-      <c r="G172" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FK</t>
+          <t xml:space="preserve">integer</t>
+        </is>
+      </c>
+      <c r="G172" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UK</t>
         </is>
       </c>
       <c r="H172" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">YES</t>
+          <t xml:space="preserve">NO</t>
         </is>
       </c>
       <c r="I172" s="4" t="inlineStr">
@@ -11352,7 +11384,7 @@
       </c>
       <c r="J172" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_users.id ON DELETE SET NULL</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K172" s="4" t="inlineStr">
@@ -11369,27 +11401,27 @@
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院業務連絡担当者</t>
+          <t xml:space="preserve">医院担当者役職</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_contacts</t>
+          <t xml:space="preserve">clinic_contact_roles</t>
         </is>
       </c>
       <c r="D173" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">氏名</t>
+          <t xml:space="preserve">作成日時</t>
         </is>
       </c>
       <c r="E173" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">created_at</t>
         </is>
       </c>
       <c r="F173" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">timestamptz</t>
         </is>
       </c>
       <c r="G173" s="4" t="inlineStr">
@@ -11404,7 +11436,7 @@
       </c>
       <c r="I173" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">now()</t>
         </is>
       </c>
       <c r="J173" s="4" t="inlineStr">
@@ -11426,27 +11458,27 @@
       </c>
       <c r="B174" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院業務連絡担当者</t>
+          <t xml:space="preserve">医院担当者役職</t>
         </is>
       </c>
       <c r="C174" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_contacts</t>
+          <t xml:space="preserve">clinic_contact_roles</t>
         </is>
       </c>
       <c r="D174" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">部署</t>
+          <t xml:space="preserve">更新日時</t>
         </is>
       </c>
       <c r="E174" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">department</t>
+          <t xml:space="preserve">updated_at</t>
         </is>
       </c>
       <c r="F174" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">timestamptz</t>
         </is>
       </c>
       <c r="G174" s="4" t="inlineStr">
@@ -11456,12 +11488,12 @@
       </c>
       <c r="H174" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">YES</t>
+          <t xml:space="preserve">NO</t>
         </is>
       </c>
       <c r="I174" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">now()</t>
         </is>
       </c>
       <c r="J174" s="4" t="inlineStr">
@@ -11493,32 +11525,32 @@
       </c>
       <c r="D175" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">役職</t>
+          <t xml:space="preserve">担当者ID</t>
         </is>
       </c>
       <c r="E175" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">title</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="F175" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="G175" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">uuid</t>
+        </is>
+      </c>
+      <c r="G175" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK</t>
         </is>
       </c>
       <c r="H175" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">YES</t>
+          <t xml:space="preserve">NO</t>
         </is>
       </c>
       <c r="I175" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">gen_random_uuid()</t>
         </is>
       </c>
       <c r="J175" s="4" t="inlineStr">
@@ -11550,12 +11582,12 @@
       </c>
       <c r="D176" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">メールアドレス</t>
+          <t xml:space="preserve">得意先コード</t>
         </is>
       </c>
       <c r="E176" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">email</t>
+          <t xml:space="preserve">customer_code</t>
         </is>
       </c>
       <c r="F176" s="4" t="inlineStr">
@@ -11563,14 +11595,14 @@
           <t xml:space="preserve">text</t>
         </is>
       </c>
-      <c r="G176" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="G176" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
         </is>
       </c>
       <c r="H176" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">YES</t>
+          <t xml:space="preserve">NO</t>
         </is>
       </c>
       <c r="I176" s="4" t="inlineStr">
@@ -11580,7 +11612,7 @@
       </c>
       <c r="J176" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">clinics.customer_code ON DELETE RESTRICT</t>
         </is>
       </c>
       <c r="K176" s="4" t="inlineStr">
@@ -11607,27 +11639,27 @@
       </c>
       <c r="D177" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">電話番号</t>
+          <t xml:space="preserve">認証アカウント内部ID</t>
         </is>
       </c>
       <c r="E177" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">phone</t>
+          <t xml:space="preserve">clinic_user_id</t>
         </is>
       </c>
       <c r="F177" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="G177" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">uuid</t>
+        </is>
+      </c>
+      <c r="G177" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UK / FK</t>
         </is>
       </c>
       <c r="H177" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">YES</t>
+          <t xml:space="preserve">NO</t>
         </is>
       </c>
       <c r="I177" s="4" t="inlineStr">
@@ -11637,7 +11669,7 @@
       </c>
       <c r="J177" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">clinic_users.(id, customer_code) ON DELETE RESTRICT</t>
         </is>
       </c>
       <c r="K177" s="4" t="inlineStr">
@@ -11664,17 +11696,17 @@
       </c>
       <c r="D178" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">主担当</t>
+          <t xml:space="preserve">氏名</t>
         </is>
       </c>
       <c r="E178" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">is_primary</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="F178" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">boolean</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="G178" s="4" t="inlineStr">
@@ -11689,7 +11721,7 @@
       </c>
       <c r="I178" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J178" s="4" t="inlineStr">
@@ -11721,12 +11753,12 @@
       </c>
       <c r="D179" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">状態</t>
+          <t xml:space="preserve">部署</t>
         </is>
       </c>
       <c r="E179" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">status</t>
+          <t xml:space="preserve">department</t>
         </is>
       </c>
       <c r="F179" s="4" t="inlineStr">
@@ -11741,17 +11773,17 @@
       </c>
       <c r="H179" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO</t>
+          <t xml:space="preserve">YES</t>
         </is>
       </c>
       <c r="I179" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">active</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J179" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">active / inactive</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K179" s="4" t="inlineStr">
@@ -11778,12 +11810,12 @@
       </c>
       <c r="D180" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">備考</t>
+          <t xml:space="preserve">役職キー</t>
         </is>
       </c>
       <c r="E180" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">notes</t>
+          <t xml:space="preserve">role_key</t>
         </is>
       </c>
       <c r="F180" s="4" t="inlineStr">
@@ -11791,24 +11823,24 @@
           <t xml:space="preserve">text</t>
         </is>
       </c>
-      <c r="G180" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="G180" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
         </is>
       </c>
       <c r="H180" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">YES</t>
+          <t xml:space="preserve">NO</t>
         </is>
       </c>
       <c r="I180" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">other</t>
         </is>
       </c>
       <c r="J180" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">clinic_contact_roles.role_key ON DELETE RESTRICT</t>
         </is>
       </c>
       <c r="K180" s="4" t="inlineStr">
@@ -11835,17 +11867,17 @@
       </c>
       <c r="D181" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">排他バージョン</t>
+          <t xml:space="preserve">メールアドレス</t>
         </is>
       </c>
       <c r="E181" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">version</t>
+          <t xml:space="preserve">email</t>
         </is>
       </c>
       <c r="F181" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">integer</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="G181" s="4" t="inlineStr">
@@ -11855,12 +11887,12 @@
       </c>
       <c r="H181" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO</t>
+          <t xml:space="preserve">YES</t>
         </is>
       </c>
       <c r="I181" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J181" s="4" t="inlineStr">
@@ -11892,17 +11924,17 @@
       </c>
       <c r="D182" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">論理削除日時</t>
+          <t xml:space="preserve">電話番号</t>
         </is>
       </c>
       <c r="E182" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">deleted_at</t>
+          <t xml:space="preserve">phone</t>
         </is>
       </c>
       <c r="F182" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">timestamptz</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="G182" s="4" t="inlineStr">
@@ -11949,17 +11981,17 @@
       </c>
       <c r="D183" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">作成日時</t>
+          <t xml:space="preserve">主担当</t>
         </is>
       </c>
       <c r="E183" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">created_at</t>
+          <t xml:space="preserve">is_primary</t>
         </is>
       </c>
       <c r="F183" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">timestamptz</t>
+          <t xml:space="preserve">boolean</t>
         </is>
       </c>
       <c r="G183" s="4" t="inlineStr">
@@ -11974,7 +12006,7 @@
       </c>
       <c r="I183" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">now()</t>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="J183" s="4" t="inlineStr">
@@ -12006,17 +12038,17 @@
       </c>
       <c r="D184" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">更新日時</t>
+          <t xml:space="preserve">状態</t>
         </is>
       </c>
       <c r="E184" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">updated_at</t>
+          <t xml:space="preserve">status</t>
         </is>
       </c>
       <c r="F184" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">timestamptz</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="G184" s="4" t="inlineStr">
@@ -12031,12 +12063,12 @@
       </c>
       <c r="I184" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">now()</t>
+          <t xml:space="preserve">active</t>
         </is>
       </c>
       <c r="J184" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">active / inactive</t>
         </is>
       </c>
       <c r="K184" s="4" t="inlineStr">
@@ -12053,42 +12085,42 @@
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院ポータルログイン</t>
+          <t xml:space="preserve">医院業務連絡担当者</t>
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_users</t>
+          <t xml:space="preserve">clinic_contacts</t>
         </is>
       </c>
       <c r="D185" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院ログインID</t>
+          <t xml:space="preserve">備考</t>
         </is>
       </c>
       <c r="E185" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">notes</t>
         </is>
       </c>
       <c r="F185" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">uuid</t>
-        </is>
-      </c>
-      <c r="G185" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PK</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G185" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H185" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO</t>
+          <t xml:space="preserve">YES</t>
         </is>
       </c>
       <c r="I185" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">gen_random_uuid()</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J185" s="4" t="inlineStr">
@@ -12110,32 +12142,32 @@
       </c>
       <c r="B186" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院ポータルログイン</t>
+          <t xml:space="preserve">医院業務連絡担当者</t>
         </is>
       </c>
       <c r="C186" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_users</t>
+          <t xml:space="preserve">clinic_contacts</t>
         </is>
       </c>
       <c r="D186" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">得意先コード</t>
+          <t xml:space="preserve">排他バージョン</t>
         </is>
       </c>
       <c r="E186" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">customer_code</t>
+          <t xml:space="preserve">version</t>
         </is>
       </c>
       <c r="F186" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="G186" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FK</t>
+          <t xml:space="preserve">integer</t>
+        </is>
+      </c>
+      <c r="G186" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H186" s="4" t="inlineStr">
@@ -12145,12 +12177,12 @@
       </c>
       <c r="I186" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J186" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinics.customer_code ON DELETE CASCADE</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K186" s="4" t="inlineStr">
@@ -12167,37 +12199,37 @@
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院ポータルログイン</t>
+          <t xml:space="preserve">医院業務連絡担当者</t>
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_users</t>
+          <t xml:space="preserve">clinic_contacts</t>
         </is>
       </c>
       <c r="D187" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ログインID</t>
+          <t xml:space="preserve">論理削除日時</t>
         </is>
       </c>
       <c r="E187" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">login_id</t>
+          <t xml:space="preserve">deleted_at</t>
         </is>
       </c>
       <c r="F187" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="G187" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UK</t>
+          <t xml:space="preserve">timestamptz</t>
+        </is>
+      </c>
+      <c r="G187" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H187" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO</t>
+          <t xml:space="preserve">YES</t>
         </is>
       </c>
       <c r="I187" s="4" t="inlineStr">
@@ -12224,27 +12256,27 @@
       </c>
       <c r="B188" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院ポータルログイン</t>
+          <t xml:space="preserve">医院業務連絡担当者</t>
         </is>
       </c>
       <c r="C188" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_users</t>
+          <t xml:space="preserve">clinic_contacts</t>
         </is>
       </c>
       <c r="D188" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">パスワードハッシュ</t>
+          <t xml:space="preserve">作成日時</t>
         </is>
       </c>
       <c r="E188" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">password_hash</t>
+          <t xml:space="preserve">created_at</t>
         </is>
       </c>
       <c r="F188" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">timestamptz</t>
         </is>
       </c>
       <c r="G188" s="4" t="inlineStr">
@@ -12259,7 +12291,7 @@
       </c>
       <c r="I188" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">now()</t>
         </is>
       </c>
       <c r="J188" s="4" t="inlineStr">
@@ -12281,27 +12313,27 @@
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院ポータルログイン</t>
+          <t xml:space="preserve">医院業務連絡担当者</t>
         </is>
       </c>
       <c r="C189" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_users</t>
+          <t xml:space="preserve">clinic_contacts</t>
         </is>
       </c>
       <c r="D189" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">表示名</t>
+          <t xml:space="preserve">更新日時</t>
         </is>
       </c>
       <c r="E189" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">updated_at</t>
         </is>
       </c>
       <c r="F189" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">timestamptz</t>
         </is>
       </c>
       <c r="G189" s="4" t="inlineStr">
@@ -12311,12 +12343,12 @@
       </c>
       <c r="H189" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">YES</t>
+          <t xml:space="preserve">NO</t>
         </is>
       </c>
       <c r="I189" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">now()</t>
         </is>
       </c>
       <c r="J189" s="4" t="inlineStr">
@@ -12348,32 +12380,32 @@
       </c>
       <c r="D190" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">メールアドレス</t>
+          <t xml:space="preserve">医院ログインID</t>
         </is>
       </c>
       <c r="E190" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">email</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="F190" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="G190" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">uuid</t>
+        </is>
+      </c>
+      <c r="G190" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK</t>
         </is>
       </c>
       <c r="H190" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">YES</t>
+          <t xml:space="preserve">NO</t>
         </is>
       </c>
       <c r="I190" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">gen_random_uuid()</t>
         </is>
       </c>
       <c r="J190" s="4" t="inlineStr">
@@ -12405,12 +12437,12 @@
       </c>
       <c r="D191" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">状態</t>
+          <t xml:space="preserve">得意先コード</t>
         </is>
       </c>
       <c r="E191" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">status</t>
+          <t xml:space="preserve">customer_code</t>
         </is>
       </c>
       <c r="F191" s="4" t="inlineStr">
@@ -12418,9 +12450,9 @@
           <t xml:space="preserve">text</t>
         </is>
       </c>
-      <c r="G191" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="G191" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
         </is>
       </c>
       <c r="H191" s="4" t="inlineStr">
@@ -12430,12 +12462,12 @@
       </c>
       <c r="I191" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">有効</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J191" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">有効 / 無効</t>
+          <t xml:space="preserve">clinics.customer_code ON DELETE CASCADE</t>
         </is>
       </c>
       <c r="K191" s="4" t="inlineStr">
@@ -12462,22 +12494,22 @@
       </c>
       <c r="D192" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">作成日時</t>
+          <t xml:space="preserve">担当者ID兼ログインID</t>
         </is>
       </c>
       <c r="E192" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">created_at</t>
+          <t xml:space="preserve">login_id</t>
         </is>
       </c>
       <c r="F192" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">timestamptz</t>
-        </is>
-      </c>
-      <c r="G192" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G192" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UK</t>
         </is>
       </c>
       <c r="H192" s="4" t="inlineStr">
@@ -12487,7 +12519,7 @@
       </c>
       <c r="I192" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">now()</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J192" s="4" t="inlineStr">
@@ -12497,7 +12529,7 @@
       </c>
       <c r="K192" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">A+6桁。画面では担当者IDとして表示し、この値でログインする</t>
         </is>
       </c>
     </row>
@@ -12519,17 +12551,17 @@
       </c>
       <c r="D193" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">更新日時</t>
+          <t xml:space="preserve">パスワードハッシュ</t>
         </is>
       </c>
       <c r="E193" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">updated_at</t>
+          <t xml:space="preserve">password_hash</t>
         </is>
       </c>
       <c r="F193" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">timestamptz</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="G193" s="4" t="inlineStr">
@@ -12544,7 +12576,7 @@
       </c>
       <c r="I193" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">now()</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J193" s="4" t="inlineStr">
@@ -12576,17 +12608,17 @@
       </c>
       <c r="D194" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ログイン失敗回数</t>
+          <t xml:space="preserve">表示名</t>
         </is>
       </c>
       <c r="E194" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">failed_login_attempts</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="F194" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">integer</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="G194" s="4" t="inlineStr">
@@ -12596,12 +12628,12 @@
       </c>
       <c r="H194" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO</t>
+          <t xml:space="preserve">YES</t>
         </is>
       </c>
       <c r="I194" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J194" s="4" t="inlineStr">
@@ -12633,17 +12665,17 @@
       </c>
       <c r="D195" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ロック解除日時</t>
+          <t xml:space="preserve">メールアドレス</t>
         </is>
       </c>
       <c r="E195" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">locked_until</t>
+          <t xml:space="preserve">email</t>
         </is>
       </c>
       <c r="F195" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">timestamptz</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="G195" s="4" t="inlineStr">
@@ -12690,17 +12722,17 @@
       </c>
       <c r="D196" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">セッション世代</t>
+          <t xml:space="preserve">状態</t>
         </is>
       </c>
       <c r="E196" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">session_version</t>
+          <t xml:space="preserve">status</t>
         </is>
       </c>
       <c r="F196" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">integer</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="G196" s="4" t="inlineStr">
@@ -12715,17 +12747,17 @@
       </c>
       <c r="I196" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">有効</t>
         </is>
       </c>
       <c r="J196" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">&gt; 0</t>
+          <t xml:space="preserve">有効 / 無効</t>
         </is>
       </c>
       <c r="K196" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">無効化・パスワード変更時に加算し旧セッションを失効</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
@@ -12747,12 +12779,12 @@
       </c>
       <c r="D197" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">最終ログイン日時</t>
+          <t xml:space="preserve">作成日時</t>
         </is>
       </c>
       <c r="E197" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">last_login_at</t>
+          <t xml:space="preserve">created_at</t>
         </is>
       </c>
       <c r="F197" s="4" t="inlineStr">
@@ -12767,12 +12799,12 @@
       </c>
       <c r="H197" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">YES</t>
+          <t xml:space="preserve">NO</t>
         </is>
       </c>
       <c r="I197" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">now()</t>
         </is>
       </c>
       <c r="J197" s="4" t="inlineStr">
@@ -12804,12 +12836,12 @@
       </c>
       <c r="D198" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">パスワード変更日時</t>
+          <t xml:space="preserve">更新日時</t>
         </is>
       </c>
       <c r="E198" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">password_changed_at</t>
+          <t xml:space="preserve">updated_at</t>
         </is>
       </c>
       <c r="F198" s="4" t="inlineStr">
@@ -12824,12 +12856,12 @@
       </c>
       <c r="H198" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">YES</t>
+          <t xml:space="preserve">NO</t>
         </is>
       </c>
       <c r="I198" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">now()</t>
         </is>
       </c>
       <c r="J198" s="4" t="inlineStr">
@@ -12851,32 +12883,32 @@
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院ポータル権限</t>
+          <t xml:space="preserve">医院ポータルログイン</t>
         </is>
       </c>
       <c r="C199" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_portal_roles</t>
+          <t xml:space="preserve">clinic_users</t>
         </is>
       </c>
       <c r="D199" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">権限キー</t>
+          <t xml:space="preserve">ログイン失敗回数</t>
         </is>
       </c>
       <c r="E199" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">role_key</t>
+          <t xml:space="preserve">failed_login_attempts</t>
         </is>
       </c>
       <c r="F199" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="G199" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PK</t>
+          <t xml:space="preserve">integer</t>
+        </is>
+      </c>
+      <c r="G199" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H199" s="4" t="inlineStr">
@@ -12886,12 +12918,12 @@
       </c>
       <c r="I199" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="J199" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin / staff / viewer</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K199" s="4" t="inlineStr">
@@ -12908,37 +12940,37 @@
       </c>
       <c r="B200" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院ポータル権限</t>
+          <t xml:space="preserve">医院ポータルログイン</t>
         </is>
       </c>
       <c r="C200" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_portal_roles</t>
+          <t xml:space="preserve">clinic_users</t>
         </is>
       </c>
       <c r="D200" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">権限名</t>
+          <t xml:space="preserve">ロック解除日時</t>
         </is>
       </c>
       <c r="E200" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">label</t>
+          <t xml:space="preserve">locked_until</t>
         </is>
       </c>
       <c r="F200" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="G200" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UK</t>
+          <t xml:space="preserve">timestamptz</t>
+        </is>
+      </c>
+      <c r="G200" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H200" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO</t>
+          <t xml:space="preserve">YES</t>
         </is>
       </c>
       <c r="I200" s="4" t="inlineStr">
@@ -12965,27 +12997,27 @@
       </c>
       <c r="B201" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院ポータル権限</t>
+          <t xml:space="preserve">医院ポータルログイン</t>
         </is>
       </c>
       <c r="C201" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_portal_roles</t>
+          <t xml:space="preserve">clinic_users</t>
         </is>
       </c>
       <c r="D201" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">説明</t>
+          <t xml:space="preserve">セッション世代</t>
         </is>
       </c>
       <c r="E201" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">description</t>
+          <t xml:space="preserve">session_version</t>
         </is>
       </c>
       <c r="F201" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">integer</t>
         </is>
       </c>
       <c r="G201" s="4" t="inlineStr">
@@ -13000,17 +13032,17 @@
       </c>
       <c r="I201" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J201" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">&gt; 0</t>
         </is>
       </c>
       <c r="K201" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">無効化・パスワード変更時に加算し旧セッションを失効</t>
         </is>
       </c>
     </row>
@@ -13022,37 +13054,37 @@
       </c>
       <c r="B202" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院ポータル権限</t>
+          <t xml:space="preserve">医院ポータルログイン</t>
         </is>
       </c>
       <c r="C202" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_portal_roles</t>
+          <t xml:space="preserve">clinic_users</t>
         </is>
       </c>
       <c r="D202" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">表示順</t>
+          <t xml:space="preserve">最終ログイン日時</t>
         </is>
       </c>
       <c r="E202" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">sort_order</t>
+          <t xml:space="preserve">last_login_at</t>
         </is>
       </c>
       <c r="F202" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">integer</t>
-        </is>
-      </c>
-      <c r="G202" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UK</t>
+          <t xml:space="preserve">timestamptz</t>
+        </is>
+      </c>
+      <c r="G202" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H202" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO</t>
+          <t xml:space="preserve">YES</t>
         </is>
       </c>
       <c r="I202" s="4" t="inlineStr">
@@ -13079,22 +13111,22 @@
       </c>
       <c r="B203" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院ポータル権限</t>
+          <t xml:space="preserve">医院ポータルログイン</t>
         </is>
       </c>
       <c r="C203" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_portal_roles</t>
+          <t xml:space="preserve">clinic_users</t>
         </is>
       </c>
       <c r="D203" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">作成日時</t>
+          <t xml:space="preserve">パスワード変更日時</t>
         </is>
       </c>
       <c r="E203" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">created_at</t>
+          <t xml:space="preserve">password_changed_at</t>
         </is>
       </c>
       <c r="F203" s="4" t="inlineStr">
@@ -13109,12 +13141,12 @@
       </c>
       <c r="H203" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO</t>
+          <t xml:space="preserve">YES</t>
         </is>
       </c>
       <c r="I203" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">now()</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J203" s="4" t="inlineStr">
@@ -13136,27 +13168,27 @@
       </c>
       <c r="B204" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院ポータル権限</t>
+          <t xml:space="preserve">医院ポータルログイン</t>
         </is>
       </c>
       <c r="C204" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_portal_roles</t>
+          <t xml:space="preserve">clinic_users</t>
         </is>
       </c>
       <c r="D204" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">更新日時</t>
+          <t xml:space="preserve">初回変更必須</t>
         </is>
       </c>
       <c r="E204" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">updated_at</t>
+          <t xml:space="preserve">must_change_password</t>
         </is>
       </c>
       <c r="F204" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">timestamptz</t>
+          <t xml:space="preserve">boolean</t>
         </is>
       </c>
       <c r="G204" s="4" t="inlineStr">
@@ -13171,7 +13203,7 @@
       </c>
       <c r="I204" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">now()</t>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="J204" s="4" t="inlineStr">
@@ -13181,7 +13213,7 @@
       </c>
       <c r="K204" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">新規発行時true。初回変更または既存リセット完了時false</t>
         </is>
       </c>
     </row>
@@ -13193,12 +13225,12 @@
       </c>
       <c r="B205" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院ポータル権限機能</t>
+          <t xml:space="preserve">医院ポータル権限</t>
         </is>
       </c>
       <c r="C205" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_portal_role_permissions</t>
+          <t xml:space="preserve">clinic_portal_roles</t>
         </is>
       </c>
       <c r="D205" s="4" t="inlineStr">
@@ -13218,7 +13250,7 @@
       </c>
       <c r="G205" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">PK / FK</t>
+          <t xml:space="preserve">PK</t>
         </is>
       </c>
       <c r="H205" s="4" t="inlineStr">
@@ -13233,7 +13265,7 @@
       </c>
       <c r="J205" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_portal_roles.role_key ON DELETE RESTRICT</t>
+          <t xml:space="preserve">admin / staff / viewer</t>
         </is>
       </c>
       <c r="K205" s="4" t="inlineStr">
@@ -13250,22 +13282,22 @@
       </c>
       <c r="B206" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院ポータル権限機能</t>
+          <t xml:space="preserve">医院ポータル権限</t>
         </is>
       </c>
       <c r="C206" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_portal_role_permissions</t>
+          <t xml:space="preserve">clinic_portal_roles</t>
         </is>
       </c>
       <c r="D206" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">機能キー</t>
+          <t xml:space="preserve">権限名</t>
         </is>
       </c>
       <c r="E206" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">permission_key</t>
+          <t xml:space="preserve">label</t>
         </is>
       </c>
       <c r="F206" s="4" t="inlineStr">
@@ -13273,9 +13305,9 @@
           <t xml:space="preserve">text</t>
         </is>
       </c>
-      <c r="G206" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PK</t>
+      <c r="G206" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UK</t>
         </is>
       </c>
       <c r="H206" s="4" t="inlineStr">
@@ -13290,7 +13322,7 @@
       </c>
       <c r="J206" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">view_contacts / manage_contacts / manage_logins</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K206" s="4" t="inlineStr">
@@ -13307,27 +13339,27 @@
       </c>
       <c r="B207" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院ポータル権限機能</t>
+          <t xml:space="preserve">医院ポータル権限</t>
         </is>
       </c>
       <c r="C207" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_portal_role_permissions</t>
+          <t xml:space="preserve">clinic_portal_roles</t>
         </is>
       </c>
       <c r="D207" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">作成日時</t>
+          <t xml:space="preserve">説明</t>
         </is>
       </c>
       <c r="E207" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">created_at</t>
+          <t xml:space="preserve">description</t>
         </is>
       </c>
       <c r="F207" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">timestamptz</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="G207" s="4" t="inlineStr">
@@ -13342,7 +13374,7 @@
       </c>
       <c r="I207" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">now()</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J207" s="4" t="inlineStr">
@@ -13364,32 +13396,32 @@
       </c>
       <c r="B208" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院ログイン権限割当</t>
+          <t xml:space="preserve">医院ポータル権限</t>
         </is>
       </c>
       <c r="C208" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_user_role_assignments</t>
+          <t xml:space="preserve">clinic_portal_roles</t>
         </is>
       </c>
       <c r="D208" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院ログインID</t>
+          <t xml:space="preserve">表示順</t>
         </is>
       </c>
       <c r="E208" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_user_id</t>
+          <t xml:space="preserve">sort_order</t>
         </is>
       </c>
       <c r="F208" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">uuid</t>
-        </is>
-      </c>
-      <c r="G208" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PK / FK</t>
+          <t xml:space="preserve">integer</t>
+        </is>
+      </c>
+      <c r="G208" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UK</t>
         </is>
       </c>
       <c r="H208" s="4" t="inlineStr">
@@ -13404,7 +13436,7 @@
       </c>
       <c r="J208" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_users.id ON DELETE CASCADE</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K208" s="4" t="inlineStr">
@@ -13421,32 +13453,32 @@
       </c>
       <c r="B209" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院ログイン権限割当</t>
+          <t xml:space="preserve">医院ポータル権限</t>
         </is>
       </c>
       <c r="C209" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_user_role_assignments</t>
+          <t xml:space="preserve">clinic_portal_roles</t>
         </is>
       </c>
       <c r="D209" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">権限キー</t>
+          <t xml:space="preserve">作成日時</t>
         </is>
       </c>
       <c r="E209" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">role_key</t>
+          <t xml:space="preserve">created_at</t>
         </is>
       </c>
       <c r="F209" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="G209" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FK</t>
+          <t xml:space="preserve">timestamptz</t>
+        </is>
+      </c>
+      <c r="G209" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H209" s="4" t="inlineStr">
@@ -13456,12 +13488,12 @@
       </c>
       <c r="I209" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">now()</t>
         </is>
       </c>
       <c r="J209" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_portal_roles.role_key ON DELETE RESTRICT</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K209" s="4" t="inlineStr">
@@ -13478,27 +13510,27 @@
       </c>
       <c r="B210" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院ログイン権限割当</t>
+          <t xml:space="preserve">医院ポータル権限</t>
         </is>
       </c>
       <c r="C210" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_user_role_assignments</t>
+          <t xml:space="preserve">clinic_portal_roles</t>
         </is>
       </c>
       <c r="D210" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">割当操作者</t>
+          <t xml:space="preserve">更新日時</t>
         </is>
       </c>
       <c r="E210" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">assigned_by</t>
+          <t xml:space="preserve">updated_at</t>
         </is>
       </c>
       <c r="F210" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">timestamptz</t>
         </is>
       </c>
       <c r="G210" s="4" t="inlineStr">
@@ -13513,7 +13545,7 @@
       </c>
       <c r="I210" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">system</t>
+          <t xml:space="preserve">now()</t>
         </is>
       </c>
       <c r="J210" s="4" t="inlineStr">
@@ -13535,32 +13567,32 @@
       </c>
       <c r="B211" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院ログイン権限割当</t>
+          <t xml:space="preserve">医院ポータル権限機能</t>
         </is>
       </c>
       <c r="C211" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_user_role_assignments</t>
+          <t xml:space="preserve">clinic_portal_role_permissions</t>
         </is>
       </c>
       <c r="D211" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">作成日時</t>
+          <t xml:space="preserve">権限キー</t>
         </is>
       </c>
       <c r="E211" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">created_at</t>
+          <t xml:space="preserve">role_key</t>
         </is>
       </c>
       <c r="F211" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">timestamptz</t>
-        </is>
-      </c>
-      <c r="G211" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G211" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK / FK</t>
         </is>
       </c>
       <c r="H211" s="4" t="inlineStr">
@@ -13570,12 +13602,12 @@
       </c>
       <c r="I211" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">now()</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J211" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">clinic_portal_roles.role_key ON DELETE RESTRICT</t>
         </is>
       </c>
       <c r="K211" s="4" t="inlineStr">
@@ -13592,32 +13624,32 @@
       </c>
       <c r="B212" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院ログイン権限割当</t>
+          <t xml:space="preserve">医院ポータル権限機能</t>
         </is>
       </c>
       <c r="C212" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_user_role_assignments</t>
+          <t xml:space="preserve">clinic_portal_role_permissions</t>
         </is>
       </c>
       <c r="D212" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">更新日時</t>
+          <t xml:space="preserve">機能キー</t>
         </is>
       </c>
       <c r="E212" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">updated_at</t>
+          <t xml:space="preserve">permission_key</t>
         </is>
       </c>
       <c r="F212" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">timestamptz</t>
-        </is>
-      </c>
-      <c r="G212" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G212" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK</t>
         </is>
       </c>
       <c r="H212" s="4" t="inlineStr">
@@ -13627,12 +13659,12 @@
       </c>
       <c r="I212" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">now()</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J212" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">view_contacts / manage_contacts / manage_logins</t>
         </is>
       </c>
       <c r="K212" s="4" t="inlineStr">
@@ -13649,32 +13681,32 @@
       </c>
       <c r="B213" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">担当者通知設定</t>
+          <t xml:space="preserve">医院ポータル権限機能</t>
         </is>
       </c>
       <c r="C213" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_contact_notification_preferences</t>
+          <t xml:space="preserve">clinic_portal_role_permissions</t>
         </is>
       </c>
       <c r="D213" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">担当者ID</t>
+          <t xml:space="preserve">作成日時</t>
         </is>
       </c>
       <c r="E213" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">contact_id</t>
+          <t xml:space="preserve">created_at</t>
         </is>
       </c>
       <c r="F213" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">uuid</t>
-        </is>
-      </c>
-      <c r="G213" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PK / FK</t>
+          <t xml:space="preserve">timestamptz</t>
+        </is>
+      </c>
+      <c r="G213" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H213" s="4" t="inlineStr">
@@ -13684,12 +13716,12 @@
       </c>
       <c r="I213" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">now()</t>
         </is>
       </c>
       <c r="J213" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_contacts.id ON DELETE RESTRICT</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K213" s="4" t="inlineStr">
@@ -13706,32 +13738,32 @@
       </c>
       <c r="B214" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">担当者通知設定</t>
+          <t xml:space="preserve">医院ログイン権限割当</t>
         </is>
       </c>
       <c r="C214" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_contact_notification_preferences</t>
+          <t xml:space="preserve">clinic_user_role_assignments</t>
         </is>
       </c>
       <c r="D214" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">通知種別</t>
+          <t xml:space="preserve">医院ログインID</t>
         </is>
       </c>
       <c r="E214" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">topic</t>
+          <t xml:space="preserve">clinic_user_id</t>
         </is>
       </c>
       <c r="F214" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">uuid</t>
         </is>
       </c>
       <c r="G214" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">PK</t>
+          <t xml:space="preserve">PK / FK</t>
         </is>
       </c>
       <c r="H214" s="4" t="inlineStr">
@@ -13746,7 +13778,7 @@
       </c>
       <c r="J214" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">webinar / orders / billing / product / system / sales</t>
+          <t xml:space="preserve">clinic_users.id ON DELETE CASCADE</t>
         </is>
       </c>
       <c r="K214" s="4" t="inlineStr">
@@ -13763,22 +13795,22 @@
       </c>
       <c r="B215" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">担当者通知設定</t>
+          <t xml:space="preserve">医院ログイン権限割当</t>
         </is>
       </c>
       <c r="C215" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_contact_notification_preferences</t>
+          <t xml:space="preserve">clinic_user_role_assignments</t>
         </is>
       </c>
       <c r="D215" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">連絡方法</t>
+          <t xml:space="preserve">権限キー</t>
         </is>
       </c>
       <c r="E215" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">channel</t>
+          <t xml:space="preserve">role_key</t>
         </is>
       </c>
       <c r="F215" s="4" t="inlineStr">
@@ -13786,9 +13818,9 @@
           <t xml:space="preserve">text</t>
         </is>
       </c>
-      <c r="G215" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PK</t>
+      <c r="G215" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
         </is>
       </c>
       <c r="H215" s="4" t="inlineStr">
@@ -13803,7 +13835,7 @@
       </c>
       <c r="J215" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">email / phone</t>
+          <t xml:space="preserve">clinic_portal_roles.role_key ON DELETE RESTRICT</t>
         </is>
       </c>
       <c r="K215" s="4" t="inlineStr">
@@ -13820,27 +13852,27 @@
       </c>
       <c r="B216" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">担当者通知設定</t>
+          <t xml:space="preserve">医院ログイン権限割当</t>
         </is>
       </c>
       <c r="C216" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_contact_notification_preferences</t>
+          <t xml:space="preserve">clinic_user_role_assignments</t>
         </is>
       </c>
       <c r="D216" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">有効</t>
+          <t xml:space="preserve">割当操作者</t>
         </is>
       </c>
       <c r="E216" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">enabled</t>
+          <t xml:space="preserve">assigned_by</t>
         </is>
       </c>
       <c r="F216" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">boolean</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="G216" s="4" t="inlineStr">
@@ -13855,7 +13887,7 @@
       </c>
       <c r="I216" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">true</t>
+          <t xml:space="preserve">system</t>
         </is>
       </c>
       <c r="J216" s="4" t="inlineStr">
@@ -13877,12 +13909,12 @@
       </c>
       <c r="B217" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">担当者通知設定</t>
+          <t xml:space="preserve">医院ログイン権限割当</t>
         </is>
       </c>
       <c r="C217" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_contact_notification_preferences</t>
+          <t xml:space="preserve">clinic_user_role_assignments</t>
         </is>
       </c>
       <c r="D217" s="4" t="inlineStr">
@@ -13934,12 +13966,12 @@
       </c>
       <c r="B218" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">担当者通知設定</t>
+          <t xml:space="preserve">医院ログイン権限割当</t>
         </is>
       </c>
       <c r="C218" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_contact_notification_preferences</t>
+          <t xml:space="preserve">clinic_user_role_assignments</t>
         </is>
       </c>
       <c r="D218" s="4" t="inlineStr">
@@ -13991,22 +14023,22 @@
       </c>
       <c r="B219" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">担当者操作履歴</t>
+          <t xml:space="preserve">担当者通知設定</t>
         </is>
       </c>
       <c r="C219" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_contact_events</t>
+          <t xml:space="preserve">clinic_contact_notification_preferences</t>
         </is>
       </c>
       <c r="D219" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">イベントID</t>
+          <t xml:space="preserve">担当者ID</t>
         </is>
       </c>
       <c r="E219" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">contact_id</t>
         </is>
       </c>
       <c r="F219" s="4" t="inlineStr">
@@ -14016,7 +14048,7 @@
       </c>
       <c r="G219" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">PK</t>
+          <t xml:space="preserve">PK / FK</t>
         </is>
       </c>
       <c r="H219" s="4" t="inlineStr">
@@ -14026,12 +14058,12 @@
       </c>
       <c r="I219" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">gen_random_uuid()</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J219" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">clinic_contacts.id ON DELETE RESTRICT</t>
         </is>
       </c>
       <c r="K219" s="4" t="inlineStr">
@@ -14048,32 +14080,32 @@
       </c>
       <c r="B220" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">担当者操作履歴</t>
+          <t xml:space="preserve">担当者通知設定</t>
         </is>
       </c>
       <c r="C220" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_contact_events</t>
+          <t xml:space="preserve">clinic_contact_notification_preferences</t>
         </is>
       </c>
       <c r="D220" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">担当者ID</t>
+          <t xml:space="preserve">通知種別</t>
         </is>
       </c>
       <c r="E220" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">contact_id</t>
+          <t xml:space="preserve">topic</t>
         </is>
       </c>
       <c r="F220" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">uuid</t>
-        </is>
-      </c>
-      <c r="G220" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FK</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G220" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK</t>
         </is>
       </c>
       <c r="H220" s="4" t="inlineStr">
@@ -14088,7 +14120,7 @@
       </c>
       <c r="J220" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_contacts.id ON DELETE RESTRICT</t>
+          <t xml:space="preserve">webinar / orders / billing / product / system / sales</t>
         </is>
       </c>
       <c r="K220" s="4" t="inlineStr">
@@ -14105,22 +14137,22 @@
       </c>
       <c r="B221" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">担当者操作履歴</t>
+          <t xml:space="preserve">担当者通知設定</t>
         </is>
       </c>
       <c r="C221" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_contact_events</t>
+          <t xml:space="preserve">clinic_contact_notification_preferences</t>
         </is>
       </c>
       <c r="D221" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">イベント種別</t>
+          <t xml:space="preserve">連絡方法</t>
         </is>
       </c>
       <c r="E221" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">event_type</t>
+          <t xml:space="preserve">channel</t>
         </is>
       </c>
       <c r="F221" s="4" t="inlineStr">
@@ -14128,9 +14160,9 @@
           <t xml:space="preserve">text</t>
         </is>
       </c>
-      <c r="G221" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="G221" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK</t>
         </is>
       </c>
       <c r="H221" s="4" t="inlineStr">
@@ -14145,7 +14177,7 @@
       </c>
       <c r="J221" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">email / phone</t>
         </is>
       </c>
       <c r="K221" s="4" t="inlineStr">
@@ -14162,27 +14194,27 @@
       </c>
       <c r="B222" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">担当者操作履歴</t>
+          <t xml:space="preserve">担当者通知設定</t>
         </is>
       </c>
       <c r="C222" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_contact_events</t>
+          <t xml:space="preserve">clinic_contact_notification_preferences</t>
         </is>
       </c>
       <c r="D222" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">操作者種別</t>
+          <t xml:space="preserve">有効</t>
         </is>
       </c>
       <c r="E222" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">actor_type</t>
+          <t xml:space="preserve">enabled</t>
         </is>
       </c>
       <c r="F222" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">boolean</t>
         </is>
       </c>
       <c r="G222" s="4" t="inlineStr">
@@ -14197,7 +14229,7 @@
       </c>
       <c r="I222" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">true</t>
         </is>
       </c>
       <c r="J222" s="4" t="inlineStr">
@@ -14219,27 +14251,27 @@
       </c>
       <c r="B223" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">担当者操作履歴</t>
+          <t xml:space="preserve">担当者通知設定</t>
         </is>
       </c>
       <c r="C223" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_contact_events</t>
+          <t xml:space="preserve">clinic_contact_notification_preferences</t>
         </is>
       </c>
       <c r="D223" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">操作者識別子</t>
+          <t xml:space="preserve">作成日時</t>
         </is>
       </c>
       <c r="E223" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">actor_identifier</t>
+          <t xml:space="preserve">created_at</t>
         </is>
       </c>
       <c r="F223" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">timestamptz</t>
         </is>
       </c>
       <c r="G223" s="4" t="inlineStr">
@@ -14254,7 +14286,7 @@
       </c>
       <c r="I223" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">now()</t>
         </is>
       </c>
       <c r="J223" s="4" t="inlineStr">
@@ -14276,27 +14308,27 @@
       </c>
       <c r="B224" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">担当者操作履歴</t>
+          <t xml:space="preserve">担当者通知設定</t>
         </is>
       </c>
       <c r="C224" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_contact_events</t>
+          <t xml:space="preserve">clinic_contact_notification_preferences</t>
         </is>
       </c>
       <c r="D224" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">追加情報</t>
+          <t xml:space="preserve">更新日時</t>
         </is>
       </c>
       <c r="E224" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">metadata</t>
+          <t xml:space="preserve">updated_at</t>
         </is>
       </c>
       <c r="F224" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">jsonb</t>
+          <t xml:space="preserve">timestamptz</t>
         </is>
       </c>
       <c r="G224" s="4" t="inlineStr">
@@ -14311,7 +14343,7 @@
       </c>
       <c r="I224" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">{}</t>
+          <t xml:space="preserve">now()</t>
         </is>
       </c>
       <c r="J224" s="4" t="inlineStr">
@@ -14343,40 +14375,382 @@
       </c>
       <c r="D225" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">イベントID</t>
+        </is>
+      </c>
+      <c r="E225" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">id</t>
+        </is>
+      </c>
+      <c r="F225" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">uuid</t>
+        </is>
+      </c>
+      <c r="G225" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK</t>
+        </is>
+      </c>
+      <c r="H225" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I225" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gen_random_uuid()</t>
+        </is>
+      </c>
+      <c r="J225" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K225" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="226" ht="30" customHeight="1">
+      <c r="A226" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B226" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">担当者操作履歴</t>
+        </is>
+      </c>
+      <c r="C226" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_contact_events</t>
+        </is>
+      </c>
+      <c r="D226" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">担当者ID</t>
+        </is>
+      </c>
+      <c r="E226" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">contact_id</t>
+        </is>
+      </c>
+      <c r="F226" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">uuid</t>
+        </is>
+      </c>
+      <c r="G226" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
+        </is>
+      </c>
+      <c r="H226" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I226" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J226" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_contacts.id ON DELETE RESTRICT</t>
+        </is>
+      </c>
+      <c r="K226" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="227" ht="30" customHeight="1">
+      <c r="A227" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B227" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">担当者操作履歴</t>
+        </is>
+      </c>
+      <c r="C227" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_contact_events</t>
+        </is>
+      </c>
+      <c r="D227" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">イベント種別</t>
+        </is>
+      </c>
+      <c r="E227" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">event_type</t>
+        </is>
+      </c>
+      <c r="F227" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G227" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H227" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I227" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J227" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K227" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="228" ht="30" customHeight="1">
+      <c r="A228" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B228" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">担当者操作履歴</t>
+        </is>
+      </c>
+      <c r="C228" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_contact_events</t>
+        </is>
+      </c>
+      <c r="D228" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">操作者種別</t>
+        </is>
+      </c>
+      <c r="E228" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actor_type</t>
+        </is>
+      </c>
+      <c r="F228" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G228" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H228" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I228" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J228" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K228" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="229" ht="30" customHeight="1">
+      <c r="A229" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B229" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">担当者操作履歴</t>
+        </is>
+      </c>
+      <c r="C229" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_contact_events</t>
+        </is>
+      </c>
+      <c r="D229" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">操作者識別子</t>
+        </is>
+      </c>
+      <c r="E229" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actor_identifier</t>
+        </is>
+      </c>
+      <c r="F229" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G229" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H229" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I229" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J229" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K229" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="230" ht="30" customHeight="1">
+      <c r="A230" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B230" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">担当者操作履歴</t>
+        </is>
+      </c>
+      <c r="C230" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_contact_events</t>
+        </is>
+      </c>
+      <c r="D230" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">追加情報</t>
+        </is>
+      </c>
+      <c r="E230" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metadata</t>
+        </is>
+      </c>
+      <c r="F230" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jsonb</t>
+        </is>
+      </c>
+      <c r="G230" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H230" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I230" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{}</t>
+        </is>
+      </c>
+      <c r="J230" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K230" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="231" ht="30" customHeight="1">
+      <c r="A231" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B231" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">担当者操作履歴</t>
+        </is>
+      </c>
+      <c r="C231" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_contact_events</t>
+        </is>
+      </c>
+      <c r="D231" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">発生日時</t>
         </is>
       </c>
-      <c r="E225" s="4" t="inlineStr">
+      <c r="E231" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">created_at</t>
         </is>
       </c>
-      <c r="F225" s="4" t="inlineStr">
+      <c r="F231" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">timestamptz</t>
         </is>
       </c>
-      <c r="G225" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H225" s="4" t="inlineStr">
+      <c r="G231" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H231" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">NO</t>
         </is>
       </c>
-      <c r="I225" s="4" t="inlineStr">
+      <c r="I231" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">now()</t>
         </is>
       </c>
-      <c r="J225" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="K225" s="4" t="inlineStr">
+      <c r="J231" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K231" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -14387,7 +14761,7 @@
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A2:K2"/>
   </mergeCells>
-  <autoFilter ref="A4:K225"/>
+  <autoFilter ref="A4:K231"/>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0" paperSize="9"/>
 </worksheet>
@@ -19112,7 +19486,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G76"/>
+  <dimension ref="A1:G77"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -19733,17 +20107,17 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_user_id WHERE deleted_at IS NULL</t>
+          <t xml:space="preserve">clinic_user_id</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">PARTIAL UNIQUE</t>
+          <t xml:space="preserve">UNIQUE</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1ログインと複数担当者の誤関連防止。</t>
+          <t xml:space="preserve">1担当者と1認証アカウントを必須の一対一にする。</t>
         </is>
       </c>
     </row>
@@ -19775,7 +20149,7 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ログインIDの重複防止。</t>
+          <t xml:space="preserve">担当者ID兼ログインIDの重複防止。</t>
         </is>
       </c>
     </row>
@@ -20901,12 +21275,12 @@
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院ログイン</t>
+          <t xml:space="preserve">医院担当者役職</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_users.id</t>
+          <t xml:space="preserve">clinic_contact_roles.role_key</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -20916,12 +21290,12 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">0..1</t>
+          <t xml:space="preserve">N</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_contacts.clinic_user_id</t>
+          <t xml:space="preserve">clinic_contacts.role_key</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
@@ -20931,19 +21305,19 @@
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK・SET NULL</t>
+          <t xml:space="preserve">FK・RESTRICT</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院</t>
+          <t xml:space="preserve">医院認証アカウント</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinics.customer_code</t>
+          <t xml:space="preserve">clinic_users.(id, customer_code)</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -20953,34 +21327,34 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">N</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_users.customer_code</t>
+          <t xml:space="preserve">clinic_contacts.(clinic_user_id, customer_code)</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院ポータルログイン</t>
+          <t xml:space="preserve">医院業務連絡担当者</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK・CASCADE</t>
+          <t xml:space="preserve">UK・複合FK・RESTRICT</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院ポータル権限</t>
+          <t xml:space="preserve">医院</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_portal_roles.role_key</t>
+          <t xml:space="preserve">clinics.customer_code</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -20995,29 +21369,29 @@
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_portal_role_permissions.role_key</t>
+          <t xml:space="preserve">clinic_users.customer_code</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">権限機能</t>
+          <t xml:space="preserve">医院ポータルログイン</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">PK・FK・RESTRICT</t>
+          <t xml:space="preserve">FK・CASCADE</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院ポータルログイン</t>
+          <t xml:space="preserve">医院ポータル権限</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_users.id</t>
+          <t xml:space="preserve">clinic_portal_roles.role_key</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -21027,34 +21401,34 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">0..1</t>
+          <t xml:space="preserve">N</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_user_role_assignments.clinic_user_id</t>
+          <t xml:space="preserve">clinic_portal_role_permissions.role_key</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">権限割当</t>
+          <t xml:space="preserve">権限機能</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">PK・FK・CASCADE</t>
+          <t xml:space="preserve">PK・FK・RESTRICT</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院ポータル権限</t>
+          <t xml:space="preserve">医院ポータルログイン</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_portal_roles.role_key</t>
+          <t xml:space="preserve">clinic_users.id</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -21064,12 +21438,12 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">N</t>
+          <t xml:space="preserve">0..1</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_user_role_assignments.role_key</t>
+          <t xml:space="preserve">clinic_user_role_assignments.clinic_user_id</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
@@ -21079,19 +21453,19 @@
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK・RESTRICT</t>
+          <t xml:space="preserve">PK・FK・CASCADE</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院業務連絡担当者</t>
+          <t xml:space="preserve">医院ポータル権限</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_contacts.id</t>
+          <t xml:space="preserve">clinic_portal_roles.role_key</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -21106,17 +21480,17 @@
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_contact_notification_preferences.contact_id</t>
+          <t xml:space="preserve">clinic_user_role_assignments.role_key</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">担当者通知設定</t>
+          <t xml:space="preserve">権限割当</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">PK・FK・RESTRICT</t>
+          <t xml:space="preserve">FK・RESTRICT</t>
         </is>
       </c>
     </row>
@@ -21143,98 +21517,98 @@
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">clinic_contact_notification_preferences.contact_id</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">担当者通知設定</t>
+        </is>
+      </c>
+      <c r="G63" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK・FK・RESTRICT</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">医院業務連絡担当者</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_contacts.id</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">clinic_contact_events.contact_id</t>
         </is>
       </c>
-      <c r="F63" s="4" t="inlineStr">
+      <c r="F64" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">担当者操作履歴</t>
         </is>
       </c>
-      <c r="G63" s="4" t="inlineStr">
+      <c r="G64" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">FK・RESTRICT</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">将来リレーション案</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="3" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">親DB日本語名</t>
         </is>
       </c>
-      <c r="B66" s="3" t="inlineStr">
+      <c r="B67" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">親KEY</t>
         </is>
       </c>
-      <c r="C66" s="3" t="inlineStr">
+      <c r="C67" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">親多重度</t>
         </is>
       </c>
-      <c r="D66" s="3" t="inlineStr">
+      <c r="D67" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">子多重度</t>
         </is>
       </c>
-      <c r="E66" s="3" t="inlineStr">
+      <c r="E67" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">子FK</t>
         </is>
       </c>
-      <c r="F66" s="3" t="inlineStr">
+      <c r="F67" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">子DB日本語名</t>
         </is>
       </c>
-      <c r="G66" s="3" t="inlineStr">
+      <c r="G67" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">削除・備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">患者注文</t>
-        </is>
-      </c>
-      <c r="B67" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">patient_orders.id</t>
-        </is>
-      </c>
-      <c r="C67" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="D67" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="E67" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">order_transaction_projections.order_id</t>
-        </is>
-      </c>
-      <c r="F67" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">決済返金投影</t>
-        </is>
-      </c>
-      <c r="G67" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FK</t>
         </is>
       </c>
     </row>
@@ -21261,12 +21635,12 @@
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_fulfillments.order_id</t>
+          <t xml:space="preserve">order_transaction_projections.order_id</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">受取配送</t>
+          <t xml:space="preserve">決済返金投影</t>
         </is>
       </c>
       <c r="G68" s="4" t="inlineStr">
@@ -21278,32 +21652,32 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">患者注文</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_orders.id</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_fulfillments.order_id</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">受取配送</t>
-        </is>
-      </c>
-      <c r="B69" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">patient_fulfillments.id</t>
-        </is>
-      </c>
-      <c r="C69" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="D69" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="E69" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">patient_fulfillment_items.fulfillment_id</t>
-        </is>
-      </c>
-      <c r="F69" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">受取配送明細</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr">
@@ -21315,12 +21689,12 @@
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文明細</t>
+          <t xml:space="preserve">受取配送</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_order_items.id</t>
+          <t xml:space="preserve">patient_fulfillments.id</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -21335,7 +21709,7 @@
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_fulfillment_items.order_item_id</t>
+          <t xml:space="preserve">patient_fulfillment_items.fulfillment_id</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
@@ -21352,12 +21726,12 @@
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部コマース接続</t>
+          <t xml:space="preserve">注文明細</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_accounts.id</t>
+          <t xml:space="preserve">patient_order_items.id</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
@@ -21372,12 +21746,12 @@
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders.commerce_account_id</t>
+          <t xml:space="preserve">patient_fulfillment_items.order_item_id</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文</t>
+          <t xml:space="preserve">受取配送明細</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr">
@@ -21409,12 +21783,12 @@
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_webhook_events.commerce_account_id</t>
+          <t xml:space="preserve">patient_orders.commerce_account_id</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部受信イベント</t>
+          <t xml:space="preserve">患者注文</t>
         </is>
       </c>
       <c r="G72" s="4" t="inlineStr">
@@ -21446,12 +21820,12 @@
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_outbox.commerce_account_id</t>
+          <t xml:space="preserve">commerce_webhook_events.commerce_account_id</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部送信キュー</t>
+          <t xml:space="preserve">外部受信イベント</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr">
@@ -21463,12 +21837,12 @@
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者</t>
+          <t xml:space="preserve">外部コマース接続</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patients.id</t>
+          <t xml:space="preserve">commerce_accounts.id</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
@@ -21483,12 +21857,12 @@
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_subscriptions.patient_id</t>
+          <t xml:space="preserve">commerce_outbox.commerce_account_id</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者定期購入</t>
+          <t xml:space="preserve">外部送信キュー</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr">
@@ -21500,32 +21874,32 @@
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">患者</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patients.id</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscriptions.patient_id</t>
+        </is>
+      </c>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">患者定期購入</t>
-        </is>
-      </c>
-      <c r="B75" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">patient_subscriptions.id</t>
-        </is>
-      </c>
-      <c r="C75" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="D75" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="E75" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">patient_subscription_items.subscription_id</t>
-        </is>
-      </c>
-      <c r="F75" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">定期購入明細</t>
         </is>
       </c>
       <c r="G75" s="4" t="inlineStr">
@@ -21547,25 +21921,62 @@
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscription_items.subscription_id</t>
+        </is>
+      </c>
+      <c r="F76" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">定期購入明細</t>
+        </is>
+      </c>
+      <c r="G76" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">患者定期購入</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscriptions.id</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">0..1</t>
         </is>
       </c>
-      <c r="D76" s="4" t="inlineStr">
+      <c r="D77" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="E76" s="4" t="inlineStr">
+      <c r="E77" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">patient_orders.subscription_id</t>
         </is>
       </c>
-      <c r="F76" s="4" t="inlineStr">
+      <c r="F77" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">患者注文</t>
         </is>
       </c>
-      <c r="G76" s="4" t="inlineStr">
+      <c r="G77" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">FK</t>
         </is>
@@ -21576,7 +21987,7 @@
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A32:H32"/>
-    <mergeCell ref="A65:H65"/>
+    <mergeCell ref="A66:H66"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0" paperSize="9"/>
@@ -21585,7 +21996,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Q103"/>
+  <dimension ref="A1:Q104"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -23568,12 +23979,12 @@
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院ログイン</t>
+          <t xml:space="preserve">医院担当者役職</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_users.id</t>
+          <t xml:space="preserve">clinic_contact_roles.role_key</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
@@ -23583,12 +23994,12 @@
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">0..1</t>
+          <t xml:space="preserve">N</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_contacts.clinic_user_id</t>
+          <t xml:space="preserve">clinic_contacts.role_key</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
@@ -23598,19 +24009,19 @@
       </c>
       <c r="G97" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK・SET NULL</t>
+          <t xml:space="preserve">FK・RESTRICT</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院</t>
+          <t xml:space="preserve">医院認証アカウント</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinics.customer_code</t>
+          <t xml:space="preserve">clinic_users.(id, customer_code)</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
@@ -23620,34 +24031,34 @@
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">N</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_users.customer_code</t>
+          <t xml:space="preserve">clinic_contacts.(clinic_user_id, customer_code)</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院ポータルログイン</t>
+          <t xml:space="preserve">医院業務連絡担当者</t>
         </is>
       </c>
       <c r="G98" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK・CASCADE</t>
+          <t xml:space="preserve">UK・複合FK・RESTRICT</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院ポータル権限</t>
+          <t xml:space="preserve">医院</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_portal_roles.role_key</t>
+          <t xml:space="preserve">clinics.customer_code</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
@@ -23662,29 +24073,29 @@
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_portal_role_permissions.role_key</t>
+          <t xml:space="preserve">clinic_users.customer_code</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">権限機能</t>
+          <t xml:space="preserve">医院ポータルログイン</t>
         </is>
       </c>
       <c r="G99" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">PK・FK・RESTRICT</t>
+          <t xml:space="preserve">FK・CASCADE</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院ポータルログイン</t>
+          <t xml:space="preserve">医院ポータル権限</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_users.id</t>
+          <t xml:space="preserve">clinic_portal_roles.role_key</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
@@ -23694,34 +24105,34 @@
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">0..1</t>
+          <t xml:space="preserve">N</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_user_role_assignments.clinic_user_id</t>
+          <t xml:space="preserve">clinic_portal_role_permissions.role_key</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">権限割当</t>
+          <t xml:space="preserve">権限機能</t>
         </is>
       </c>
       <c r="G100" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">PK・FK・CASCADE</t>
+          <t xml:space="preserve">PK・FK・RESTRICT</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院ポータル権限</t>
+          <t xml:space="preserve">医院ポータルログイン</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_portal_roles.role_key</t>
+          <t xml:space="preserve">clinic_users.id</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
@@ -23731,12 +24142,12 @@
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">N</t>
+          <t xml:space="preserve">0..1</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_user_role_assignments.role_key</t>
+          <t xml:space="preserve">clinic_user_role_assignments.clinic_user_id</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
@@ -23746,19 +24157,19 @@
       </c>
       <c r="G101" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK・RESTRICT</t>
+          <t xml:space="preserve">PK・FK・CASCADE</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院業務連絡担当者</t>
+          <t xml:space="preserve">医院ポータル権限</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_contacts.id</t>
+          <t xml:space="preserve">clinic_portal_roles.role_key</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
@@ -23773,17 +24184,17 @@
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_contact_notification_preferences.contact_id</t>
+          <t xml:space="preserve">clinic_user_role_assignments.role_key</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">担当者通知設定</t>
+          <t xml:space="preserve">権限割当</t>
         </is>
       </c>
       <c r="G102" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">PK・FK・RESTRICT</t>
+          <t xml:space="preserve">FK・RESTRICT</t>
         </is>
       </c>
     </row>
@@ -23810,15 +24221,52 @@
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">clinic_contact_notification_preferences.contact_id</t>
+        </is>
+      </c>
+      <c r="F103" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">担当者通知設定</t>
+        </is>
+      </c>
+      <c r="G103" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK・FK・RESTRICT</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">医院業務連絡担当者</t>
+        </is>
+      </c>
+      <c r="B104" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_contacts.id</t>
+        </is>
+      </c>
+      <c r="C104" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D104" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E104" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">clinic_contact_events.contact_id</t>
         </is>
       </c>
-      <c r="F103" s="4" t="inlineStr">
+      <c r="F104" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">担当者操作履歴</t>
         </is>
       </c>
-      <c r="G103" s="4" t="inlineStr">
+      <c r="G104" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">FK・RESTRICT</t>
         </is>

--- a/project_clinic_order_management_db_definition.xlsx
+++ b/project_clinic_order_management_db_definition.xlsx
@@ -19486,7 +19486,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G77"/>
+  <dimension ref="A1:G75"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -20065,7 +20065,7 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">UK11</t>
+          <t xml:space="preserve">UK12</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -20075,17 +20075,17 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">customer_code, lower(email) WHERE deleted_at IS NULL</t>
+          <t xml:space="preserve">clinic_user_id</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">PARTIAL UNIQUE</t>
+          <t xml:space="preserve">UNIQUE</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院内の担当者メール重複防止。</t>
+          <t xml:space="preserve">1担当者と1認証アカウントを必須の一対一にする。</t>
         </is>
       </c>
     </row>
@@ -20097,17 +20097,17 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">UK12</t>
+          <t xml:space="preserve">UK13</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_contacts</t>
+          <t xml:space="preserve">clinic_users</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_user_id</t>
+          <t xml:space="preserve">login_id</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
@@ -20117,29 +20117,29 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1担当者と1認証アカウントを必須の一対一にする。</t>
+          <t xml:space="preserve">担当者ID兼ログインIDの重複防止。</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">現行</t>
+          <t xml:space="preserve">将来案</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">UK13</t>
+          <t xml:space="preserve">UK1</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_users</t>
+          <t xml:space="preserve">commerce_accounts</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">login_id</t>
+          <t xml:space="preserve">provider, external_account_id</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
@@ -20149,39 +20149,39 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">担当者ID兼ログインIDの重複防止。</t>
+          <t xml:space="preserve">外部接続先の重複防止。</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">現行</t>
+          <t xml:space="preserve">将来案</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">UK14</t>
+          <t xml:space="preserve">UK2</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_users</t>
+          <t xml:space="preserve">patient_fulfillment_items</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">email WHERE email IS NOT NULL</t>
+          <t xml:space="preserve">fulfillment_id, order_item_id</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">PARTIAL UNIQUE</t>
+          <t xml:space="preserve">UNIQUE</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">パスワード再設定先の重複防止。</t>
+          <t xml:space="preserve">同一配送への明細重複防止。</t>
         </is>
       </c>
     </row>
@@ -20193,17 +20193,17 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">UK1</t>
+          <t xml:space="preserve">UK3</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_accounts</t>
+          <t xml:space="preserve">patient_subscriptions</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">provider, external_account_id</t>
+          <t xml:space="preserve">commerce_account_id, external_subscription_id</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
@@ -20213,7 +20213,7 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部接続先の重複防止。</t>
+          <t xml:space="preserve">外部契約の重複防止。</t>
         </is>
       </c>
     </row>
@@ -20225,17 +20225,17 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">UK2</t>
+          <t xml:space="preserve">UK4</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_fulfillment_items</t>
+          <t xml:space="preserve">commerce_webhook_events</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">fulfillment_id, order_item_id</t>
+          <t xml:space="preserve">commerce_account_id, external_event_id</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
@@ -20245,7 +20245,7 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">同一配送への明細重複防止。</t>
+          <t xml:space="preserve">Webhook重複配信の無害化。</t>
         </is>
       </c>
     </row>
@@ -20257,17 +20257,17 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">UK3</t>
+          <t xml:space="preserve">UK5</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_subscriptions</t>
+          <t xml:space="preserve">patient_orders</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_account_id, external_subscription_id</t>
+          <t xml:space="preserve">commerce_account_id, external_order_id</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -20277,7 +20277,7 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部契約の重複防止。</t>
+          <t xml:space="preserve">複数ストアを考慮した外部注文の一意性。</t>
         </is>
       </c>
     </row>
@@ -20289,17 +20289,17 @@
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">UK4</t>
+          <t xml:space="preserve">UK6</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_webhook_events</t>
+          <t xml:space="preserve">commerce_outbox</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_account_id, external_event_id</t>
+          <t xml:space="preserve">idempotency_key</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
@@ -20309,127 +20309,137 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Webhook重複配信の無害化。</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">将来案</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UK5</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">patient_orders</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">commerce_account_id, external_order_id</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UNIQUE</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">複数ストアを考慮した外部注文の一意性。</t>
+          <t xml:space="preserve">外部送信コマンドの二重実行防止。</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">将来案</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UK6</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">commerce_outbox</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">idempotency_key</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UNIQUE</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">外部送信コマンドの二重実行防止。</t>
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行リレーション</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">親DB日本語名</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">親KEY</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">親多重度</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">子多重度</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">子FK</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">子DB日本語名</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">削除・備考</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">現行リレーション</t>
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">医院</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinics.customer_code</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0..1</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_terms.customer_code</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">医院契約情報</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK・FK・CASCADE</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">親DB日本語名</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">親KEY</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">親多重度</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">子多重度</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">子FK</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">子DB日本語名</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">削除・備考</t>
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">医院</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinics.customer_code</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_product_settings.customer_code</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">医院商品設定</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK・FK・CASCADE</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院</t>
+          <t xml:space="preserve">商品</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinics.customer_code</t>
+          <t xml:space="preserve">products.id</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -20439,17 +20449,17 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">0..1</t>
+          <t xml:space="preserve">N</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_terms.customer_code</t>
+          <t xml:space="preserve">clinic_product_settings.product_id</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院契約情報</t>
+          <t xml:space="preserve">医院商品設定</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
@@ -20481,29 +20491,29 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_product_settings.customer_code</t>
+          <t xml:space="preserve">patient_orders.customer_code</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院商品設定</t>
+          <t xml:space="preserve">患者注文</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">PK・FK・CASCADE</t>
+          <t xml:space="preserve">FK</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">商品</t>
+          <t xml:space="preserve">患者</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">products.id</t>
+          <t xml:space="preserve">patients.id</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -20518,29 +20528,29 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_product_settings.product_id</t>
+          <t xml:space="preserve">patient_orders.patient_id</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院商品設定</t>
+          <t xml:space="preserve">患者注文</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">PK・FK・CASCADE</t>
+          <t xml:space="preserve">FK・現状CASCADE</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院</t>
+          <t xml:space="preserve">患者注文</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinics.customer_code</t>
+          <t xml:space="preserve">patient_orders.id</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -20555,29 +20565,29 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders.customer_code</t>
+          <t xml:space="preserve">patient_order_items.order_id</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文</t>
+          <t xml:space="preserve">患者注文明細</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK</t>
+          <t xml:space="preserve">FK・CASCADE</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者</t>
+          <t xml:space="preserve">医院</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patients.id</t>
+          <t xml:space="preserve">clinics.customer_code</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -20592,29 +20602,29 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders.patient_id</t>
+          <t xml:space="preserve">delivery_destinations.clinic_customer_code</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文</t>
+          <t xml:space="preserve">送り先マスタ</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK・現状CASCADE</t>
+          <t xml:space="preserve">FK・RESTRICT</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文</t>
+          <t xml:space="preserve">患者</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders.id</t>
+          <t xml:space="preserve">patients.id</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -20629,29 +20639,29 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_order_items.order_id</t>
+          <t xml:space="preserve">delivery_destinations.patient_id</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文明細</t>
+          <t xml:space="preserve">送り先マスタ</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK・CASCADE</t>
+          <t xml:space="preserve">FK・RESTRICT</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院</t>
+          <t xml:space="preserve">送り先マスタ</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinics.customer_code</t>
+          <t xml:space="preserve">delivery_destinations.id</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -20666,12 +20676,12 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery_destinations.clinic_customer_code</t>
+          <t xml:space="preserve">order_delivery_destinations.delivery_destination_id</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">送り先マスタ</t>
+          <t xml:space="preserve">注文配送先</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
@@ -20683,12 +20693,12 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者</t>
+          <t xml:space="preserve">患者注文</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patients.id</t>
+          <t xml:space="preserve">patient_orders.id</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -20698,34 +20708,34 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">N</t>
+          <t xml:space="preserve">0..1</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery_destinations.patient_id</t>
+          <t xml:space="preserve">order_delivery_destinations.order_id</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">送り先マスタ</t>
+          <t xml:space="preserve">注文配送先</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK・RESTRICT</t>
+          <t xml:space="preserve">PK・FK・CASCADE</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">送り先マスタ</t>
+          <t xml:space="preserve">患者注文</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery_destinations.id</t>
+          <t xml:space="preserve">patient_orders.id</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -20740,66 +20750,66 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">order_delivery_destinations.delivery_destination_id</t>
+          <t xml:space="preserve">patient_order_events.order_id</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文配送先</t>
+          <t xml:space="preserve">注文操作履歴</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK・RESTRICT</t>
+          <t xml:space="preserve">FK・CASCADE</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文</t>
+          <t xml:space="preserve">商品</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders.id</t>
+          <t xml:space="preserve">products.id</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">0..1</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">0..1</t>
+          <t xml:space="preserve">N</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">order_delivery_destinations.order_id</t>
+          <t xml:space="preserve">patient_order_items.product_id</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文配送先</t>
+          <t xml:space="preserve">患者注文明細</t>
         </is>
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">PK・FK・CASCADE</t>
+          <t xml:space="preserve">FK・SET NULL</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文</t>
+          <t xml:space="preserve">医院</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders.id</t>
+          <t xml:space="preserve">clinics.customer_code</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -20814,34 +20824,34 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_order_events.order_id</t>
+          <t xml:space="preserve">patient_subscription_requests.customer_code</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文操作履歴</t>
+          <t xml:space="preserve">定期購入申込</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK・CASCADE</t>
+          <t xml:space="preserve">FK・RESTRICT</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">商品</t>
+          <t xml:space="preserve">患者</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">products.id</t>
+          <t xml:space="preserve">patients.id</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">0..1</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -20851,29 +20861,29 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_order_items.product_id</t>
+          <t xml:space="preserve">patient_subscription_requests.patient_id</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文明細</t>
+          <t xml:space="preserve">定期購入申込</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK・SET NULL</t>
+          <t xml:space="preserve">FK・RESTRICT</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院</t>
+          <t xml:space="preserve">定期購入申込</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinics.customer_code</t>
+          <t xml:space="preserve">patient_subscription_requests.id</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -20888,29 +20898,29 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_subscription_requests.customer_code</t>
+          <t xml:space="preserve">patient_subscription_request_items.request_id</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">定期購入申込</t>
+          <t xml:space="preserve">定期購入申込明細</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK・RESTRICT</t>
+          <t xml:space="preserve">FK・CASCADE</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者</t>
+          <t xml:space="preserve">定期購入申込</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patients.id</t>
+          <t xml:space="preserve">patient_subscription_requests.id</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -20920,22 +20930,22 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">N</t>
+          <t xml:space="preserve">0..1</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_subscription_requests.patient_id</t>
+          <t xml:space="preserve">patient_subscription_request_destinations.request_id</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">定期購入申込</t>
+          <t xml:space="preserve">定期購入申込配送先</t>
         </is>
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK・RESTRICT</t>
+          <t xml:space="preserve">PK・FK・CASCADE</t>
         </is>
       </c>
     </row>
@@ -20962,12 +20972,12 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_subscription_request_items.request_id</t>
+          <t xml:space="preserve">patient_subscription_request_events.request_id</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">定期購入申込明細</t>
+          <t xml:space="preserve">定期購入申込履歴</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
@@ -20979,12 +20989,12 @@
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">定期購入申込</t>
+          <t xml:space="preserve">送り先マスタ</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_subscription_requests.id</t>
+          <t xml:space="preserve">delivery_destinations.id</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -20994,12 +21004,12 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">0..1</t>
+          <t xml:space="preserve">N</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_subscription_request_destinations.request_id</t>
+          <t xml:space="preserve">patient_subscription_request_destinations.delivery_destination_id</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
@@ -21009,19 +21019,19 @@
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">PK・FK・CASCADE</t>
+          <t xml:space="preserve">FK・RESTRICT</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">定期購入申込</t>
+          <t xml:space="preserve">ウェビナー</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_subscription_requests.id</t>
+          <t xml:space="preserve">webinars.id</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -21036,12 +21046,12 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_subscription_request_events.request_id</t>
+          <t xml:space="preserve">webinar_sessions.webinar_id</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">定期購入申込履歴</t>
+          <t xml:space="preserve">ウェビナー開催枠</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
@@ -21053,12 +21063,12 @@
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">送り先マスタ</t>
+          <t xml:space="preserve">ウェビナー</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery_destinations.id</t>
+          <t xml:space="preserve">webinars.id</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -21073,29 +21083,29 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_subscription_request_destinations.delivery_destination_id</t>
+          <t xml:space="preserve">webinar_target_clinics.webinar_id</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">定期購入申込配送先</t>
+          <t xml:space="preserve">ウェビナー対象医院</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK・RESTRICT</t>
+          <t xml:space="preserve">PK・FK・CASCADE</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ウェビナー</t>
+          <t xml:space="preserve">医院</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">webinars.id</t>
+          <t xml:space="preserve">clinics.customer_code</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -21110,17 +21120,17 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">webinar_sessions.webinar_id</t>
+          <t xml:space="preserve">webinar_target_clinics.customer_code</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ウェビナー開催枠</t>
+          <t xml:space="preserve">ウェビナー対象医院</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK・CASCADE</t>
+          <t xml:space="preserve">PK・FK・RESTRICT</t>
         </is>
       </c>
     </row>
@@ -21147,17 +21157,17 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">webinar_target_clinics.webinar_id</t>
+          <t xml:space="preserve">webinar_events.webinar_id</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ウェビナー対象医院</t>
+          <t xml:space="preserve">ウェビナー操作履歴</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">PK・FK・CASCADE</t>
+          <t xml:space="preserve">FK・CASCADE</t>
         </is>
       </c>
     </row>
@@ -21184,29 +21194,29 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">webinar_target_clinics.customer_code</t>
+          <t xml:space="preserve">clinic_contacts.customer_code</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ウェビナー対象医院</t>
+          <t xml:space="preserve">医院業務連絡担当者</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">PK・FK・RESTRICT</t>
+          <t xml:space="preserve">FK・RESTRICT</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ウェビナー</t>
+          <t xml:space="preserve">医院担当者役職</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">webinars.id</t>
+          <t xml:space="preserve">clinic_contact_roles.role_key</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -21221,29 +21231,29 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">webinar_events.webinar_id</t>
+          <t xml:space="preserve">clinic_contacts.role_key</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ウェビナー操作履歴</t>
+          <t xml:space="preserve">医院業務連絡担当者</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK・CASCADE</t>
+          <t xml:space="preserve">FK・RESTRICT</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院</t>
+          <t xml:space="preserve">医院認証アカウント</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinics.customer_code</t>
+          <t xml:space="preserve">clinic_users.(id, customer_code)</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -21253,12 +21263,12 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">N</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_contacts.customer_code</t>
+          <t xml:space="preserve">clinic_contacts.(clinic_user_id, customer_code)</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
@@ -21268,19 +21278,19 @@
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK・RESTRICT</t>
+          <t xml:space="preserve">UK・複合FK・RESTRICT</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院担当者役職</t>
+          <t xml:space="preserve">医院</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_contact_roles.role_key</t>
+          <t xml:space="preserve">clinics.customer_code</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -21295,29 +21305,29 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_contacts.role_key</t>
+          <t xml:space="preserve">clinic_users.customer_code</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院業務連絡担当者</t>
+          <t xml:space="preserve">医院ポータルログイン</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK・RESTRICT</t>
+          <t xml:space="preserve">FK・CASCADE</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院認証アカウント</t>
+          <t xml:space="preserve">医院ポータル権限</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_users.(id, customer_code)</t>
+          <t xml:space="preserve">clinic_portal_roles.role_key</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -21327,34 +21337,34 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">N</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_contacts.(clinic_user_id, customer_code)</t>
+          <t xml:space="preserve">clinic_portal_role_permissions.role_key</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院業務連絡担当者</t>
+          <t xml:space="preserve">権限機能</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">UK・複合FK・RESTRICT</t>
+          <t xml:space="preserve">PK・FK・RESTRICT</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院</t>
+          <t xml:space="preserve">医院ポータルログイン</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinics.customer_code</t>
+          <t xml:space="preserve">clinic_users.id</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -21364,22 +21374,22 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">N</t>
+          <t xml:space="preserve">0..1</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_users.customer_code</t>
+          <t xml:space="preserve">clinic_user_role_assignments.clinic_user_id</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院ポータルログイン</t>
+          <t xml:space="preserve">権限割当</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK・CASCADE</t>
+          <t xml:space="preserve">PK・FK・CASCADE</t>
         </is>
       </c>
     </row>
@@ -21406,29 +21416,29 @@
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_portal_role_permissions.role_key</t>
+          <t xml:space="preserve">clinic_user_role_assignments.role_key</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">権限機能</t>
+          <t xml:space="preserve">権限割当</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">PK・FK・RESTRICT</t>
+          <t xml:space="preserve">FK・RESTRICT</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院ポータルログイン</t>
+          <t xml:space="preserve">医院業務連絡担当者</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_users.id</t>
+          <t xml:space="preserve">clinic_contacts.id</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -21438,34 +21448,34 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">0..1</t>
+          <t xml:space="preserve">N</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_user_role_assignments.clinic_user_id</t>
+          <t xml:space="preserve">clinic_contact_notification_preferences.contact_id</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">権限割当</t>
+          <t xml:space="preserve">担当者通知設定</t>
         </is>
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">PK・FK・CASCADE</t>
+          <t xml:space="preserve">PK・FK・RESTRICT</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院ポータル権限</t>
+          <t xml:space="preserve">医院業務連絡担当者</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_portal_roles.role_key</t>
+          <t xml:space="preserve">clinic_contacts.id</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -21480,12 +21490,12 @@
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_user_role_assignments.role_key</t>
+          <t xml:space="preserve">clinic_contact_events.contact_id</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">権限割当</t>
+          <t xml:space="preserve">担当者操作履歴</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr">
@@ -21494,133 +21504,133 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">医院業務連絡担当者</t>
-        </is>
-      </c>
-      <c r="B63" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">clinic_contacts.id</t>
-        </is>
-      </c>
-      <c r="C63" s="4" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">将来リレーション案</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">親DB日本語名</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">親KEY</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">親多重度</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">子多重度</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">子FK</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">子DB日本語名</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">削除・備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">患者注文</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_orders.id</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="D63" s="4" t="inlineStr">
+      <c r="D66" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="E63" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">clinic_contact_notification_preferences.contact_id</t>
-        </is>
-      </c>
-      <c r="F63" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">担当者通知設定</t>
-        </is>
-      </c>
-      <c r="G63" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PK・FK・RESTRICT</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">医院業務連絡担当者</t>
-        </is>
-      </c>
-      <c r="B64" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">clinic_contacts.id</t>
-        </is>
-      </c>
-      <c r="C64" s="4" t="inlineStr">
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">order_transaction_projections.order_id</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">決済返金投影</t>
+        </is>
+      </c>
+      <c r="G66" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">患者注文</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_orders.id</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="D64" s="4" t="inlineStr">
+      <c r="D67" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="E64" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">clinic_contact_events.contact_id</t>
-        </is>
-      </c>
-      <c r="F64" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">担当者操作履歴</t>
-        </is>
-      </c>
-      <c r="G64" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FK・RESTRICT</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">将来リレーション案</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">親DB日本語名</t>
-        </is>
-      </c>
-      <c r="B67" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">親KEY</t>
-        </is>
-      </c>
-      <c r="C67" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">親多重度</t>
-        </is>
-      </c>
-      <c r="D67" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">子多重度</t>
-        </is>
-      </c>
-      <c r="E67" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">子FK</t>
-        </is>
-      </c>
-      <c r="F67" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">子DB日本語名</t>
-        </is>
-      </c>
-      <c r="G67" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">削除・備考</t>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_fulfillments.order_id</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">受取配送</t>
+        </is>
+      </c>
+      <c r="G67" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文</t>
+          <t xml:space="preserve">受取配送</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders.id</t>
+          <t xml:space="preserve">patient_fulfillments.id</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -21635,12 +21645,12 @@
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">order_transaction_projections.order_id</t>
+          <t xml:space="preserve">patient_fulfillment_items.fulfillment_id</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">決済返金投影</t>
+          <t xml:space="preserve">受取配送明細</t>
         </is>
       </c>
       <c r="G68" s="4" t="inlineStr">
@@ -21652,12 +21662,12 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文</t>
+          <t xml:space="preserve">注文明細</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders.id</t>
+          <t xml:space="preserve">patient_order_items.id</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -21672,12 +21682,12 @@
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_fulfillments.order_id</t>
+          <t xml:space="preserve">patient_fulfillment_items.order_item_id</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">受取配送</t>
+          <t xml:space="preserve">受取配送明細</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr">
@@ -21689,12 +21699,12 @@
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">受取配送</t>
+          <t xml:space="preserve">外部コマース接続</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_fulfillments.id</t>
+          <t xml:space="preserve">commerce_accounts.id</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -21709,12 +21719,12 @@
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_fulfillment_items.fulfillment_id</t>
+          <t xml:space="preserve">patient_orders.commerce_account_id</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">受取配送明細</t>
+          <t xml:space="preserve">患者注文</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr">
@@ -21726,12 +21736,12 @@
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文明細</t>
+          <t xml:space="preserve">外部コマース接続</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_order_items.id</t>
+          <t xml:space="preserve">commerce_accounts.id</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
@@ -21746,12 +21756,12 @@
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_fulfillment_items.order_item_id</t>
+          <t xml:space="preserve">commerce_webhook_events.commerce_account_id</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">受取配送明細</t>
+          <t xml:space="preserve">外部受信イベント</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr">
@@ -21783,12 +21793,12 @@
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders.commerce_account_id</t>
+          <t xml:space="preserve">commerce_outbox.commerce_account_id</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文</t>
+          <t xml:space="preserve">外部送信キュー</t>
         </is>
       </c>
       <c r="G72" s="4" t="inlineStr">
@@ -21800,12 +21810,12 @@
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部コマース接続</t>
+          <t xml:space="preserve">患者</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_accounts.id</t>
+          <t xml:space="preserve">patients.id</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
@@ -21820,12 +21830,12 @@
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_webhook_events.commerce_account_id</t>
+          <t xml:space="preserve">patient_subscriptions.patient_id</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部受信イベント</t>
+          <t xml:space="preserve">患者定期購入</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr">
@@ -21837,12 +21847,12 @@
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部コマース接続</t>
+          <t xml:space="preserve">患者定期購入</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_accounts.id</t>
+          <t xml:space="preserve">patient_subscriptions.id</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
@@ -21857,12 +21867,12 @@
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_outbox.commerce_account_id</t>
+          <t xml:space="preserve">patient_subscription_items.subscription_id</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部送信キュー</t>
+          <t xml:space="preserve">定期購入明細</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr">
@@ -21874,17 +21884,17 @@
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者</t>
+          <t xml:space="preserve">患者定期購入</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patients.id</t>
+          <t xml:space="preserve">patient_subscriptions.id</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">0..1</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -21894,89 +21904,15 @@
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_subscriptions.patient_id</t>
+          <t xml:space="preserve">patient_orders.subscription_id</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者定期購入</t>
+          <t xml:space="preserve">患者注文</t>
         </is>
       </c>
       <c r="G75" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FK</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">患者定期購入</t>
-        </is>
-      </c>
-      <c r="B76" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">patient_subscriptions.id</t>
-        </is>
-      </c>
-      <c r="C76" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="D76" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="E76" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">patient_subscription_items.subscription_id</t>
-        </is>
-      </c>
-      <c r="F76" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">定期購入明細</t>
-        </is>
-      </c>
-      <c r="G76" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FK</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">患者定期購入</t>
-        </is>
-      </c>
-      <c r="B77" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">patient_subscriptions.id</t>
-        </is>
-      </c>
-      <c r="C77" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0..1</t>
-        </is>
-      </c>
-      <c r="D77" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="E77" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">patient_orders.subscription_id</t>
-        </is>
-      </c>
-      <c r="F77" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">患者注文</t>
-        </is>
-      </c>
-      <c r="G77" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">FK</t>
         </is>
@@ -21986,8 +21922,8 @@
   <mergeCells count="4">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A32:H32"/>
-    <mergeCell ref="A66:H66"/>
+    <mergeCell ref="A30:H30"/>
+    <mergeCell ref="A64:H64"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0" paperSize="9"/>

--- a/project_clinic_order_management_db_definition.xlsx
+++ b/project_clinic_order_management_db_definition.xlsx
@@ -476,7 +476,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -999,7 +999,7 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">実装済み・Phase 1</t>
+          <t xml:space="preserve">実装済み</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">実装済み・Phase 1</t>
+          <t xml:space="preserve">実装済み・Google Meet連携</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
@@ -1063,7 +1063,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">実装済み・Phase 1</t>
+          <t xml:space="preserve">実装済み</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
@@ -1085,22 +1085,22 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ウェビナー操作履歴</t>
+          <t xml:space="preserve">ウェビナー送付先担当者</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">webinar_events</t>
+          <t xml:space="preserve">webinar_target_contacts</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">実装済み・Phase 1</t>
+          <t xml:space="preserve">実装済み</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">作成・編集・公開・中止を監査保存する。</t>
+          <t xml:space="preserve">公開メールを送る担当者をウェビナーごとに個別保持する多対多中間表。</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -1117,12 +1117,12 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院担当者役職</t>
+          <t xml:space="preserve">ウェビナー操作履歴</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_contact_roles</t>
+          <t xml:space="preserve">webinar_events</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院担当者の役職を選択肢として一元管理する。</t>
+          <t xml:space="preserve">作成・編集・公開・中止を監査保存する。</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院業務連絡担当者</t>
+          <t xml:space="preserve">医院担当者役職</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_contacts</t>
+          <t xml:space="preserve">clinic_contact_roles</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院ごとに複数の業務連絡担当者と主担当、論理削除、排他制御を管理する。</t>
+          <t xml:space="preserve">医院担当者の役職を選択肢として一元管理する。</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
@@ -1181,22 +1181,22 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院ポータルログイン</t>
+          <t xml:space="preserve">医院業務連絡担当者</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_users</t>
+          <t xml:space="preserve">clinic_contacts</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">実装済み・Phase 1</t>
+          <t xml:space="preserve">実装済み</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">担当者ID・認証情報・所属得意先・セッション世代を保持する。全担当者が1対1でclinic_contactsを持つ。</t>
+          <t xml:space="preserve">医院ごとに複数の業務連絡担当者と主担当、論理削除、排他制御を管理する。</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
@@ -1213,12 +1213,12 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院ポータル権限</t>
+          <t xml:space="preserve">医院ポータルログイン</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_portal_roles</t>
+          <t xml:space="preserve">clinic_users</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">管理者・一般・閲覧専用の権限マスタ。</t>
+          <t xml:space="preserve">担当者ID・認証情報・所属得意先・セッション世代を保持する。全担当者が1対1でclinic_contactsを持つ。</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -1245,12 +1245,12 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院ポータル権限機能</t>
+          <t xml:space="preserve">医院ポータル権限</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_portal_role_permissions</t>
+          <t xml:space="preserve">clinic_portal_roles</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">権限と操作可能な機能を多対多で管理する。</t>
+          <t xml:space="preserve">管理者・一般・閲覧専用の権限マスタ。</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -1277,12 +1277,12 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院ログイン権限割当</t>
+          <t xml:space="preserve">医院ポータル権限機能</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_user_role_assignments</t>
+          <t xml:space="preserve">clinic_portal_role_permissions</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1ログインに1権限を割り当て、認証情報と権限マスタを分離する。</t>
+          <t xml:space="preserve">権限と操作可能な機能を多対多で管理する。</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
@@ -1309,22 +1309,22 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">担当者通知設定</t>
+          <t xml:space="preserve">医院ログイン権限割当</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_contact_notification_preferences</t>
+          <t xml:space="preserve">clinic_user_role_assignments</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">実装済み</t>
+          <t xml:space="preserve">実装済み・Phase 1</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">担当者ごとの連絡内容と方法を多値属性として分離する。</t>
+          <t xml:space="preserve">1ログインに1権限を割り当て、認証情報と権限マスタを分離する。</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
@@ -1341,12 +1341,12 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">担当者操作履歴</t>
+          <t xml:space="preserve">担当者通知設定</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_contact_events</t>
+          <t xml:space="preserve">clinic_contact_notification_preferences</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">登録・更新・無効化・主担当変更・論理削除を監査保存する。</t>
+          <t xml:space="preserve">担当者ごとの連絡内容と方法を多値属性として分離する。</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
@@ -1368,27 +1368,27 @@
     <row r="31" ht="34" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shopify接続</t>
+          <t xml:space="preserve">現行</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部コマース接続</t>
+          <t xml:space="preserve">担当者操作履歴</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_accounts</t>
+          <t xml:space="preserve">clinic_contact_events</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">将来案</t>
+          <t xml:space="preserve">実装済み</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shopifyストア等の外部接続先。医院との対応方式は接続構成確定後に決定する。</t>
+          <t xml:space="preserve">登録・更新・無効化・主担当変更・論理削除を監査保存する。</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -1405,22 +1405,22 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文拡張</t>
+          <t xml:space="preserve">外部コマース接続</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders</t>
+          <t xml:space="preserve">commerce_accounts</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">既存テーブル拡張案</t>
+          <t xml:space="preserve">将来案</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">既存IDを維持し、外部・金額・排他制御の列を追加する。</t>
+          <t xml:space="preserve">Shopifyストア等の外部接続先。医院との対応方式は接続構成確定後に決定する。</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文明細拡張</t>
+          <t xml:space="preserve">患者注文拡張</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_order_items</t>
+          <t xml:space="preserve">patient_orders</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部明細と通貨を明確化し、既存スナップショットを維持する。</t>
+          <t xml:space="preserve">既存IDを維持し、外部・金額・排他制御の列を追加する。</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -1464,27 +1464,27 @@
     <row r="34" ht="34" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">決済接続</t>
+          <t xml:space="preserve">Shopify接続</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">決済返金投影</t>
+          <t xml:space="preserve">患者注文明細拡張</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">order_transaction_projections</t>
+          <t xml:space="preserve">patient_order_items</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">将来案</t>
+          <t xml:space="preserve">既存テーブル拡張案</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shopify上の決済・返金を表示する投影。会計台帳ではない。</t>
+          <t xml:space="preserve">外部明細と通貨を明確化し、既存スナップショットを維持する。</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -1496,17 +1496,17 @@
     <row r="35" ht="34" customHeight="1">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">配送開始</t>
+          <t xml:space="preserve">決済接続</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">受取配送</t>
+          <t xml:space="preserve">決済返金投影</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_fulfillments</t>
+          <t xml:space="preserve">order_transaction_projections</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -1516,7 +1516,7 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院受け取り・配送・部分引き渡しの単位。</t>
+          <t xml:space="preserve">Shopify上の決済・返金を表示する投影。会計台帳ではない。</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
@@ -1533,12 +1533,12 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">受取配送明細</t>
+          <t xml:space="preserve">受取配送</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_fulfillment_items</t>
+          <t xml:space="preserve">patient_fulfillments</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">部分受け取り・部分配送時の対象明細と数量。</t>
+          <t xml:space="preserve">医院受け取り・配送・部分引き渡しの単位。</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
@@ -1560,17 +1560,17 @@
     <row r="37" ht="34" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">定期購入接続</t>
+          <t xml:space="preserve">配送開始</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者定期購入</t>
+          <t xml:space="preserve">受取配送明細</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_subscriptions</t>
+          <t xml:space="preserve">patient_fulfillment_items</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shopify上の定期購入契約を患者ポータルへ表示する投影。</t>
+          <t xml:space="preserve">部分受け取り・部分配送時の対象明細と数量。</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">定期購入明細</t>
+          <t xml:space="preserve">患者定期購入</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_subscription_items</t>
+          <t xml:space="preserve">patient_subscriptions</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">契約時点の商品・数量・単価の投影。</t>
+          <t xml:space="preserve">Shopify上の定期購入契約を患者ポータルへ表示する投影。</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
@@ -1624,17 +1624,17 @@
     <row r="39" ht="34" customHeight="1">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shopify接続</t>
+          <t xml:space="preserve">定期購入接続</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部受信イベント</t>
+          <t xml:space="preserve">定期購入明細</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_webhook_events</t>
+          <t xml:space="preserve">patient_subscription_items</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -1644,7 +1644,7 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Webhookを先に永続化し、重複排除・再試行するInbox。</t>
+          <t xml:space="preserve">契約時点の商品・数量・単価の投影。</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
@@ -1661,57 +1661,89 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">外部受信イベント</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">commerce_webhook_events</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">将来案</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Webhookを先に永続化し、重複排除・再試行するInbox。</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="34" customHeight="1">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shopify接続</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">外部送信キュー</t>
         </is>
       </c>
-      <c r="C40" s="4" t="inlineStr">
+      <c r="C41" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">commerce_outbox</t>
         </is>
       </c>
-      <c r="D40" s="4" t="inlineStr">
+      <c r="D41" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">将来案</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr">
+      <c r="E41" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">外部APIへ送る処理を永続化するOutbox。</t>
         </is>
       </c>
-      <c r="F40" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="8" t="inlineStr">
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">別ドメイン</t>
         </is>
       </c>
-      <c r="B41" s="8" t="inlineStr">
+      <c r="B42" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">医院仕入注文</t>
         </is>
       </c>
-      <c r="C41" s="8" t="inlineStr">
+      <c r="C42" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">clinic_orders</t>
         </is>
       </c>
-      <c r="D41" s="8" t="inlineStr">
+      <c r="D42" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">実装済み</t>
         </is>
       </c>
-      <c r="E41" s="8" t="inlineStr">
+      <c r="E42" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">BGJから医院へのB2B仕入・売上履歴</t>
         </is>
       </c>
-      <c r="F41" s="8" t="inlineStr">
+      <c r="F42" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">患者注文系列へ統合しない</t>
         </is>
@@ -1722,7 +1754,7 @@
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
   </mergeCells>
-  <autoFilter ref="A4:F41"/>
+  <autoFilter ref="A4:F42"/>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0" paperSize="9"/>
 </worksheet>
@@ -1730,7 +1762,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K231"/>
+  <dimension ref="A1:K234"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -10534,7 +10566,7 @@
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">API連携後に使用</t>
+          <t xml:space="preserve">Google Calendar予定ID</t>
         </is>
       </c>
     </row>
@@ -10831,22 +10863,22 @@
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ウェビナー操作履歴</t>
+          <t xml:space="preserve">ウェビナー送付先担当者</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">webinar_events</t>
+          <t xml:space="preserve">webinar_target_contacts</t>
         </is>
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">イベントID</t>
+          <t xml:space="preserve">ウェビナーID</t>
         </is>
       </c>
       <c r="E163" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">webinar_id</t>
         </is>
       </c>
       <c r="F163" s="4" t="inlineStr">
@@ -10856,7 +10888,7 @@
       </c>
       <c r="G163" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">PK</t>
+          <t xml:space="preserve">PK / FK</t>
         </is>
       </c>
       <c r="H163" s="4" t="inlineStr">
@@ -10866,12 +10898,12 @@
       </c>
       <c r="I163" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">gen_random_uuid()</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J163" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">webinars.id ON DELETE CASCADE</t>
         </is>
       </c>
       <c r="K163" s="4" t="inlineStr">
@@ -10888,22 +10920,22 @@
       </c>
       <c r="B164" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ウェビナー操作履歴</t>
+          <t xml:space="preserve">ウェビナー送付先担当者</t>
         </is>
       </c>
       <c r="C164" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">webinar_events</t>
+          <t xml:space="preserve">webinar_target_contacts</t>
         </is>
       </c>
       <c r="D164" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ウェビナーID</t>
+          <t xml:space="preserve">担当者ID</t>
         </is>
       </c>
       <c r="E164" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">webinar_id</t>
+          <t xml:space="preserve">contact_id</t>
         </is>
       </c>
       <c r="F164" s="4" t="inlineStr">
@@ -10911,9 +10943,9 @@
           <t xml:space="preserve">uuid</t>
         </is>
       </c>
-      <c r="G164" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FK</t>
+      <c r="G164" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK / FK</t>
         </is>
       </c>
       <c r="H164" s="4" t="inlineStr">
@@ -10928,7 +10960,7 @@
       </c>
       <c r="J164" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">webinars.id ON DELETE CASCADE</t>
+          <t xml:space="preserve">clinic_contacts.id ON DELETE RESTRICT</t>
         </is>
       </c>
       <c r="K164" s="4" t="inlineStr">
@@ -10945,27 +10977,27 @@
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ウェビナー操作履歴</t>
+          <t xml:space="preserve">ウェビナー送付先担当者</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">webinar_events</t>
+          <t xml:space="preserve">webinar_target_contacts</t>
         </is>
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">イベント種別</t>
+          <t xml:space="preserve">作成日時</t>
         </is>
       </c>
       <c r="E165" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">event_type</t>
+          <t xml:space="preserve">created_at</t>
         </is>
       </c>
       <c r="F165" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">timestamptz</t>
         </is>
       </c>
       <c r="G165" s="4" t="inlineStr">
@@ -10980,7 +11012,7 @@
       </c>
       <c r="I165" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">now()</t>
         </is>
       </c>
       <c r="J165" s="4" t="inlineStr">
@@ -11012,22 +11044,22 @@
       </c>
       <c r="D166" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">操作者メール</t>
+          <t xml:space="preserve">イベントID</t>
         </is>
       </c>
       <c r="E166" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">actor_email</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="F166" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="G166" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">uuid</t>
+        </is>
+      </c>
+      <c r="G166" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK</t>
         </is>
       </c>
       <c r="H166" s="4" t="inlineStr">
@@ -11037,7 +11069,7 @@
       </c>
       <c r="I166" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">gen_random_uuid()</t>
         </is>
       </c>
       <c r="J166" s="4" t="inlineStr">
@@ -11069,27 +11101,27 @@
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">変更前状態</t>
+          <t xml:space="preserve">ウェビナーID</t>
         </is>
       </c>
       <c r="E167" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">from_status</t>
+          <t xml:space="preserve">webinar_id</t>
         </is>
       </c>
       <c r="F167" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="G167" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">uuid</t>
+        </is>
+      </c>
+      <c r="G167" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
         </is>
       </c>
       <c r="H167" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">YES</t>
+          <t xml:space="preserve">NO</t>
         </is>
       </c>
       <c r="I167" s="4" t="inlineStr">
@@ -11099,7 +11131,7 @@
       </c>
       <c r="J167" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">webinars.id ON DELETE CASCADE</t>
         </is>
       </c>
       <c r="K167" s="4" t="inlineStr">
@@ -11126,12 +11158,12 @@
       </c>
       <c r="D168" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">変更後状態</t>
+          <t xml:space="preserve">イベント種別</t>
         </is>
       </c>
       <c r="E168" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">to_status</t>
+          <t xml:space="preserve">event_type</t>
         </is>
       </c>
       <c r="F168" s="4" t="inlineStr">
@@ -11183,17 +11215,17 @@
       </c>
       <c r="D169" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">発生日時</t>
+          <t xml:space="preserve">操作者メール</t>
         </is>
       </c>
       <c r="E169" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">created_at</t>
+          <t xml:space="preserve">actor_email</t>
         </is>
       </c>
       <c r="F169" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">timestamptz</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="G169" s="4" t="inlineStr">
@@ -11208,7 +11240,7 @@
       </c>
       <c r="I169" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">now()</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J169" s="4" t="inlineStr">
@@ -11230,22 +11262,22 @@
       </c>
       <c r="B170" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院担当者役職</t>
+          <t xml:space="preserve">ウェビナー操作履歴</t>
         </is>
       </c>
       <c r="C170" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_contact_roles</t>
+          <t xml:space="preserve">webinar_events</t>
         </is>
       </c>
       <c r="D170" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">役職キー</t>
+          <t xml:space="preserve">変更前状態</t>
         </is>
       </c>
       <c r="E170" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">role_key</t>
+          <t xml:space="preserve">from_status</t>
         </is>
       </c>
       <c r="F170" s="4" t="inlineStr">
@@ -11253,14 +11285,14 @@
           <t xml:space="preserve">text</t>
         </is>
       </c>
-      <c r="G170" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PK</t>
+      <c r="G170" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H170" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO</t>
+          <t xml:space="preserve">YES</t>
         </is>
       </c>
       <c r="I170" s="4" t="inlineStr">
@@ -11270,7 +11302,7 @@
       </c>
       <c r="J170" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">physician / dentist / nurse / dental_hygienist / receptionist / other</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K170" s="4" t="inlineStr">
@@ -11287,22 +11319,22 @@
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院担当者役職</t>
+          <t xml:space="preserve">ウェビナー操作履歴</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_contact_roles</t>
+          <t xml:space="preserve">webinar_events</t>
         </is>
       </c>
       <c r="D171" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">役職名</t>
+          <t xml:space="preserve">変更後状態</t>
         </is>
       </c>
       <c r="E171" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">label</t>
+          <t xml:space="preserve">to_status</t>
         </is>
       </c>
       <c r="F171" s="4" t="inlineStr">
@@ -11310,9 +11342,9 @@
           <t xml:space="preserve">text</t>
         </is>
       </c>
-      <c r="G171" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UK</t>
+      <c r="G171" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H171" s="4" t="inlineStr">
@@ -11344,32 +11376,32 @@
       </c>
       <c r="B172" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院担当者役職</t>
+          <t xml:space="preserve">ウェビナー操作履歴</t>
         </is>
       </c>
       <c r="C172" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_contact_roles</t>
+          <t xml:space="preserve">webinar_events</t>
         </is>
       </c>
       <c r="D172" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">表示順</t>
+          <t xml:space="preserve">発生日時</t>
         </is>
       </c>
       <c r="E172" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">sort_order</t>
+          <t xml:space="preserve">created_at</t>
         </is>
       </c>
       <c r="F172" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">integer</t>
-        </is>
-      </c>
-      <c r="G172" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UK</t>
+          <t xml:space="preserve">timestamptz</t>
+        </is>
+      </c>
+      <c r="G172" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H172" s="4" t="inlineStr">
@@ -11379,7 +11411,7 @@
       </c>
       <c r="I172" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">now()</t>
         </is>
       </c>
       <c r="J172" s="4" t="inlineStr">
@@ -11411,22 +11443,22 @@
       </c>
       <c r="D173" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">作成日時</t>
+          <t xml:space="preserve">役職キー</t>
         </is>
       </c>
       <c r="E173" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">created_at</t>
+          <t xml:space="preserve">role_key</t>
         </is>
       </c>
       <c r="F173" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">timestamptz</t>
-        </is>
-      </c>
-      <c r="G173" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G173" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK</t>
         </is>
       </c>
       <c r="H173" s="4" t="inlineStr">
@@ -11436,12 +11468,12 @@
       </c>
       <c r="I173" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">now()</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J173" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">physician / dentist / nurse / dental_hygienist / receptionist / other</t>
         </is>
       </c>
       <c r="K173" s="4" t="inlineStr">
@@ -11468,22 +11500,22 @@
       </c>
       <c r="D174" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">更新日時</t>
+          <t xml:space="preserve">役職名</t>
         </is>
       </c>
       <c r="E174" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">updated_at</t>
+          <t xml:space="preserve">label</t>
         </is>
       </c>
       <c r="F174" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">timestamptz</t>
-        </is>
-      </c>
-      <c r="G174" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G174" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UK</t>
         </is>
       </c>
       <c r="H174" s="4" t="inlineStr">
@@ -11493,7 +11525,7 @@
       </c>
       <c r="I174" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">now()</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J174" s="4" t="inlineStr">
@@ -11515,32 +11547,32 @@
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院業務連絡担当者</t>
+          <t xml:space="preserve">医院担当者役職</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_contacts</t>
+          <t xml:space="preserve">clinic_contact_roles</t>
         </is>
       </c>
       <c r="D175" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">担当者ID</t>
+          <t xml:space="preserve">表示順</t>
         </is>
       </c>
       <c r="E175" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">sort_order</t>
         </is>
       </c>
       <c r="F175" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">uuid</t>
-        </is>
-      </c>
-      <c r="G175" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PK</t>
+          <t xml:space="preserve">integer</t>
+        </is>
+      </c>
+      <c r="G175" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UK</t>
         </is>
       </c>
       <c r="H175" s="4" t="inlineStr">
@@ -11550,7 +11582,7 @@
       </c>
       <c r="I175" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">gen_random_uuid()</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J175" s="4" t="inlineStr">
@@ -11572,32 +11604,32 @@
       </c>
       <c r="B176" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院業務連絡担当者</t>
+          <t xml:space="preserve">医院担当者役職</t>
         </is>
       </c>
       <c r="C176" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_contacts</t>
+          <t xml:space="preserve">clinic_contact_roles</t>
         </is>
       </c>
       <c r="D176" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">得意先コード</t>
+          <t xml:space="preserve">作成日時</t>
         </is>
       </c>
       <c r="E176" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">customer_code</t>
+          <t xml:space="preserve">created_at</t>
         </is>
       </c>
       <c r="F176" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="G176" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FK</t>
+          <t xml:space="preserve">timestamptz</t>
+        </is>
+      </c>
+      <c r="G176" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H176" s="4" t="inlineStr">
@@ -11607,12 +11639,12 @@
       </c>
       <c r="I176" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">now()</t>
         </is>
       </c>
       <c r="J176" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinics.customer_code ON DELETE RESTRICT</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K176" s="4" t="inlineStr">
@@ -11629,32 +11661,32 @@
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院業務連絡担当者</t>
+          <t xml:space="preserve">医院担当者役職</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_contacts</t>
+          <t xml:space="preserve">clinic_contact_roles</t>
         </is>
       </c>
       <c r="D177" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">認証アカウント内部ID</t>
+          <t xml:space="preserve">更新日時</t>
         </is>
       </c>
       <c r="E177" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_user_id</t>
+          <t xml:space="preserve">updated_at</t>
         </is>
       </c>
       <c r="F177" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">uuid</t>
-        </is>
-      </c>
-      <c r="G177" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UK / FK</t>
+          <t xml:space="preserve">timestamptz</t>
+        </is>
+      </c>
+      <c r="G177" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H177" s="4" t="inlineStr">
@@ -11664,12 +11696,12 @@
       </c>
       <c r="I177" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">now()</t>
         </is>
       </c>
       <c r="J177" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_users.(id, customer_code) ON DELETE RESTRICT</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K177" s="4" t="inlineStr">
@@ -11696,22 +11728,22 @@
       </c>
       <c r="D178" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">氏名</t>
+          <t xml:space="preserve">担当者ID</t>
         </is>
       </c>
       <c r="E178" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="F178" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="G178" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">uuid</t>
+        </is>
+      </c>
+      <c r="G178" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK</t>
         </is>
       </c>
       <c r="H178" s="4" t="inlineStr">
@@ -11721,7 +11753,7 @@
       </c>
       <c r="I178" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">gen_random_uuid()</t>
         </is>
       </c>
       <c r="J178" s="4" t="inlineStr">
@@ -11753,12 +11785,12 @@
       </c>
       <c r="D179" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">部署</t>
+          <t xml:space="preserve">得意先コード</t>
         </is>
       </c>
       <c r="E179" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">department</t>
+          <t xml:space="preserve">customer_code</t>
         </is>
       </c>
       <c r="F179" s="4" t="inlineStr">
@@ -11766,14 +11798,14 @@
           <t xml:space="preserve">text</t>
         </is>
       </c>
-      <c r="G179" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="G179" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
         </is>
       </c>
       <c r="H179" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">YES</t>
+          <t xml:space="preserve">NO</t>
         </is>
       </c>
       <c r="I179" s="4" t="inlineStr">
@@ -11783,7 +11815,7 @@
       </c>
       <c r="J179" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">clinics.customer_code ON DELETE RESTRICT</t>
         </is>
       </c>
       <c r="K179" s="4" t="inlineStr">
@@ -11810,22 +11842,22 @@
       </c>
       <c r="D180" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">役職キー</t>
+          <t xml:space="preserve">認証アカウント内部ID</t>
         </is>
       </c>
       <c r="E180" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">role_key</t>
+          <t xml:space="preserve">clinic_user_id</t>
         </is>
       </c>
       <c r="F180" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">uuid</t>
         </is>
       </c>
       <c r="G180" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK</t>
+          <t xml:space="preserve">UK / FK</t>
         </is>
       </c>
       <c r="H180" s="4" t="inlineStr">
@@ -11835,12 +11867,12 @@
       </c>
       <c r="I180" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">other</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J180" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_contact_roles.role_key ON DELETE RESTRICT</t>
+          <t xml:space="preserve">clinic_users.(id, customer_code) ON DELETE RESTRICT</t>
         </is>
       </c>
       <c r="K180" s="4" t="inlineStr">
@@ -11867,12 +11899,12 @@
       </c>
       <c r="D181" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">メールアドレス</t>
+          <t xml:space="preserve">氏名</t>
         </is>
       </c>
       <c r="E181" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">email</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="F181" s="4" t="inlineStr">
@@ -11887,7 +11919,7 @@
       </c>
       <c r="H181" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">YES</t>
+          <t xml:space="preserve">NO</t>
         </is>
       </c>
       <c r="I181" s="4" t="inlineStr">
@@ -11924,12 +11956,12 @@
       </c>
       <c r="D182" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">電話番号</t>
+          <t xml:space="preserve">部署</t>
         </is>
       </c>
       <c r="E182" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">phone</t>
+          <t xml:space="preserve">department</t>
         </is>
       </c>
       <c r="F182" s="4" t="inlineStr">
@@ -11981,22 +12013,22 @@
       </c>
       <c r="D183" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">主担当</t>
+          <t xml:space="preserve">役職キー</t>
         </is>
       </c>
       <c r="E183" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">is_primary</t>
+          <t xml:space="preserve">role_key</t>
         </is>
       </c>
       <c r="F183" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">boolean</t>
-        </is>
-      </c>
-      <c r="G183" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G183" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
         </is>
       </c>
       <c r="H183" s="4" t="inlineStr">
@@ -12006,12 +12038,12 @@
       </c>
       <c r="I183" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">other</t>
         </is>
       </c>
       <c r="J183" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">clinic_contact_roles.role_key ON DELETE RESTRICT</t>
         </is>
       </c>
       <c r="K183" s="4" t="inlineStr">
@@ -12038,12 +12070,12 @@
       </c>
       <c r="D184" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">状態</t>
+          <t xml:space="preserve">メールアドレス</t>
         </is>
       </c>
       <c r="E184" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">status</t>
+          <t xml:space="preserve">email</t>
         </is>
       </c>
       <c r="F184" s="4" t="inlineStr">
@@ -12058,17 +12090,17 @@
       </c>
       <c r="H184" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO</t>
+          <t xml:space="preserve">YES</t>
         </is>
       </c>
       <c r="I184" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">active</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J184" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">active / inactive</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K184" s="4" t="inlineStr">
@@ -12095,12 +12127,12 @@
       </c>
       <c r="D185" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">備考</t>
+          <t xml:space="preserve">電話番号</t>
         </is>
       </c>
       <c r="E185" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">notes</t>
+          <t xml:space="preserve">phone</t>
         </is>
       </c>
       <c r="F185" s="4" t="inlineStr">
@@ -12152,17 +12184,17 @@
       </c>
       <c r="D186" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">排他バージョン</t>
+          <t xml:space="preserve">主担当</t>
         </is>
       </c>
       <c r="E186" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">version</t>
+          <t xml:space="preserve">is_primary</t>
         </is>
       </c>
       <c r="F186" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">integer</t>
+          <t xml:space="preserve">boolean</t>
         </is>
       </c>
       <c r="G186" s="4" t="inlineStr">
@@ -12177,7 +12209,7 @@
       </c>
       <c r="I186" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="J186" s="4" t="inlineStr">
@@ -12209,17 +12241,17 @@
       </c>
       <c r="D187" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">論理削除日時</t>
+          <t xml:space="preserve">状態</t>
         </is>
       </c>
       <c r="E187" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">deleted_at</t>
+          <t xml:space="preserve">status</t>
         </is>
       </c>
       <c r="F187" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">timestamptz</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="G187" s="4" t="inlineStr">
@@ -12229,17 +12261,17 @@
       </c>
       <c r="H187" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">YES</t>
+          <t xml:space="preserve">NO</t>
         </is>
       </c>
       <c r="I187" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">active</t>
         </is>
       </c>
       <c r="J187" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">active / inactive</t>
         </is>
       </c>
       <c r="K187" s="4" t="inlineStr">
@@ -12266,17 +12298,17 @@
       </c>
       <c r="D188" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">作成日時</t>
+          <t xml:space="preserve">備考</t>
         </is>
       </c>
       <c r="E188" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">created_at</t>
+          <t xml:space="preserve">notes</t>
         </is>
       </c>
       <c r="F188" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">timestamptz</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="G188" s="4" t="inlineStr">
@@ -12286,12 +12318,12 @@
       </c>
       <c r="H188" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO</t>
+          <t xml:space="preserve">YES</t>
         </is>
       </c>
       <c r="I188" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">now()</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J188" s="4" t="inlineStr">
@@ -12323,17 +12355,17 @@
       </c>
       <c r="D189" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">更新日時</t>
+          <t xml:space="preserve">排他バージョン</t>
         </is>
       </c>
       <c r="E189" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">updated_at</t>
+          <t xml:space="preserve">version</t>
         </is>
       </c>
       <c r="F189" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">timestamptz</t>
+          <t xml:space="preserve">integer</t>
         </is>
       </c>
       <c r="G189" s="4" t="inlineStr">
@@ -12348,7 +12380,7 @@
       </c>
       <c r="I189" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">now()</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J189" s="4" t="inlineStr">
@@ -12370,42 +12402,42 @@
       </c>
       <c r="B190" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院ポータルログイン</t>
+          <t xml:space="preserve">医院業務連絡担当者</t>
         </is>
       </c>
       <c r="C190" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_users</t>
+          <t xml:space="preserve">clinic_contacts</t>
         </is>
       </c>
       <c r="D190" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院ログインID</t>
+          <t xml:space="preserve">論理削除日時</t>
         </is>
       </c>
       <c r="E190" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">deleted_at</t>
         </is>
       </c>
       <c r="F190" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">uuid</t>
-        </is>
-      </c>
-      <c r="G190" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PK</t>
+          <t xml:space="preserve">timestamptz</t>
+        </is>
+      </c>
+      <c r="G190" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H190" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO</t>
+          <t xml:space="preserve">YES</t>
         </is>
       </c>
       <c r="I190" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">gen_random_uuid()</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J190" s="4" t="inlineStr">
@@ -12427,32 +12459,32 @@
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院ポータルログイン</t>
+          <t xml:space="preserve">医院業務連絡担当者</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_users</t>
+          <t xml:space="preserve">clinic_contacts</t>
         </is>
       </c>
       <c r="D191" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">得意先コード</t>
+          <t xml:space="preserve">作成日時</t>
         </is>
       </c>
       <c r="E191" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">customer_code</t>
+          <t xml:space="preserve">created_at</t>
         </is>
       </c>
       <c r="F191" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="G191" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FK</t>
+          <t xml:space="preserve">timestamptz</t>
+        </is>
+      </c>
+      <c r="G191" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H191" s="4" t="inlineStr">
@@ -12462,12 +12494,12 @@
       </c>
       <c r="I191" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">now()</t>
         </is>
       </c>
       <c r="J191" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinics.customer_code ON DELETE CASCADE</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K191" s="4" t="inlineStr">
@@ -12484,32 +12516,32 @@
       </c>
       <c r="B192" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院ポータルログイン</t>
+          <t xml:space="preserve">医院業務連絡担当者</t>
         </is>
       </c>
       <c r="C192" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_users</t>
+          <t xml:space="preserve">clinic_contacts</t>
         </is>
       </c>
       <c r="D192" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">担当者ID兼ログインID</t>
+          <t xml:space="preserve">更新日時</t>
         </is>
       </c>
       <c r="E192" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">login_id</t>
+          <t xml:space="preserve">updated_at</t>
         </is>
       </c>
       <c r="F192" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="G192" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UK</t>
+          <t xml:space="preserve">timestamptz</t>
+        </is>
+      </c>
+      <c r="G192" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H192" s="4" t="inlineStr">
@@ -12519,7 +12551,7 @@
       </c>
       <c r="I192" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">now()</t>
         </is>
       </c>
       <c r="J192" s="4" t="inlineStr">
@@ -12529,7 +12561,7 @@
       </c>
       <c r="K192" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">A+6桁。画面では担当者IDとして表示し、この値でログインする</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
@@ -12551,22 +12583,22 @@
       </c>
       <c r="D193" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">パスワードハッシュ</t>
+          <t xml:space="preserve">医院ログインID</t>
         </is>
       </c>
       <c r="E193" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">password_hash</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="F193" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="G193" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">uuid</t>
+        </is>
+      </c>
+      <c r="G193" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK</t>
         </is>
       </c>
       <c r="H193" s="4" t="inlineStr">
@@ -12576,7 +12608,7 @@
       </c>
       <c r="I193" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">gen_random_uuid()</t>
         </is>
       </c>
       <c r="J193" s="4" t="inlineStr">
@@ -12608,12 +12640,12 @@
       </c>
       <c r="D194" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">表示名</t>
+          <t xml:space="preserve">得意先コード</t>
         </is>
       </c>
       <c r="E194" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">customer_code</t>
         </is>
       </c>
       <c r="F194" s="4" t="inlineStr">
@@ -12621,14 +12653,14 @@
           <t xml:space="preserve">text</t>
         </is>
       </c>
-      <c r="G194" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="G194" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
         </is>
       </c>
       <c r="H194" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">YES</t>
+          <t xml:space="preserve">NO</t>
         </is>
       </c>
       <c r="I194" s="4" t="inlineStr">
@@ -12638,7 +12670,7 @@
       </c>
       <c r="J194" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">clinics.customer_code ON DELETE CASCADE</t>
         </is>
       </c>
       <c r="K194" s="4" t="inlineStr">
@@ -12665,12 +12697,12 @@
       </c>
       <c r="D195" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">メールアドレス</t>
+          <t xml:space="preserve">担当者ID兼ログインID</t>
         </is>
       </c>
       <c r="E195" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">email</t>
+          <t xml:space="preserve">login_id</t>
         </is>
       </c>
       <c r="F195" s="4" t="inlineStr">
@@ -12678,14 +12710,14 @@
           <t xml:space="preserve">text</t>
         </is>
       </c>
-      <c r="G195" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="G195" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UK</t>
         </is>
       </c>
       <c r="H195" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">YES</t>
+          <t xml:space="preserve">NO</t>
         </is>
       </c>
       <c r="I195" s="4" t="inlineStr">
@@ -12700,7 +12732,7 @@
       </c>
       <c r="K195" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">A+6桁。画面では担当者IDとして表示し、この値でログインする</t>
         </is>
       </c>
     </row>
@@ -12722,12 +12754,12 @@
       </c>
       <c r="D196" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">状態</t>
+          <t xml:space="preserve">パスワードハッシュ</t>
         </is>
       </c>
       <c r="E196" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">status</t>
+          <t xml:space="preserve">password_hash</t>
         </is>
       </c>
       <c r="F196" s="4" t="inlineStr">
@@ -12747,12 +12779,12 @@
       </c>
       <c r="I196" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">有効</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J196" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">有効 / 無効</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K196" s="4" t="inlineStr">
@@ -12779,17 +12811,17 @@
       </c>
       <c r="D197" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">作成日時</t>
+          <t xml:space="preserve">表示名</t>
         </is>
       </c>
       <c r="E197" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">created_at</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="F197" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">timestamptz</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="G197" s="4" t="inlineStr">
@@ -12799,12 +12831,12 @@
       </c>
       <c r="H197" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO</t>
+          <t xml:space="preserve">YES</t>
         </is>
       </c>
       <c r="I197" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">now()</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J197" s="4" t="inlineStr">
@@ -12836,17 +12868,17 @@
       </c>
       <c r="D198" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">更新日時</t>
+          <t xml:space="preserve">メールアドレス</t>
         </is>
       </c>
       <c r="E198" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">updated_at</t>
+          <t xml:space="preserve">email</t>
         </is>
       </c>
       <c r="F198" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">timestamptz</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="G198" s="4" t="inlineStr">
@@ -12856,12 +12888,12 @@
       </c>
       <c r="H198" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO</t>
+          <t xml:space="preserve">YES</t>
         </is>
       </c>
       <c r="I198" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">now()</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J198" s="4" t="inlineStr">
@@ -12893,17 +12925,17 @@
       </c>
       <c r="D199" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ログイン失敗回数</t>
+          <t xml:space="preserve">状態</t>
         </is>
       </c>
       <c r="E199" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">failed_login_attempts</t>
+          <t xml:space="preserve">status</t>
         </is>
       </c>
       <c r="F199" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">integer</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="G199" s="4" t="inlineStr">
@@ -12918,12 +12950,12 @@
       </c>
       <c r="I199" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">有効</t>
         </is>
       </c>
       <c r="J199" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">有効 / 無効</t>
         </is>
       </c>
       <c r="K199" s="4" t="inlineStr">
@@ -12950,12 +12982,12 @@
       </c>
       <c r="D200" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ロック解除日時</t>
+          <t xml:space="preserve">作成日時</t>
         </is>
       </c>
       <c r="E200" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">locked_until</t>
+          <t xml:space="preserve">created_at</t>
         </is>
       </c>
       <c r="F200" s="4" t="inlineStr">
@@ -12970,12 +13002,12 @@
       </c>
       <c r="H200" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">YES</t>
+          <t xml:space="preserve">NO</t>
         </is>
       </c>
       <c r="I200" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">now()</t>
         </is>
       </c>
       <c r="J200" s="4" t="inlineStr">
@@ -13007,17 +13039,17 @@
       </c>
       <c r="D201" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">セッション世代</t>
+          <t xml:space="preserve">更新日時</t>
         </is>
       </c>
       <c r="E201" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">session_version</t>
+          <t xml:space="preserve">updated_at</t>
         </is>
       </c>
       <c r="F201" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">integer</t>
+          <t xml:space="preserve">timestamptz</t>
         </is>
       </c>
       <c r="G201" s="4" t="inlineStr">
@@ -13032,17 +13064,17 @@
       </c>
       <c r="I201" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">now()</t>
         </is>
       </c>
       <c r="J201" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">&gt; 0</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K201" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">無効化・パスワード変更時に加算し旧セッションを失効</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
@@ -13064,17 +13096,17 @@
       </c>
       <c r="D202" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">最終ログイン日時</t>
+          <t xml:space="preserve">ログイン失敗回数</t>
         </is>
       </c>
       <c r="E202" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">last_login_at</t>
+          <t xml:space="preserve">failed_login_attempts</t>
         </is>
       </c>
       <c r="F202" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">timestamptz</t>
+          <t xml:space="preserve">integer</t>
         </is>
       </c>
       <c r="G202" s="4" t="inlineStr">
@@ -13084,12 +13116,12 @@
       </c>
       <c r="H202" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">YES</t>
+          <t xml:space="preserve">NO</t>
         </is>
       </c>
       <c r="I202" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="J202" s="4" t="inlineStr">
@@ -13121,12 +13153,12 @@
       </c>
       <c r="D203" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">パスワード変更日時</t>
+          <t xml:space="preserve">ロック解除日時</t>
         </is>
       </c>
       <c r="E203" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">password_changed_at</t>
+          <t xml:space="preserve">locked_until</t>
         </is>
       </c>
       <c r="F203" s="4" t="inlineStr">
@@ -13178,17 +13210,17 @@
       </c>
       <c r="D204" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">初回変更必須</t>
+          <t xml:space="preserve">セッション世代</t>
         </is>
       </c>
       <c r="E204" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">must_change_password</t>
+          <t xml:space="preserve">session_version</t>
         </is>
       </c>
       <c r="F204" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">boolean</t>
+          <t xml:space="preserve">integer</t>
         </is>
       </c>
       <c r="G204" s="4" t="inlineStr">
@@ -13203,17 +13235,17 @@
       </c>
       <c r="I204" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J204" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">&gt; 0</t>
         </is>
       </c>
       <c r="K204" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">新規発行時true。初回変更または既存リセット完了時false</t>
+          <t xml:space="preserve">無効化・パスワード変更時に加算し旧セッションを失効</t>
         </is>
       </c>
     </row>
@@ -13225,37 +13257,37 @@
       </c>
       <c r="B205" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院ポータル権限</t>
+          <t xml:space="preserve">医院ポータルログイン</t>
         </is>
       </c>
       <c r="C205" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_portal_roles</t>
+          <t xml:space="preserve">clinic_users</t>
         </is>
       </c>
       <c r="D205" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">権限キー</t>
+          <t xml:space="preserve">最終ログイン日時</t>
         </is>
       </c>
       <c r="E205" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">role_key</t>
+          <t xml:space="preserve">last_login_at</t>
         </is>
       </c>
       <c r="F205" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="G205" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PK</t>
+          <t xml:space="preserve">timestamptz</t>
+        </is>
+      </c>
+      <c r="G205" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H205" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO</t>
+          <t xml:space="preserve">YES</t>
         </is>
       </c>
       <c r="I205" s="4" t="inlineStr">
@@ -13265,7 +13297,7 @@
       </c>
       <c r="J205" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin / staff / viewer</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K205" s="4" t="inlineStr">
@@ -13282,37 +13314,37 @@
       </c>
       <c r="B206" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院ポータル権限</t>
+          <t xml:space="preserve">医院ポータルログイン</t>
         </is>
       </c>
       <c r="C206" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_portal_roles</t>
+          <t xml:space="preserve">clinic_users</t>
         </is>
       </c>
       <c r="D206" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">権限名</t>
+          <t xml:space="preserve">パスワード変更日時</t>
         </is>
       </c>
       <c r="E206" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">label</t>
+          <t xml:space="preserve">password_changed_at</t>
         </is>
       </c>
       <c r="F206" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="G206" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UK</t>
+          <t xml:space="preserve">timestamptz</t>
+        </is>
+      </c>
+      <c r="G206" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H206" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NO</t>
+          <t xml:space="preserve">YES</t>
         </is>
       </c>
       <c r="I206" s="4" t="inlineStr">
@@ -13339,27 +13371,27 @@
       </c>
       <c r="B207" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院ポータル権限</t>
+          <t xml:space="preserve">医院ポータルログイン</t>
         </is>
       </c>
       <c r="C207" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_portal_roles</t>
+          <t xml:space="preserve">clinic_users</t>
         </is>
       </c>
       <c r="D207" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">説明</t>
+          <t xml:space="preserve">初回変更必須</t>
         </is>
       </c>
       <c r="E207" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">description</t>
+          <t xml:space="preserve">must_change_password</t>
         </is>
       </c>
       <c r="F207" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">boolean</t>
         </is>
       </c>
       <c r="G207" s="4" t="inlineStr">
@@ -13374,7 +13406,7 @@
       </c>
       <c r="I207" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="J207" s="4" t="inlineStr">
@@ -13384,7 +13416,7 @@
       </c>
       <c r="K207" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">新規発行時true。初回変更または既存リセット完了時false</t>
         </is>
       </c>
     </row>
@@ -13406,22 +13438,22 @@
       </c>
       <c r="D208" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">表示順</t>
+          <t xml:space="preserve">権限キー</t>
         </is>
       </c>
       <c r="E208" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">sort_order</t>
+          <t xml:space="preserve">role_key</t>
         </is>
       </c>
       <c r="F208" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">integer</t>
-        </is>
-      </c>
-      <c r="G208" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UK</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G208" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK</t>
         </is>
       </c>
       <c r="H208" s="4" t="inlineStr">
@@ -13436,7 +13468,7 @@
       </c>
       <c r="J208" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">admin / staff / viewer</t>
         </is>
       </c>
       <c r="K208" s="4" t="inlineStr">
@@ -13463,22 +13495,22 @@
       </c>
       <c r="D209" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">作成日時</t>
+          <t xml:space="preserve">権限名</t>
         </is>
       </c>
       <c r="E209" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">created_at</t>
+          <t xml:space="preserve">label</t>
         </is>
       </c>
       <c r="F209" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">timestamptz</t>
-        </is>
-      </c>
-      <c r="G209" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G209" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UK</t>
         </is>
       </c>
       <c r="H209" s="4" t="inlineStr">
@@ -13488,7 +13520,7 @@
       </c>
       <c r="I209" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">now()</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J209" s="4" t="inlineStr">
@@ -13520,17 +13552,17 @@
       </c>
       <c r="D210" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">更新日時</t>
+          <t xml:space="preserve">説明</t>
         </is>
       </c>
       <c r="E210" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">updated_at</t>
+          <t xml:space="preserve">description</t>
         </is>
       </c>
       <c r="F210" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">timestamptz</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="G210" s="4" t="inlineStr">
@@ -13545,7 +13577,7 @@
       </c>
       <c r="I210" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">now()</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J210" s="4" t="inlineStr">
@@ -13567,32 +13599,32 @@
       </c>
       <c r="B211" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院ポータル権限機能</t>
+          <t xml:space="preserve">医院ポータル権限</t>
         </is>
       </c>
       <c r="C211" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_portal_role_permissions</t>
+          <t xml:space="preserve">clinic_portal_roles</t>
         </is>
       </c>
       <c r="D211" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">権限キー</t>
+          <t xml:space="preserve">表示順</t>
         </is>
       </c>
       <c r="E211" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">role_key</t>
+          <t xml:space="preserve">sort_order</t>
         </is>
       </c>
       <c r="F211" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="G211" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PK / FK</t>
+          <t xml:space="preserve">integer</t>
+        </is>
+      </c>
+      <c r="G211" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UK</t>
         </is>
       </c>
       <c r="H211" s="4" t="inlineStr">
@@ -13607,7 +13639,7 @@
       </c>
       <c r="J211" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_portal_roles.role_key ON DELETE RESTRICT</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K211" s="4" t="inlineStr">
@@ -13624,32 +13656,32 @@
       </c>
       <c r="B212" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院ポータル権限機能</t>
+          <t xml:space="preserve">医院ポータル権限</t>
         </is>
       </c>
       <c r="C212" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_portal_role_permissions</t>
+          <t xml:space="preserve">clinic_portal_roles</t>
         </is>
       </c>
       <c r="D212" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">機能キー</t>
+          <t xml:space="preserve">作成日時</t>
         </is>
       </c>
       <c r="E212" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">permission_key</t>
+          <t xml:space="preserve">created_at</t>
         </is>
       </c>
       <c r="F212" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="G212" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PK</t>
+          <t xml:space="preserve">timestamptz</t>
+        </is>
+      </c>
+      <c r="G212" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H212" s="4" t="inlineStr">
@@ -13659,12 +13691,12 @@
       </c>
       <c r="I212" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">now()</t>
         </is>
       </c>
       <c r="J212" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">view_contacts / manage_contacts / manage_logins</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K212" s="4" t="inlineStr">
@@ -13681,22 +13713,22 @@
       </c>
       <c r="B213" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院ポータル権限機能</t>
+          <t xml:space="preserve">医院ポータル権限</t>
         </is>
       </c>
       <c r="C213" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_portal_role_permissions</t>
+          <t xml:space="preserve">clinic_portal_roles</t>
         </is>
       </c>
       <c r="D213" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">作成日時</t>
+          <t xml:space="preserve">更新日時</t>
         </is>
       </c>
       <c r="E213" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">created_at</t>
+          <t xml:space="preserve">updated_at</t>
         </is>
       </c>
       <c r="F213" s="4" t="inlineStr">
@@ -13738,27 +13770,27 @@
       </c>
       <c r="B214" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院ログイン権限割当</t>
+          <t xml:space="preserve">医院ポータル権限機能</t>
         </is>
       </c>
       <c r="C214" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_user_role_assignments</t>
+          <t xml:space="preserve">clinic_portal_role_permissions</t>
         </is>
       </c>
       <c r="D214" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院ログインID</t>
+          <t xml:space="preserve">権限キー</t>
         </is>
       </c>
       <c r="E214" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_user_id</t>
+          <t xml:space="preserve">role_key</t>
         </is>
       </c>
       <c r="F214" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">uuid</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="G214" s="5" t="inlineStr">
@@ -13778,7 +13810,7 @@
       </c>
       <c r="J214" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_users.id ON DELETE CASCADE</t>
+          <t xml:space="preserve">clinic_portal_roles.role_key ON DELETE RESTRICT</t>
         </is>
       </c>
       <c r="K214" s="4" t="inlineStr">
@@ -13795,22 +13827,22 @@
       </c>
       <c r="B215" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院ログイン権限割当</t>
+          <t xml:space="preserve">医院ポータル権限機能</t>
         </is>
       </c>
       <c r="C215" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_user_role_assignments</t>
+          <t xml:space="preserve">clinic_portal_role_permissions</t>
         </is>
       </c>
       <c r="D215" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">権限キー</t>
+          <t xml:space="preserve">機能キー</t>
         </is>
       </c>
       <c r="E215" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">role_key</t>
+          <t xml:space="preserve">permission_key</t>
         </is>
       </c>
       <c r="F215" s="4" t="inlineStr">
@@ -13818,9 +13850,9 @@
           <t xml:space="preserve">text</t>
         </is>
       </c>
-      <c r="G215" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FK</t>
+      <c r="G215" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK</t>
         </is>
       </c>
       <c r="H215" s="4" t="inlineStr">
@@ -13835,7 +13867,7 @@
       </c>
       <c r="J215" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_portal_roles.role_key ON DELETE RESTRICT</t>
+          <t xml:space="preserve">view_contacts / manage_contacts / manage_logins</t>
         </is>
       </c>
       <c r="K215" s="4" t="inlineStr">
@@ -13852,27 +13884,27 @@
       </c>
       <c r="B216" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院ログイン権限割当</t>
+          <t xml:space="preserve">医院ポータル権限機能</t>
         </is>
       </c>
       <c r="C216" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_user_role_assignments</t>
+          <t xml:space="preserve">clinic_portal_role_permissions</t>
         </is>
       </c>
       <c r="D216" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">割当操作者</t>
+          <t xml:space="preserve">作成日時</t>
         </is>
       </c>
       <c r="E216" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">assigned_by</t>
+          <t xml:space="preserve">created_at</t>
         </is>
       </c>
       <c r="F216" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">timestamptz</t>
         </is>
       </c>
       <c r="G216" s="4" t="inlineStr">
@@ -13887,7 +13919,7 @@
       </c>
       <c r="I216" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">system</t>
+          <t xml:space="preserve">now()</t>
         </is>
       </c>
       <c r="J216" s="4" t="inlineStr">
@@ -13919,22 +13951,22 @@
       </c>
       <c r="D217" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">作成日時</t>
+          <t xml:space="preserve">医院ログインID</t>
         </is>
       </c>
       <c r="E217" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">created_at</t>
+          <t xml:space="preserve">clinic_user_id</t>
         </is>
       </c>
       <c r="F217" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">timestamptz</t>
-        </is>
-      </c>
-      <c r="G217" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">uuid</t>
+        </is>
+      </c>
+      <c r="G217" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK / FK</t>
         </is>
       </c>
       <c r="H217" s="4" t="inlineStr">
@@ -13944,12 +13976,12 @@
       </c>
       <c r="I217" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">now()</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J217" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">clinic_users.id ON DELETE CASCADE</t>
         </is>
       </c>
       <c r="K217" s="4" t="inlineStr">
@@ -13976,22 +14008,22 @@
       </c>
       <c r="D218" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">更新日時</t>
+          <t xml:space="preserve">権限キー</t>
         </is>
       </c>
       <c r="E218" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">updated_at</t>
+          <t xml:space="preserve">role_key</t>
         </is>
       </c>
       <c r="F218" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">timestamptz</t>
-        </is>
-      </c>
-      <c r="G218" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G218" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
         </is>
       </c>
       <c r="H218" s="4" t="inlineStr">
@@ -14001,12 +14033,12 @@
       </c>
       <c r="I218" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">now()</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J218" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">clinic_portal_roles.role_key ON DELETE RESTRICT</t>
         </is>
       </c>
       <c r="K218" s="4" t="inlineStr">
@@ -14023,32 +14055,32 @@
       </c>
       <c r="B219" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">担当者通知設定</t>
+          <t xml:space="preserve">医院ログイン権限割当</t>
         </is>
       </c>
       <c r="C219" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_contact_notification_preferences</t>
+          <t xml:space="preserve">clinic_user_role_assignments</t>
         </is>
       </c>
       <c r="D219" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">担当者ID</t>
+          <t xml:space="preserve">割当操作者</t>
         </is>
       </c>
       <c r="E219" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">contact_id</t>
+          <t xml:space="preserve">assigned_by</t>
         </is>
       </c>
       <c r="F219" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">uuid</t>
-        </is>
-      </c>
-      <c r="G219" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PK / FK</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G219" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H219" s="4" t="inlineStr">
@@ -14058,12 +14090,12 @@
       </c>
       <c r="I219" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">system</t>
         </is>
       </c>
       <c r="J219" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_contacts.id ON DELETE RESTRICT</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K219" s="4" t="inlineStr">
@@ -14080,32 +14112,32 @@
       </c>
       <c r="B220" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">担当者通知設定</t>
+          <t xml:space="preserve">医院ログイン権限割当</t>
         </is>
       </c>
       <c r="C220" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_contact_notification_preferences</t>
+          <t xml:space="preserve">clinic_user_role_assignments</t>
         </is>
       </c>
       <c r="D220" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">通知種別</t>
+          <t xml:space="preserve">作成日時</t>
         </is>
       </c>
       <c r="E220" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">topic</t>
+          <t xml:space="preserve">created_at</t>
         </is>
       </c>
       <c r="F220" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="G220" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PK</t>
+          <t xml:space="preserve">timestamptz</t>
+        </is>
+      </c>
+      <c r="G220" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H220" s="4" t="inlineStr">
@@ -14115,12 +14147,12 @@
       </c>
       <c r="I220" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">now()</t>
         </is>
       </c>
       <c r="J220" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">webinar / orders / billing / product / system / sales</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K220" s="4" t="inlineStr">
@@ -14137,32 +14169,32 @@
       </c>
       <c r="B221" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">担当者通知設定</t>
+          <t xml:space="preserve">医院ログイン権限割当</t>
         </is>
       </c>
       <c r="C221" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_contact_notification_preferences</t>
+          <t xml:space="preserve">clinic_user_role_assignments</t>
         </is>
       </c>
       <c r="D221" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">連絡方法</t>
+          <t xml:space="preserve">更新日時</t>
         </is>
       </c>
       <c r="E221" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">channel</t>
+          <t xml:space="preserve">updated_at</t>
         </is>
       </c>
       <c r="F221" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="G221" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PK</t>
+          <t xml:space="preserve">timestamptz</t>
+        </is>
+      </c>
+      <c r="G221" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H221" s="4" t="inlineStr">
@@ -14172,12 +14204,12 @@
       </c>
       <c r="I221" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">now()</t>
         </is>
       </c>
       <c r="J221" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">email / phone</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K221" s="4" t="inlineStr">
@@ -14204,22 +14236,22 @@
       </c>
       <c r="D222" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">有効</t>
+          <t xml:space="preserve">担当者ID</t>
         </is>
       </c>
       <c r="E222" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">enabled</t>
+          <t xml:space="preserve">contact_id</t>
         </is>
       </c>
       <c r="F222" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">boolean</t>
-        </is>
-      </c>
-      <c r="G222" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">uuid</t>
+        </is>
+      </c>
+      <c r="G222" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK / FK</t>
         </is>
       </c>
       <c r="H222" s="4" t="inlineStr">
@@ -14229,12 +14261,12 @@
       </c>
       <c r="I222" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">true</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J222" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">clinic_contacts.id ON DELETE RESTRICT</t>
         </is>
       </c>
       <c r="K222" s="4" t="inlineStr">
@@ -14261,22 +14293,22 @@
       </c>
       <c r="D223" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">作成日時</t>
+          <t xml:space="preserve">通知種別</t>
         </is>
       </c>
       <c r="E223" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">created_at</t>
+          <t xml:space="preserve">topic</t>
         </is>
       </c>
       <c r="F223" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">timestamptz</t>
-        </is>
-      </c>
-      <c r="G223" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G223" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK</t>
         </is>
       </c>
       <c r="H223" s="4" t="inlineStr">
@@ -14286,12 +14318,12 @@
       </c>
       <c r="I223" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">now()</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J223" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">webinar / orders / billing / product / system / sales</t>
         </is>
       </c>
       <c r="K223" s="4" t="inlineStr">
@@ -14318,22 +14350,22 @@
       </c>
       <c r="D224" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">更新日時</t>
+          <t xml:space="preserve">連絡方法</t>
         </is>
       </c>
       <c r="E224" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">updated_at</t>
+          <t xml:space="preserve">channel</t>
         </is>
       </c>
       <c r="F224" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">timestamptz</t>
-        </is>
-      </c>
-      <c r="G224" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G224" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK</t>
         </is>
       </c>
       <c r="H224" s="4" t="inlineStr">
@@ -14343,12 +14375,12 @@
       </c>
       <c r="I224" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">now()</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J224" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">email / phone</t>
         </is>
       </c>
       <c r="K224" s="4" t="inlineStr">
@@ -14365,32 +14397,32 @@
       </c>
       <c r="B225" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">担当者操作履歴</t>
+          <t xml:space="preserve">担当者通知設定</t>
         </is>
       </c>
       <c r="C225" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_contact_events</t>
+          <t xml:space="preserve">clinic_contact_notification_preferences</t>
         </is>
       </c>
       <c r="D225" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">イベントID</t>
+          <t xml:space="preserve">有効</t>
         </is>
       </c>
       <c r="E225" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">enabled</t>
         </is>
       </c>
       <c r="F225" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">uuid</t>
-        </is>
-      </c>
-      <c r="G225" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PK</t>
+          <t xml:space="preserve">boolean</t>
+        </is>
+      </c>
+      <c r="G225" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H225" s="4" t="inlineStr">
@@ -14400,7 +14432,7 @@
       </c>
       <c r="I225" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">gen_random_uuid()</t>
+          <t xml:space="preserve">true</t>
         </is>
       </c>
       <c r="J225" s="4" t="inlineStr">
@@ -14422,32 +14454,32 @@
       </c>
       <c r="B226" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">担当者操作履歴</t>
+          <t xml:space="preserve">担当者通知設定</t>
         </is>
       </c>
       <c r="C226" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_contact_events</t>
+          <t xml:space="preserve">clinic_contact_notification_preferences</t>
         </is>
       </c>
       <c r="D226" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">担当者ID</t>
+          <t xml:space="preserve">作成日時</t>
         </is>
       </c>
       <c r="E226" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">contact_id</t>
+          <t xml:space="preserve">created_at</t>
         </is>
       </c>
       <c r="F226" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">uuid</t>
-        </is>
-      </c>
-      <c r="G226" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FK</t>
+          <t xml:space="preserve">timestamptz</t>
+        </is>
+      </c>
+      <c r="G226" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H226" s="4" t="inlineStr">
@@ -14457,12 +14489,12 @@
       </c>
       <c r="I226" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">now()</t>
         </is>
       </c>
       <c r="J226" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_contacts.id ON DELETE RESTRICT</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K226" s="4" t="inlineStr">
@@ -14479,27 +14511,27 @@
       </c>
       <c r="B227" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">担当者操作履歴</t>
+          <t xml:space="preserve">担当者通知設定</t>
         </is>
       </c>
       <c r="C227" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_contact_events</t>
+          <t xml:space="preserve">clinic_contact_notification_preferences</t>
         </is>
       </c>
       <c r="D227" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">イベント種別</t>
+          <t xml:space="preserve">更新日時</t>
         </is>
       </c>
       <c r="E227" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">event_type</t>
+          <t xml:space="preserve">updated_at</t>
         </is>
       </c>
       <c r="F227" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">timestamptz</t>
         </is>
       </c>
       <c r="G227" s="4" t="inlineStr">
@@ -14514,7 +14546,7 @@
       </c>
       <c r="I227" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">now()</t>
         </is>
       </c>
       <c r="J227" s="4" t="inlineStr">
@@ -14546,22 +14578,22 @@
       </c>
       <c r="D228" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">操作者種別</t>
+          <t xml:space="preserve">イベントID</t>
         </is>
       </c>
       <c r="E228" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">actor_type</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="F228" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="G228" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">uuid</t>
+        </is>
+      </c>
+      <c r="G228" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK</t>
         </is>
       </c>
       <c r="H228" s="4" t="inlineStr">
@@ -14571,7 +14603,7 @@
       </c>
       <c r="I228" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">gen_random_uuid()</t>
         </is>
       </c>
       <c r="J228" s="4" t="inlineStr">
@@ -14603,22 +14635,22 @@
       </c>
       <c r="D229" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">操作者識別子</t>
+          <t xml:space="preserve">担当者ID</t>
         </is>
       </c>
       <c r="E229" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">actor_identifier</t>
+          <t xml:space="preserve">contact_id</t>
         </is>
       </c>
       <c r="F229" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="G229" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">uuid</t>
+        </is>
+      </c>
+      <c r="G229" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
         </is>
       </c>
       <c r="H229" s="4" t="inlineStr">
@@ -14633,7 +14665,7 @@
       </c>
       <c r="J229" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">clinic_contacts.id ON DELETE RESTRICT</t>
         </is>
       </c>
       <c r="K229" s="4" t="inlineStr">
@@ -14660,17 +14692,17 @@
       </c>
       <c r="D230" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">追加情報</t>
+          <t xml:space="preserve">イベント種別</t>
         </is>
       </c>
       <c r="E230" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">metadata</t>
+          <t xml:space="preserve">event_type</t>
         </is>
       </c>
       <c r="F230" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">jsonb</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="G230" s="4" t="inlineStr">
@@ -14685,7 +14717,7 @@
       </c>
       <c r="I230" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">{}</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J230" s="4" t="inlineStr">
@@ -14717,40 +14749,211 @@
       </c>
       <c r="D231" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">操作者種別</t>
+        </is>
+      </c>
+      <c r="E231" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actor_type</t>
+        </is>
+      </c>
+      <c r="F231" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G231" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H231" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I231" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J231" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K231" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="232" ht="30" customHeight="1">
+      <c r="A232" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B232" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">担当者操作履歴</t>
+        </is>
+      </c>
+      <c r="C232" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_contact_events</t>
+        </is>
+      </c>
+      <c r="D232" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">操作者識別子</t>
+        </is>
+      </c>
+      <c r="E232" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">actor_identifier</t>
+        </is>
+      </c>
+      <c r="F232" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="G232" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H232" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I232" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J232" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K232" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="233" ht="30" customHeight="1">
+      <c r="A233" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B233" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">担当者操作履歴</t>
+        </is>
+      </c>
+      <c r="C233" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_contact_events</t>
+        </is>
+      </c>
+      <c r="D233" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">追加情報</t>
+        </is>
+      </c>
+      <c r="E233" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metadata</t>
+        </is>
+      </c>
+      <c r="F233" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jsonb</t>
+        </is>
+      </c>
+      <c r="G233" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H233" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO</t>
+        </is>
+      </c>
+      <c r="I233" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{}</t>
+        </is>
+      </c>
+      <c r="J233" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K233" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="234" ht="30" customHeight="1">
+      <c r="A234" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">現行</t>
+        </is>
+      </c>
+      <c r="B234" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">担当者操作履歴</t>
+        </is>
+      </c>
+      <c r="C234" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_contact_events</t>
+        </is>
+      </c>
+      <c r="D234" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">発生日時</t>
         </is>
       </c>
-      <c r="E231" s="4" t="inlineStr">
+      <c r="E234" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">created_at</t>
         </is>
       </c>
-      <c r="F231" s="4" t="inlineStr">
+      <c r="F234" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">timestamptz</t>
         </is>
       </c>
-      <c r="G231" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H231" s="4" t="inlineStr">
+      <c r="G234" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H234" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">NO</t>
         </is>
       </c>
-      <c r="I231" s="4" t="inlineStr">
+      <c r="I234" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">now()</t>
         </is>
       </c>
-      <c r="J231" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="K231" s="4" t="inlineStr">
+      <c r="J234" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K234" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -14761,7 +14964,7 @@
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A2:K2"/>
   </mergeCells>
-  <autoFilter ref="A4:K231"/>
+  <autoFilter ref="A4:K234"/>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0" paperSize="9"/>
 </worksheet>
@@ -19486,7 +19689,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G75"/>
+  <dimension ref="A1:G79"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -20038,22 +20241,22 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_contacts</t>
+          <t xml:space="preserve">webinar_target_contacts</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">customer_code WHERE is_primary AND status='active' AND deleted_at IS NULL</t>
+          <t xml:space="preserve">webinar_id, contact_id</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">PARTIAL UNIQUE</t>
+          <t xml:space="preserve">PRIMARY KEY</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院ごとの有効な主担当を1人に限定。</t>
+          <t xml:space="preserve">同一ウェビナーの送付先担当者重複防止。</t>
         </is>
       </c>
     </row>
@@ -20063,29 +20266,29 @@
           <t xml:space="preserve">現行</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UK12</t>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IDX7</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_contacts</t>
+          <t xml:space="preserve">webinar_target_contacts</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_user_id</t>
+          <t xml:space="preserve">contact_id, webinar_id</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNIQUE</t>
+          <t xml:space="preserve">INDEX</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1担当者と1認証アカウントを必須の一対一にする。</t>
+          <t xml:space="preserve">担当者から送付対象ウェビナーを検索。</t>
         </is>
       </c>
     </row>
@@ -20097,49 +20300,49 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">UK13</t>
+          <t xml:space="preserve">UK11</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_users</t>
+          <t xml:space="preserve">clinic_contacts</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">login_id</t>
+          <t xml:space="preserve">customer_code WHERE is_primary AND status='active' AND deleted_at IS NULL</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNIQUE</t>
+          <t xml:space="preserve">PARTIAL UNIQUE</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">担当者ID兼ログインIDの重複防止。</t>
+          <t xml:space="preserve">医院ごとの有効な主担当を1人に限定。</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">将来案</t>
+          <t xml:space="preserve">現行</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">UK1</t>
+          <t xml:space="preserve">UK12</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_accounts</t>
+          <t xml:space="preserve">clinic_contacts</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">provider, external_account_id</t>
+          <t xml:space="preserve">clinic_user_id</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
@@ -20149,29 +20352,29 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部接続先の重複防止。</t>
+          <t xml:space="preserve">1担当者と1認証アカウントを必須の一対一にする。</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">将来案</t>
+          <t xml:space="preserve">現行</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">UK2</t>
+          <t xml:space="preserve">UK13</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_fulfillment_items</t>
+          <t xml:space="preserve">clinic_users</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">fulfillment_id, order_item_id</t>
+          <t xml:space="preserve">login_id</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
@@ -20181,7 +20384,7 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">同一配送への明細重複防止。</t>
+          <t xml:space="preserve">担当者ID兼ログインIDの重複防止。</t>
         </is>
       </c>
     </row>
@@ -20193,17 +20396,17 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">UK3</t>
+          <t xml:space="preserve">UK1</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_subscriptions</t>
+          <t xml:space="preserve">commerce_accounts</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_account_id, external_subscription_id</t>
+          <t xml:space="preserve">provider, external_account_id</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
@@ -20213,7 +20416,7 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部契約の重複防止。</t>
+          <t xml:space="preserve">外部接続先の重複防止。</t>
         </is>
       </c>
     </row>
@@ -20225,17 +20428,17 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">UK4</t>
+          <t xml:space="preserve">UK2</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_webhook_events</t>
+          <t xml:space="preserve">patient_fulfillment_items</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_account_id, external_event_id</t>
+          <t xml:space="preserve">fulfillment_id, order_item_id</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
@@ -20245,7 +20448,7 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Webhook重複配信の無害化。</t>
+          <t xml:space="preserve">同一配送への明細重複防止。</t>
         </is>
       </c>
     </row>
@@ -20257,17 +20460,17 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">UK5</t>
+          <t xml:space="preserve">UK3</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders</t>
+          <t xml:space="preserve">patient_subscriptions</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_account_id, external_order_id</t>
+          <t xml:space="preserve">commerce_account_id, external_subscription_id</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -20277,7 +20480,7 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">複数ストアを考慮した外部注文の一意性。</t>
+          <t xml:space="preserve">外部契約の重複防止。</t>
         </is>
       </c>
     </row>
@@ -20289,157 +20492,147 @@
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">UK4</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">commerce_webhook_events</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">commerce_account_id, external_event_id</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UNIQUE</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Webhook重複配信の無害化。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">将来案</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UK5</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_orders</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">commerce_account_id, external_order_id</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UNIQUE</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">複数ストアを考慮した外部注文の一意性。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">将来案</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">UK6</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">commerce_outbox</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="D30" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">idempotency_key</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
+      <c r="E30" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">UNIQUE</t>
         </is>
       </c>
-      <c r="F28" s="4" t="inlineStr">
+      <c r="F30" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">外部送信コマンドの二重実行防止。</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">現行リレーション</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">親DB日本語名</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">親KEY</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">親多重度</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">子多重度</t>
         </is>
       </c>
-      <c r="E31" s="3" t="inlineStr">
+      <c r="E33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">子FK</t>
         </is>
       </c>
-      <c r="F31" s="3" t="inlineStr">
+      <c r="F33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">子DB日本語名</t>
         </is>
       </c>
-      <c r="G31" s="3" t="inlineStr">
+      <c r="G33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">削除・備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">医院</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">clinics.customer_code</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0..1</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">clinic_terms.customer_code</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">医院契約情報</t>
-        </is>
-      </c>
-      <c r="G32" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PK・FK・CASCADE</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">医院</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">clinics.customer_code</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">clinic_product_settings.customer_code</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">医院商品設定</t>
-        </is>
-      </c>
-      <c r="G33" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PK・FK・CASCADE</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">商品</t>
+          <t xml:space="preserve">医院</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">products.id</t>
+          <t xml:space="preserve">clinics.customer_code</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -20449,17 +20642,17 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">N</t>
+          <t xml:space="preserve">0..1</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_product_settings.product_id</t>
+          <t xml:space="preserve">clinic_terms.customer_code</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院商品設定</t>
+          <t xml:space="preserve">医院契約情報</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
@@ -20491,29 +20684,29 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders.customer_code</t>
+          <t xml:space="preserve">clinic_product_settings.customer_code</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文</t>
+          <t xml:space="preserve">医院商品設定</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK</t>
+          <t xml:space="preserve">PK・FK・CASCADE</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者</t>
+          <t xml:space="preserve">商品</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patients.id</t>
+          <t xml:space="preserve">products.id</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -20528,66 +20721,66 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders.patient_id</t>
+          <t xml:space="preserve">clinic_product_settings.product_id</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文</t>
+          <t xml:space="preserve">医院商品設定</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK・現状CASCADE</t>
+          <t xml:space="preserve">PK・FK・CASCADE</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">医院</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinics.customer_code</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_orders.customer_code</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">患者注文</t>
         </is>
       </c>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">patient_orders.id</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="D37" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">patient_order_items.order_id</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">患者注文明細</t>
-        </is>
-      </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK・CASCADE</t>
+          <t xml:space="preserve">FK</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院</t>
+          <t xml:space="preserve">患者</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinics.customer_code</t>
+          <t xml:space="preserve">patients.id</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -20602,29 +20795,29 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery_destinations.clinic_customer_code</t>
+          <t xml:space="preserve">patient_orders.patient_id</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">送り先マスタ</t>
+          <t xml:space="preserve">患者注文</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK・RESTRICT</t>
+          <t xml:space="preserve">FK・現状CASCADE</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者</t>
+          <t xml:space="preserve">患者注文</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patients.id</t>
+          <t xml:space="preserve">patient_orders.id</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -20639,49 +20832,49 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery_destinations.patient_id</t>
+          <t xml:space="preserve">patient_order_items.order_id</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">送り先マスタ</t>
+          <t xml:space="preserve">患者注文明細</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK・RESTRICT</t>
+          <t xml:space="preserve">FK・CASCADE</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">医院</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinics.customer_code</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">delivery_destinations.clinic_customer_code</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">送り先マスタ</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">delivery_destinations.id</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="D40" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">order_delivery_destinations.delivery_destination_id</t>
-        </is>
-      </c>
-      <c r="F40" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">注文配送先</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
@@ -20693,12 +20886,12 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文</t>
+          <t xml:space="preserve">患者</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders.id</t>
+          <t xml:space="preserve">patients.id</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -20708,34 +20901,34 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">0..1</t>
+          <t xml:space="preserve">N</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">order_delivery_destinations.order_id</t>
+          <t xml:space="preserve">delivery_destinations.patient_id</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文配送先</t>
+          <t xml:space="preserve">送り先マスタ</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">PK・FK・CASCADE</t>
+          <t xml:space="preserve">FK・RESTRICT</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文</t>
+          <t xml:space="preserve">送り先マスタ</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders.id</t>
+          <t xml:space="preserve">delivery_destinations.id</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -20750,66 +20943,66 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_order_events.order_id</t>
+          <t xml:space="preserve">order_delivery_destinations.delivery_destination_id</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">注文操作履歴</t>
+          <t xml:space="preserve">注文配送先</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK・CASCADE</t>
+          <t xml:space="preserve">FK・RESTRICT</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">商品</t>
+          <t xml:space="preserve">患者注文</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">products.id</t>
+          <t xml:space="preserve">patient_orders.id</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">0..1</t>
         </is>
       </c>
-      <c r="D43" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_order_items.product_id</t>
+          <t xml:space="preserve">order_delivery_destinations.order_id</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文明細</t>
+          <t xml:space="preserve">注文配送先</t>
         </is>
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK・SET NULL</t>
+          <t xml:space="preserve">PK・FK・CASCADE</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院</t>
+          <t xml:space="preserve">患者注文</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinics.customer_code</t>
+          <t xml:space="preserve">patient_orders.id</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -20824,34 +21017,34 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_subscription_requests.customer_code</t>
+          <t xml:space="preserve">patient_order_events.order_id</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">定期購入申込</t>
+          <t xml:space="preserve">注文操作履歴</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK・RESTRICT</t>
+          <t xml:space="preserve">FK・CASCADE</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者</t>
+          <t xml:space="preserve">商品</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patients.id</t>
+          <t xml:space="preserve">products.id</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">0..1</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -20861,91 +21054,91 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_subscription_requests.patient_id</t>
+          <t xml:space="preserve">patient_order_items.product_id</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">定期購入申込</t>
+          <t xml:space="preserve">患者注文明細</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK・RESTRICT</t>
+          <t xml:space="preserve">FK・SET NULL</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">医院</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinics.customer_code</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscription_requests.customer_code</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">定期購入申込</t>
         </is>
       </c>
-      <c r="B46" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">patient_subscription_requests.id</t>
-        </is>
-      </c>
-      <c r="C46" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="D46" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="E46" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">patient_subscription_request_items.request_id</t>
-        </is>
-      </c>
-      <c r="F46" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">定期購入申込明細</t>
-        </is>
-      </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK・CASCADE</t>
+          <t xml:space="preserve">FK・RESTRICT</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">患者</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patients.id</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscription_requests.patient_id</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">定期購入申込</t>
         </is>
       </c>
-      <c r="B47" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">patient_subscription_requests.id</t>
-        </is>
-      </c>
-      <c r="C47" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="D47" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0..1</t>
-        </is>
-      </c>
-      <c r="E47" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">patient_subscription_request_destinations.request_id</t>
-        </is>
-      </c>
-      <c r="F47" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">定期購入申込配送先</t>
-        </is>
-      </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">PK・FK・CASCADE</t>
+          <t xml:space="preserve">FK・RESTRICT</t>
         </is>
       </c>
     </row>
@@ -20972,12 +21165,12 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_subscription_request_events.request_id</t>
+          <t xml:space="preserve">patient_subscription_request_items.request_id</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">定期購入申込履歴</t>
+          <t xml:space="preserve">定期購入申込明細</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
@@ -20989,12 +21182,12 @@
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">送り先マスタ</t>
+          <t xml:space="preserve">定期購入申込</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">delivery_destinations.id</t>
+          <t xml:space="preserve">patient_subscription_requests.id</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -21004,12 +21197,12 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">N</t>
+          <t xml:space="preserve">0..1</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_subscription_request_destinations.delivery_destination_id</t>
+          <t xml:space="preserve">patient_subscription_request_destinations.request_id</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
@@ -21019,19 +21212,19 @@
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK・RESTRICT</t>
+          <t xml:space="preserve">PK・FK・CASCADE</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ウェビナー</t>
+          <t xml:space="preserve">定期購入申込</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">webinars.id</t>
+          <t xml:space="preserve">patient_subscription_requests.id</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -21046,12 +21239,12 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">webinar_sessions.webinar_id</t>
+          <t xml:space="preserve">patient_subscription_request_events.request_id</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ウェビナー開催枠</t>
+          <t xml:space="preserve">定期購入申込履歴</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
@@ -21063,12 +21256,12 @@
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ウェビナー</t>
+          <t xml:space="preserve">送り先マスタ</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">webinars.id</t>
+          <t xml:space="preserve">delivery_destinations.id</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -21083,29 +21276,29 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">webinar_target_clinics.webinar_id</t>
+          <t xml:space="preserve">patient_subscription_request_destinations.delivery_destination_id</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ウェビナー対象医院</t>
+          <t xml:space="preserve">定期購入申込配送先</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">PK・FK・CASCADE</t>
+          <t xml:space="preserve">FK・RESTRICT</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院</t>
+          <t xml:space="preserve">ウェビナー</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinics.customer_code</t>
+          <t xml:space="preserve">webinars.id</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -21120,17 +21313,17 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">webinar_target_clinics.customer_code</t>
+          <t xml:space="preserve">webinar_sessions.webinar_id</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ウェビナー対象医院</t>
+          <t xml:space="preserve">ウェビナー開催枠</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">PK・FK・RESTRICT</t>
+          <t xml:space="preserve">FK・CASCADE</t>
         </is>
       </c>
     </row>
@@ -21157,17 +21350,17 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">webinar_events.webinar_id</t>
+          <t xml:space="preserve">webinar_target_clinics.webinar_id</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ウェビナー操作履歴</t>
+          <t xml:space="preserve">ウェビナー対象医院</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK・CASCADE</t>
+          <t xml:space="preserve">PK・FK・CASCADE</t>
         </is>
       </c>
     </row>
@@ -21194,29 +21387,29 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_contacts.customer_code</t>
+          <t xml:space="preserve">webinar_target_clinics.customer_code</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院業務連絡担当者</t>
+          <t xml:space="preserve">ウェビナー対象医院</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK・RESTRICT</t>
+          <t xml:space="preserve">PK・FK・RESTRICT</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院担当者役職</t>
+          <t xml:space="preserve">ウェビナー</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_contact_roles.role_key</t>
+          <t xml:space="preserve">webinars.id</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -21231,29 +21424,29 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_contacts.role_key</t>
+          <t xml:space="preserve">webinar_target_contacts.webinar_id</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院業務連絡担当者</t>
+          <t xml:space="preserve">ウェビナー送付先担当者</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK・RESTRICT</t>
+          <t xml:space="preserve">PK・FK・CASCADE</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院認証アカウント</t>
+          <t xml:space="preserve">医院業務連絡担当者</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_users.(id, customer_code)</t>
+          <t xml:space="preserve">clinic_contacts.id</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -21263,34 +21456,34 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">N</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_contacts.(clinic_user_id, customer_code)</t>
+          <t xml:space="preserve">webinar_target_contacts.contact_id</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院業務連絡担当者</t>
+          <t xml:space="preserve">ウェビナー送付先担当者</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">UK・複合FK・RESTRICT</t>
+          <t xml:space="preserve">PK・FK・RESTRICT</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院</t>
+          <t xml:space="preserve">ウェビナー</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinics.customer_code</t>
+          <t xml:space="preserve">webinars.id</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -21305,12 +21498,12 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_users.customer_code</t>
+          <t xml:space="preserve">webinar_events.webinar_id</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院ポータルログイン</t>
+          <t xml:space="preserve">ウェビナー操作履歴</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr">
@@ -21322,12 +21515,12 @@
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院ポータル権限</t>
+          <t xml:space="preserve">医院</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_portal_roles.role_key</t>
+          <t xml:space="preserve">clinics.customer_code</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -21342,29 +21535,29 @@
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_portal_role_permissions.role_key</t>
+          <t xml:space="preserve">clinic_contacts.customer_code</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">権限機能</t>
+          <t xml:space="preserve">医院業務連絡担当者</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">PK・FK・RESTRICT</t>
+          <t xml:space="preserve">FK・RESTRICT</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院ポータルログイン</t>
+          <t xml:space="preserve">医院担当者役職</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_users.id</t>
+          <t xml:space="preserve">clinic_contact_roles.role_key</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -21374,34 +21567,34 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">0..1</t>
+          <t xml:space="preserve">N</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_user_role_assignments.clinic_user_id</t>
+          <t xml:space="preserve">clinic_contacts.role_key</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">権限割当</t>
+          <t xml:space="preserve">医院業務連絡担当者</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">PK・FK・CASCADE</t>
+          <t xml:space="preserve">FK・RESTRICT</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院ポータル権限</t>
+          <t xml:space="preserve">医院認証アカウント</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_portal_roles.role_key</t>
+          <t xml:space="preserve">clinic_users.(id, customer_code)</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -21411,34 +21604,34 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">N</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_user_role_assignments.role_key</t>
+          <t xml:space="preserve">clinic_contacts.(clinic_user_id, customer_code)</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">権限割当</t>
+          <t xml:space="preserve">医院業務連絡担当者</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK・RESTRICT</t>
+          <t xml:space="preserve">UK・複合FK・RESTRICT</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院業務連絡担当者</t>
+          <t xml:space="preserve">医院</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_contacts.id</t>
+          <t xml:space="preserve">clinics.customer_code</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -21453,110 +21646,177 @@
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_contact_notification_preferences.contact_id</t>
+          <t xml:space="preserve">clinic_users.customer_code</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">担当者通知設定</t>
+          <t xml:space="preserve">医院ポータルログイン</t>
         </is>
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">PK・FK・RESTRICT</t>
+          <t xml:space="preserve">FK・CASCADE</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">医院ポータル権限</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_portal_roles.role_key</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_portal_role_permissions.role_key</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">権限機能</t>
+        </is>
+      </c>
+      <c r="G62" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK・FK・RESTRICT</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">医院ポータルログイン</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_users.id</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0..1</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_user_role_assignments.clinic_user_id</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">権限割当</t>
+        </is>
+      </c>
+      <c r="G63" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK・FK・CASCADE</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">医院ポータル権限</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_portal_roles.role_key</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_user_role_assignments.role_key</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">権限割当</t>
+        </is>
+      </c>
+      <c r="G64" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK・RESTRICT</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">医院業務連絡担当者</t>
         </is>
       </c>
-      <c r="B62" s="4" t="inlineStr">
+      <c r="B65" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">clinic_contacts.id</t>
         </is>
       </c>
-      <c r="C62" s="4" t="inlineStr">
+      <c r="C65" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="D62" s="4" t="inlineStr">
+      <c r="D65" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="E62" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">clinic_contact_events.contact_id</t>
-        </is>
-      </c>
-      <c r="F62" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">担当者操作履歴</t>
-        </is>
-      </c>
-      <c r="G62" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FK・RESTRICT</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">将来リレーション案</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">親DB日本語名</t>
-        </is>
-      </c>
-      <c r="B65" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">親KEY</t>
-        </is>
-      </c>
-      <c r="C65" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">親多重度</t>
-        </is>
-      </c>
-      <c r="D65" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">子多重度</t>
-        </is>
-      </c>
-      <c r="E65" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">子FK</t>
-        </is>
-      </c>
-      <c r="F65" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">子DB日本語名</t>
-        </is>
-      </c>
-      <c r="G65" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">削除・備考</t>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_contact_notification_preferences.contact_id</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">担当者通知設定</t>
+        </is>
+      </c>
+      <c r="G65" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK・FK・RESTRICT</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文</t>
+          <t xml:space="preserve">医院業務連絡担当者</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders.id</t>
+          <t xml:space="preserve">clinic_contacts.id</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -21571,140 +21831,73 @@
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">order_transaction_projections.order_id</t>
+          <t xml:space="preserve">clinic_contact_events.contact_id</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">決済返金投影</t>
+          <t xml:space="preserve">担当者操作履歴</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">患者注文</t>
-        </is>
-      </c>
-      <c r="B67" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">patient_orders.id</t>
-        </is>
-      </c>
-      <c r="C67" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="D67" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="E67" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">patient_fulfillments.order_id</t>
-        </is>
-      </c>
-      <c r="F67" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">受取配送</t>
-        </is>
-      </c>
-      <c r="G67" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FK</t>
+          <t xml:space="preserve">FK・RESTRICT</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">受取配送</t>
-        </is>
-      </c>
-      <c r="B68" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">patient_fulfillments.id</t>
-        </is>
-      </c>
-      <c r="C68" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="D68" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="E68" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">patient_fulfillment_items.fulfillment_id</t>
-        </is>
-      </c>
-      <c r="F68" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">受取配送明細</t>
-        </is>
-      </c>
-      <c r="G68" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FK</t>
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">将来リレーション案</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">注文明細</t>
-        </is>
-      </c>
-      <c r="B69" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">patient_order_items.id</t>
-        </is>
-      </c>
-      <c r="C69" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="D69" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="E69" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">patient_fulfillment_items.order_item_id</t>
-        </is>
-      </c>
-      <c r="F69" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">受取配送明細</t>
-        </is>
-      </c>
-      <c r="G69" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FK</t>
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">親DB日本語名</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">親KEY</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">親多重度</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">子多重度</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">子FK</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">子DB日本語名</t>
+        </is>
+      </c>
+      <c r="G69" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">削除・備考</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部コマース接続</t>
+          <t xml:space="preserve">患者注文</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_accounts.id</t>
+          <t xml:space="preserve">patient_orders.id</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -21719,12 +21912,12 @@
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_orders.commerce_account_id</t>
+          <t xml:space="preserve">order_transaction_projections.order_id</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者注文</t>
+          <t xml:space="preserve">決済返金投影</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr">
@@ -21736,12 +21929,12 @@
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部コマース接続</t>
+          <t xml:space="preserve">患者注文</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_accounts.id</t>
+          <t xml:space="preserve">patient_orders.id</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
@@ -21756,12 +21949,12 @@
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_webhook_events.commerce_account_id</t>
+          <t xml:space="preserve">patient_fulfillments.order_id</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部受信イベント</t>
+          <t xml:space="preserve">受取配送</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr">
@@ -21773,12 +21966,12 @@
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部コマース接続</t>
+          <t xml:space="preserve">受取配送</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_accounts.id</t>
+          <t xml:space="preserve">patient_fulfillments.id</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
@@ -21793,12 +21986,12 @@
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">commerce_outbox.commerce_account_id</t>
+          <t xml:space="preserve">patient_fulfillment_items.fulfillment_id</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">外部送信キュー</t>
+          <t xml:space="preserve">受取配送明細</t>
         </is>
       </c>
       <c r="G72" s="4" t="inlineStr">
@@ -21810,12 +22003,12 @@
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者</t>
+          <t xml:space="preserve">注文明細</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patients.id</t>
+          <t xml:space="preserve">patient_order_items.id</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
@@ -21830,12 +22023,12 @@
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_subscriptions.patient_id</t>
+          <t xml:space="preserve">patient_fulfillment_items.order_item_id</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者定期購入</t>
+          <t xml:space="preserve">受取配送明細</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr">
@@ -21847,12 +22040,12 @@
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">患者定期購入</t>
+          <t xml:space="preserve">外部コマース接続</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_subscriptions.id</t>
+          <t xml:space="preserve">commerce_accounts.id</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
@@ -21867,12 +22060,12 @@
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">patient_subscription_items.subscription_id</t>
+          <t xml:space="preserve">patient_orders.commerce_account_id</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">定期購入明細</t>
+          <t xml:space="preserve">患者注文</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr">
@@ -21884,35 +22077,183 @@
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">外部コマース接続</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">commerce_accounts.id</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">commerce_webhook_events.commerce_account_id</t>
+        </is>
+      </c>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">外部受信イベント</t>
+        </is>
+      </c>
+      <c r="G75" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">外部コマース接続</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">commerce_accounts.id</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">commerce_outbox.commerce_account_id</t>
+        </is>
+      </c>
+      <c r="F76" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">外部送信キュー</t>
+        </is>
+      </c>
+      <c r="G76" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">患者</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patients.id</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscriptions.patient_id</t>
+        </is>
+      </c>
+      <c r="F77" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">患者定期購入</t>
         </is>
       </c>
-      <c r="B75" s="4" t="inlineStr">
+      <c r="G77" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">患者定期購入</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">patient_subscriptions.id</t>
         </is>
       </c>
-      <c r="C75" s="4" t="inlineStr">
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D78" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscription_items.subscription_id</t>
+        </is>
+      </c>
+      <c r="F78" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">定期購入明細</t>
+        </is>
+      </c>
+      <c r="G78" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">患者定期購入</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_subscriptions.id</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">0..1</t>
         </is>
       </c>
-      <c r="D75" s="4" t="inlineStr">
+      <c r="D79" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="E75" s="4" t="inlineStr">
+      <c r="E79" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">patient_orders.subscription_id</t>
         </is>
       </c>
-      <c r="F75" s="4" t="inlineStr">
+      <c r="F79" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">患者注文</t>
         </is>
       </c>
-      <c r="G75" s="4" t="inlineStr">
+      <c r="G79" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">FK</t>
         </is>
@@ -21922,8 +22263,8 @@
   <mergeCells count="4">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A30:H30"/>
-    <mergeCell ref="A64:H64"/>
+    <mergeCell ref="A32:H32"/>
+    <mergeCell ref="A68:H68"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0" paperSize="9"/>
@@ -21932,7 +22273,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Q104"/>
+  <dimension ref="A1:Q106"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -23861,29 +24202,29 @@
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">webinar_events.webinar_id</t>
+          <t xml:space="preserve">webinar_target_contacts.webinar_id</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ウェビナー操作履歴</t>
+          <t xml:space="preserve">ウェビナー送付先担当者</t>
         </is>
       </c>
       <c r="G95" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK・CASCADE</t>
+          <t xml:space="preserve">PK・FK・CASCADE</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院</t>
+          <t xml:space="preserve">医院業務連絡担当者</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinics.customer_code</t>
+          <t xml:space="preserve">clinic_contacts.id</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
@@ -23898,29 +24239,29 @@
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_contacts.customer_code</t>
+          <t xml:space="preserve">webinar_target_contacts.contact_id</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院業務連絡担当者</t>
+          <t xml:space="preserve">ウェビナー送付先担当者</t>
         </is>
       </c>
       <c r="G96" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK・RESTRICT</t>
+          <t xml:space="preserve">PK・FK・RESTRICT</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院担当者役職</t>
+          <t xml:space="preserve">ウェビナー</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_contact_roles.role_key</t>
+          <t xml:space="preserve">webinars.id</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
@@ -23935,29 +24276,29 @@
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_contacts.role_key</t>
+          <t xml:space="preserve">webinar_events.webinar_id</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院業務連絡担当者</t>
+          <t xml:space="preserve">ウェビナー操作履歴</t>
         </is>
       </c>
       <c r="G97" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK・RESTRICT</t>
+          <t xml:space="preserve">FK・CASCADE</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院認証アカウント</t>
+          <t xml:space="preserve">医院</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_users.(id, customer_code)</t>
+          <t xml:space="preserve">clinics.customer_code</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
@@ -23967,12 +24308,12 @@
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">N</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_contacts.(clinic_user_id, customer_code)</t>
+          <t xml:space="preserve">clinic_contacts.customer_code</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
@@ -23982,19 +24323,19 @@
       </c>
       <c r="G98" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">UK・複合FK・RESTRICT</t>
+          <t xml:space="preserve">FK・RESTRICT</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院</t>
+          <t xml:space="preserve">医院担当者役職</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinics.customer_code</t>
+          <t xml:space="preserve">clinic_contact_roles.role_key</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
@@ -24009,29 +24350,29 @@
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_users.customer_code</t>
+          <t xml:space="preserve">clinic_contacts.role_key</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院ポータルログイン</t>
+          <t xml:space="preserve">医院業務連絡担当者</t>
         </is>
       </c>
       <c r="G99" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK・CASCADE</t>
+          <t xml:space="preserve">FK・RESTRICT</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院ポータル権限</t>
+          <t xml:space="preserve">医院認証アカウント</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_portal_roles.role_key</t>
+          <t xml:space="preserve">clinic_users.(id, customer_code)</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
@@ -24041,59 +24382,59 @@
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">N</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_portal_role_permissions.role_key</t>
+          <t xml:space="preserve">clinic_contacts.(clinic_user_id, customer_code)</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">権限機能</t>
+          <t xml:space="preserve">医院業務連絡担当者</t>
         </is>
       </c>
       <c r="G100" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">PK・FK・RESTRICT</t>
+          <t xml:space="preserve">UK・複合FK・RESTRICT</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">医院</t>
+        </is>
+      </c>
+      <c r="B101" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinics.customer_code</t>
+        </is>
+      </c>
+      <c r="C101" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D101" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E101" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_users.customer_code</t>
+        </is>
+      </c>
+      <c r="F101" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">医院ポータルログイン</t>
         </is>
       </c>
-      <c r="B101" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">clinic_users.id</t>
-        </is>
-      </c>
-      <c r="C101" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="D101" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0..1</t>
-        </is>
-      </c>
-      <c r="E101" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">clinic_user_role_assignments.clinic_user_id</t>
-        </is>
-      </c>
-      <c r="F101" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">権限割当</t>
-        </is>
-      </c>
       <c r="G101" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">PK・FK・CASCADE</t>
+          <t xml:space="preserve">FK・CASCADE</t>
         </is>
       </c>
     </row>
@@ -24120,29 +24461,29 @@
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_user_role_assignments.role_key</t>
+          <t xml:space="preserve">clinic_portal_role_permissions.role_key</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">権限割当</t>
+          <t xml:space="preserve">権限機能</t>
         </is>
       </c>
       <c r="G102" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FK・RESTRICT</t>
+          <t xml:space="preserve">PK・FK・RESTRICT</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">医院業務連絡担当者</t>
+          <t xml:space="preserve">医院ポータルログイン</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_contacts.id</t>
+          <t xml:space="preserve">clinic_users.id</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
@@ -24152,57 +24493,131 @@
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">N</t>
+          <t xml:space="preserve">0..1</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinic_contact_notification_preferences.contact_id</t>
+          <t xml:space="preserve">clinic_user_role_assignments.clinic_user_id</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">担当者通知設定</t>
+          <t xml:space="preserve">権限割当</t>
         </is>
       </c>
       <c r="G103" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">PK・FK・RESTRICT</t>
+          <t xml:space="preserve">PK・FK・CASCADE</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">医院ポータル権限</t>
+        </is>
+      </c>
+      <c r="B104" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_portal_roles.role_key</t>
+        </is>
+      </c>
+      <c r="C104" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D104" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E104" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_user_role_assignments.role_key</t>
+        </is>
+      </c>
+      <c r="F104" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">権限割当</t>
+        </is>
+      </c>
+      <c r="G104" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FK・RESTRICT</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">医院業務連絡担当者</t>
         </is>
       </c>
-      <c r="B104" s="4" t="inlineStr">
+      <c r="B105" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">clinic_contacts.id</t>
         </is>
       </c>
-      <c r="C104" s="4" t="inlineStr">
+      <c r="C105" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="D104" s="4" t="inlineStr">
+      <c r="D105" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="E104" s="4" t="inlineStr">
+      <c r="E105" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_contact_notification_preferences.contact_id</t>
+        </is>
+      </c>
+      <c r="F105" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">担当者通知設定</t>
+        </is>
+      </c>
+      <c r="G105" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PK・FK・RESTRICT</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">医院業務連絡担当者</t>
+        </is>
+      </c>
+      <c r="B106" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">clinic_contacts.id</t>
+        </is>
+      </c>
+      <c r="C106" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D106" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E106" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">clinic_contact_events.contact_id</t>
         </is>
       </c>
-      <c r="F104" s="4" t="inlineStr">
+      <c r="F106" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">担当者操作履歴</t>
         </is>
       </c>
-      <c r="G104" s="4" t="inlineStr">
+      <c r="G106" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">FK・RESTRICT</t>
         </is>
